--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G10">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G97">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G110">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G126">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G185">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G186">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G196">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O224">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36860,10 +36860,10 @@
         <v>0</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC224">
         <v>0</v>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O225">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P225">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37023,10 +37023,10 @@
         <v>0</v>
       </c>
       <c r="AA225">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB225">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC225">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G10">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G31">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G126">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G185">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G186">

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU236"/>
+  <dimension ref="A1:AU239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G8">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G10">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G22">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,22 +12329,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G74">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G75">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-08-30 11:00:00</t>
+          <t>2026-08-30 11:30:00</t>
         </is>
       </c>
     </row>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G76">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="G77">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G78">
@@ -13144,22 +13144,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G80">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G81">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-08-30 11:30:00</t>
+          <t>2026-08-30 11:45:00</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G83">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-08-30 11:45:00</t>
+          <t>2026-08-30 12:00:00</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,22 +14285,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G86">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,22 +14611,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G89">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G91">
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G92">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,22 +16078,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Deportivo Alavés W</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Deportivo Alavés W</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G103">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G137">
@@ -22756,12 +22756,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G138">
@@ -22907,7 +22907,7 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>2026-08-30 13:05:00</t>
+          <t>2026-08-30 13:00:00</t>
         </is>
       </c>
     </row>
@@ -22919,12 +22919,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G139">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-08-30 13:15:00</t>
+          <t>2026-08-30 13:05:00</t>
         </is>
       </c>
     </row>
@@ -23087,22 +23087,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G140">
@@ -23245,12 +23245,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G141">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-08-30 13:30:00</t>
+          <t>2026-08-30 13:15:00</t>
         </is>
       </c>
     </row>
@@ -23413,22 +23413,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G142">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G143">
@@ -23739,22 +23739,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G144">
@@ -23902,22 +23902,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G147">
@@ -24386,12 +24386,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G148">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-08-30 14:00:00</t>
+          <t>2026-08-30 13:30:00</t>
         </is>
       </c>
     </row>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G149">
@@ -24717,22 +24717,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G150">
@@ -24880,22 +24880,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G153">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G154">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G156">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,22 +26021,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G159">
@@ -26347,22 +26347,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G162">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G163">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G164">
@@ -27157,12 +27157,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G165">
@@ -27308,7 +27308,7 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>2026-08-30 14:15:00</t>
+          <t>2026-08-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -27320,27 +27320,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G166">
@@ -27471,7 +27471,7 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>2026-08-30 14:15:00</t>
+          <t>2026-08-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G167">
@@ -27651,22 +27651,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G168">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G169">
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G170">
@@ -28135,12 +28135,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G171">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>2026-08-30 14:30:00</t>
+          <t>2026-08-30 14:15:00</t>
         </is>
       </c>
     </row>
@@ -28298,12 +28298,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G172">
@@ -28449,7 +28449,7 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>2026-08-30 14:30:00</t>
+          <t>2026-08-30 14:15:00</t>
         </is>
       </c>
     </row>
@@ -28461,12 +28461,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G173">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-08-30 15:00:00</t>
+          <t>2026-08-30 14:30:00</t>
         </is>
       </c>
     </row>
@@ -28624,12 +28624,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G174">
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-08-30 15:00:00</t>
+          <t>2026-08-30 14:30:00</t>
         </is>
       </c>
     </row>
@@ -28792,22 +28792,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G175">
@@ -28955,22 +28955,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G176">
@@ -29118,22 +29118,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,22 +29281,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G178">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,22 +29607,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,22 +29933,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G184">
@@ -30422,7 +30422,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G185">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G186">
@@ -30743,12 +30743,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G187">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>2026-08-30 15:15:00</t>
+          <t>2026-08-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -30906,12 +30906,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G188">
@@ -31057,7 +31057,7 @@
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>2026-08-30 15:15:00</t>
+          <t>2026-08-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G189">
@@ -31232,12 +31232,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G190">
@@ -31383,7 +31383,7 @@
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>2026-08-30 15:30:00</t>
+          <t>2026-08-30 15:15:00</t>
         </is>
       </c>
     </row>
@@ -31395,12 +31395,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G191">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>2026-08-30 15:30:00</t>
+          <t>2026-08-30 15:15:00</t>
         </is>
       </c>
     </row>
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G192">
@@ -31726,22 +31726,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G196">
@@ -32378,22 +32378,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G197">
@@ -32536,27 +32536,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G198">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>2026-08-30 15:45:00</t>
+          <t>2026-08-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -32699,12 +32699,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G199">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>2026-08-30 15:45:00</t>
+          <t>2026-08-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G200">
@@ -33025,12 +33025,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G201">
@@ -33176,7 +33176,7 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>2026-08-30 16:00:00</t>
+          <t>2026-08-30 15:45:00</t>
         </is>
       </c>
     </row>
@@ -33188,12 +33188,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G202">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>2026-08-30 16:00:00</t>
+          <t>2026-08-30 15:45:00</t>
         </is>
       </c>
     </row>
@@ -33356,22 +33356,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G204">
@@ -33682,22 +33682,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,22 +33845,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,22 +34008,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,22 +34334,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,22 +34823,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,7 +34986,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G213">
@@ -35149,22 +35149,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G214">
@@ -35307,27 +35307,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G215">
@@ -35458,7 +35458,7 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>2026-08-30 16:15:00</t>
+          <t>2026-08-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -35470,12 +35470,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G216">
@@ -35621,7 +35621,7 @@
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>2026-08-30 16:30:00</t>
+          <t>2026-08-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -35633,27 +35633,27 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G217">
@@ -35784,7 +35784,7 @@
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>2026-08-30 16:30:00</t>
+          <t>2026-08-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -35796,27 +35796,27 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G218">
@@ -35947,7 +35947,7 @@
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>2026-08-30 16:30:00</t>
+          <t>2026-08-30 16:15:00</t>
         </is>
       </c>
     </row>
@@ -35959,27 +35959,27 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G219">
@@ -36110,7 +36110,7 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>2026-08-30 17:00:00</t>
+          <t>2026-08-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -36122,27 +36122,27 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G220">
@@ -36273,7 +36273,7 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>2026-08-30 17:30:00</t>
+          <t>2026-08-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -36285,27 +36285,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G221">
@@ -36436,7 +36436,7 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>2026-08-30 18:00:00</t>
+          <t>2026-08-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -36448,12 +36448,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G222">
@@ -36599,7 +36599,7 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>2026-08-30 18:00:00</t>
+          <t>2026-08-30 17:00:00</t>
         </is>
       </c>
     </row>
@@ -36611,12 +36611,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G223">
@@ -36762,7 +36762,7 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>2026-08-30 18:30:00</t>
+          <t>2026-08-30 17:30:00</t>
         </is>
       </c>
     </row>
@@ -36774,12 +36774,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O224">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P224">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36860,10 +36860,10 @@
         <v>0</v>
       </c>
       <c r="AA224">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB224">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC224">
         <v>0</v>
@@ -36925,7 +36925,7 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>2026-08-30 18:30:00</t>
+          <t>2026-08-30 18:00:00</t>
         </is>
       </c>
     </row>
@@ -36937,12 +36937,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G225">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>2026-08-30 18:30:00</t>
+          <t>2026-08-30 18:00:00</t>
         </is>
       </c>
     </row>
@@ -37105,7 +37105,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37349,10 +37349,10 @@
         <v>0</v>
       </c>
       <c r="AA227">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB227">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC227">
         <v>0</v>
@@ -37431,7 +37431,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G228">
@@ -37589,12 +37589,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G229">
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>2026-08-30 19:00:00</t>
+          <t>2026-08-30 18:30:00</t>
         </is>
       </c>
     </row>
@@ -37752,12 +37752,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O230">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P230">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37838,10 +37838,10 @@
         <v>0</v>
       </c>
       <c r="AA230">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB230">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC230">
         <v>0</v>
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>2026-08-30 19:30:00</t>
+          <t>2026-08-30 18:30:00</t>
         </is>
       </c>
     </row>
@@ -37915,12 +37915,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G231">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-08-30 20:00:00</t>
+          <t>2026-08-30 18:30:00</t>
         </is>
       </c>
     </row>
@@ -38078,12 +38078,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G232">
@@ -38229,7 +38229,7 @@
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>2026-08-30 20:00:00</t>
+          <t>2026-08-30 19:00:00</t>
         </is>
       </c>
     </row>
@@ -38241,12 +38241,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38327,10 +38327,10 @@
         <v>0</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC233">
         <v>0</v>
@@ -38392,7 +38392,7 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>2026-08-30 20:00:00</t>
+          <t>2026-08-30 19:30:00</t>
         </is>
       </c>
     </row>
@@ -38404,12 +38404,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G234">
@@ -38555,7 +38555,7 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>2026-08-30 21:00:00</t>
+          <t>2026-08-30 20:00:00</t>
         </is>
       </c>
     </row>
@@ -38567,27 +38567,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G235">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>2026-08-30 21:00:00</t>
+          <t>2026-08-30 20:00:00</t>
         </is>
       </c>
     </row>
@@ -38730,156 +38730,645 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="G236">
+        <v>0</v>
+      </c>
+      <c r="H236">
+        <v>0</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>0</v>
+      </c>
+      <c r="L236">
+        <v>0</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N236">
+        <v>0</v>
+      </c>
+      <c r="O236">
+        <v>0</v>
+      </c>
+      <c r="P236">
+        <v>0</v>
+      </c>
+      <c r="Q236">
+        <v>0</v>
+      </c>
+      <c r="R236">
+        <v>0</v>
+      </c>
+      <c r="S236">
+        <v>0</v>
+      </c>
+      <c r="T236">
+        <v>0</v>
+      </c>
+      <c r="U236">
+        <v>0</v>
+      </c>
+      <c r="V236">
+        <v>0</v>
+      </c>
+      <c r="W236">
+        <v>0</v>
+      </c>
+      <c r="X236">
+        <v>0</v>
+      </c>
+      <c r="Y236">
+        <v>0</v>
+      </c>
+      <c r="Z236">
+        <v>0</v>
+      </c>
+      <c r="AA236">
+        <v>0</v>
+      </c>
+      <c r="AB236">
+        <v>0</v>
+      </c>
+      <c r="AC236">
+        <v>0</v>
+      </c>
+      <c r="AD236">
+        <v>0</v>
+      </c>
+      <c r="AE236">
+        <v>0</v>
+      </c>
+      <c r="AF236">
+        <v>0</v>
+      </c>
+      <c r="AG236">
+        <v>0</v>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ236">
+        <v>0</v>
+      </c>
+      <c r="AK236">
+        <v>0</v>
+      </c>
+      <c r="AL236">
+        <v>0</v>
+      </c>
+      <c r="AM236">
+        <v>-1</v>
+      </c>
+      <c r="AN236">
+        <v>-1</v>
+      </c>
+      <c r="AO236">
+        <v>-1</v>
+      </c>
+      <c r="AP236">
+        <v>-1</v>
+      </c>
+      <c r="AQ236">
+        <v>0</v>
+      </c>
+      <c r="AR236">
+        <v>0</v>
+      </c>
+      <c r="AS236">
+        <v>0</v>
+      </c>
+      <c r="AT236">
+        <v>0</v>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>2026-08-30 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="G237">
+        <v>0</v>
+      </c>
+      <c r="H237">
+        <v>0</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N237">
+        <v>0</v>
+      </c>
+      <c r="O237">
+        <v>0</v>
+      </c>
+      <c r="P237">
+        <v>0</v>
+      </c>
+      <c r="Q237">
+        <v>0</v>
+      </c>
+      <c r="R237">
+        <v>0</v>
+      </c>
+      <c r="S237">
+        <v>0</v>
+      </c>
+      <c r="T237">
+        <v>0</v>
+      </c>
+      <c r="U237">
+        <v>0</v>
+      </c>
+      <c r="V237">
+        <v>0</v>
+      </c>
+      <c r="W237">
+        <v>0</v>
+      </c>
+      <c r="X237">
+        <v>0</v>
+      </c>
+      <c r="Y237">
+        <v>0</v>
+      </c>
+      <c r="Z237">
+        <v>0</v>
+      </c>
+      <c r="AA237">
+        <v>0</v>
+      </c>
+      <c r="AB237">
+        <v>0</v>
+      </c>
+      <c r="AC237">
+        <v>0</v>
+      </c>
+      <c r="AD237">
+        <v>0</v>
+      </c>
+      <c r="AE237">
+        <v>0</v>
+      </c>
+      <c r="AF237">
+        <v>0</v>
+      </c>
+      <c r="AG237">
+        <v>0</v>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ237">
+        <v>0</v>
+      </c>
+      <c r="AK237">
+        <v>0</v>
+      </c>
+      <c r="AL237">
+        <v>0</v>
+      </c>
+      <c r="AM237">
+        <v>-1</v>
+      </c>
+      <c r="AN237">
+        <v>-1</v>
+      </c>
+      <c r="AO237">
+        <v>-1</v>
+      </c>
+      <c r="AP237">
+        <v>-1</v>
+      </c>
+      <c r="AQ237">
+        <v>0</v>
+      </c>
+      <c r="AR237">
+        <v>0</v>
+      </c>
+      <c r="AS237">
+        <v>0</v>
+      </c>
+      <c r="AT237">
+        <v>0</v>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>2026-08-30 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
         <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>GD Estoril Praia</t>
+        </is>
+      </c>
+      <c r="G238">
+        <v>0</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N238">
+        <v>0</v>
+      </c>
+      <c r="O238">
+        <v>0</v>
+      </c>
+      <c r="P238">
+        <v>0</v>
+      </c>
+      <c r="Q238">
+        <v>0</v>
+      </c>
+      <c r="R238">
+        <v>0</v>
+      </c>
+      <c r="S238">
+        <v>0</v>
+      </c>
+      <c r="T238">
+        <v>0</v>
+      </c>
+      <c r="U238">
+        <v>0</v>
+      </c>
+      <c r="V238">
+        <v>0</v>
+      </c>
+      <c r="W238">
+        <v>0</v>
+      </c>
+      <c r="X238">
+        <v>0</v>
+      </c>
+      <c r="Y238">
+        <v>0</v>
+      </c>
+      <c r="Z238">
+        <v>0</v>
+      </c>
+      <c r="AA238">
+        <v>0</v>
+      </c>
+      <c r="AB238">
+        <v>0</v>
+      </c>
+      <c r="AC238">
+        <v>0</v>
+      </c>
+      <c r="AD238">
+        <v>0</v>
+      </c>
+      <c r="AE238">
+        <v>0</v>
+      </c>
+      <c r="AF238">
+        <v>0</v>
+      </c>
+      <c r="AG238">
+        <v>0</v>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ238">
+        <v>0</v>
+      </c>
+      <c r="AK238">
+        <v>0</v>
+      </c>
+      <c r="AL238">
+        <v>0</v>
+      </c>
+      <c r="AM238">
+        <v>-1</v>
+      </c>
+      <c r="AN238">
+        <v>-1</v>
+      </c>
+      <c r="AO238">
+        <v>-1</v>
+      </c>
+      <c r="AP238">
+        <v>-1</v>
+      </c>
+      <c r="AQ238">
+        <v>0</v>
+      </c>
+      <c r="AR238">
+        <v>0</v>
+      </c>
+      <c r="AS238">
+        <v>0</v>
+      </c>
+      <c r="AT238">
+        <v>0</v>
+      </c>
+      <c r="AU238" t="inlineStr">
+        <is>
+          <t>2026-08-30 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
         <is>
           <t>Sporting Braga</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="F239" t="inlineStr">
         <is>
           <t>Vitória Guimarães</t>
         </is>
       </c>
-      <c r="G236">
-        <v>0</v>
-      </c>
-      <c r="H236">
-        <v>0</v>
-      </c>
-      <c r="I236">
-        <v>0</v>
-      </c>
-      <c r="J236">
-        <v>0</v>
-      </c>
-      <c r="K236">
-        <v>0</v>
-      </c>
-      <c r="L236">
-        <v>0</v>
-      </c>
-      <c r="M236" t="inlineStr">
+      <c r="G239">
+        <v>0</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>0</v>
+      </c>
+      <c r="L239">
+        <v>0</v>
+      </c>
+      <c r="M239" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N236">
-        <v>0</v>
-      </c>
-      <c r="O236">
-        <v>0</v>
-      </c>
-      <c r="P236">
-        <v>0</v>
-      </c>
-      <c r="Q236">
-        <v>0</v>
-      </c>
-      <c r="R236">
-        <v>0</v>
-      </c>
-      <c r="S236">
-        <v>0</v>
-      </c>
-      <c r="T236">
-        <v>0</v>
-      </c>
-      <c r="U236">
-        <v>0</v>
-      </c>
-      <c r="V236">
-        <v>0</v>
-      </c>
-      <c r="W236">
-        <v>0</v>
-      </c>
-      <c r="X236">
-        <v>0</v>
-      </c>
-      <c r="Y236">
-        <v>0</v>
-      </c>
-      <c r="Z236">
-        <v>0</v>
-      </c>
-      <c r="AA236">
-        <v>0</v>
-      </c>
-      <c r="AB236">
-        <v>0</v>
-      </c>
-      <c r="AC236">
-        <v>0</v>
-      </c>
-      <c r="AD236">
-        <v>0</v>
-      </c>
-      <c r="AE236">
-        <v>0</v>
-      </c>
-      <c r="AF236">
-        <v>0</v>
-      </c>
-      <c r="AG236">
-        <v>0</v>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ236">
-        <v>0</v>
-      </c>
-      <c r="AK236">
-        <v>0</v>
-      </c>
-      <c r="AL236">
-        <v>0</v>
-      </c>
-      <c r="AM236">
-        <v>-1</v>
-      </c>
-      <c r="AN236">
-        <v>-1</v>
-      </c>
-      <c r="AO236">
-        <v>-1</v>
-      </c>
-      <c r="AP236">
-        <v>-1</v>
-      </c>
-      <c r="AQ236">
-        <v>0</v>
-      </c>
-      <c r="AR236">
-        <v>0</v>
-      </c>
-      <c r="AS236">
-        <v>0</v>
-      </c>
-      <c r="AT236">
-        <v>0</v>
-      </c>
-      <c r="AU236" t="inlineStr">
+      <c r="N239">
+        <v>0</v>
+      </c>
+      <c r="O239">
+        <v>0</v>
+      </c>
+      <c r="P239">
+        <v>0</v>
+      </c>
+      <c r="Q239">
+        <v>0</v>
+      </c>
+      <c r="R239">
+        <v>0</v>
+      </c>
+      <c r="S239">
+        <v>0</v>
+      </c>
+      <c r="T239">
+        <v>0</v>
+      </c>
+      <c r="U239">
+        <v>0</v>
+      </c>
+      <c r="V239">
+        <v>0</v>
+      </c>
+      <c r="W239">
+        <v>0</v>
+      </c>
+      <c r="X239">
+        <v>0</v>
+      </c>
+      <c r="Y239">
+        <v>0</v>
+      </c>
+      <c r="Z239">
+        <v>0</v>
+      </c>
+      <c r="AA239">
+        <v>0</v>
+      </c>
+      <c r="AB239">
+        <v>0</v>
+      </c>
+      <c r="AC239">
+        <v>0</v>
+      </c>
+      <c r="AD239">
+        <v>0</v>
+      </c>
+      <c r="AE239">
+        <v>0</v>
+      </c>
+      <c r="AF239">
+        <v>0</v>
+      </c>
+      <c r="AG239">
+        <v>0</v>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ239">
+        <v>0</v>
+      </c>
+      <c r="AK239">
+        <v>0</v>
+      </c>
+      <c r="AL239">
+        <v>0</v>
+      </c>
+      <c r="AM239">
+        <v>-1</v>
+      </c>
+      <c r="AN239">
+        <v>-1</v>
+      </c>
+      <c r="AO239">
+        <v>-1</v>
+      </c>
+      <c r="AP239">
+        <v>-1</v>
+      </c>
+      <c r="AQ239">
+        <v>0</v>
+      </c>
+      <c r="AR239">
+        <v>0</v>
+      </c>
+      <c r="AS239">
+        <v>0</v>
+      </c>
+      <c r="AT239">
+        <v>0</v>
+      </c>
+      <c r="AU239" t="inlineStr">
         <is>
           <t>2026-08-30 21:00:00</t>
         </is>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G46">

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G67">

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -644,55 +644,55 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL2">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU239"/>
+  <dimension ref="A1:AU244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G10">
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G62">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G63">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G67">
@@ -11351,22 +11351,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,22 +11677,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,22 +12329,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G74">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G75">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-08-30 11:30:00</t>
+          <t>2026-08-30 11:00:00</t>
         </is>
       </c>
     </row>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G76">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G77">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="G78">
@@ -13144,22 +13144,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G80">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G81">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-08-30 11:45:00</t>
+          <t>2026-08-30 11:30:00</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G83">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-08-30 12:00:00</t>
+          <t>2026-08-30 11:45:00</t>
         </is>
       </c>
     </row>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G110">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G114">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-08-30 12:30:00</t>
+          <t>2026-08-30 12:15:00</t>
         </is>
       </c>
     </row>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G119">
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-08-30 12:45:00</t>
+          <t>2026-08-30 12:30:00</t>
         </is>
       </c>
     </row>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G121">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-30 13:00:00</t>
+          <t>2026-08-30 12:30:00</t>
         </is>
       </c>
     </row>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G122">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-08-30 13:00:00</t>
+          <t>2026-08-30 12:30:00</t>
         </is>
       </c>
     </row>
@@ -20311,12 +20311,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-08-30 13:00:00</t>
+          <t>2026-08-30 12:30:00</t>
         </is>
       </c>
     </row>
@@ -20474,12 +20474,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G124">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-08-30 13:00:00</t>
+          <t>2026-08-30 12:30:00</t>
         </is>
       </c>
     </row>
@@ -20637,27 +20637,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G125">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-08-30 13:00:00</t>
+          <t>2026-08-30 12:45:00</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,22 +21131,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,22 +21457,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,22 +21946,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,22 +22272,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G138">
@@ -22919,12 +22919,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G139">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-08-30 13:05:00</t>
+          <t>2026-08-30 13:00:00</t>
         </is>
       </c>
     </row>
@@ -23082,12 +23082,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G140">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>2026-08-30 13:15:00</t>
+          <t>2026-08-30 13:00:00</t>
         </is>
       </c>
     </row>
@@ -23245,27 +23245,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G141">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-08-30 13:15:00</t>
+          <t>2026-08-30 13:00:00</t>
         </is>
       </c>
     </row>
@@ -23408,27 +23408,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G142">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-08-30 13:30:00</t>
+          <t>2026-08-30 13:00:00</t>
         </is>
       </c>
     </row>
@@ -23571,12 +23571,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G143">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-08-30 13:30:00</t>
+          <t>2026-08-30 13:00:00</t>
         </is>
       </c>
     </row>
@@ -23734,12 +23734,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G144">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-08-30 13:30:00</t>
+          <t>2026-08-30 13:05:00</t>
         </is>
       </c>
     </row>
@@ -23897,27 +23897,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G145">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>2026-08-30 13:30:00</t>
+          <t>2026-08-30 13:15:00</t>
         </is>
       </c>
     </row>
@@ -24060,12 +24060,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G146">
@@ -24211,7 +24211,7 @@
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>2026-08-30 13:30:00</t>
+          <t>2026-08-30 13:15:00</t>
         </is>
       </c>
     </row>
@@ -24223,27 +24223,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G147">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>2026-08-30 13:30:00</t>
+          <t>2026-08-30 13:15:00</t>
         </is>
       </c>
     </row>
@@ -24391,22 +24391,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G148">
@@ -24549,12 +24549,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G149">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>2026-08-30 14:00:00</t>
+          <t>2026-08-30 13:30:00</t>
         </is>
       </c>
     </row>
@@ -24712,12 +24712,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G150">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>2026-08-30 14:00:00</t>
+          <t>2026-08-30 13:30:00</t>
         </is>
       </c>
     </row>
@@ -24875,12 +24875,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G151">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>2026-08-30 14:00:00</t>
+          <t>2026-08-30 13:30:00</t>
         </is>
       </c>
     </row>
@@ -25038,12 +25038,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G152">
@@ -25189,7 +25189,7 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>2026-08-30 14:00:00</t>
+          <t>2026-08-30 13:30:00</t>
         </is>
       </c>
     </row>
@@ -25201,12 +25201,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G153">
@@ -25352,7 +25352,7 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>2026-08-30 14:00:00</t>
+          <t>2026-08-30 13:30:00</t>
         </is>
       </c>
     </row>
@@ -25364,12 +25364,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G154">
@@ -25515,7 +25515,7 @@
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>2026-08-30 14:00:00</t>
+          <t>2026-08-30 13:30:00</t>
         </is>
       </c>
     </row>
@@ -25532,7 +25532,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G155">
@@ -25695,7 +25695,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G156">
@@ -25858,22 +25858,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G158">
@@ -26184,22 +26184,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G159">
@@ -26347,22 +26347,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G162">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G163">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G164">
@@ -27162,22 +27162,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G165">
@@ -27325,22 +27325,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G166">
@@ -27483,12 +27483,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G167">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>2026-08-30 14:15:00</t>
+          <t>2026-08-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -27646,27 +27646,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G168">
@@ -27797,7 +27797,7 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>2026-08-30 14:15:00</t>
+          <t>2026-08-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -27809,12 +27809,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G169">
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>2026-08-30 14:15:00</t>
+          <t>2026-08-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -27972,12 +27972,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G170">
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>2026-08-30 14:15:00</t>
+          <t>2026-08-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -28135,12 +28135,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G171">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>2026-08-30 14:15:00</t>
+          <t>2026-08-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -28298,12 +28298,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G172">
@@ -28449,7 +28449,7 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>2026-08-30 14:15:00</t>
+          <t>2026-08-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -28461,12 +28461,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G173">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-08-30 14:30:00</t>
+          <t>2026-08-30 14:15:00</t>
         </is>
       </c>
     </row>
@@ -28624,27 +28624,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G174">
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-08-30 14:30:00</t>
+          <t>2026-08-30 14:15:00</t>
         </is>
       </c>
     </row>
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G175">
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-08-30 15:00:00</t>
+          <t>2026-08-30 14:15:00</t>
         </is>
       </c>
     </row>
@@ -28950,12 +28950,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G176">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-08-30 15:00:00</t>
+          <t>2026-08-30 14:15:00</t>
         </is>
       </c>
     </row>
@@ -29113,27 +29113,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G177">
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-08-30 15:00:00</t>
+          <t>2026-08-30 14:15:00</t>
         </is>
       </c>
     </row>
@@ -29276,27 +29276,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G178">
@@ -29427,7 +29427,7 @@
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>2026-08-30 15:00:00</t>
+          <t>2026-08-30 14:15:00</t>
         </is>
       </c>
     </row>
@@ -29439,12 +29439,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G179">
@@ -29590,7 +29590,7 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>2026-08-30 15:00:00</t>
+          <t>2026-08-30 14:30:00</t>
         </is>
       </c>
     </row>
@@ -29602,12 +29602,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G180">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>2026-08-30 15:00:00</t>
+          <t>2026-08-30 14:30:00</t>
         </is>
       </c>
     </row>
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,22 +29933,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,22 +30096,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,22 +30259,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G184">
@@ -30422,7 +30422,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G185">
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G186">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G187">
@@ -30911,22 +30911,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G188">
@@ -31069,12 +31069,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G189">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>2026-08-30 15:15:00</t>
+          <t>2026-08-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -31232,12 +31232,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G190">
@@ -31383,7 +31383,7 @@
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>2026-08-30 15:15:00</t>
+          <t>2026-08-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -31395,12 +31395,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G191">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>2026-08-30 15:15:00</t>
+          <t>2026-08-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -31558,12 +31558,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G192">
@@ -31709,7 +31709,7 @@
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>2026-08-30 15:30:00</t>
+          <t>2026-08-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -31721,12 +31721,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G193">
@@ -31872,7 +31872,7 @@
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>2026-08-30 15:30:00</t>
+          <t>2026-08-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -31884,27 +31884,27 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G194">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>2026-08-30 15:30:00</t>
+          <t>2026-08-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -32047,27 +32047,27 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G195">
@@ -32198,7 +32198,7 @@
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>2026-08-30 15:30:00</t>
+          <t>2026-08-30 15:15:00</t>
         </is>
       </c>
     </row>
@@ -32210,27 +32210,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G196">
@@ -32361,7 +32361,7 @@
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>2026-08-30 15:30:00</t>
+          <t>2026-08-30 15:15:00</t>
         </is>
       </c>
     </row>
@@ -32373,27 +32373,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G197">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>2026-08-30 15:30:00</t>
+          <t>2026-08-30 15:15:00</t>
         </is>
       </c>
     </row>
@@ -32541,22 +32541,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G198">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G199">
@@ -32862,27 +32862,27 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G200">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>2026-08-30 15:45:00</t>
+          <t>2026-08-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -33025,27 +33025,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G201">
@@ -33176,7 +33176,7 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>2026-08-30 15:45:00</t>
+          <t>2026-08-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -33188,27 +33188,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G202">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>2026-08-30 15:45:00</t>
+          <t>2026-08-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -33351,27 +33351,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G203">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-08-30 16:00:00</t>
+          <t>2026-08-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -33514,27 +33514,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G204">
@@ -33665,7 +33665,7 @@
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>2026-08-30 16:00:00</t>
+          <t>2026-08-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -33677,27 +33677,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G205">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>2026-08-30 16:00:00</t>
+          <t>2026-08-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -33840,12 +33840,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G206">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>2026-08-30 16:00:00</t>
+          <t>2026-08-30 15:45:00</t>
         </is>
       </c>
     </row>
@@ -34003,12 +34003,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G207">
@@ -34154,7 +34154,7 @@
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>2026-08-30 16:00:00</t>
+          <t>2026-08-30 15:45:00</t>
         </is>
       </c>
     </row>
@@ -34166,27 +34166,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G208">
@@ -34317,7 +34317,7 @@
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>2026-08-30 16:00:00</t>
+          <t>2026-08-30 15:45:00</t>
         </is>
       </c>
     </row>
@@ -34334,22 +34334,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,22 +34497,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,22 +34660,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,22 +34823,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,7 +34986,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G213">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G214">
@@ -35312,22 +35312,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,22 +35475,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G217">
@@ -35796,27 +35796,27 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G218">
@@ -35947,7 +35947,7 @@
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>2026-08-30 16:15:00</t>
+          <t>2026-08-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -35959,27 +35959,27 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G219">
@@ -36110,7 +36110,7 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>2026-08-30 16:30:00</t>
+          <t>2026-08-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -36122,12 +36122,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G220">
@@ -36273,7 +36273,7 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>2026-08-30 16:30:00</t>
+          <t>2026-08-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -36285,12 +36285,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G221">
@@ -36436,7 +36436,7 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>2026-08-30 16:30:00</t>
+          <t>2026-08-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -36448,27 +36448,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G222">
@@ -36599,7 +36599,7 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>2026-08-30 17:00:00</t>
+          <t>2026-08-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -36611,27 +36611,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G223">
@@ -36762,7 +36762,7 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>2026-08-30 17:30:00</t>
+          <t>2026-08-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -36774,12 +36774,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G224">
@@ -36925,7 +36925,7 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>2026-08-30 18:00:00</t>
+          <t>2026-08-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -36937,12 +36937,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G225">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>2026-08-30 18:00:00</t>
+          <t>2026-08-30 16:15:00</t>
         </is>
       </c>
     </row>
@@ -37100,27 +37100,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G226">
@@ -37251,7 +37251,7 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>2026-08-30 18:30:00</t>
+          <t>2026-08-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -37263,27 +37263,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O227">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P227">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37349,10 +37349,10 @@
         <v>0</v>
       </c>
       <c r="AA227">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB227">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC227">
         <v>0</v>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>2026-08-30 18:30:00</t>
+          <t>2026-08-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -37426,27 +37426,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G228">
@@ -37577,7 +37577,7 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>2026-08-30 18:30:00</t>
+          <t>2026-08-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -37589,12 +37589,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G229">
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>2026-08-30 18:30:00</t>
+          <t>2026-08-30 17:00:00</t>
         </is>
       </c>
     </row>
@@ -37752,12 +37752,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G230">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>2026-08-30 18:30:00</t>
+          <t>2026-08-30 17:30:00</t>
         </is>
       </c>
     </row>
@@ -37915,12 +37915,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G231">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-08-30 18:30:00</t>
+          <t>2026-08-30 18:00:00</t>
         </is>
       </c>
     </row>
@@ -38078,12 +38078,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G232">
@@ -38229,7 +38229,7 @@
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>2026-08-30 19:00:00</t>
+          <t>2026-08-30 18:00:00</t>
         </is>
       </c>
     </row>
@@ -38241,12 +38241,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O233">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P233">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38327,10 +38327,10 @@
         <v>0</v>
       </c>
       <c r="AA233">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB233">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC233">
         <v>0</v>
@@ -38392,7 +38392,7 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>2026-08-30 19:30:00</t>
+          <t>2026-08-30 18:30:00</t>
         </is>
       </c>
     </row>
@@ -38404,12 +38404,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38490,10 +38490,10 @@
         <v>0</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC234">
         <v>0</v>
@@ -38555,7 +38555,7 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>2026-08-30 20:00:00</t>
+          <t>2026-08-30 18:30:00</t>
         </is>
       </c>
     </row>
@@ -38567,12 +38567,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G235">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>2026-08-30 20:00:00</t>
+          <t>2026-08-30 18:30:00</t>
         </is>
       </c>
     </row>
@@ -38730,12 +38730,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G236">
@@ -38881,7 +38881,7 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>2026-08-30 20:00:00</t>
+          <t>2026-08-30 18:30:00</t>
         </is>
       </c>
     </row>
@@ -38893,12 +38893,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G237">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>2026-08-30 21:00:00</t>
+          <t>2026-08-30 18:30:00</t>
         </is>
       </c>
     </row>
@@ -39056,27 +39056,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G238">
@@ -39207,7 +39207,7 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>2026-08-30 21:00:00</t>
+          <t>2026-08-30 18:30:00</t>
         </is>
       </c>
     </row>
@@ -39219,156 +39219,971 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Pacific FC</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>HFX Wanderers FC</t>
+        </is>
+      </c>
+      <c r="G239">
+        <v>0</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>0</v>
+      </c>
+      <c r="L239">
+        <v>0</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N239">
+        <v>0</v>
+      </c>
+      <c r="O239">
+        <v>0</v>
+      </c>
+      <c r="P239">
+        <v>0</v>
+      </c>
+      <c r="Q239">
+        <v>0</v>
+      </c>
+      <c r="R239">
+        <v>0</v>
+      </c>
+      <c r="S239">
+        <v>0</v>
+      </c>
+      <c r="T239">
+        <v>0</v>
+      </c>
+      <c r="U239">
+        <v>0</v>
+      </c>
+      <c r="V239">
+        <v>0</v>
+      </c>
+      <c r="W239">
+        <v>0</v>
+      </c>
+      <c r="X239">
+        <v>0</v>
+      </c>
+      <c r="Y239">
+        <v>0</v>
+      </c>
+      <c r="Z239">
+        <v>0</v>
+      </c>
+      <c r="AA239">
+        <v>0</v>
+      </c>
+      <c r="AB239">
+        <v>0</v>
+      </c>
+      <c r="AC239">
+        <v>0</v>
+      </c>
+      <c r="AD239">
+        <v>0</v>
+      </c>
+      <c r="AE239">
+        <v>0</v>
+      </c>
+      <c r="AF239">
+        <v>0</v>
+      </c>
+      <c r="AG239">
+        <v>0</v>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ239">
+        <v>0</v>
+      </c>
+      <c r="AK239">
+        <v>0</v>
+      </c>
+      <c r="AL239">
+        <v>0</v>
+      </c>
+      <c r="AM239">
+        <v>-1</v>
+      </c>
+      <c r="AN239">
+        <v>-1</v>
+      </c>
+      <c r="AO239">
+        <v>-1</v>
+      </c>
+      <c r="AP239">
+        <v>-1</v>
+      </c>
+      <c r="AQ239">
+        <v>0</v>
+      </c>
+      <c r="AR239">
+        <v>0</v>
+      </c>
+      <c r="AS239">
+        <v>0</v>
+      </c>
+      <c r="AT239">
+        <v>0</v>
+      </c>
+      <c r="AU239" t="inlineStr">
+        <is>
+          <t>2026-08-30 19:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G240">
+        <v>0</v>
+      </c>
+      <c r="H240">
+        <v>0</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>0</v>
+      </c>
+      <c r="L240">
+        <v>0</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N240">
+        <v>1.93</v>
+      </c>
+      <c r="O240">
+        <v>3.55</v>
+      </c>
+      <c r="P240">
+        <v>4.1</v>
+      </c>
+      <c r="Q240">
+        <v>0</v>
+      </c>
+      <c r="R240">
+        <v>0</v>
+      </c>
+      <c r="S240">
+        <v>0</v>
+      </c>
+      <c r="T240">
+        <v>0</v>
+      </c>
+      <c r="U240">
+        <v>0</v>
+      </c>
+      <c r="V240">
+        <v>0</v>
+      </c>
+      <c r="W240">
+        <v>0</v>
+      </c>
+      <c r="X240">
+        <v>0</v>
+      </c>
+      <c r="Y240">
+        <v>0</v>
+      </c>
+      <c r="Z240">
+        <v>0</v>
+      </c>
+      <c r="AA240">
+        <v>2</v>
+      </c>
+      <c r="AB240">
+        <v>1.8</v>
+      </c>
+      <c r="AC240">
+        <v>0</v>
+      </c>
+      <c r="AD240">
+        <v>0</v>
+      </c>
+      <c r="AE240">
+        <v>0</v>
+      </c>
+      <c r="AF240">
+        <v>0</v>
+      </c>
+      <c r="AG240">
+        <v>0</v>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ240">
+        <v>0</v>
+      </c>
+      <c r="AK240">
+        <v>0</v>
+      </c>
+      <c r="AL240">
+        <v>0</v>
+      </c>
+      <c r="AM240">
+        <v>-1</v>
+      </c>
+      <c r="AN240">
+        <v>-1</v>
+      </c>
+      <c r="AO240">
+        <v>-1</v>
+      </c>
+      <c r="AP240">
+        <v>-1</v>
+      </c>
+      <c r="AQ240">
+        <v>0</v>
+      </c>
+      <c r="AR240">
+        <v>0</v>
+      </c>
+      <c r="AS240">
+        <v>0</v>
+      </c>
+      <c r="AT240">
+        <v>0</v>
+      </c>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>2026-08-30 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Leones del Norte</t>
+        </is>
+      </c>
+      <c r="G241">
+        <v>0</v>
+      </c>
+      <c r="H241">
+        <v>0</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>0</v>
+      </c>
+      <c r="L241">
+        <v>0</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N241">
+        <v>0</v>
+      </c>
+      <c r="O241">
+        <v>0</v>
+      </c>
+      <c r="P241">
+        <v>0</v>
+      </c>
+      <c r="Q241">
+        <v>0</v>
+      </c>
+      <c r="R241">
+        <v>0</v>
+      </c>
+      <c r="S241">
+        <v>0</v>
+      </c>
+      <c r="T241">
+        <v>0</v>
+      </c>
+      <c r="U241">
+        <v>0</v>
+      </c>
+      <c r="V241">
+        <v>0</v>
+      </c>
+      <c r="W241">
+        <v>0</v>
+      </c>
+      <c r="X241">
+        <v>0</v>
+      </c>
+      <c r="Y241">
+        <v>0</v>
+      </c>
+      <c r="Z241">
+        <v>0</v>
+      </c>
+      <c r="AA241">
+        <v>0</v>
+      </c>
+      <c r="AB241">
+        <v>0</v>
+      </c>
+      <c r="AC241">
+        <v>0</v>
+      </c>
+      <c r="AD241">
+        <v>0</v>
+      </c>
+      <c r="AE241">
+        <v>0</v>
+      </c>
+      <c r="AF241">
+        <v>0</v>
+      </c>
+      <c r="AG241">
+        <v>0</v>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ241">
+        <v>0</v>
+      </c>
+      <c r="AK241">
+        <v>0</v>
+      </c>
+      <c r="AL241">
+        <v>0</v>
+      </c>
+      <c r="AM241">
+        <v>-1</v>
+      </c>
+      <c r="AN241">
+        <v>-1</v>
+      </c>
+      <c r="AO241">
+        <v>-1</v>
+      </c>
+      <c r="AP241">
+        <v>-1</v>
+      </c>
+      <c r="AQ241">
+        <v>0</v>
+      </c>
+      <c r="AR241">
+        <v>0</v>
+      </c>
+      <c r="AS241">
+        <v>0</v>
+      </c>
+      <c r="AT241">
+        <v>0</v>
+      </c>
+      <c r="AU241" t="inlineStr">
+        <is>
+          <t>2026-08-30 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Seattle Reign</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Houston Dash</t>
+        </is>
+      </c>
+      <c r="G242">
+        <v>0</v>
+      </c>
+      <c r="H242">
+        <v>0</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>0</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N242">
+        <v>0</v>
+      </c>
+      <c r="O242">
+        <v>0</v>
+      </c>
+      <c r="P242">
+        <v>0</v>
+      </c>
+      <c r="Q242">
+        <v>0</v>
+      </c>
+      <c r="R242">
+        <v>0</v>
+      </c>
+      <c r="S242">
+        <v>0</v>
+      </c>
+      <c r="T242">
+        <v>0</v>
+      </c>
+      <c r="U242">
+        <v>0</v>
+      </c>
+      <c r="V242">
+        <v>0</v>
+      </c>
+      <c r="W242">
+        <v>0</v>
+      </c>
+      <c r="X242">
+        <v>0</v>
+      </c>
+      <c r="Y242">
+        <v>0</v>
+      </c>
+      <c r="Z242">
+        <v>0</v>
+      </c>
+      <c r="AA242">
+        <v>0</v>
+      </c>
+      <c r="AB242">
+        <v>0</v>
+      </c>
+      <c r="AC242">
+        <v>0</v>
+      </c>
+      <c r="AD242">
+        <v>0</v>
+      </c>
+      <c r="AE242">
+        <v>0</v>
+      </c>
+      <c r="AF242">
+        <v>0</v>
+      </c>
+      <c r="AG242">
+        <v>0</v>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ242">
+        <v>0</v>
+      </c>
+      <c r="AK242">
+        <v>0</v>
+      </c>
+      <c r="AL242">
+        <v>0</v>
+      </c>
+      <c r="AM242">
+        <v>-1</v>
+      </c>
+      <c r="AN242">
+        <v>-1</v>
+      </c>
+      <c r="AO242">
+        <v>-1</v>
+      </c>
+      <c r="AP242">
+        <v>-1</v>
+      </c>
+      <c r="AQ242">
+        <v>0</v>
+      </c>
+      <c r="AR242">
+        <v>0</v>
+      </c>
+      <c r="AS242">
+        <v>0</v>
+      </c>
+      <c r="AT242">
+        <v>0</v>
+      </c>
+      <c r="AU242" t="inlineStr">
+        <is>
+          <t>2026-08-30 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="G243">
+        <v>0</v>
+      </c>
+      <c r="H243">
+        <v>0</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>0</v>
+      </c>
+      <c r="L243">
+        <v>0</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N243">
+        <v>0</v>
+      </c>
+      <c r="O243">
+        <v>0</v>
+      </c>
+      <c r="P243">
+        <v>0</v>
+      </c>
+      <c r="Q243">
+        <v>0</v>
+      </c>
+      <c r="R243">
+        <v>0</v>
+      </c>
+      <c r="S243">
+        <v>0</v>
+      </c>
+      <c r="T243">
+        <v>0</v>
+      </c>
+      <c r="U243">
+        <v>0</v>
+      </c>
+      <c r="V243">
+        <v>0</v>
+      </c>
+      <c r="W243">
+        <v>0</v>
+      </c>
+      <c r="X243">
+        <v>0</v>
+      </c>
+      <c r="Y243">
+        <v>0</v>
+      </c>
+      <c r="Z243">
+        <v>0</v>
+      </c>
+      <c r="AA243">
+        <v>0</v>
+      </c>
+      <c r="AB243">
+        <v>0</v>
+      </c>
+      <c r="AC243">
+        <v>0</v>
+      </c>
+      <c r="AD243">
+        <v>0</v>
+      </c>
+      <c r="AE243">
+        <v>0</v>
+      </c>
+      <c r="AF243">
+        <v>0</v>
+      </c>
+      <c r="AG243">
+        <v>0</v>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ243">
+        <v>0</v>
+      </c>
+      <c r="AK243">
+        <v>0</v>
+      </c>
+      <c r="AL243">
+        <v>0</v>
+      </c>
+      <c r="AM243">
+        <v>-1</v>
+      </c>
+      <c r="AN243">
+        <v>-1</v>
+      </c>
+      <c r="AO243">
+        <v>-1</v>
+      </c>
+      <c r="AP243">
+        <v>-1</v>
+      </c>
+      <c r="AQ243">
+        <v>0</v>
+      </c>
+      <c r="AR243">
+        <v>0</v>
+      </c>
+      <c r="AS243">
+        <v>0</v>
+      </c>
+      <c r="AT243">
+        <v>0</v>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>2026-08-30 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Portugal Liga NOS</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>Sporting Braga</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>Vitória Guimarães</t>
-        </is>
-      </c>
-      <c r="G239">
-        <v>0</v>
-      </c>
-      <c r="H239">
-        <v>0</v>
-      </c>
-      <c r="I239">
-        <v>0</v>
-      </c>
-      <c r="J239">
-        <v>0</v>
-      </c>
-      <c r="K239">
-        <v>0</v>
-      </c>
-      <c r="L239">
-        <v>0</v>
-      </c>
-      <c r="M239" t="inlineStr">
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="G244">
+        <v>0</v>
+      </c>
+      <c r="H244">
+        <v>0</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>0</v>
+      </c>
+      <c r="L244">
+        <v>0</v>
+      </c>
+      <c r="M244" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N239">
-        <v>0</v>
-      </c>
-      <c r="O239">
-        <v>0</v>
-      </c>
-      <c r="P239">
-        <v>0</v>
-      </c>
-      <c r="Q239">
-        <v>0</v>
-      </c>
-      <c r="R239">
-        <v>0</v>
-      </c>
-      <c r="S239">
-        <v>0</v>
-      </c>
-      <c r="T239">
-        <v>0</v>
-      </c>
-      <c r="U239">
-        <v>0</v>
-      </c>
-      <c r="V239">
-        <v>0</v>
-      </c>
-      <c r="W239">
-        <v>0</v>
-      </c>
-      <c r="X239">
-        <v>0</v>
-      </c>
-      <c r="Y239">
-        <v>0</v>
-      </c>
-      <c r="Z239">
-        <v>0</v>
-      </c>
-      <c r="AA239">
-        <v>0</v>
-      </c>
-      <c r="AB239">
-        <v>0</v>
-      </c>
-      <c r="AC239">
-        <v>0</v>
-      </c>
-      <c r="AD239">
-        <v>0</v>
-      </c>
-      <c r="AE239">
-        <v>0</v>
-      </c>
-      <c r="AF239">
-        <v>0</v>
-      </c>
-      <c r="AG239">
-        <v>0</v>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ239">
-        <v>0</v>
-      </c>
-      <c r="AK239">
-        <v>0</v>
-      </c>
-      <c r="AL239">
-        <v>0</v>
-      </c>
-      <c r="AM239">
-        <v>-1</v>
-      </c>
-      <c r="AN239">
-        <v>-1</v>
-      </c>
-      <c r="AO239">
-        <v>-1</v>
-      </c>
-      <c r="AP239">
-        <v>-1</v>
-      </c>
-      <c r="AQ239">
-        <v>0</v>
-      </c>
-      <c r="AR239">
-        <v>0</v>
-      </c>
-      <c r="AS239">
-        <v>0</v>
-      </c>
-      <c r="AT239">
-        <v>0</v>
-      </c>
-      <c r="AU239" t="inlineStr">
+      <c r="N244">
+        <v>0</v>
+      </c>
+      <c r="O244">
+        <v>0</v>
+      </c>
+      <c r="P244">
+        <v>0</v>
+      </c>
+      <c r="Q244">
+        <v>0</v>
+      </c>
+      <c r="R244">
+        <v>0</v>
+      </c>
+      <c r="S244">
+        <v>0</v>
+      </c>
+      <c r="T244">
+        <v>0</v>
+      </c>
+      <c r="U244">
+        <v>0</v>
+      </c>
+      <c r="V244">
+        <v>0</v>
+      </c>
+      <c r="W244">
+        <v>0</v>
+      </c>
+      <c r="X244">
+        <v>0</v>
+      </c>
+      <c r="Y244">
+        <v>0</v>
+      </c>
+      <c r="Z244">
+        <v>0</v>
+      </c>
+      <c r="AA244">
+        <v>0</v>
+      </c>
+      <c r="AB244">
+        <v>0</v>
+      </c>
+      <c r="AC244">
+        <v>0</v>
+      </c>
+      <c r="AD244">
+        <v>0</v>
+      </c>
+      <c r="AE244">
+        <v>0</v>
+      </c>
+      <c r="AF244">
+        <v>0</v>
+      </c>
+      <c r="AG244">
+        <v>0</v>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ244">
+        <v>0</v>
+      </c>
+      <c r="AK244">
+        <v>0</v>
+      </c>
+      <c r="AL244">
+        <v>0</v>
+      </c>
+      <c r="AM244">
+        <v>-1</v>
+      </c>
+      <c r="AN244">
+        <v>-1</v>
+      </c>
+      <c r="AO244">
+        <v>-1</v>
+      </c>
+      <c r="AP244">
+        <v>-1</v>
+      </c>
+      <c r="AQ244">
+        <v>0</v>
+      </c>
+      <c r="AR244">
+        <v>0</v>
+      </c>
+      <c r="AS244">
+        <v>0</v>
+      </c>
+      <c r="AT244">
+        <v>0</v>
+      </c>
+      <c r="AU244" t="inlineStr">
         <is>
           <t>2026-08-30 21:00:00</t>
         </is>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G91">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G160">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G166">

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -9609,55 +9609,55 @@
         <v>3.33</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G96">
@@ -17107,16 +17107,16 @@
         <v>0</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U103">
         <v>0</v>
@@ -17131,31 +17131,31 @@
         <v>0</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE103">
         <v>0</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G123">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S140">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U140">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V140">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W140">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y140">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z140">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE140">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG140">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK140">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S150">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T150">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U150">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V150">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W150">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y150">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z150">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC150">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD150">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE150">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF150">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG150">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK150">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G156">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O178">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC178">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,16 +2600,16 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U14">
         <v>0</v>
@@ -2624,31 +2624,31 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,10 +6186,10 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -6198,10 +6198,10 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W36">
         <v>0</v>
@@ -6210,31 +6210,31 @@
         <v>0</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,10 +9283,10 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -9295,10 +9295,10 @@
         <v>0</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W55">
         <v>0</v>
@@ -9307,31 +9307,31 @@
         <v>0</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE55">
         <v>0</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10774,31 +10774,31 @@
         <v>0</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE64">
         <v>0</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10913,55 +10913,55 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11106,25 +11106,25 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,10 +11565,10 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -11577,10 +11577,10 @@
         <v>0</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W69">
         <v>0</v>
@@ -11595,25 +11595,25 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,10 +11728,10 @@
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -11740,10 +11740,10 @@
         <v>0</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W70">
         <v>0</v>
@@ -11758,25 +11758,25 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,55 +12380,55 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14662,55 +14662,55 @@
         <v>0</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14855,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G93">
@@ -15477,55 +15477,55 @@
         <v>0</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G110">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21997,10 +21997,10 @@
         <v>0</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S133">
         <v>0</v>
@@ -22009,10 +22009,10 @@
         <v>0</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W133">
         <v>0</v>
@@ -22027,25 +22027,25 @@
         <v>0</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE133">
         <v>0</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22323,55 +22323,55 @@
         <v>0</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T138">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U138">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V138">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W138">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE138">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF138">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG138">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK138">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G143">
@@ -24931,55 +24931,55 @@
         <v>0</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S151">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T151">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U151">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V151">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W151">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X151">
         <v>0</v>
       </c>
       <c r="Y151">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z151">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC151">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD151">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE151">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF151">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG151">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK151">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q158">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R158">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S158">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T158">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U158">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V158">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W158">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X158">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z158">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA158">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB158">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC158">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD158">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE158">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF158">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG158">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK158">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O160">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P160">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q160">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R160">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S160">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T160">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U160">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V160">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W160">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X160">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y160">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z160">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA160">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB160">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC160">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD160">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE160">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF160">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG160">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK160">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S161">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T161">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U161">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V161">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W161">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X161">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y161">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z161">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA161">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC161">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AD161">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE161">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG161">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK161">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S162">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T162">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U162">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V162">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W162">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X162">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y162">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z162">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA162">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB162">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC162">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD162">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE162">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF162">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG162">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK162">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S163">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T163">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U163">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V163">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W163">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X163">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y163">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z163">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA163">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB163">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC163">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD163">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG163">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK163">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S164">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T164">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U164">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V164">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W164">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X164">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y164">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z164">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="AA164">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB164">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC164">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD164">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK164">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q165">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R165">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S165">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T165">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U165">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V165">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W165">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X165">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y165">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z165">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA165">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC165">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD165">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE165">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF165">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG165">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK165">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S166">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T166">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U166">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V166">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W166">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X166">
         <v>0</v>
       </c>
       <c r="Y166">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z166">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA166">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB166">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AC166">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD166">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE166">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG166">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK166">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S167">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T167">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U167">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V167">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W167">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X167">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y167">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z167">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA167">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB167">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC167">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD167">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE167">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF167">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG167">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK167">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27693,64 +27693,64 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q170">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R170">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S170">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T170">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U170">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V170">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X170">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y170">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z170">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC170">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD170">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF170">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG170">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK170">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S174">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T174">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U174">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V174">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W174">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X174">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y174">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z174">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC174">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD174">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE174">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF174">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG174">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK174">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30177,10 +30177,10 @@
         <v>0</v>
       </c>
       <c r="AA183">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB183">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC183">
         <v>0</v>
@@ -30301,64 +30301,64 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S184">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T184">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U184">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="V184">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W184">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X184">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y184">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z184">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA184">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB184">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC184">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD184">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE184">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF184">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG184">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK184">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S188">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T188">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U188">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V188">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W188">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X188">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y188">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z188">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA188">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB188">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC188">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD188">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE188">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF188">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG188">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK188">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q189">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R189">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S189">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T189">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U189">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V189">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W189">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X189">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y189">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z189">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB189">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC189">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD189">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE189">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF189">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG189">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK189">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S191">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T191">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U191">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V191">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W191">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X191">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y191">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z191">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AC191">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD191">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG191">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK191">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O200">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S201">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T201">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V201">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W201">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X201">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y201">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z201">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA201">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB201">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC201">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD201">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE201">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG201">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK201">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O202">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R202">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S202">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T202">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U202">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V202">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W202">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X202">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y202">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z202">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA202">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB202">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC202">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD202">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE202">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF202">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG202">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK202">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q203">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R203">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S203">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T203">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U203">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V203">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W203">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X203">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y203">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z203">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA203">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB203">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC203">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD203">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE203">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF203">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG203">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK203">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S204">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T204">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U204">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V204">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W204">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X204">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y204">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z204">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA204">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB204">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC204">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD204">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE204">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF204">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG204">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK204">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G212">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G213">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O215">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S215">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T215">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U215">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V215">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W215">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X215">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y215">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z215">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA215">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB215">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC215">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD215">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG215">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK215">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O216">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q216">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R216">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S216">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T216">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U216">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V216">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W216">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X216">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y216">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z216">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA216">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB216">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC216">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AD216">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE216">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF216">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG216">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK216">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35680,64 +35680,64 @@
         </is>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O217">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S217">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T217">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U217">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V217">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W217">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y217">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z217">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA217">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB217">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC217">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD217">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE217">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF217">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG217">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AK217">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O219">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q219">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.88</v>
+        <v>3.24</v>
       </c>
       <c r="O19">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="P19">
-        <v>4.6</v>
+        <v>2.16</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.24</v>
+        <v>2.84</v>
       </c>
       <c r="O20">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.84</v>
+        <v>6.51</v>
       </c>
       <c r="O21">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P21">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>6.51</v>
+        <v>1.88</v>
       </c>
       <c r="O22">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="P22">
-        <v>1.48</v>
+        <v>4.6</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="O30">
+        <v>3.5</v>
+      </c>
+      <c r="P30">
+        <v>2.05</v>
+      </c>
+      <c r="Q30">
         <v>3.6</v>
       </c>
-      <c r="P30">
-        <v>3.85</v>
-      </c>
-      <c r="Q30">
-        <v>2.28</v>
-      </c>
       <c r="R30">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="S30">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T30">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="U30">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="V30">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
-        <v>4.55</v>
+        <v>5.48</v>
       </c>
       <c r="AA30">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AB30">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AC30">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="AD30">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AE30">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF30">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AG30">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK30">
-        <v>2.01</v>
+        <v>1.29</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>2.05</v>
+        <v>3.85</v>
       </c>
       <c r="Q31">
-        <v>3.6</v>
+        <v>2.28</v>
       </c>
       <c r="R31">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="S31">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T31">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="U31">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="V31">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>5.48</v>
+        <v>4.55</v>
       </c>
       <c r="AA31">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AB31">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AC31">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AD31">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AE31">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF31">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AG31">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.29</v>
+        <v>2.01</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,80 +7644,80 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.13</v>
+        <v>3.9</v>
       </c>
       <c r="O45">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P45">
-        <v>13</v>
+        <v>1.8</v>
       </c>
       <c r="Q45">
-        <v>1.45</v>
+        <v>3.65</v>
       </c>
       <c r="R45">
-        <v>3.22</v>
+        <v>2.5</v>
       </c>
       <c r="S45">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T45">
-        <v>4.8</v>
+        <v>3.88</v>
       </c>
       <c r="U45">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="V45">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="W45">
+        <v>1.16</v>
+      </c>
+      <c r="X45">
+        <v>1.02</v>
+      </c>
+      <c r="Y45">
+        <v>1.12</v>
+      </c>
+      <c r="Z45">
+        <v>6</v>
+      </c>
+      <c r="AA45">
+        <v>1.39</v>
+      </c>
+      <c r="AB45">
+        <v>2.75</v>
+      </c>
+      <c r="AC45">
+        <v>2.03</v>
+      </c>
+      <c r="AD45">
+        <v>1.7</v>
+      </c>
+      <c r="AE45">
+        <v>1.31</v>
+      </c>
+      <c r="AF45">
+        <v>1.4</v>
+      </c>
+      <c r="AG45">
+        <v>2.61</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
         <v>1.22</v>
       </c>
-      <c r="X45">
-        <v>1.01</v>
-      </c>
-      <c r="Y45">
-        <v>1.03</v>
-      </c>
-      <c r="Z45">
-        <v>8</v>
-      </c>
-      <c r="AA45">
-        <v>1.29</v>
-      </c>
-      <c r="AB45">
-        <v>3.53</v>
-      </c>
-      <c r="AC45">
-        <v>1.78</v>
-      </c>
-      <c r="AD45">
-        <v>2.06</v>
-      </c>
-      <c r="AE45">
-        <v>1.43</v>
-      </c>
-      <c r="AF45">
-        <v>1.81</v>
-      </c>
-      <c r="AG45">
-        <v>1.87</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.06</v>
-      </c>
       <c r="AK45">
-        <v>5.25</v>
+        <v>1.25</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.9</v>
+        <v>1.13</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P46">
-        <v>1.8</v>
+        <v>13</v>
       </c>
       <c r="Q46">
-        <v>3.65</v>
+        <v>1.45</v>
       </c>
       <c r="R46">
-        <v>2.5</v>
+        <v>3.22</v>
       </c>
       <c r="S46">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T46">
-        <v>3.88</v>
+        <v>4.8</v>
       </c>
       <c r="U46">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="V46">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="W46">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="Z46">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA46">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AB46">
-        <v>2.75</v>
+        <v>3.53</v>
       </c>
       <c r="AC46">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="AD46">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AE46">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AF46">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AG46">
-        <v>2.61</v>
+        <v>1.87</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK46">
-        <v>1.25</v>
+        <v>5.25</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P48">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="Q48">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S48">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T48">
-        <v>2.93</v>
+        <v>2.56</v>
       </c>
       <c r="U48">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="V48">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y48">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="AA48">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AB48">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AC48">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="AD48">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG48">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK48">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="O49">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P49">
-        <v>2.91</v>
+        <v>3.72</v>
       </c>
       <c r="Q49">
-        <v>3.13</v>
+        <v>2.34</v>
       </c>
       <c r="R49">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="S49">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T49">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="V49">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>3.46</v>
+        <v>3.65</v>
       </c>
       <c r="AA49">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="AB49">
-        <v>1.78</v>
+        <v>2.16</v>
       </c>
       <c r="AC49">
-        <v>3.25</v>
+        <v>2.54</v>
       </c>
       <c r="AD49">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF49">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>3.72</v>
+        <v>2.75</v>
       </c>
       <c r="Q50">
-        <v>2.34</v>
+        <v>3.18</v>
       </c>
       <c r="R50">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="U50">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V50">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z50">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="AA50">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AB50">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="AC50">
-        <v>2.54</v>
+        <v>2.96</v>
       </c>
       <c r="AD50">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AE50">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG50">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK50">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="O67">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="Q67">
+        <v>3.28</v>
+      </c>
+      <c r="R67">
+        <v>2.25</v>
+      </c>
+      <c r="S67">
+        <v>1.34</v>
+      </c>
+      <c r="T67">
         <v>3.15</v>
       </c>
-      <c r="R67">
-        <v>2.23</v>
-      </c>
-      <c r="S67">
-        <v>1.41</v>
-      </c>
-      <c r="T67">
-        <v>2.69</v>
-      </c>
       <c r="U67">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="V67">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z67">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="AA67">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB67">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC67">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AD67">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AE67">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF67">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG67">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AK67">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P68">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="Q68">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="R68">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S68">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="T68">
-        <v>3.15</v>
+        <v>2.69</v>
       </c>
       <c r="U68">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="V68">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W68">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y68">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z68">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="AA68">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB68">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AC68">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD68">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE68">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG68">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AK68">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="O159">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P159">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="Q159">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R159">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S159">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T159">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U159">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V159">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W159">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X159">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z159">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC159">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD159">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE159">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF159">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG159">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK159">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="O160">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P160">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="Q160">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R160">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S160">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T160">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U160">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V160">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W160">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X160">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y160">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z160">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA160">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB160">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC160">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD160">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE160">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF160">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG160">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK160">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="O215">
-        <v>4.95</v>
+        <v>3.4</v>
       </c>
       <c r="P215">
-        <v>6.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q215">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="R215">
-        <v>2.47</v>
+        <v>1.97</v>
       </c>
       <c r="S215">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="T215">
-        <v>3.4</v>
+        <v>2.68</v>
       </c>
       <c r="U215">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="V215">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="W215">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X215">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y215">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="Z215">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA215">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AB215">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC215">
-        <v>2.55</v>
+        <v>4.16</v>
       </c>
       <c r="AD215">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AE215">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AF215">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG215">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AK215">
-        <v>2.89</v>
+        <v>1.92</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
+        <v>1.38</v>
+      </c>
+      <c r="O216">
+        <v>4.95</v>
+      </c>
+      <c r="P216">
+        <v>6.8</v>
+      </c>
+      <c r="Q216">
+        <v>1.83</v>
+      </c>
+      <c r="R216">
+        <v>2.47</v>
+      </c>
+      <c r="S216">
+        <v>1.27</v>
+      </c>
+      <c r="T216">
+        <v>3.4</v>
+      </c>
+      <c r="U216">
+        <v>2.29</v>
+      </c>
+      <c r="V216">
+        <v>1.53</v>
+      </c>
+      <c r="W216">
+        <v>1.08</v>
+      </c>
+      <c r="X216">
+        <v>1.04</v>
+      </c>
+      <c r="Y216">
+        <v>1.2</v>
+      </c>
+      <c r="Z216">
+        <v>4.4</v>
+      </c>
+      <c r="AA216">
+        <v>1.6</v>
+      </c>
+      <c r="AB216">
+        <v>2.25</v>
+      </c>
+      <c r="AC216">
+        <v>2.55</v>
+      </c>
+      <c r="AD216">
+        <v>1.5</v>
+      </c>
+      <c r="AE216">
+        <v>1.2</v>
+      </c>
+      <c r="AF216">
         <v>1.85</v>
       </c>
-      <c r="O216">
-        <v>3.4</v>
-      </c>
-      <c r="P216">
-        <v>4.33</v>
-      </c>
-      <c r="Q216">
-        <v>2.4</v>
-      </c>
-      <c r="R216">
-        <v>1.97</v>
-      </c>
-      <c r="S216">
-        <v>1.43</v>
-      </c>
-      <c r="T216">
-        <v>2.68</v>
-      </c>
-      <c r="U216">
-        <v>3.15</v>
-      </c>
-      <c r="V216">
-        <v>1.3</v>
-      </c>
-      <c r="W216">
-        <v>1.04</v>
-      </c>
-      <c r="X216">
-        <v>1.05</v>
-      </c>
-      <c r="Y216">
-        <v>1.41</v>
-      </c>
-      <c r="Z216">
-        <v>2.9</v>
-      </c>
-      <c r="AA216">
-        <v>2.25</v>
-      </c>
-      <c r="AB216">
-        <v>1.7</v>
-      </c>
-      <c r="AC216">
-        <v>4.16</v>
-      </c>
-      <c r="AD216">
-        <v>1.25</v>
-      </c>
-      <c r="AE216">
-        <v>1.01</v>
-      </c>
-      <c r="AF216">
-        <v>1.98</v>
-      </c>
       <c r="AG216">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AK216">
-        <v>1.92</v>
+        <v>2.89</v>
       </c>
       <c r="AL216">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q29">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="R29">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S29">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T29">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U29">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="V29">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X29">
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z29">
-        <v>5.07</v>
+        <v>5.48</v>
       </c>
       <c r="AA29">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AB29">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AC29">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD29">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AE29">
         <v>1.22</v>
       </c>
       <c r="AF29">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG29">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK29">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>2.05</v>
+        <v>3.85</v>
       </c>
       <c r="Q30">
-        <v>3.6</v>
+        <v>2.28</v>
       </c>
       <c r="R30">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="S30">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T30">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="U30">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="V30">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="W30">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z30">
-        <v>5.48</v>
+        <v>4.55</v>
       </c>
       <c r="AA30">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AB30">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AC30">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AD30">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AE30">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AG30">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.29</v>
+        <v>2.01</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="Q31">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="R31">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="T31">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="W31">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>4.55</v>
+        <v>5.07</v>
       </c>
       <c r="AA31">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AB31">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="AC31">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AD31">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AE31">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF31">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AG31">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G69">
@@ -11565,10 +11565,10 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="R69">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -11577,10 +11577,10 @@
         <v>0</v>
       </c>
       <c r="U69">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="V69">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="W69">
         <v>0</v>
@@ -11595,25 +11595,25 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB69">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AC69">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AD69">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AE69">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AF69">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AG69">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK69">
-        <v>2.95</v>
+        <v>2.33</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G70">
@@ -11728,10 +11728,10 @@
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="R70">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -11740,10 +11740,10 @@
         <v>0</v>
       </c>
       <c r="U70">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="V70">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="W70">
         <v>0</v>
@@ -11758,25 +11758,25 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB70">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AC70">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AD70">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AE70">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AF70">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AG70">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AK70">
-        <v>2.33</v>
+        <v>2.95</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G132">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="O200">
+        <v>2.62</v>
+      </c>
+      <c r="P200">
+        <v>4.06</v>
+      </c>
+      <c r="Q200">
         <v>2.9</v>
       </c>
-      <c r="P200">
-        <v>4.2</v>
-      </c>
-      <c r="Q200">
-        <v>0</v>
-      </c>
       <c r="R200">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S200">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T200">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U200">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V200">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W200">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X200">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y200">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z200">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA200">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB200">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC200">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD200">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE200">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF200">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG200">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK200">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="O201">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="P201">
-        <v>5.08</v>
+        <v>2.87</v>
       </c>
       <c r="Q201">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="R201">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="S201">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="T201">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="U201">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="V201">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W201">
+        <v>1.02</v>
+      </c>
+      <c r="X201">
+        <v>1.12</v>
+      </c>
+      <c r="Y201">
+        <v>1.58</v>
+      </c>
+      <c r="Z201">
+        <v>2.18</v>
+      </c>
+      <c r="AA201">
+        <v>2.88</v>
+      </c>
+      <c r="AB201">
+        <v>1.35</v>
+      </c>
+      <c r="AC201">
+        <v>6</v>
+      </c>
+      <c r="AD201">
         <v>1.04</v>
       </c>
-      <c r="X201">
-        <v>1.13</v>
-      </c>
-      <c r="Y201">
-        <v>1.55</v>
-      </c>
-      <c r="Z201">
-        <v>2.38</v>
-      </c>
-      <c r="AA201">
-        <v>2.7</v>
-      </c>
-      <c r="AB201">
-        <v>1.4</v>
-      </c>
-      <c r="AC201">
-        <v>5</v>
-      </c>
-      <c r="AD201">
-        <v>1.14</v>
-      </c>
       <c r="AE201">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF201">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AG201">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK201">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,19 +33235,19 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="O202">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P202">
-        <v>4.06</v>
+        <v>4.28</v>
       </c>
       <c r="Q202">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="R202">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S202">
         <v>1.57</v>
@@ -33256,43 +33256,43 @@
         <v>2.25</v>
       </c>
       <c r="U202">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V202">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W202">
         <v>1.03</v>
       </c>
       <c r="X202">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Y202">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z202">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA202">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AB202">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC202">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD202">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE202">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF202">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG202">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK202">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="O203">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="P203">
-        <v>2.87</v>
+        <v>5.08</v>
       </c>
       <c r="Q203">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="R203">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="S203">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="T203">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="U203">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="V203">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W203">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X203">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y203">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Z203">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AA203">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AB203">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC203">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD203">
+        <v>1.14</v>
+      </c>
+      <c r="AE203">
         <v>1.04</v>
       </c>
-      <c r="AE203">
-        <v>1.02</v>
-      </c>
       <c r="AF203">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AG203">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK203">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="O204">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P204">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="Q204">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R204">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S204">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T204">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U204">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V204">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W204">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X204">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y204">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z204">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA204">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB204">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC204">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD204">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE204">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF204">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG204">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK204">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL204">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -22966,25 +22966,25 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T139">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U139">
         <v>0</v>
@@ -22999,31 +22999,31 @@
         <v>0</v>
       </c>
       <c r="Y139">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z139">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE139">
         <v>0</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK139">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q152">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R152">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S152">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T152">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U152">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V152">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W152">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X152">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y152">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z152">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA152">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB152">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC152">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD152">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG152">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK152">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q155">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R155">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S155">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T155">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U155">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="V155">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W155">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X155">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y155">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z155">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA155">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC155">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD155">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE155">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF155">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG155">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK155">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S156">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T156">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U156">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V156">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W156">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X156">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z156">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC156">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD156">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE156">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF156">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG156">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK156">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q172">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="R172">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S172">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T172">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U172">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V172">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W172">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y172">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z172">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA172">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB172">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC172">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD172">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE172">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF172">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG172">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AK172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U179">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V179">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X179">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z179">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG179">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK179">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S186">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V186">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y186">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z186">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD186">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG186">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK186">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31288,55 +31288,55 @@
         <v>0</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S190">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T190">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U190">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V190">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W190">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X190">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y190">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z190">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA190">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC190">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD190">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE190">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF190">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG190">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK190">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S197">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T197">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U197">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V197">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W197">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X197">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z197">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC197">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AD197">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE197">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF197">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG197">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK197">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O198">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S198">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T198">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U198">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V198">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W198">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X198">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y198">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z198">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA198">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB198">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC198">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD198">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE198">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF198">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG198">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK198">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O199">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Q199">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R199">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S199">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T199">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U199">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V199">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W199">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X199">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y199">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z199">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA199">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB199">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC199">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD199">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE199">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF199">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG199">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK199">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="O201">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P201">
-        <v>2.87</v>
+        <v>4.28</v>
       </c>
       <c r="Q201">
-        <v>3.35</v>
+        <v>2.72</v>
       </c>
       <c r="R201">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="S201">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="T201">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U201">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="V201">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W201">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X201">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Y201">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Z201">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AA201">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AB201">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC201">
         <v>6</v>
       </c>
       <c r="AD201">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AE201">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF201">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AG201">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AK201">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,25 +33235,25 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="O202">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P202">
-        <v>4.28</v>
+        <v>5.08</v>
       </c>
       <c r="Q202">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="R202">
         <v>1.91</v>
       </c>
       <c r="S202">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T202">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U202">
         <v>3.75</v>
@@ -33262,37 +33262,37 @@
         <v>1.22</v>
       </c>
       <c r="W202">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X202">
+        <v>1.13</v>
+      </c>
+      <c r="Y202">
+        <v>1.55</v>
+      </c>
+      <c r="Z202">
+        <v>2.38</v>
+      </c>
+      <c r="AA202">
+        <v>2.7</v>
+      </c>
+      <c r="AB202">
+        <v>1.4</v>
+      </c>
+      <c r="AC202">
+        <v>5</v>
+      </c>
+      <c r="AD202">
         <v>1.14</v>
       </c>
-      <c r="Y202">
-        <v>1.62</v>
-      </c>
-      <c r="Z202">
-        <v>2.2</v>
-      </c>
-      <c r="AA202">
-        <v>2.9</v>
-      </c>
-      <c r="AB202">
-        <v>1.36</v>
-      </c>
-      <c r="AC202">
-        <v>6</v>
-      </c>
-      <c r="AD202">
-        <v>1.11</v>
-      </c>
       <c r="AE202">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF202">
         <v>2.4</v>
       </c>
       <c r="AG202">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK202">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="O203">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P203">
-        <v>5.08</v>
+        <v>4.2</v>
       </c>
       <c r="Q203">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R203">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S203">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T203">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U203">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V203">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W203">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X203">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y203">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z203">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA203">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB203">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC203">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD203">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE203">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF203">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG203">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK203">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="O204">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="P204">
+        <v>2.87</v>
+      </c>
+      <c r="Q204">
+        <v>3.35</v>
+      </c>
+      <c r="R204">
+        <v>1.75</v>
+      </c>
+      <c r="S204">
+        <v>1.72</v>
+      </c>
+      <c r="T204">
+        <v>2.1</v>
+      </c>
+      <c r="U204">
         <v>4.2</v>
       </c>
-      <c r="Q204">
-        <v>0</v>
-      </c>
-      <c r="R204">
-        <v>0</v>
-      </c>
-      <c r="S204">
-        <v>0</v>
-      </c>
-      <c r="T204">
-        <v>0</v>
-      </c>
-      <c r="U204">
-        <v>0</v>
-      </c>
       <c r="V204">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W204">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X204">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y204">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z204">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA204">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB204">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC204">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD204">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE204">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF204">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG204">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK204">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33733,55 +33733,55 @@
         <v>0</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S205">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T205">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U205">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V205">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W205">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X205">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y205">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z205">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA205">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB205">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC205">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD205">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE205">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF205">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG205">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK205">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="R207">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S207">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T207">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U207">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V207">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W207">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X207">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y207">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z207">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AA207">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB207">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC207">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD207">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF207">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG207">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK207">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O208">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P208">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="Q208">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R208">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S208">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T208">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U208">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V208">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W208">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X208">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y208">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z208">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA208">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB208">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC208">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD208">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE208">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF208">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG208">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK208">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O209">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P209">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q209">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R209">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S209">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T209">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U209">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V209">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W209">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X209">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y209">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z209">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA209">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB209">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC209">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD209">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE209">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF209">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG209">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK209">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q210">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R210">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S210">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T210">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U210">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V210">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W210">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X210">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y210">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z210">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AA210">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB210">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC210">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD210">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE210">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF210">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG210">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK210">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -37147,64 +37147,64 @@
         </is>
       </c>
       <c r="N226">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O226">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S226">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T226">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U226">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V226">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W226">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X226">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y226">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z226">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA226">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB226">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC226">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD226">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE226">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF226">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG226">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK226">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL226">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>2.16</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>2.45</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>1.48</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>4.6</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>2.05</v>
+        <v>3.85</v>
       </c>
       <c r="Q29">
-        <v>3.6</v>
+        <v>2.28</v>
       </c>
       <c r="R29">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="S29">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T29">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="U29">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="V29">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="W29">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z29">
-        <v>5.48</v>
+        <v>4.55</v>
       </c>
       <c r="AA29">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AB29">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AC29">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AD29">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AE29">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF29">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AG29">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.29</v>
+        <v>2.01</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="O30">
+        <v>3.5</v>
+      </c>
+      <c r="P30">
+        <v>2.05</v>
+      </c>
+      <c r="Q30">
         <v>3.6</v>
       </c>
-      <c r="P30">
-        <v>3.85</v>
-      </c>
-      <c r="Q30">
-        <v>2.28</v>
-      </c>
       <c r="R30">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="S30">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T30">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="U30">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="V30">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
-        <v>4.55</v>
+        <v>5.48</v>
       </c>
       <c r="AA30">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AB30">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AC30">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="AD30">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AE30">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF30">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AG30">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK30">
-        <v>2.01</v>
+        <v>1.29</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -7108,27 +7108,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-08-30 09:15:00</t>
+          <t>2026-08-30 09:00:00</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-08-30 09:30:00</t>
+          <t>2026-08-30 09:15:00</t>
         </is>
       </c>
     </row>
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.27</v>
+        <v>1.85</v>
       </c>
       <c r="O44">
-        <v>5.65</v>
+        <v>3.55</v>
       </c>
       <c r="P44">
-        <v>6.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q44">
+        <v>2.42</v>
+      </c>
+      <c r="R44">
+        <v>2.16</v>
+      </c>
+      <c r="S44">
+        <v>1.31</v>
+      </c>
+      <c r="T44">
+        <v>3.25</v>
+      </c>
+      <c r="U44">
+        <v>2.41</v>
+      </c>
+      <c r="V44">
+        <v>1.47</v>
+      </c>
+      <c r="W44">
+        <v>1.11</v>
+      </c>
+      <c r="X44">
+        <v>1.02</v>
+      </c>
+      <c r="Y44">
+        <v>1.17</v>
+      </c>
+      <c r="Z44">
+        <v>3.95</v>
+      </c>
+      <c r="AA44">
         <v>1.67</v>
       </c>
-      <c r="R44">
-        <v>2.82</v>
-      </c>
-      <c r="S44">
-        <v>1.14</v>
-      </c>
-      <c r="T44">
-        <v>4.25</v>
-      </c>
-      <c r="U44">
-        <v>1.85</v>
-      </c>
-      <c r="V44">
-        <v>1.84</v>
-      </c>
-      <c r="W44">
-        <v>1.2</v>
-      </c>
-      <c r="X44">
-        <v>1.01</v>
-      </c>
-      <c r="Y44">
-        <v>1.08</v>
-      </c>
-      <c r="Z44">
-        <v>6.25</v>
-      </c>
-      <c r="AA44">
-        <v>1.3</v>
-      </c>
       <c r="AB44">
-        <v>2.99</v>
+        <v>2.07</v>
       </c>
       <c r="AC44">
-        <v>1.85</v>
+        <v>2.59</v>
       </c>
       <c r="AD44">
-        <v>1.95</v>
+        <v>1.39</v>
       </c>
       <c r="AE44">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AF44">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG44">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>2.94</v>
+        <v>1.78</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7602,22 +7602,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.9</v>
+        <v>1.27</v>
       </c>
       <c r="O45">
-        <v>4</v>
+        <v>5.65</v>
       </c>
       <c r="P45">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="Q45">
-        <v>3.65</v>
+        <v>1.67</v>
       </c>
       <c r="R45">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="S45">
+        <v>1.14</v>
+      </c>
+      <c r="T45">
+        <v>4.25</v>
+      </c>
+      <c r="U45">
+        <v>1.85</v>
+      </c>
+      <c r="V45">
+        <v>1.84</v>
+      </c>
+      <c r="W45">
         <v>1.2</v>
       </c>
-      <c r="T45">
-        <v>3.88</v>
-      </c>
-      <c r="U45">
-        <v>2.01</v>
-      </c>
-      <c r="V45">
-        <v>1.7</v>
-      </c>
-      <c r="W45">
-        <v>1.16</v>
-      </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z45">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AA45">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AB45">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="AC45">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AD45">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AE45">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF45">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG45">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK45">
-        <v>1.25</v>
+        <v>2.94</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.13</v>
+        <v>3.9</v>
       </c>
       <c r="O46">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>13</v>
+        <v>1.8</v>
       </c>
       <c r="Q46">
-        <v>1.45</v>
+        <v>3.65</v>
       </c>
       <c r="R46">
-        <v>3.22</v>
+        <v>2.5</v>
       </c>
       <c r="S46">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
-        <v>4.8</v>
+        <v>3.88</v>
       </c>
       <c r="U46">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="V46">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="W46">
+        <v>1.16</v>
+      </c>
+      <c r="X46">
+        <v>1.02</v>
+      </c>
+      <c r="Y46">
+        <v>1.12</v>
+      </c>
+      <c r="Z46">
+        <v>6</v>
+      </c>
+      <c r="AA46">
+        <v>1.39</v>
+      </c>
+      <c r="AB46">
+        <v>2.75</v>
+      </c>
+      <c r="AC46">
+        <v>2.03</v>
+      </c>
+      <c r="AD46">
+        <v>1.7</v>
+      </c>
+      <c r="AE46">
+        <v>1.31</v>
+      </c>
+      <c r="AF46">
+        <v>1.4</v>
+      </c>
+      <c r="AG46">
+        <v>2.61</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.22</v>
       </c>
-      <c r="X46">
-        <v>1.01</v>
-      </c>
-      <c r="Y46">
-        <v>1.03</v>
-      </c>
-      <c r="Z46">
-        <v>8</v>
-      </c>
-      <c r="AA46">
-        <v>1.29</v>
-      </c>
-      <c r="AB46">
-        <v>3.53</v>
-      </c>
-      <c r="AC46">
-        <v>1.78</v>
-      </c>
-      <c r="AD46">
-        <v>2.06</v>
-      </c>
-      <c r="AE46">
-        <v>1.43</v>
-      </c>
-      <c r="AF46">
-        <v>1.81</v>
-      </c>
-      <c r="AG46">
-        <v>1.87</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.06</v>
-      </c>
       <c r="AK46">
-        <v>5.25</v>
+        <v>1.25</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.98</v>
+        <v>1.13</v>
       </c>
       <c r="O47">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="P47">
-        <v>3.25</v>
+        <v>13</v>
       </c>
       <c r="Q47">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="R47">
-        <v>2.39</v>
+        <v>3.22</v>
       </c>
       <c r="S47">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="U47">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="V47">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="Z47">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="AA47">
-        <v>1.73</v>
+        <v>1.29</v>
       </c>
       <c r="AB47">
-        <v>2.2</v>
+        <v>3.53</v>
       </c>
       <c r="AC47">
-        <v>2.56</v>
+        <v>1.78</v>
       </c>
       <c r="AD47">
-        <v>1.45</v>
+        <v>2.06</v>
       </c>
       <c r="AE47">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AF47">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="AG47">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="AK47">
-        <v>1.74</v>
+        <v>5.25</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-08-30 09:45:00</t>
+          <t>2026-08-30 09:30:00</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="O48">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="P48">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="Q48">
-        <v>3.13</v>
+        <v>2.5</v>
       </c>
       <c r="R48">
-        <v>2.01</v>
+        <v>2.39</v>
       </c>
       <c r="S48">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
+        <v>3.3</v>
+      </c>
+      <c r="U48">
+        <v>2.3</v>
+      </c>
+      <c r="V48">
+        <v>1.55</v>
+      </c>
+      <c r="W48">
+        <v>1.08</v>
+      </c>
+      <c r="X48">
+        <v>1.04</v>
+      </c>
+      <c r="Y48">
+        <v>1.2</v>
+      </c>
+      <c r="Z48">
+        <v>4.1</v>
+      </c>
+      <c r="AA48">
+        <v>1.73</v>
+      </c>
+      <c r="AB48">
+        <v>2.2</v>
+      </c>
+      <c r="AC48">
         <v>2.56</v>
       </c>
-      <c r="U48">
-        <v>3</v>
-      </c>
-      <c r="V48">
-        <v>1.33</v>
-      </c>
-      <c r="W48">
-        <v>1.05</v>
-      </c>
-      <c r="X48">
-        <v>1.05</v>
-      </c>
-      <c r="Y48">
-        <v>1.3</v>
-      </c>
-      <c r="Z48">
-        <v>3.46</v>
-      </c>
-      <c r="AA48">
-        <v>2.08</v>
-      </c>
-      <c r="AB48">
-        <v>1.78</v>
-      </c>
-      <c r="AC48">
-        <v>3.25</v>
-      </c>
       <c r="AD48">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="AG48">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK48">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-08-30 10:00:00</t>
+          <t>2026-08-30 09:45:00</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="O49">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P49">
-        <v>3.72</v>
+        <v>2.91</v>
       </c>
       <c r="Q49">
-        <v>2.34</v>
+        <v>3.13</v>
       </c>
       <c r="R49">
-        <v>2.22</v>
+        <v>2.01</v>
       </c>
       <c r="S49">
+        <v>1.43</v>
+      </c>
+      <c r="T49">
+        <v>2.56</v>
+      </c>
+      <c r="U49">
+        <v>3</v>
+      </c>
+      <c r="V49">
         <v>1.33</v>
       </c>
-      <c r="T49">
-        <v>3.3</v>
-      </c>
-      <c r="U49">
-        <v>2.52</v>
-      </c>
-      <c r="V49">
-        <v>1.5</v>
-      </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z49">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="AA49">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="AB49">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="AC49">
-        <v>2.54</v>
+        <v>3.25</v>
       </c>
       <c r="AD49">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AE49">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AG49">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK49">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,65 +8459,65 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="O50">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
-        <v>2.75</v>
+        <v>3.72</v>
       </c>
       <c r="Q50">
-        <v>3.18</v>
+        <v>2.34</v>
       </c>
       <c r="R50">
+        <v>2.22</v>
+      </c>
+      <c r="S50">
+        <v>1.33</v>
+      </c>
+      <c r="T50">
+        <v>3.3</v>
+      </c>
+      <c r="U50">
+        <v>2.52</v>
+      </c>
+      <c r="V50">
+        <v>1.5</v>
+      </c>
+      <c r="W50">
+        <v>1.11</v>
+      </c>
+      <c r="X50">
+        <v>1.01</v>
+      </c>
+      <c r="Y50">
+        <v>1.2</v>
+      </c>
+      <c r="Z50">
+        <v>3.65</v>
+      </c>
+      <c r="AA50">
+        <v>1.72</v>
+      </c>
+      <c r="AB50">
+        <v>2.16</v>
+      </c>
+      <c r="AC50">
+        <v>2.54</v>
+      </c>
+      <c r="AD50">
+        <v>1.46</v>
+      </c>
+      <c r="AE50">
+        <v>1.16</v>
+      </c>
+      <c r="AF50">
+        <v>1.6</v>
+      </c>
+      <c r="AG50">
         <v>2.2</v>
       </c>
-      <c r="S50">
-        <v>1.4</v>
-      </c>
-      <c r="T50">
-        <v>2.93</v>
-      </c>
-      <c r="U50">
-        <v>2.58</v>
-      </c>
-      <c r="V50">
-        <v>1.43</v>
-      </c>
-      <c r="W50">
-        <v>1.07</v>
-      </c>
-      <c r="X50">
-        <v>1</v>
-      </c>
-      <c r="Y50">
-        <v>1.26</v>
-      </c>
-      <c r="Z50">
-        <v>3.48</v>
-      </c>
-      <c r="AA50">
-        <v>1.92</v>
-      </c>
-      <c r="AB50">
-        <v>1.92</v>
-      </c>
-      <c r="AC50">
-        <v>2.96</v>
-      </c>
-      <c r="AD50">
-        <v>1.37</v>
-      </c>
-      <c r="AE50">
-        <v>1.08</v>
-      </c>
-      <c r="AF50">
-        <v>1.65</v>
-      </c>
-      <c r="AG50">
-        <v>2.15</v>
-      </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="O51">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="Q51">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="R51">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>2.56</v>
+        <v>2.93</v>
       </c>
       <c r="U51">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="V51">
+        <v>1.43</v>
+      </c>
+      <c r="W51">
+        <v>1.07</v>
+      </c>
+      <c r="X51">
+        <v>1</v>
+      </c>
+      <c r="Y51">
+        <v>1.26</v>
+      </c>
+      <c r="Z51">
+        <v>3.48</v>
+      </c>
+      <c r="AA51">
+        <v>1.92</v>
+      </c>
+      <c r="AB51">
+        <v>1.92</v>
+      </c>
+      <c r="AC51">
+        <v>2.96</v>
+      </c>
+      <c r="AD51">
         <v>1.37</v>
       </c>
-      <c r="W51">
-        <v>1.05</v>
-      </c>
-      <c r="X51">
-        <v>1.05</v>
-      </c>
-      <c r="Y51">
-        <v>1.31</v>
-      </c>
-      <c r="Z51">
-        <v>2.89</v>
-      </c>
-      <c r="AA51">
-        <v>1.98</v>
-      </c>
-      <c r="AB51">
-        <v>1.71</v>
-      </c>
-      <c r="AC51">
-        <v>3.7</v>
-      </c>
-      <c r="AD51">
-        <v>1.26</v>
-      </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK51">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="O52">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P52">
-        <v>4.53</v>
+        <v>3.75</v>
       </c>
       <c r="Q52">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R52">
         <v>2.05</v>
       </c>
       <c r="S52">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T52">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U52">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V52">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y52">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="Z52">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AA52">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AB52">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AC52">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD52">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE52">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AG52">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.32</v>
       </c>
       <c r="AK52">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="O53">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P53">
-        <v>3.95</v>
+        <v>4.53</v>
       </c>
       <c r="Q53">
         <v>2.4</v>
       </c>
       <c r="R53">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T53">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U53">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V53">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W53">
         <v>1.06</v>
       </c>
       <c r="X53">
+        <v>1.03</v>
+      </c>
+      <c r="Y53">
+        <v>1.42</v>
+      </c>
+      <c r="Z53">
+        <v>2.75</v>
+      </c>
+      <c r="AA53">
+        <v>2.25</v>
+      </c>
+      <c r="AB53">
+        <v>1.6</v>
+      </c>
+      <c r="AC53">
+        <v>3.9</v>
+      </c>
+      <c r="AD53">
+        <v>1.18</v>
+      </c>
+      <c r="AE53">
         <v>1.01</v>
       </c>
-      <c r="Y53">
-        <v>1.25</v>
-      </c>
-      <c r="Z53">
-        <v>3.28</v>
-      </c>
-      <c r="AA53">
-        <v>1.93</v>
-      </c>
-      <c r="AB53">
-        <v>1.86</v>
-      </c>
-      <c r="AC53">
-        <v>3.2</v>
-      </c>
-      <c r="AD53">
-        <v>1.3</v>
-      </c>
-      <c r="AE53">
-        <v>1.1</v>
-      </c>
       <c r="AF53">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AG53">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK53">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="O54">
         <v>3.35</v>
       </c>
       <c r="P54">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q54">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="R54">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S54">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T54">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="U54">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="V54">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W54">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.25</v>
       </c>
       <c r="Z54">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="AA54">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AB54">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AC54">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AD54">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE54">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG54">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK54">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,80 +9274,80 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q55">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="R55">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U55">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="V55">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z55">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AA55">
+        <v>1.71</v>
+      </c>
+      <c r="AB55">
+        <v>1.98</v>
+      </c>
+      <c r="AC55">
+        <v>2.75</v>
+      </c>
+      <c r="AD55">
+        <v>1.38</v>
+      </c>
+      <c r="AE55">
+        <v>1.09</v>
+      </c>
+      <c r="AF55">
+        <v>1.61</v>
+      </c>
+      <c r="AG55">
+        <v>2.18</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <v>1.26</v>
+      </c>
+      <c r="AK55">
         <v>1.6</v>
-      </c>
-      <c r="AB55">
-        <v>2.08</v>
-      </c>
-      <c r="AC55">
-        <v>2.48</v>
-      </c>
-      <c r="AD55">
-        <v>1.43</v>
-      </c>
-      <c r="AE55">
-        <v>0</v>
-      </c>
-      <c r="AF55">
-        <v>1.5</v>
-      </c>
-      <c r="AG55">
-        <v>2.33</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.22</v>
-      </c>
-      <c r="AK55">
-        <v>1.38</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="S56">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T56">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U56">
-        <v>3.02</v>
+        <v>2.25</v>
       </c>
       <c r="V56">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="W56">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y56">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="Z56">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="AA56">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AB56">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AC56">
-        <v>3.54</v>
+        <v>2.48</v>
       </c>
       <c r="AD56">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE56">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF56">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AG56">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="O57">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P57">
-        <v>3.33</v>
+        <v>2.35</v>
       </c>
       <c r="Q57">
-        <v>2.33</v>
+        <v>3.16</v>
       </c>
       <c r="R57">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="S57">
+        <v>1.4</v>
+      </c>
+      <c r="T57">
+        <v>2.79</v>
+      </c>
+      <c r="U57">
+        <v>3.02</v>
+      </c>
+      <c r="V57">
+        <v>1.34</v>
+      </c>
+      <c r="W57">
+        <v>1.03</v>
+      </c>
+      <c r="X57">
+        <v>1.02</v>
+      </c>
+      <c r="Y57">
         <v>1.31</v>
       </c>
-      <c r="T57">
-        <v>3.12</v>
-      </c>
-      <c r="U57">
-        <v>2.59</v>
-      </c>
-      <c r="V57">
-        <v>1.45</v>
-      </c>
-      <c r="W57">
-        <v>1.11</v>
-      </c>
-      <c r="X57">
-        <v>1</v>
-      </c>
-      <c r="Y57">
-        <v>1.19</v>
-      </c>
       <c r="Z57">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA57">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AB57">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="AC57">
-        <v>3.03</v>
+        <v>3.54</v>
       </c>
       <c r="AD57">
+        <v>1.25</v>
+      </c>
+      <c r="AE57">
+        <v>1.04</v>
+      </c>
+      <c r="AF57">
+        <v>1.78</v>
+      </c>
+      <c r="AG57">
+        <v>1.91</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>1.26</v>
+      </c>
+      <c r="AK57">
         <v>1.33</v>
-      </c>
-      <c r="AE57">
-        <v>1.09</v>
-      </c>
-      <c r="AF57">
-        <v>1.65</v>
-      </c>
-      <c r="AG57">
-        <v>2.11</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.17</v>
-      </c>
-      <c r="AK57">
-        <v>1.85</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.91</v>
+        <v>2.12</v>
       </c>
       <c r="O58">
-        <v>3.21</v>
+        <v>3.32</v>
       </c>
       <c r="P58">
-        <v>2</v>
+        <v>3.33</v>
       </c>
       <c r="Q58">
-        <v>4.3</v>
+        <v>2.33</v>
       </c>
       <c r="R58">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S58">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T58">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="U58">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V58">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y58">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z58">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA58">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AB58">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AC58">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="AD58">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE58">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF58">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG58">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AK58">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G110">
@@ -20693,55 +20693,55 @@
         <v>0</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G132">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q133">
         <v>4.1</v>
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S180">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T180">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V180">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W180">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X180">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y180">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z180">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC180">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD180">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK180">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29984,55 +29984,55 @@
         <v>0</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S182">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T182">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="U182">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V182">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W182">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y182">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z182">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA182">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB182">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC182">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD182">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE182">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF182">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG182">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK182">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S185">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T185">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U185">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V185">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W185">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X185">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y185">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z185">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC185">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD185">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE185">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG185">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK185">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G194">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U196">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V196">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W196">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X196">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z196">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC196">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD196">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE196">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF196">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG196">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AK196">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>4.98</v>
+        <v>1.62</v>
       </c>
       <c r="O198">
         <v>4</v>
       </c>
       <c r="P198">
-        <v>1.6</v>
+        <v>5.05</v>
       </c>
       <c r="Q198">
-        <v>4.85</v>
+        <v>2.1</v>
       </c>
       <c r="R198">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S198">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T198">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="U198">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="V198">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W198">
+        <v>1.07</v>
+      </c>
+      <c r="X198">
+        <v>1.02</v>
+      </c>
+      <c r="Y198">
+        <v>1.22</v>
+      </c>
+      <c r="Z198">
+        <v>3.78</v>
+      </c>
+      <c r="AA198">
+        <v>1.75</v>
+      </c>
+      <c r="AB198">
+        <v>2.05</v>
+      </c>
+      <c r="AC198">
+        <v>2.72</v>
+      </c>
+      <c r="AD198">
+        <v>1.36</v>
+      </c>
+      <c r="AE198">
         <v>1.1</v>
       </c>
-      <c r="X198">
-        <v>1.04</v>
-      </c>
-      <c r="Y198">
-        <v>1.17</v>
-      </c>
-      <c r="Z198">
-        <v>4.3</v>
-      </c>
-      <c r="AA198">
-        <v>1.61</v>
-      </c>
-      <c r="AB198">
-        <v>2.25</v>
-      </c>
-      <c r="AC198">
-        <v>2.39</v>
-      </c>
-      <c r="AD198">
-        <v>1.49</v>
-      </c>
-      <c r="AE198">
-        <v>1.16</v>
-      </c>
       <c r="AF198">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG198">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK198">
-        <v>1.17</v>
+        <v>2.2</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.62</v>
+        <v>4.98</v>
       </c>
       <c r="O199">
         <v>4</v>
       </c>
       <c r="P199">
-        <v>5.05</v>
+        <v>1.6</v>
       </c>
       <c r="Q199">
-        <v>2.1</v>
+        <v>4.85</v>
       </c>
       <c r="R199">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S199">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T199">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="U199">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="V199">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="W199">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X199">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y199">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z199">
-        <v>3.78</v>
+        <v>4.3</v>
       </c>
       <c r="AA199">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB199">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC199">
-        <v>2.72</v>
+        <v>2.39</v>
       </c>
       <c r="AD199">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AE199">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF199">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG199">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK199">
-        <v>2.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,19 +32909,19 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="O200">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P200">
-        <v>4.06</v>
+        <v>4.28</v>
       </c>
       <c r="Q200">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="R200">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S200">
         <v>1.57</v>
@@ -32930,43 +32930,43 @@
         <v>2.25</v>
       </c>
       <c r="U200">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V200">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W200">
         <v>1.03</v>
       </c>
       <c r="X200">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Y200">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z200">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA200">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AB200">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC200">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD200">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE200">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF200">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG200">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK200">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="O201">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P201">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="Q201">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R201">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S201">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T201">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U201">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V201">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W201">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X201">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y201">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z201">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA201">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB201">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC201">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD201">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE201">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF201">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG201">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK201">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="O202">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="P202">
-        <v>5.08</v>
+        <v>2.87</v>
       </c>
       <c r="Q202">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="R202">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="S202">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="T202">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="U202">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="V202">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W202">
+        <v>1.02</v>
+      </c>
+      <c r="X202">
+        <v>1.12</v>
+      </c>
+      <c r="Y202">
+        <v>1.58</v>
+      </c>
+      <c r="Z202">
+        <v>2.18</v>
+      </c>
+      <c r="AA202">
+        <v>2.88</v>
+      </c>
+      <c r="AB202">
+        <v>1.35</v>
+      </c>
+      <c r="AC202">
+        <v>6</v>
+      </c>
+      <c r="AD202">
         <v>1.04</v>
       </c>
-      <c r="X202">
-        <v>1.13</v>
-      </c>
-      <c r="Y202">
-        <v>1.55</v>
-      </c>
-      <c r="Z202">
-        <v>2.38</v>
-      </c>
-      <c r="AA202">
-        <v>2.7</v>
-      </c>
-      <c r="AB202">
-        <v>1.4</v>
-      </c>
-      <c r="AC202">
-        <v>5</v>
-      </c>
-      <c r="AD202">
-        <v>1.14</v>
-      </c>
       <c r="AE202">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF202">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AG202">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK202">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="O203">
+        <v>2.62</v>
+      </c>
+      <c r="P203">
+        <v>4.06</v>
+      </c>
+      <c r="Q203">
         <v>2.9</v>
       </c>
-      <c r="P203">
-        <v>4.2</v>
-      </c>
-      <c r="Q203">
-        <v>0</v>
-      </c>
       <c r="R203">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S203">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T203">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U203">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V203">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W203">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X203">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y203">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z203">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA203">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB203">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC203">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD203">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE203">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF203">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG203">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK203">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="O204">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="P204">
-        <v>2.87</v>
+        <v>5.08</v>
       </c>
       <c r="Q204">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="R204">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="S204">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="T204">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="U204">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="V204">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W204">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X204">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y204">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Z204">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AA204">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AB204">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC204">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD204">
+        <v>1.14</v>
+      </c>
+      <c r="AE204">
         <v>1.04</v>
       </c>
-      <c r="AE204">
-        <v>1.02</v>
-      </c>
       <c r="AF204">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AG204">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK204">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q206">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R206">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S206">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T206">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U206">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V206">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W206">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X206">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y206">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z206">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA206">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB206">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC206">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD206">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE206">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF206">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG206">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK206">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,34 +34376,34 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="O209">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P209">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="Q209">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="R209">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="S209">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T209">
-        <v>2.39</v>
+        <v>2.57</v>
       </c>
       <c r="U209">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="V209">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W209">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X209">
         <v>1.05</v>
@@ -34412,28 +34412,28 @@
         <v>1.44</v>
       </c>
       <c r="Z209">
-        <v>2.55</v>
+        <v>2.79</v>
       </c>
       <c r="AA209">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AB209">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC209">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="AD209">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE209">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF209">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG209">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK209">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,34 +34539,34 @@
         </is>
       </c>
       <c r="N210">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="O210">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="P210">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="Q210">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="R210">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="S210">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T210">
-        <v>2.57</v>
+        <v>2.39</v>
       </c>
       <c r="U210">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="V210">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W210">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X210">
         <v>1.05</v>
@@ -34575,28 +34575,28 @@
         <v>1.44</v>
       </c>
       <c r="Z210">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="AA210">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AB210">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC210">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="AD210">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE210">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF210">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG210">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK210">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -35852,55 +35852,55 @@
         <v>0</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R218">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S218">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T218">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U218">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V218">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W218">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X218">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y218">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z218">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA218">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB218">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC218">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD218">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG218">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK218">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36015,55 +36015,55 @@
         <v>4.41</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S219">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T219">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U219">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V219">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W219">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X219">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y219">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z219">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA219">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB219">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC219">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD219">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE219">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF219">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG219">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK219">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36830,55 +36830,55 @@
         <v>0</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S224">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T224">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U224">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V224">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X224">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y224">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z224">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC224">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD224">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG224">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK224">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O225">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S225">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T225">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U225">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V225">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W225">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X225">
         <v>0</v>
       </c>
       <c r="Y225">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z225">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA225">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB225">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC225">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD225">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AG225">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK225">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q227">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R227">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S227">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T227">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U227">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V227">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W227">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X227">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y227">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z227">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA227">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB227">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC227">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD227">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE227">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF227">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG227">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK227">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O228">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S228">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T228">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U228">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V228">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W228">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X228">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y228">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z228">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA228">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB228">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC228">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD228">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE228">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF228">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG228">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK228">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O229">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O230">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P230">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q230">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R230">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S230">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T230">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U230">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V230">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W230">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X230">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y230">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z230">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA230">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB230">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC230">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="AD230">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE230">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF230">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG230">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK230">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38134,55 +38134,55 @@
         <v>0</v>
       </c>
       <c r="Q232">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R232">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S232">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T232">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U232">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V232">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X232">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y232">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z232">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA232">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB232">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC232">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD232">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE232">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF232">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG232">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK232">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38460,34 +38460,34 @@
         <v>1.96</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S234">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T234">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U234">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V234">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X234">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y234">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z234">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA234">
         <v>2.2</v>
@@ -38496,19 +38496,19 @@
         <v>1.65</v>
       </c>
       <c r="AC234">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD234">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE234">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF234">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG234">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK234">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -38653,10 +38653,10 @@
         <v>0</v>
       </c>
       <c r="AA235">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB235">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC235">
         <v>0</v>
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q236">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R236">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S236">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T236">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U236">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V236">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W236">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X236">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y236">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z236">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA236">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB236">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC236">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD236">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE236">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF236">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG236">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK236">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39305,10 +39305,10 @@
         <v>0</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC239">
         <v>0</v>
@@ -39438,34 +39438,34 @@
         <v>4.1</v>
       </c>
       <c r="Q240">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R240">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S240">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T240">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U240">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V240">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W240">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X240">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y240">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z240">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA240">
         <v>2</v>
@@ -39474,19 +39474,19 @@
         <v>1.8</v>
       </c>
       <c r="AC240">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD240">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE240">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF240">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG240">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK240">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39592,64 +39592,64 @@
         </is>
       </c>
       <c r="N241">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O241">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P241">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q241">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R241">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S241">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T241">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U241">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V241">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W241">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X241">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y241">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z241">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA241">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB241">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC241">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AD241">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE241">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF241">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG241">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK241">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39764,55 +39764,55 @@
         <v>0</v>
       </c>
       <c r="Q242">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R242">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S242">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T242">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U242">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V242">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W242">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X242">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y242">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z242">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA242">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB242">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC242">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD242">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE242">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF242">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG242">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK242">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -39918,64 +39918,64 @@
         </is>
       </c>
       <c r="N243">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O243">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P243">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q243">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R243">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S243">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T243">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U243">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V243">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W243">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X243">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y243">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z243">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA243">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB243">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC243">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD243">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE243">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF243">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG243">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK243">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40081,64 +40081,64 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R244">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S244">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T244">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U244">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V244">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W244">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X244">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y244">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z244">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA244">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB244">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE244">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF244">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG244">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK244">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL244">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.9</v>
+        <v>1.13</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P46">
-        <v>1.8</v>
+        <v>13</v>
       </c>
       <c r="Q46">
-        <v>3.65</v>
+        <v>1.45</v>
       </c>
       <c r="R46">
-        <v>2.5</v>
+        <v>3.22</v>
       </c>
       <c r="S46">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T46">
-        <v>3.88</v>
+        <v>4.8</v>
       </c>
       <c r="U46">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="V46">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="W46">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="Z46">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA46">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AB46">
-        <v>2.75</v>
+        <v>3.53</v>
       </c>
       <c r="AC46">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="AD46">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AE46">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AF46">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AG46">
-        <v>2.61</v>
+        <v>1.87</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK46">
-        <v>1.25</v>
+        <v>5.25</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.13</v>
+        <v>3.9</v>
       </c>
       <c r="O47">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>13</v>
+        <v>1.8</v>
       </c>
       <c r="Q47">
-        <v>1.45</v>
+        <v>3.65</v>
       </c>
       <c r="R47">
-        <v>3.22</v>
+        <v>2.5</v>
       </c>
       <c r="S47">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T47">
-        <v>4.8</v>
+        <v>3.88</v>
       </c>
       <c r="U47">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="V47">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="W47">
+        <v>1.16</v>
+      </c>
+      <c r="X47">
+        <v>1.02</v>
+      </c>
+      <c r="Y47">
+        <v>1.12</v>
+      </c>
+      <c r="Z47">
+        <v>6</v>
+      </c>
+      <c r="AA47">
+        <v>1.39</v>
+      </c>
+      <c r="AB47">
+        <v>2.75</v>
+      </c>
+      <c r="AC47">
+        <v>2.03</v>
+      </c>
+      <c r="AD47">
+        <v>1.7</v>
+      </c>
+      <c r="AE47">
+        <v>1.31</v>
+      </c>
+      <c r="AF47">
+        <v>1.4</v>
+      </c>
+      <c r="AG47">
+        <v>2.61</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
         <v>1.22</v>
       </c>
-      <c r="X47">
-        <v>1.01</v>
-      </c>
-      <c r="Y47">
-        <v>1.03</v>
-      </c>
-      <c r="Z47">
-        <v>8</v>
-      </c>
-      <c r="AA47">
-        <v>1.29</v>
-      </c>
-      <c r="AB47">
-        <v>3.53</v>
-      </c>
-      <c r="AC47">
-        <v>1.78</v>
-      </c>
-      <c r="AD47">
-        <v>2.06</v>
-      </c>
-      <c r="AE47">
-        <v>1.43</v>
-      </c>
-      <c r="AF47">
-        <v>1.81</v>
-      </c>
-      <c r="AG47">
-        <v>1.87</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.06</v>
-      </c>
       <c r="AK47">
-        <v>5.25</v>
+        <v>1.25</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G69">
@@ -11565,10 +11565,10 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="R69">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -11577,10 +11577,10 @@
         <v>0</v>
       </c>
       <c r="U69">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="V69">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="W69">
         <v>0</v>
@@ -11595,25 +11595,25 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB69">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AC69">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AD69">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AE69">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AF69">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AG69">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AK69">
-        <v>2.33</v>
+        <v>2.95</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G70">
@@ -11728,10 +11728,10 @@
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="R70">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -11740,10 +11740,10 @@
         <v>0</v>
       </c>
       <c r="U70">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="V70">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="W70">
         <v>0</v>
@@ -11758,25 +11758,25 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB70">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AC70">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AD70">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AE70">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AF70">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AG70">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK70">
-        <v>2.95</v>
+        <v>2.33</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G110">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="O203">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="P203">
-        <v>4.06</v>
+        <v>5.08</v>
       </c>
       <c r="Q203">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R203">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S203">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T203">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U203">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V203">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W203">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X203">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Y203">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="Z203">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AA203">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB203">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC203">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD203">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AE203">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF203">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG203">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK203">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,80 +33561,80 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="O204">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="P204">
-        <v>5.08</v>
+        <v>4.06</v>
       </c>
       <c r="Q204">
+        <v>2.9</v>
+      </c>
+      <c r="R204">
+        <v>1.83</v>
+      </c>
+      <c r="S204">
+        <v>1.57</v>
+      </c>
+      <c r="T204">
+        <v>2.25</v>
+      </c>
+      <c r="U204">
+        <v>4</v>
+      </c>
+      <c r="V204">
+        <v>1.2</v>
+      </c>
+      <c r="W204">
+        <v>1.03</v>
+      </c>
+      <c r="X204">
+        <v>1.17</v>
+      </c>
+      <c r="Y204">
+        <v>1.7</v>
+      </c>
+      <c r="Z204">
+        <v>2.05</v>
+      </c>
+      <c r="AA204">
+        <v>3.25</v>
+      </c>
+      <c r="AB204">
+        <v>1.3</v>
+      </c>
+      <c r="AC204">
+        <v>7</v>
+      </c>
+      <c r="AD204">
+        <v>1.08</v>
+      </c>
+      <c r="AE204">
+        <v>1.02</v>
+      </c>
+      <c r="AF204">
         <v>2.5</v>
       </c>
-      <c r="R204">
-        <v>1.91</v>
-      </c>
-      <c r="S204">
-        <v>1.5</v>
-      </c>
-      <c r="T204">
-        <v>2.4</v>
-      </c>
-      <c r="U204">
-        <v>3.75</v>
-      </c>
-      <c r="V204">
-        <v>1.22</v>
-      </c>
-      <c r="W204">
-        <v>1.04</v>
-      </c>
-      <c r="X204">
-        <v>1.13</v>
-      </c>
-      <c r="Y204">
-        <v>1.55</v>
-      </c>
-      <c r="Z204">
-        <v>2.38</v>
-      </c>
-      <c r="AA204">
-        <v>2.7</v>
-      </c>
-      <c r="AB204">
-        <v>1.4</v>
-      </c>
-      <c r="AC204">
-        <v>5</v>
-      </c>
-      <c r="AD204">
-        <v>1.14</v>
-      </c>
-      <c r="AE204">
-        <v>1.04</v>
-      </c>
-      <c r="AF204">
-        <v>2.4</v>
-      </c>
       <c r="AG204">
+        <v>1.44</v>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ204">
+        <v>1.44</v>
+      </c>
+      <c r="AK204">
         <v>1.62</v>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ204">
-        <v>1.36</v>
-      </c>
-      <c r="AK204">
-        <v>1.95</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G223">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,64 +38451,64 @@
         </is>
       </c>
       <c r="N234">
-        <v>4.1</v>
+        <v>1.55</v>
       </c>
       <c r="O234">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="P234">
-        <v>1.96</v>
+        <v>5.97</v>
       </c>
       <c r="Q234">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R234">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S234">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T234">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U234">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V234">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W234">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X234">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y234">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z234">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AA234">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB234">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC234">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD234">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE234">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF234">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG234">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK234">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,65 +38614,65 @@
         </is>
       </c>
       <c r="N235">
-        <v>1.55</v>
+        <v>4.1</v>
       </c>
       <c r="O235">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="P235">
-        <v>5.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q235">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R235">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S235">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T235">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U235">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V235">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W235">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X235">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y235">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z235">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA235">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB235">
+        <v>1.65</v>
+      </c>
+      <c r="AC235">
+        <v>3.58</v>
+      </c>
+      <c r="AD235">
+        <v>1.26</v>
+      </c>
+      <c r="AE235">
+        <v>1.06</v>
+      </c>
+      <c r="AF235">
+        <v>1.8</v>
+      </c>
+      <c r="AG235">
         <v>1.95</v>
       </c>
-      <c r="AC235">
-        <v>0</v>
-      </c>
-      <c r="AD235">
-        <v>0</v>
-      </c>
-      <c r="AE235">
-        <v>0</v>
-      </c>
-      <c r="AF235">
-        <v>0</v>
-      </c>
-      <c r="AG235">
-        <v>0</v>
-      </c>
       <c r="AH235" t="inlineStr">
         <is>
           <t>[]</t>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK235">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL235">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -644,22 +644,22 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>6.3</v>
+        <v>4.94</v>
       </c>
       <c r="R2">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="S2">
         <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="U2">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
         <v>1.03</v>
@@ -668,22 +668,22 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z2">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AA2">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AB2">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC2">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="AD2">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
         <v>1.04</v>
@@ -692,7 +692,7 @@
         <v>2.11</v>
       </c>
       <c r="AG2">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK2">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,10 +2274,10 @@
         <v>2.2</v>
       </c>
       <c r="Q12">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R12">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S12">
         <v>1.22</v>
@@ -2289,7 +2289,7 @@
         <v>2.2</v>
       </c>
       <c r="V12">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W12">
         <v>1.14</v>
@@ -2301,25 +2301,25 @@
         <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA12">
         <v>1.44</v>
       </c>
       <c r="AB12">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC12">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AD12">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE12">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF12">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG12">
         <v>2.66</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>2.74</v>
       </c>
       <c r="R13">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="S13">
         <v>1.48</v>
@@ -2452,7 +2452,7 @@
         <v>3.22</v>
       </c>
       <c r="V13">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W13">
         <v>1.01</v>
@@ -2473,7 +2473,7 @@
         <v>1.63</v>
       </c>
       <c r="AC13">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="AD13">
         <v>1.17</v>
@@ -2501,7 +2501,7 @@
         <v>1.32</v>
       </c>
       <c r="AK13">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q14">
-        <v>3.2</v>
+        <v>3.71</v>
       </c>
       <c r="R14">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="S14">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T14">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA14">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC14">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AD14">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.41</v>
       </c>
       <c r="AK14">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2923,25 +2923,25 @@
         <v>4.33</v>
       </c>
       <c r="P16">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q16">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="R16">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S16">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="T16">
         <v>4.5</v>
       </c>
       <c r="U16">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="V16">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W16">
         <v>1.17</v>
@@ -2956,22 +2956,22 @@
         <v>6.25</v>
       </c>
       <c r="AA16">
+        <v>1.41</v>
+      </c>
+      <c r="AB16">
+        <v>2.91</v>
+      </c>
+      <c r="AC16">
+        <v>2.02</v>
+      </c>
+      <c r="AD16">
+        <v>1.76</v>
+      </c>
+      <c r="AE16">
+        <v>1.28</v>
+      </c>
+      <c r="AF16">
         <v>1.4</v>
-      </c>
-      <c r="AB16">
-        <v>2.9</v>
-      </c>
-      <c r="AC16">
-        <v>1.99</v>
-      </c>
-      <c r="AD16">
-        <v>1.83</v>
-      </c>
-      <c r="AE16">
-        <v>1.32</v>
-      </c>
-      <c r="AF16">
-        <v>1.43</v>
       </c>
       <c r="AG16">
         <v>2.7</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,13 +3083,13 @@
         <v>4.22</v>
       </c>
       <c r="O17">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P17">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="Q17">
-        <v>4.47</v>
+        <v>4.2</v>
       </c>
       <c r="R17">
         <v>2.6</v>
@@ -3098,7 +3098,7 @@
         <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U17">
         <v>2.17</v>
@@ -3107,7 +3107,7 @@
         <v>1.65</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
         <v>1.02</v>
@@ -3119,22 +3119,22 @@
         <v>5.45</v>
       </c>
       <c r="AA17">
+        <v>1.48</v>
+      </c>
+      <c r="AB17">
+        <v>2.62</v>
+      </c>
+      <c r="AC17">
+        <v>2.15</v>
+      </c>
+      <c r="AD17">
+        <v>1.64</v>
+      </c>
+      <c r="AE17">
+        <v>1.26</v>
+      </c>
+      <c r="AF17">
         <v>1.47</v>
-      </c>
-      <c r="AB17">
-        <v>2.65</v>
-      </c>
-      <c r="AC17">
-        <v>2.09</v>
-      </c>
-      <c r="AD17">
-        <v>1.67</v>
-      </c>
-      <c r="AE17">
-        <v>1.28</v>
-      </c>
-      <c r="AF17">
-        <v>1.45</v>
       </c>
       <c r="AG17">
         <v>2.5</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.18</v>
+        <v>2.12</v>
       </c>
       <c r="AK17">
         <v>1.16</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q18">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R18">
         <v>2.22</v>
@@ -3261,7 +3261,7 @@
         <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
         <v>2.24</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK18">
         <v>1.87</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="O19">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q19">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S19">
         <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="U19">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z19">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="AA19">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AB19">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AC19">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="AD19">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
+        <v>5.75</v>
+      </c>
+      <c r="O20">
+        <v>3.8</v>
+      </c>
+      <c r="P20">
+        <v>1.48</v>
+      </c>
+      <c r="Q20">
+        <v>6</v>
+      </c>
+      <c r="R20">
+        <v>2.3</v>
+      </c>
+      <c r="S20">
+        <v>1.33</v>
+      </c>
+      <c r="T20">
         <v>3.1</v>
       </c>
-      <c r="O20">
-        <v>3.1</v>
-      </c>
-      <c r="P20">
-        <v>2.15</v>
-      </c>
-      <c r="Q20">
-        <v>3.6</v>
-      </c>
-      <c r="R20">
-        <v>2.02</v>
-      </c>
-      <c r="S20">
-        <v>1.4</v>
-      </c>
-      <c r="T20">
-        <v>2.73</v>
-      </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z20">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="AA20">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB20">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AC20">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="AD20">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AG20">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>5.75</v>
+        <v>2.7</v>
       </c>
       <c r="O21">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="P21">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q21">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S21">
+        <v>1.4</v>
+      </c>
+      <c r="T21">
+        <v>2.62</v>
+      </c>
+      <c r="U21">
+        <v>3</v>
+      </c>
+      <c r="V21">
         <v>1.33</v>
       </c>
-      <c r="T21">
-        <v>3.1</v>
-      </c>
-      <c r="U21">
-        <v>2.5</v>
-      </c>
-      <c r="V21">
-        <v>1.44</v>
-      </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Z21">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="AA21">
+        <v>2.21</v>
+      </c>
+      <c r="AB21">
+        <v>1.64</v>
+      </c>
+      <c r="AC21">
+        <v>3.94</v>
+      </c>
+      <c r="AD21">
+        <v>1.2</v>
+      </c>
+      <c r="AE21">
+        <v>1.04</v>
+      </c>
+      <c r="AF21">
         <v>1.85</v>
       </c>
-      <c r="AB21">
-        <v>1.9</v>
-      </c>
-      <c r="AC21">
-        <v>3.41</v>
-      </c>
-      <c r="AD21">
-        <v>1.3</v>
-      </c>
-      <c r="AE21">
-        <v>1.07</v>
-      </c>
-      <c r="AF21">
-        <v>1.97</v>
-      </c>
       <c r="AG21">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AK21">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P25">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="Q25">
-        <v>4.5</v>
+        <v>4.88</v>
       </c>
       <c r="R25">
         <v>2.25</v>
@@ -4405,7 +4405,7 @@
         <v>3.34</v>
       </c>
       <c r="U25">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V25">
         <v>1.52</v>
@@ -4417,31 +4417,31 @@
         <v>1.03</v>
       </c>
       <c r="Y25">
+        <v>1.17</v>
+      </c>
+      <c r="Z25">
+        <v>4.6</v>
+      </c>
+      <c r="AA25">
+        <v>1.62</v>
+      </c>
+      <c r="AB25">
+        <v>2.3</v>
+      </c>
+      <c r="AC25">
+        <v>2.42</v>
+      </c>
+      <c r="AD25">
+        <v>1.49</v>
+      </c>
+      <c r="AE25">
         <v>1.14</v>
       </c>
-      <c r="Z25">
-        <v>4.45</v>
-      </c>
-      <c r="AA25">
-        <v>1.61</v>
-      </c>
-      <c r="AB25">
-        <v>2.31</v>
-      </c>
-      <c r="AC25">
-        <v>2.55</v>
-      </c>
-      <c r="AD25">
-        <v>1.5</v>
-      </c>
-      <c r="AE25">
-        <v>1.19</v>
-      </c>
       <c r="AF25">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>2.2</v>
       </c>
       <c r="AK25">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4879,25 +4879,25 @@
         <v>3.25</v>
       </c>
       <c r="P28">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q28">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="R28">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="S28">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T28">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="U28">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V28">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W28">
         <v>1.09</v>
@@ -4906,22 +4906,22 @@
         <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z28">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="AA28">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB28">
         <v>2.35</v>
       </c>
       <c r="AC28">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AD28">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE28">
         <v>1.18</v>
@@ -4930,7 +4930,7 @@
         <v>1.44</v>
       </c>
       <c r="AG28">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,55 +5036,55 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="O29">
+        <v>3.82</v>
+      </c>
+      <c r="P29">
+        <v>2.05</v>
+      </c>
+      <c r="Q29">
+        <v>3.25</v>
+      </c>
+      <c r="R29">
+        <v>2.45</v>
+      </c>
+      <c r="S29">
+        <v>1.25</v>
+      </c>
+      <c r="T29">
         <v>3.8</v>
       </c>
-      <c r="P29">
-        <v>2.95</v>
-      </c>
-      <c r="Q29">
-        <v>2.45</v>
-      </c>
-      <c r="R29">
-        <v>2.4</v>
-      </c>
-      <c r="S29">
-        <v>1.24</v>
-      </c>
-      <c r="T29">
-        <v>3.5</v>
-      </c>
       <c r="U29">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V29">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z29">
-        <v>5.07</v>
+        <v>5.25</v>
       </c>
       <c r="AA29">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AB29">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="AC29">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD29">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AE29">
         <v>1.22</v>
@@ -5093,7 +5093,7 @@
         <v>1.44</v>
       </c>
       <c r="AG29">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AK29">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,34 +5199,34 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>2.05</v>
+        <v>2.77</v>
       </c>
       <c r="Q30">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="R30">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S30">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T30">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="U30">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="V30">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W30">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
         <v>1.02</v>
@@ -5235,44 +5235,44 @@
         <v>1.14</v>
       </c>
       <c r="Z30">
-        <v>5.48</v>
+        <v>5.07</v>
       </c>
       <c r="AA30">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AB30">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AC30">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD30">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE30">
+        <v>1.18</v>
+      </c>
+      <c r="AF30">
+        <v>1.44</v>
+      </c>
+      <c r="AG30">
+        <v>2.5</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.22</v>
       </c>
-      <c r="AF30">
-        <v>1.41</v>
-      </c>
-      <c r="AG30">
-        <v>2.6</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.19</v>
-      </c>
       <c r="AK30">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
         <v>3.85</v>
       </c>
       <c r="Q31">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="R31">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
         <v>1.27</v>
@@ -5383,22 +5383,22 @@
         <v>3.4</v>
       </c>
       <c r="U31">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
         <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA31">
         <v>1.61</v>
@@ -5407,19 +5407,19 @@
         <v>2.23</v>
       </c>
       <c r="AC31">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AD31">
         <v>1.48</v>
       </c>
       <c r="AE31">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG31">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q32">
         <v>4.45</v>
@@ -5540,13 +5540,13 @@
         <v>2.26</v>
       </c>
       <c r="S32">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U32">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="V32">
         <v>1.57</v>
@@ -5564,7 +5564,7 @@
         <v>4.45</v>
       </c>
       <c r="AA32">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB32">
         <v>2.21</v>
@@ -5579,7 +5579,7 @@
         <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG32">
         <v>2.23</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="O34">
-        <v>3.53</v>
+        <v>3.59</v>
       </c>
       <c r="P34">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6014,34 +6014,34 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O35">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
         <v>3.25</v>
       </c>
       <c r="Q35">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="U35">
         <v>2.15</v>
       </c>
       <c r="V35">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1.02</v>
@@ -6050,28 +6050,28 @@
         <v>1.16</v>
       </c>
       <c r="Z35">
-        <v>5.24</v>
+        <v>4.75</v>
       </c>
       <c r="AA35">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AB35">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AC35">
         <v>2.35</v>
       </c>
       <c r="AD35">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AE35">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF35">
         <v>1.44</v>
       </c>
       <c r="AG35">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AK35">
         <v>1.64</v>
@@ -6506,16 +6506,16 @@
         <v>3.9</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P38">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q38">
-        <v>4.38</v>
+        <v>4.5</v>
       </c>
       <c r="R38">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="S38">
         <v>1.41</v>
@@ -6539,13 +6539,13 @@
         <v>1.3</v>
       </c>
       <c r="Z38">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="AA38">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AB38">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AC38">
         <v>3.24</v>
@@ -6560,7 +6560,7 @@
         <v>1.78</v>
       </c>
       <c r="AG38">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.88</v>
       </c>
       <c r="AK38">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O39">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="P39">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="Q39">
         <v>2.83</v>
@@ -6681,22 +6681,22 @@
         <v>2.49</v>
       </c>
       <c r="S39">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U39">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V39">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W39">
         <v>1.1</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
         <v>1.18</v>
@@ -6705,25 +6705,25 @@
         <v>4.5</v>
       </c>
       <c r="AA39">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AB39">
         <v>2.31</v>
       </c>
       <c r="AC39">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AD39">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE39">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF39">
         <v>1.5</v>
       </c>
       <c r="AG39">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK39">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>6.05</v>
+        <v>5.5</v>
       </c>
       <c r="O40">
         <v>4.2</v>
@@ -6838,46 +6838,46 @@
         <v>1.44</v>
       </c>
       <c r="Q40">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="R40">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="S40">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U40">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V40">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="W40">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z40">
         <v>5.5</v>
       </c>
       <c r="AA40">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AB40">
         <v>2.57</v>
       </c>
       <c r="AC40">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD40">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AE40">
         <v>1.23</v>
@@ -6902,7 +6902,7 @@
         <v>1.16</v>
       </c>
       <c r="AK40">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7004,19 +7004,19 @@
         <v>3.75</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S41">
         <v>1.35</v>
       </c>
       <c r="T41">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U41">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
         <v>1.07</v>
@@ -7164,16 +7164,16 @@
         <v>2</v>
       </c>
       <c r="Q42">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="R42">
         <v>2.12</v>
       </c>
       <c r="S42">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T42">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U42">
         <v>2.75</v>
@@ -7188,13 +7188,13 @@
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z42">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AA42">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AB42">
         <v>1.83</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AK42">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,22 +7481,22 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O44">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="Q44">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="R44">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T44">
         <v>3.25</v>
@@ -7505,40 +7505,40 @@
         <v>2.41</v>
       </c>
       <c r="V44">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X44">
         <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z44">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA44">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB44">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC44">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="AD44">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE44">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG44">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK44">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7813,10 +7813,10 @@
         <v>8</v>
       </c>
       <c r="P46">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q46">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R46">
         <v>3.22</v>
@@ -7828,10 +7828,10 @@
         <v>4.8</v>
       </c>
       <c r="U46">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="V46">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="W46">
         <v>1.22</v>
@@ -7843,10 +7843,10 @@
         <v>1.03</v>
       </c>
       <c r="Z46">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AA46">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB46">
         <v>3.53</v>
@@ -7855,16 +7855,16 @@
         <v>1.78</v>
       </c>
       <c r="AD46">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AE46">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF46">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG46">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK46">
-        <v>5.25</v>
+        <v>5.7</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="O47">
         <v>4</v>
@@ -7979,19 +7979,19 @@
         <v>1.8</v>
       </c>
       <c r="Q47">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="R47">
         <v>2.5</v>
       </c>
       <c r="S47">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T47">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="U47">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="V47">
         <v>1.7</v>
@@ -8009,25 +8009,25 @@
         <v>6</v>
       </c>
       <c r="AA47">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AB47">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AC47">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AD47">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE47">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AF47">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>2.06</v>
       </c>
       <c r="AK47">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O48">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q48">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R48">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="S48">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="V48">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W48">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="AA48">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB48">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AC48">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AD48">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE48">
         <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG48">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.29</v>
       </c>
       <c r="AK48">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,25 +8296,25 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="O49">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P49">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="Q49">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="R49">
         <v>2.01</v>
       </c>
       <c r="S49">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T49">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="U49">
         <v>3</v>
@@ -8326,22 +8326,22 @@
         <v>1.05</v>
       </c>
       <c r="X49">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
         <v>1.3</v>
       </c>
       <c r="Z49">
-        <v>3.46</v>
+        <v>3.14</v>
       </c>
       <c r="AA49">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AB49">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AC49">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="AD49">
         <v>1.31</v>
@@ -8353,7 +8353,7 @@
         <v>1.76</v>
       </c>
       <c r="AG49">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8459,58 +8459,58 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="Q50">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="R50">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="S50">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
         <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="V50">
         <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="AA50">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB50">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AC50">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="AD50">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
         <v>1.6</v>
@@ -8532,7 +8532,7 @@
         <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q51">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S51">
+        <v>1.36</v>
+      </c>
+      <c r="T51">
+        <v>3.15</v>
+      </c>
+      <c r="U51">
+        <v>2.81</v>
+      </c>
+      <c r="V51">
         <v>1.4</v>
       </c>
-      <c r="T51">
-        <v>2.93</v>
-      </c>
-      <c r="U51">
-        <v>2.58</v>
-      </c>
-      <c r="V51">
-        <v>1.43</v>
-      </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z51">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AA51">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB51">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC51">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="AD51">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
         <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG51">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AK51">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,61 +8785,61 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="O52">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="P52">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="Q52">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R52">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="S52">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T52">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="U52">
         <v>2.8</v>
       </c>
       <c r="V52">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W52">
+        <v>1.06</v>
+      </c>
+      <c r="X52">
+        <v>1.01</v>
+      </c>
+      <c r="Y52">
+        <v>1.35</v>
+      </c>
+      <c r="Z52">
+        <v>3.08</v>
+      </c>
+      <c r="AA52">
+        <v>2.05</v>
+      </c>
+      <c r="AB52">
+        <v>1.75</v>
+      </c>
+      <c r="AC52">
+        <v>3.48</v>
+      </c>
+      <c r="AD52">
+        <v>1.33</v>
+      </c>
+      <c r="AE52">
         <v>1.05</v>
       </c>
-      <c r="X52">
-        <v>1.05</v>
-      </c>
-      <c r="Y52">
-        <v>1.31</v>
-      </c>
-      <c r="Z52">
-        <v>2.89</v>
-      </c>
-      <c r="AA52">
-        <v>1.98</v>
-      </c>
-      <c r="AB52">
-        <v>1.71</v>
-      </c>
-      <c r="AC52">
-        <v>3.7</v>
-      </c>
-      <c r="AD52">
-        <v>1.26</v>
-      </c>
-      <c r="AE52">
-        <v>1.07</v>
-      </c>
       <c r="AF52">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG52">
         <v>1.9</v>
@@ -8858,7 +8858,7 @@
         <v>1.32</v>
       </c>
       <c r="AK52">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,25 +8948,25 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="O53">
         <v>3.1</v>
       </c>
       <c r="P53">
-        <v>4.53</v>
+        <v>3.4</v>
       </c>
       <c r="Q53">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="R53">
         <v>2.05</v>
       </c>
       <c r="S53">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T53">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U53">
         <v>3.2</v>
@@ -8975,10 +8975,10 @@
         <v>1.3</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y53">
         <v>1.42</v>
@@ -8993,19 +8993,19 @@
         <v>1.6</v>
       </c>
       <c r="AC53">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD53">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE53">
         <v>1.01</v>
       </c>
       <c r="AF53">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AG53">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9117,10 +9117,10 @@
         <v>3.35</v>
       </c>
       <c r="P54">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="Q54">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="R54">
         <v>2.07</v>
@@ -9129,16 +9129,16 @@
         <v>1.36</v>
       </c>
       <c r="T54">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U54">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="V54">
         <v>1.36</v>
       </c>
       <c r="W54">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
         <v>1.01</v>
@@ -9147,28 +9147,28 @@
         <v>1.25</v>
       </c>
       <c r="Z54">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AA54">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB54">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC54">
         <v>3.2</v>
       </c>
       <c r="AD54">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE54">
         <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG54">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9274,61 +9274,61 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="O55">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P55">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="Q55">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="R55">
         <v>2.12</v>
       </c>
       <c r="S55">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T55">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="U55">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="V55">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W55">
         <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z55">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA55">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AB55">
         <v>1.98</v>
       </c>
       <c r="AC55">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="AD55">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE55">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF55">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG55">
         <v>2.18</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,28 +9600,28 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="O57">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="Q57">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S57">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T57">
         <v>2.79</v>
       </c>
       <c r="U57">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="V57">
         <v>1.34</v>
@@ -9633,31 +9633,31 @@
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z57">
         <v>3.1</v>
       </c>
       <c r="AA57">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB57">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC57">
         <v>3.54</v>
       </c>
       <c r="AD57">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE57">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG57">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
         <v>1.33</v>
@@ -9766,61 +9766,61 @@
         <v>2.12</v>
       </c>
       <c r="O58">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P58">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="Q58">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="R58">
         <v>2.16</v>
       </c>
       <c r="S58">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="U58">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="V58">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
         <v>1.19</v>
       </c>
       <c r="Z58">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="AA58">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB58">
         <v>2.01</v>
       </c>
       <c r="AC58">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="AD58">
         <v>1.33</v>
       </c>
       <c r="AE58">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF58">
         <v>1.65</v>
       </c>
       <c r="AG58">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK58">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O59">
         <v>3.6</v>
       </c>
       <c r="P59">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q59">
+        <v>2.5</v>
+      </c>
+      <c r="R59">
+        <v>2.28</v>
+      </c>
+      <c r="S59">
+        <v>1.33</v>
+      </c>
+      <c r="T59">
+        <v>3</v>
+      </c>
+      <c r="U59">
         <v>2.55</v>
       </c>
-      <c r="R59">
-        <v>2.2</v>
-      </c>
-      <c r="S59">
-        <v>1.35</v>
-      </c>
-      <c r="T59">
-        <v>2.87</v>
-      </c>
-      <c r="U59">
-        <v>2.44</v>
-      </c>
       <c r="V59">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W59">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y59">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z59">
         <v>4</v>
       </c>
       <c r="AA59">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AB59">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC59">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD59">
         <v>1.39</v>
       </c>
       <c r="AE59">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF59">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG59">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK59">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q65">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="R65">
         <v>2.38</v>
@@ -10925,13 +10925,13 @@
         <v>3.75</v>
       </c>
       <c r="U65">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V65">
         <v>1.57</v>
       </c>
       <c r="W65">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
         <v>1</v>
@@ -10940,28 +10940,28 @@
         <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA65">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB65">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="AC65">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AD65">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE65">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF65">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG65">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
         <v>1.59</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.05</v>
+        <v>4.25</v>
       </c>
       <c r="AK66">
         <v>1.02</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P67">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="Q67">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="R67">
         <v>2.25</v>
       </c>
       <c r="S67">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T67">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="U67">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V67">
         <v>1.43</v>
       </c>
       <c r="W67">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
         <v>3.75</v>
       </c>
       <c r="AA67">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB67">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC67">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="AD67">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE67">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF67">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG67">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O68">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P68">
         <v>2.7</v>
@@ -11408,49 +11408,49 @@
         <v>2.23</v>
       </c>
       <c r="S68">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T68">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U68">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="V68">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>3.24</v>
+        <v>3.56</v>
       </c>
       <c r="AA68">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB68">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC68">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="AD68">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE68">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF68">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AG68">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11882,52 +11882,52 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="O71">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P71">
         <v>2.3</v>
       </c>
       <c r="Q71">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="R71">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S71">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U71">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V71">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W71">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y71">
         <v>1.15</v>
       </c>
       <c r="Z71">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA71">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB71">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC71">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AD71">
         <v>1.51</v>
@@ -11936,10 +11936,10 @@
         <v>1.15</v>
       </c>
       <c r="AF71">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG71">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK71">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,31 +12208,31 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O73">
         <v>3.6</v>
       </c>
       <c r="P73">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q73">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="R73">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S73">
         <v>1.3</v>
       </c>
       <c r="T73">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U73">
         <v>2.3</v>
       </c>
       <c r="V73">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W73">
         <v>1.12</v>
@@ -12241,31 +12241,31 @@
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z73">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA73">
         <v>1.65</v>
       </c>
       <c r="AB73">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC73">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AD73">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE73">
         <v>1.18</v>
       </c>
       <c r="AF73">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG73">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="AK73">
         <v>1.33</v>
@@ -12380,55 +12380,55 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="R74">
         <v>1.91</v>
       </c>
       <c r="S74">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="T74">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="U74">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="V74">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X74">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z74">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AA74">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AB74">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AC74">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="AD74">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE74">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF74">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG74">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK74">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="O75">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="P75">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12697,25 +12697,25 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="O76">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P76">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Q76">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R76">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S76">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T76">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U76">
         <v>2.1</v>
@@ -12730,16 +12730,16 @@
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z76">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA76">
         <v>1.5</v>
       </c>
       <c r="AB76">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC76">
         <v>2.23</v>
@@ -12751,7 +12751,7 @@
         <v>1.22</v>
       </c>
       <c r="AF76">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG76">
         <v>2.6</v>
@@ -12770,7 +12770,7 @@
         <v>1.35</v>
       </c>
       <c r="AK76">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,28 +12860,28 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="O77">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P77">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q77">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R77">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="S77">
         <v>1.16</v>
       </c>
       <c r="T77">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="U77">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V77">
         <v>1.85</v>
@@ -12893,16 +12893,16 @@
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z77">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AA77">
         <v>1.27</v>
       </c>
       <c r="AB77">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="AC77">
         <v>1.79</v>
@@ -12911,7 +12911,7 @@
         <v>1.99</v>
       </c>
       <c r="AE77">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF77">
         <v>1.35</v>
@@ -13195,19 +13195,19 @@
         <v>1.94</v>
       </c>
       <c r="Q79">
-        <v>3.47</v>
+        <v>3.9</v>
       </c>
       <c r="R79">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="S79">
         <v>1.25</v>
       </c>
       <c r="T79">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U79">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V79">
         <v>1.55</v>
@@ -13219,10 +13219,10 @@
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z79">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA79">
         <v>1.74</v>
@@ -13234,13 +13234,13 @@
         <v>2.52</v>
       </c>
       <c r="AD79">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AE79">
         <v>1.13</v>
       </c>
       <c r="AF79">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG79">
         <v>2.32</v>
@@ -13259,7 +13259,7 @@
         <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,49 +13349,49 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O80">
         <v>3.9</v>
       </c>
       <c r="P80">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q80">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R80">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="S80">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T80">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="U80">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V80">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W80">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X80">
         <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z80">
-        <v>5.64</v>
+        <v>5.6</v>
       </c>
       <c r="AA80">
         <v>1.38</v>
       </c>
       <c r="AB80">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AC80">
         <v>2.03</v>
@@ -13422,7 +13422,7 @@
         <v>1.17</v>
       </c>
       <c r="AK80">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13675,19 +13675,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="O82">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="P82">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="Q82">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R82">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="S82">
         <v>1.3</v>
@@ -13696,10 +13696,10 @@
         <v>3.38</v>
       </c>
       <c r="U82">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V82">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W82">
         <v>1.11</v>
@@ -13711,28 +13711,28 @@
         <v>1.16</v>
       </c>
       <c r="Z82">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA82">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AB82">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AC82">
         <v>2.44</v>
       </c>
       <c r="AD82">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AE82">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF82">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG82">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK82">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="O83">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q83">
         <v>2.91</v>
@@ -13856,31 +13856,31 @@
         <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U83">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V83">
         <v>1.4</v>
       </c>
       <c r="W83">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X83">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
         <v>1.29</v>
       </c>
       <c r="Z83">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AA83">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB83">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC83">
         <v>3.35</v>
@@ -13895,7 +13895,7 @@
         <v>1.7</v>
       </c>
       <c r="AG83">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK83">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="N84">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O84">
         <v>4.4</v>
@@ -14010,22 +14010,22 @@
         <v>1.53</v>
       </c>
       <c r="Q84">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="R84">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="S84">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T84">
         <v>4.2</v>
       </c>
       <c r="U84">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="V84">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W84">
         <v>1.17</v>
@@ -14034,31 +14034,31 @@
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z84">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA84">
         <v>1.4</v>
       </c>
       <c r="AB84">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AC84">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AD84">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE84">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF84">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG84">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK84">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O85">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Q85">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R85">
         <v>2.5</v>
@@ -14191,28 +14191,28 @@
         <v>1.77</v>
       </c>
       <c r="W85">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z85">
-        <v>6</v>
+        <v>6.39</v>
       </c>
       <c r="AA85">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AB85">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC85">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AD85">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE85">
         <v>1.26</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14828,16 +14828,16 @@
         <v>1.99</v>
       </c>
       <c r="R89">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="S89">
         <v>1.34</v>
       </c>
       <c r="T89">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="U89">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="V89">
         <v>1.4</v>
@@ -14846,19 +14846,19 @@
         <v>1.04</v>
       </c>
       <c r="X89">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z89">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="AA89">
         <v>1.87</v>
       </c>
       <c r="AB89">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC89">
         <v>3.11</v>
@@ -14873,7 +14873,7 @@
         <v>1.93</v>
       </c>
       <c r="AG89">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK89">
         <v>2.54</v>
@@ -14979,10 +14979,10 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="O90">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="P90">
         <v>3.66</v>
@@ -15018,10 +15018,10 @@
         <v>0</v>
       </c>
       <c r="AA90">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB90">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.26</v>
+        <v>2.35</v>
       </c>
       <c r="O91">
-        <v>5.4</v>
+        <v>3.35</v>
       </c>
       <c r="P91">
-        <v>8.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q91">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="R91">
-        <v>2.8</v>
+        <v>2.07</v>
       </c>
       <c r="S91">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T91">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="U91">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="V91">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="W91">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y91">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="Z91">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA91">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AB91">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="AC91">
-        <v>2.36</v>
+        <v>3.3</v>
       </c>
       <c r="AD91">
+        <v>1.28</v>
+      </c>
+      <c r="AE91">
+        <v>1.07</v>
+      </c>
+      <c r="AF91">
         <v>1.63</v>
       </c>
-      <c r="AE91">
-        <v>1.22</v>
-      </c>
-      <c r="AF91">
-        <v>1.8</v>
-      </c>
       <c r="AG91">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AK91">
-        <v>3.2</v>
+        <v>1.44</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.37</v>
+        <v>1.26</v>
       </c>
       <c r="O92">
-        <v>3.42</v>
+        <v>5.5</v>
       </c>
       <c r="P92">
-        <v>2.74</v>
+        <v>8.6</v>
       </c>
       <c r="Q92">
-        <v>2.74</v>
+        <v>1.67</v>
       </c>
       <c r="R92">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="S92">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="T92">
-        <v>3.05</v>
+        <v>3.68</v>
       </c>
       <c r="U92">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="V92">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="W92">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X92">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z92">
-        <v>3.25</v>
+        <v>5.09</v>
       </c>
       <c r="AA92">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AB92">
-        <v>1.95</v>
+        <v>2.52</v>
       </c>
       <c r="AC92">
-        <v>2.92</v>
+        <v>2.25</v>
       </c>
       <c r="AD92">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AE92">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AF92">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG92">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AK92">
-        <v>1.46</v>
+        <v>3.75</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="O93">
         <v>3.75</v>
       </c>
       <c r="P93">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q93">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R93">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S93">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T93">
         <v>3.8</v>
       </c>
       <c r="U93">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="V93">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W93">
         <v>1.14</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z93">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA93">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB93">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AC93">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AD93">
         <v>1.67</v>
       </c>
       <c r="AE93">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF93">
         <v>1.4</v>
       </c>
       <c r="AG93">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK93">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16283,61 +16283,61 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="O98">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="P98">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Q98">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R98">
-        <v>3.41</v>
+        <v>3</v>
       </c>
       <c r="S98">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T98">
         <v>4.6</v>
       </c>
       <c r="U98">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="V98">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W98">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X98">
         <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z98">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA98">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AB98">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="AC98">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AD98">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AE98">
         <v>1.35</v>
       </c>
       <c r="AF98">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG98">
         <v>1.73</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AK98">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O99">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="P99">
         <v>2.25</v>
@@ -16461,19 +16461,19 @@
         <v>2.13</v>
       </c>
       <c r="S99">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T99">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="U99">
         <v>2.62</v>
       </c>
       <c r="V99">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W99">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X99">
         <v>1.01</v>
@@ -16482,7 +16482,7 @@
         <v>1.25</v>
       </c>
       <c r="Z99">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="AA99">
         <v>1.89</v>
@@ -16491,16 +16491,16 @@
         <v>1.78</v>
       </c>
       <c r="AC99">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AD99">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE99">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF99">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG99">
         <v>1.99</v>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK99">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,19 +16609,19 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="O100">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="P100">
-        <v>2.95</v>
+        <v>2.67</v>
       </c>
       <c r="Q100">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="R100">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="S100">
         <v>1.25</v>
@@ -16630,10 +16630,10 @@
         <v>3.4</v>
       </c>
       <c r="U100">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="V100">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W100">
         <v>1.11</v>
@@ -16642,28 +16642,28 @@
         <v>1.04</v>
       </c>
       <c r="Y100">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z100">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="AA100">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB100">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC100">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="AD100">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AE100">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF100">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AG100">
         <v>2.4</v>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AK100">
         <v>1.57</v>
@@ -17107,55 +17107,55 @@
         <v>0</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -18583,13 +18583,13 @@
         <v>1.37</v>
       </c>
       <c r="T112">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U112">
         <v>2.6</v>
       </c>
       <c r="V112">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W112">
         <v>1.09</v>
@@ -18604,7 +18604,7 @@
         <v>3.3</v>
       </c>
       <c r="AA112">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AB112">
         <v>1.83</v>
@@ -18613,7 +18613,7 @@
         <v>3</v>
       </c>
       <c r="AD112">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE112">
         <v>1.07</v>
@@ -18622,7 +18622,7 @@
         <v>2.05</v>
       </c>
       <c r="AG112">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>1.29</v>
       </c>
       <c r="AK112">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -26591,10 +26591,10 @@
         <v>0</v>
       </c>
       <c r="AA161">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC161">
         <v>0</v>
@@ -29332,55 +29332,55 @@
         <v>0</v>
       </c>
       <c r="Q178">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R178">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S178">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T178">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U178">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V178">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W178">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y178">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z178">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC178">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD178">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE178">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF178">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG178">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK178">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q206">
         <v>3.26</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q214">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O3">
         <v>4</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G4">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="O4">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="P4">
-        <v>2.4</v>
+        <v>4.16</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O9">
         <v>3.6</v>
       </c>
       <c r="P9">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P19">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q19">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="R19">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="T19">
-        <v>2.73</v>
+        <v>2.34</v>
       </c>
       <c r="U19">
-        <v>2.88</v>
+        <v>3.48</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
+        <v>1.08</v>
+      </c>
+      <c r="Y19">
+        <v>1.45</v>
+      </c>
+      <c r="Z19">
+        <v>2.7</v>
+      </c>
+      <c r="AA19">
+        <v>2.45</v>
+      </c>
+      <c r="AB19">
+        <v>1.57</v>
+      </c>
+      <c r="AC19">
+        <v>4.96</v>
+      </c>
+      <c r="AD19">
+        <v>1.19</v>
+      </c>
+      <c r="AE19">
         <v>1.01</v>
       </c>
-      <c r="Y19">
-        <v>1.28</v>
-      </c>
-      <c r="Z19">
-        <v>3.12</v>
-      </c>
-      <c r="AA19">
-        <v>2</v>
-      </c>
-      <c r="AB19">
-        <v>1.78</v>
-      </c>
-      <c r="AC19">
-        <v>3.38</v>
-      </c>
-      <c r="AD19">
-        <v>1.24</v>
-      </c>
-      <c r="AE19">
-        <v>1.08</v>
-      </c>
       <c r="AF19">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AG19">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK19">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,40 +3569,40 @@
         </is>
       </c>
       <c r="N20">
-        <v>5.75</v>
+        <v>4.65</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="Q20">
-        <v>6</v>
+        <v>4.84</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U20">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z20">
         <v>3.24</v>
@@ -3611,22 +3611,22 @@
         <v>1.85</v>
       </c>
       <c r="AB20">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC20">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="AD20">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AG20">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="Q21">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="R21">
         <v>2</v>
@@ -3750,46 +3750,46 @@
         <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U21">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V21">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z21">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AA21">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AB21">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AC21">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="AD21">
         <v>1.2</v>
       </c>
       <c r="AE21">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG21">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK21">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,65 +3895,65 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.31</v>
+        <v>3.2</v>
       </c>
       <c r="O22">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="P22">
+        <v>2.05</v>
+      </c>
+      <c r="Q22">
+        <v>3.6</v>
+      </c>
+      <c r="R22">
+        <v>2.02</v>
+      </c>
+      <c r="S22">
+        <v>1.4</v>
+      </c>
+      <c r="T22">
+        <v>2.73</v>
+      </c>
+      <c r="U22">
+        <v>2.77</v>
+      </c>
+      <c r="V22">
+        <v>1.37</v>
+      </c>
+      <c r="W22">
+        <v>1.03</v>
+      </c>
+      <c r="X22">
+        <v>1.01</v>
+      </c>
+      <c r="Y22">
+        <v>1.29</v>
+      </c>
+      <c r="Z22">
+        <v>3.05</v>
+      </c>
+      <c r="AA22">
+        <v>2.03</v>
+      </c>
+      <c r="AB22">
+        <v>1.76</v>
+      </c>
+      <c r="AC22">
+        <v>3.6</v>
+      </c>
+      <c r="AD22">
+        <v>1.23</v>
+      </c>
+      <c r="AE22">
+        <v>1.08</v>
+      </c>
+      <c r="AF22">
+        <v>1.79</v>
+      </c>
+      <c r="AG22">
         <v>1.92</v>
       </c>
-      <c r="Q22">
-        <v>2.4</v>
-      </c>
-      <c r="R22">
-        <v>2</v>
-      </c>
-      <c r="S22">
-        <v>1.55</v>
-      </c>
-      <c r="T22">
-        <v>2.36</v>
-      </c>
-      <c r="U22">
-        <v>3.42</v>
-      </c>
-      <c r="V22">
-        <v>1.33</v>
-      </c>
-      <c r="W22">
-        <v>1.06</v>
-      </c>
-      <c r="X22">
-        <v>1.06</v>
-      </c>
-      <c r="Y22">
-        <v>1.42</v>
-      </c>
-      <c r="Z22">
-        <v>2.8</v>
-      </c>
-      <c r="AA22">
-        <v>2.29</v>
-      </c>
-      <c r="AB22">
-        <v>1.62</v>
-      </c>
-      <c r="AC22">
-        <v>4.55</v>
-      </c>
-      <c r="AD22">
-        <v>1.13</v>
-      </c>
-      <c r="AE22">
-        <v>1.01</v>
-      </c>
-      <c r="AF22">
-        <v>1.97</v>
-      </c>
-      <c r="AG22">
-        <v>1.65</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4064,7 +4064,7 @@
         <v>3.28</v>
       </c>
       <c r="P23">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="Q23">
         <v>2.55</v>
@@ -4079,10 +4079,10 @@
         <v>3.34</v>
       </c>
       <c r="U23">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W23">
         <v>1.1</v>
@@ -4091,7 +4091,7 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z23">
         <v>4.5</v>
@@ -4100,22 +4100,22 @@
         <v>1.57</v>
       </c>
       <c r="AB23">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AC23">
         <v>2.35</v>
       </c>
       <c r="AD23">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE23">
         <v>1.16</v>
       </c>
       <c r="AF23">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG23">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>3.45</v>
       </c>
       <c r="P24">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -4236,16 +4236,16 @@
         <v>2.05</v>
       </c>
       <c r="S24">
+        <v>1.36</v>
+      </c>
+      <c r="T24">
+        <v>2.84</v>
+      </c>
+      <c r="U24">
+        <v>2.8</v>
+      </c>
+      <c r="V24">
         <v>1.34</v>
-      </c>
-      <c r="T24">
-        <v>2.7</v>
-      </c>
-      <c r="U24">
-        <v>2.75</v>
-      </c>
-      <c r="V24">
-        <v>1.4</v>
       </c>
       <c r="W24">
         <v>1.07</v>
@@ -4257,28 +4257,28 @@
         <v>1.3</v>
       </c>
       <c r="Z24">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA24">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB24">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC24">
-        <v>3.57</v>
+        <v>3.35</v>
       </c>
       <c r="AD24">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE24">
         <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG24">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AK24">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="O30">
         <v>3.8</v>
       </c>
       <c r="P30">
-        <v>2.77</v>
+        <v>3.85</v>
       </c>
       <c r="Q30">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="R30">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T30">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U30">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="V30">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
+        <v>1.2</v>
+      </c>
+      <c r="Z30">
+        <v>4.5</v>
+      </c>
+      <c r="AA30">
+        <v>1.61</v>
+      </c>
+      <c r="AB30">
+        <v>2.23</v>
+      </c>
+      <c r="AC30">
+        <v>2.43</v>
+      </c>
+      <c r="AD30">
+        <v>1.48</v>
+      </c>
+      <c r="AE30">
         <v>1.14</v>
       </c>
-      <c r="Z30">
-        <v>5.07</v>
-      </c>
-      <c r="AA30">
-        <v>1.58</v>
-      </c>
-      <c r="AB30">
-        <v>2.42</v>
-      </c>
-      <c r="AC30">
-        <v>2.35</v>
-      </c>
-      <c r="AD30">
-        <v>1.57</v>
-      </c>
-      <c r="AE30">
-        <v>1.18</v>
-      </c>
       <c r="AF30">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG30">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="O31">
         <v>3.8</v>
       </c>
       <c r="P31">
-        <v>3.85</v>
+        <v>2.77</v>
       </c>
       <c r="Q31">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U31">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z31">
-        <v>4.5</v>
+        <v>5.07</v>
       </c>
       <c r="AA31">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AB31">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="AC31">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AD31">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF31">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG31">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O37">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="P37">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q37">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="R37">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="S37">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U37">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V37">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z37">
-        <v>5.5</v>
+        <v>5.06</v>
       </c>
       <c r="AA37">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB37">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="AC37">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AD37">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE37">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF37">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG37">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="O45">
         <v>5.65</v>
@@ -7656,52 +7656,52 @@
         <v>1.67</v>
       </c>
       <c r="R45">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="S45">
         <v>1.14</v>
       </c>
       <c r="T45">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="U45">
         <v>1.85</v>
       </c>
       <c r="V45">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="W45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z45">
         <v>6.25</v>
       </c>
       <c r="AA45">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB45">
         <v>2.99</v>
       </c>
       <c r="AC45">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AD45">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AE45">
         <v>1.36</v>
       </c>
       <c r="AF45">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG45">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.15</v>
       </c>
       <c r="AK45">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -10578,61 +10578,61 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="O63">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P63">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="Q63">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="R63">
         <v>2.05</v>
       </c>
       <c r="S63">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T63">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U63">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="V63">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W63">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X63">
         <v>1.08</v>
       </c>
       <c r="Y63">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z63">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="AA63">
         <v>2.25</v>
       </c>
       <c r="AB63">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC63">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AD63">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE63">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF63">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG63">
         <v>1.8</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK63">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.18</v>
+        <v>1.98</v>
       </c>
       <c r="AK64">
         <v>1.12</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AK69">
         <v>2.95</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK70">
         <v>2.33</v>
@@ -13512,10 +13512,10 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O81">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P81">
         <v>4.6</v>
@@ -13527,7 +13527,7 @@
         <v>2.41</v>
       </c>
       <c r="S81">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T81">
         <v>3.55</v>
@@ -13545,31 +13545,31 @@
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z81">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA81">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB81">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AC81">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD81">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE81">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF81">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG81">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -14659,10 +14659,10 @@
         <v>3.28</v>
       </c>
       <c r="P88">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q88">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="R88">
         <v>2.19</v>
@@ -14677,10 +14677,10 @@
         <v>2.8</v>
       </c>
       <c r="V88">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W88">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X88">
         <v>1.01</v>
@@ -14692,13 +14692,13 @@
         <v>3.18</v>
       </c>
       <c r="AA88">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB88">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC88">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="AD88">
         <v>1.25</v>
@@ -15655,10 +15655,10 @@
         <v>2.34</v>
       </c>
       <c r="V94">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W94">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X94">
         <v>1.04</v>
@@ -15670,22 +15670,22 @@
         <v>4.7</v>
       </c>
       <c r="AA94">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB94">
         <v>2.35</v>
       </c>
       <c r="AC94">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AD94">
         <v>1.55</v>
       </c>
       <c r="AE94">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF94">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG94">
         <v>2.23</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK94">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,80 +15794,80 @@
         </is>
       </c>
       <c r="N95">
+        <v>2.14</v>
+      </c>
+      <c r="O95">
+        <v>3.6</v>
+      </c>
+      <c r="P95">
         <v>2.85</v>
       </c>
-      <c r="O95">
-        <v>3.65</v>
-      </c>
-      <c r="P95">
-        <v>2.2</v>
-      </c>
       <c r="Q95">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R95">
-        <v>2.51</v>
+        <v>2.24</v>
       </c>
       <c r="S95">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T95">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U95">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="V95">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="W95">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X95">
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z95">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA95">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AB95">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AC95">
-        <v>2.31</v>
+        <v>2.67</v>
       </c>
       <c r="AD95">
+        <v>1.4</v>
+      </c>
+      <c r="AE95">
+        <v>1.13</v>
+      </c>
+      <c r="AF95">
+        <v>1.53</v>
+      </c>
+      <c r="AG95">
+        <v>2.3</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
+        <v>1.38</v>
+      </c>
+      <c r="AK95">
         <v>1.59</v>
-      </c>
-      <c r="AE95">
-        <v>1.2</v>
-      </c>
-      <c r="AF95">
-        <v>1.44</v>
-      </c>
-      <c r="AG95">
-        <v>2.5</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>1.26</v>
-      </c>
-      <c r="AK95">
-        <v>1.3</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="O96">
+        <v>3.5</v>
+      </c>
+      <c r="P96">
         <v>3.6</v>
       </c>
-      <c r="P96">
-        <v>2.94</v>
-      </c>
       <c r="Q96">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="R96">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S96">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U96">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V96">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W96">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X96">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z96">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA96">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB96">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="AC96">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="AD96">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE96">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF96">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG96">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK96">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="O97">
+        <v>3.65</v>
+      </c>
+      <c r="P97">
+        <v>2.1</v>
+      </c>
+      <c r="Q97">
+        <v>3.53</v>
+      </c>
+      <c r="R97">
+        <v>2.3</v>
+      </c>
+      <c r="S97">
+        <v>1.25</v>
+      </c>
+      <c r="T97">
         <v>3.5</v>
       </c>
-      <c r="P97">
-        <v>4.15</v>
-      </c>
-      <c r="Q97">
-        <v>2.25</v>
-      </c>
-      <c r="R97">
-        <v>2.38</v>
-      </c>
-      <c r="S97">
-        <v>1.27</v>
-      </c>
-      <c r="T97">
-        <v>3.4</v>
-      </c>
       <c r="U97">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V97">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="W97">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X97">
         <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z97">
-        <v>4.75</v>
+        <v>5.17</v>
       </c>
       <c r="AA97">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AB97">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AC97">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="AD97">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AE97">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF97">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG97">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK97">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16289,7 +16289,7 @@
         <v>7.7</v>
       </c>
       <c r="P98">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Q98">
         <v>1.5</v>
@@ -16307,7 +16307,7 @@
         <v>2.04</v>
       </c>
       <c r="V98">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W98">
         <v>1.22</v>
@@ -16322,25 +16322,25 @@
         <v>6.5</v>
       </c>
       <c r="AA98">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AB98">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="AC98">
+        <v>1.86</v>
+      </c>
+      <c r="AD98">
+        <v>1.81</v>
+      </c>
+      <c r="AE98">
+        <v>1.34</v>
+      </c>
+      <c r="AF98">
         <v>1.95</v>
       </c>
-      <c r="AD98">
-        <v>1.83</v>
-      </c>
-      <c r="AE98">
-        <v>1.35</v>
-      </c>
-      <c r="AF98">
-        <v>2.05</v>
-      </c>
       <c r="AG98">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK98">
         <v>4.8</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q126">
         <v>3.48</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q136">
         <v>3.14</v>
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -27560,7 +27560,7 @@
         <v>1.3</v>
       </c>
       <c r="X167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y167">
         <v>1.02</v>
@@ -29812,25 +29812,25 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="O181">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P181">
         <v>2.75</v>
       </c>
       <c r="Q181">
-        <v>3.42</v>
+        <v>3.07</v>
       </c>
       <c r="R181">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S181">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T181">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U181">
         <v>3.5</v>
@@ -29839,16 +29839,16 @@
         <v>1.29</v>
       </c>
       <c r="W181">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X181">
         <v>1.03</v>
       </c>
       <c r="Y181">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Z181">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="AA181">
         <v>2.25</v>
@@ -29857,19 +29857,19 @@
         <v>1.57</v>
       </c>
       <c r="AC181">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD181">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE181">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF181">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG181">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK181">
         <v>1.48</v>
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="O184">
         <v>3.05</v>
       </c>
       <c r="P184">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O185">
+        <v>2.62</v>
+      </c>
+      <c r="P185">
         <v>2.75</v>
       </c>
-      <c r="P185">
-        <v>2.6</v>
-      </c>
       <c r="Q185">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R185">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="S185">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="T185">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="U185">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="V185">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W185">
         <v>1.03</v>
       </c>
       <c r="X185">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y185">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z185">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA185">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AB185">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC185">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AD185">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE185">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF185">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG185">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK185">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.62</v>
+        <v>4.98</v>
       </c>
       <c r="O199">
         <v>4</v>
       </c>
       <c r="P199">
-        <v>5.05</v>
+        <v>1.6</v>
       </c>
       <c r="Q199">
-        <v>2.1</v>
+        <v>4.85</v>
       </c>
       <c r="R199">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S199">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T199">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="U199">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="V199">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="W199">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X199">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y199">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z199">
-        <v>3.78</v>
+        <v>4.3</v>
       </c>
       <c r="AA199">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB199">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC199">
-        <v>2.72</v>
+        <v>2.39</v>
       </c>
       <c r="AD199">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AE199">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF199">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG199">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK199">
-        <v>2.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>4.98</v>
+        <v>1.62</v>
       </c>
       <c r="O200">
         <v>4</v>
       </c>
       <c r="P200">
-        <v>1.6</v>
+        <v>5.05</v>
       </c>
       <c r="Q200">
-        <v>4.85</v>
+        <v>2.1</v>
       </c>
       <c r="R200">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S200">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T200">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="U200">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="V200">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W200">
+        <v>1.07</v>
+      </c>
+      <c r="X200">
+        <v>1.02</v>
+      </c>
+      <c r="Y200">
+        <v>1.22</v>
+      </c>
+      <c r="Z200">
+        <v>3.78</v>
+      </c>
+      <c r="AA200">
+        <v>1.75</v>
+      </c>
+      <c r="AB200">
+        <v>2.05</v>
+      </c>
+      <c r="AC200">
+        <v>2.72</v>
+      </c>
+      <c r="AD200">
+        <v>1.36</v>
+      </c>
+      <c r="AE200">
         <v>1.1</v>
       </c>
-      <c r="X200">
-        <v>1.04</v>
-      </c>
-      <c r="Y200">
-        <v>1.17</v>
-      </c>
-      <c r="Z200">
-        <v>4.3</v>
-      </c>
-      <c r="AA200">
-        <v>1.61</v>
-      </c>
-      <c r="AB200">
-        <v>2.25</v>
-      </c>
-      <c r="AC200">
-        <v>2.39</v>
-      </c>
-      <c r="AD200">
-        <v>1.49</v>
-      </c>
-      <c r="AE200">
-        <v>1.16</v>
-      </c>
       <c r="AF200">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG200">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK200">
-        <v>1.17</v>
+        <v>2.2</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="O201">
         <v>2.75</v>
@@ -33081,43 +33081,43 @@
         <v>4.28</v>
       </c>
       <c r="Q201">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="R201">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S201">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="T201">
         <v>2.25</v>
       </c>
       <c r="U201">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="V201">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W201">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X201">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y201">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z201">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA201">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AB201">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC201">
-        <v>6</v>
+        <v>5.35</v>
       </c>
       <c r="AD201">
         <v>1.11</v>
@@ -33126,10 +33126,10 @@
         <v>1.03</v>
       </c>
       <c r="AF201">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG201">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK201">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="O202">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P202">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33398,31 +33398,31 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O203">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="P203">
         <v>2.87</v>
       </c>
       <c r="Q203">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="R203">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="S203">
         <v>1.72</v>
       </c>
       <c r="T203">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U203">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="V203">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W203">
         <v>1.02</v>
@@ -33431,19 +33431,19 @@
         <v>1.12</v>
       </c>
       <c r="Y203">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="Z203">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AA203">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AB203">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AC203">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="AD203">
         <v>1.04</v>
@@ -33452,7 +33452,7 @@
         <v>1.02</v>
       </c>
       <c r="AF203">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AG203">
         <v>1.44</v>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK203">
         <v>1.44</v>
@@ -33570,52 +33570,52 @@
         <v>5.08</v>
       </c>
       <c r="Q204">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R204">
         <v>1.91</v>
       </c>
       <c r="S204">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T204">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="U204">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V204">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W204">
         <v>1.04</v>
       </c>
       <c r="X204">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y204">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Z204">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AA204">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AB204">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AC204">
         <v>5</v>
       </c>
       <c r="AD204">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE204">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF204">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="AG204">
         <v>1.62</v>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK204">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O205">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P205">
-        <v>4.06</v>
+        <v>3.6</v>
       </c>
       <c r="Q205">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R205">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="S205">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T205">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U205">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="V205">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W205">
         <v>1.03</v>
       </c>
       <c r="X205">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Y205">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Z205">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AA205">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB205">
         <v>1.3</v>
       </c>
       <c r="AC205">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AD205">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE205">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF205">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG205">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK205">
         <v>1.62</v>
@@ -36202,7 +36202,7 @@
         <v>1.11</v>
       </c>
       <c r="Y220">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="Z220">
         <v>2.44</v>
@@ -36220,7 +36220,7 @@
         <v>1.11</v>
       </c>
       <c r="AE220">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF220">
         <v>2.3</v>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK220">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -37177,7 +37177,7 @@
         <v>1.3</v>
       </c>
       <c r="X226">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y226">
         <v>1.02</v>
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q234">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
+        <v>4.65</v>
+      </c>
+      <c r="O19">
         <v>3.7</v>
       </c>
-      <c r="O19">
-        <v>3</v>
-      </c>
       <c r="P19">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="Q19">
-        <v>2.5</v>
+        <v>4.84</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="S19">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="U19">
-        <v>3.48</v>
+        <v>2.95</v>
       </c>
       <c r="V19">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W19">
+        <v>1.08</v>
+      </c>
+      <c r="X19">
         <v>1.05</v>
       </c>
-      <c r="X19">
-        <v>1.08</v>
-      </c>
       <c r="Y19">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="AA19">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AB19">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AC19">
-        <v>4.96</v>
+        <v>3.46</v>
       </c>
       <c r="AD19">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF19">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AG19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.85</v>
+        <v>1.12</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>4.65</v>
+        <v>3.2</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="P20">
-        <v>1.56</v>
+        <v>2.05</v>
       </c>
       <c r="Q20">
-        <v>4.84</v>
+        <v>3.6</v>
       </c>
       <c r="R20">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="U20">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="V20">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W20">
+        <v>1.03</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>1.29</v>
+      </c>
+      <c r="Z20">
+        <v>3.05</v>
+      </c>
+      <c r="AA20">
+        <v>2.03</v>
+      </c>
+      <c r="AB20">
+        <v>1.76</v>
+      </c>
+      <c r="AC20">
+        <v>3.6</v>
+      </c>
+      <c r="AD20">
+        <v>1.23</v>
+      </c>
+      <c r="AE20">
         <v>1.08</v>
       </c>
-      <c r="X20">
-        <v>1.05</v>
-      </c>
-      <c r="Y20">
-        <v>1.26</v>
-      </c>
-      <c r="Z20">
-        <v>3.24</v>
-      </c>
-      <c r="AA20">
-        <v>1.85</v>
-      </c>
-      <c r="AB20">
-        <v>1.86</v>
-      </c>
-      <c r="AC20">
-        <v>3.46</v>
-      </c>
-      <c r="AD20">
-        <v>1.28</v>
-      </c>
-      <c r="AE20">
-        <v>1.1</v>
-      </c>
       <c r="AF20">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AG20">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O22">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P22">
+        <v>1.93</v>
+      </c>
+      <c r="Q22">
+        <v>2.5</v>
+      </c>
+      <c r="R22">
+        <v>2</v>
+      </c>
+      <c r="S22">
+        <v>1.53</v>
+      </c>
+      <c r="T22">
+        <v>2.34</v>
+      </c>
+      <c r="U22">
+        <v>3.48</v>
+      </c>
+      <c r="V22">
+        <v>1.3</v>
+      </c>
+      <c r="W22">
+        <v>1.05</v>
+      </c>
+      <c r="X22">
+        <v>1.08</v>
+      </c>
+      <c r="Y22">
+        <v>1.45</v>
+      </c>
+      <c r="Z22">
+        <v>2.7</v>
+      </c>
+      <c r="AA22">
+        <v>2.45</v>
+      </c>
+      <c r="AB22">
+        <v>1.57</v>
+      </c>
+      <c r="AC22">
+        <v>4.96</v>
+      </c>
+      <c r="AD22">
+        <v>1.19</v>
+      </c>
+      <c r="AE22">
+        <v>1.01</v>
+      </c>
+      <c r="AF22">
         <v>2.05</v>
       </c>
-      <c r="Q22">
-        <v>3.6</v>
-      </c>
-      <c r="R22">
-        <v>2.02</v>
-      </c>
-      <c r="S22">
-        <v>1.4</v>
-      </c>
-      <c r="T22">
-        <v>2.73</v>
-      </c>
-      <c r="U22">
-        <v>2.77</v>
-      </c>
-      <c r="V22">
-        <v>1.37</v>
-      </c>
-      <c r="W22">
-        <v>1.03</v>
-      </c>
-      <c r="X22">
-        <v>1.01</v>
-      </c>
-      <c r="Y22">
-        <v>1.29</v>
-      </c>
-      <c r="Z22">
-        <v>3.05</v>
-      </c>
-      <c r="AA22">
-        <v>2.03</v>
-      </c>
-      <c r="AB22">
-        <v>1.76</v>
-      </c>
-      <c r="AC22">
-        <v>3.6</v>
-      </c>
-      <c r="AD22">
-        <v>1.23</v>
-      </c>
-      <c r="AE22">
-        <v>1.08</v>
-      </c>
-      <c r="AF22">
-        <v>1.79</v>
-      </c>
       <c r="AG22">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK22">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="O54">
         <v>3.35</v>
@@ -9120,22 +9120,22 @@
         <v>3.75</v>
       </c>
       <c r="Q54">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="R54">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S54">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T54">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U54">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="V54">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W54">
         <v>1.08</v>
@@ -9147,13 +9147,13 @@
         <v>1.25</v>
       </c>
       <c r="Z54">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AA54">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB54">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC54">
         <v>3.2</v>
@@ -9162,13 +9162,13 @@
         <v>1.26</v>
       </c>
       <c r="AE54">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF54">
         <v>1.78</v>
       </c>
       <c r="AG54">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -12380,16 +12380,16 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="R74">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S74">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T74">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="U74">
         <v>3.16</v>
@@ -12401,7 +12401,7 @@
         <v>1.02</v>
       </c>
       <c r="X74">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y74">
         <v>1.4</v>
@@ -12413,19 +12413,19 @@
         <v>2.27</v>
       </c>
       <c r="AB74">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC74">
-        <v>4.31</v>
+        <v>4</v>
       </c>
       <c r="AD74">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE74">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF74">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG74">
         <v>1.8</v>
@@ -12444,7 +12444,7 @@
         <v>1.35</v>
       </c>
       <c r="AK74">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="O91">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -15157,10 +15157,10 @@
         <v>2.07</v>
       </c>
       <c r="S91">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T91">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="U91">
         <v>2.88</v>
@@ -15178,19 +15178,19 @@
         <v>1.28</v>
       </c>
       <c r="Z91">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="AA91">
         <v>1.85</v>
       </c>
       <c r="AB91">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AC91">
         <v>3.3</v>
       </c>
       <c r="AD91">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE91">
         <v>1.07</v>
@@ -15353,10 +15353,10 @@
         <v>2.25</v>
       </c>
       <c r="AD92">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AE92">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF92">
         <v>1.77</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AK92">
         <v>3.75</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,34 +26226,34 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.27</v>
+        <v>2.81</v>
       </c>
       <c r="O159">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="P159">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="Q159">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="R159">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="S159">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T159">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U159">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V159">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W159">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X159">
         <v>1.02</v>
@@ -26262,28 +26262,28 @@
         <v>1.33</v>
       </c>
       <c r="Z159">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA159">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AB159">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC159">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AD159">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE159">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF159">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG159">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK159">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="O160">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P160">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="Q160">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R160">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S160">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T160">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U160">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V160">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W160">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X160">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y160">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z160">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA160">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AB160">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AC160">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD160">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE160">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF160">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG160">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK160">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="O161">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="P161">
-        <v>2.75</v>
+        <v>3.17</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S161">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T161">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U161">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V161">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W161">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X161">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y161">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z161">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA161">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AB161">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC161">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD161">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE161">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG161">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK161">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,64 +30301,64 @@
         </is>
       </c>
       <c r="N184">
-        <v>1.97</v>
+        <v>2.62</v>
       </c>
       <c r="O184">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="P184">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S184">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T184">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U184">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V184">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W184">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X184">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y184">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z184">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA184">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AB184">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC184">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD184">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE184">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF184">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG184">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK184">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.62</v>
+        <v>1.97</v>
       </c>
       <c r="O185">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="P185">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="Q185">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R185">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S185">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="T185">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U185">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V185">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W185">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X185">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y185">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z185">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA185">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AB185">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC185">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD185">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE185">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF185">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG185">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK185">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30630,22 +30630,22 @@
         <v>2.45</v>
       </c>
       <c r="O186">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P186">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="Q186">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="R186">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S186">
         <v>1.35</v>
       </c>
       <c r="T186">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U186">
         <v>2.55</v>
@@ -30654,37 +30654,37 @@
         <v>1.43</v>
       </c>
       <c r="W186">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X186">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y186">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z186">
-        <v>4.04</v>
+        <v>3.55</v>
       </c>
       <c r="AA186">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB186">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AC186">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AD186">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE186">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF186">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG186">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AK186">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -36993,55 +36993,55 @@
         <v>0</v>
       </c>
       <c r="Q225">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="R225">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S225">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T225">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U225">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V225">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W225">
         <v>1.07</v>
       </c>
       <c r="X225">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y225">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z225">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="AA225">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AB225">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC225">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="AD225">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE225">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF225">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG225">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AK225">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="AL225">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -23455,34 +23455,34 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q142">
         <v>3.17</v>
       </c>
       <c r="R142">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="S142">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T142">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="U142">
         <v>3.14</v>
       </c>
       <c r="V142">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W142">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X142">
         <v>1.03</v>
@@ -25097,13 +25097,13 @@
         <v>1.91</v>
       </c>
       <c r="R152">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S152">
         <v>1.25</v>
       </c>
       <c r="T152">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U152">
         <v>2.31</v>
@@ -25118,13 +25118,13 @@
         <v>0</v>
       </c>
       <c r="Y152">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z152">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA152">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AB152">
         <v>2.26</v>
@@ -25133,16 +25133,16 @@
         <v>2.57</v>
       </c>
       <c r="AD152">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE152">
         <v>1.13</v>
       </c>
       <c r="AF152">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AG152">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK152">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.46</v>
+        <v>2.35</v>
       </c>
       <c r="O163">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="P163">
-        <v>5.75</v>
+        <v>3.25</v>
       </c>
       <c r="Q163">
-        <v>1.99</v>
+        <v>2.8</v>
       </c>
       <c r="R163">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="S163">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T163">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="U163">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="V163">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="W163">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X163">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y163">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="Z163">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="AA163">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="AB163">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AC163">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD163">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE163">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF163">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG163">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AK163">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,80 +27041,80 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.35</v>
+        <v>1.46</v>
       </c>
       <c r="O164">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="P164">
+        <v>5.75</v>
+      </c>
+      <c r="Q164">
+        <v>1.99</v>
+      </c>
+      <c r="R164">
+        <v>2.38</v>
+      </c>
+      <c r="S164">
+        <v>1.3</v>
+      </c>
+      <c r="T164">
         <v>3.25</v>
       </c>
-      <c r="Q164">
-        <v>2.8</v>
-      </c>
-      <c r="R164">
-        <v>1.89</v>
-      </c>
-      <c r="S164">
-        <v>1.44</v>
-      </c>
-      <c r="T164">
+      <c r="U164">
+        <v>2.45</v>
+      </c>
+      <c r="V164">
+        <v>1.48</v>
+      </c>
+      <c r="W164">
+        <v>1.08</v>
+      </c>
+      <c r="X164">
+        <v>1.04</v>
+      </c>
+      <c r="Y164">
+        <v>1.2</v>
+      </c>
+      <c r="Z164">
+        <v>3.9</v>
+      </c>
+      <c r="AA164">
+        <v>1.77</v>
+      </c>
+      <c r="AB164">
+        <v>2.15</v>
+      </c>
+      <c r="AC164">
+        <v>2.9</v>
+      </c>
+      <c r="AD164">
+        <v>1.4</v>
+      </c>
+      <c r="AE164">
+        <v>1.13</v>
+      </c>
+      <c r="AF164">
+        <v>1.83</v>
+      </c>
+      <c r="AG164">
+        <v>1.87</v>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ164">
+        <v>1.12</v>
+      </c>
+      <c r="AK164">
         <v>2.5</v>
-      </c>
-      <c r="U164">
-        <v>2.88</v>
-      </c>
-      <c r="V164">
-        <v>1.29</v>
-      </c>
-      <c r="W164">
-        <v>1.05</v>
-      </c>
-      <c r="X164">
-        <v>1.03</v>
-      </c>
-      <c r="Y164">
-        <v>1.39</v>
-      </c>
-      <c r="Z164">
-        <v>2.92</v>
-      </c>
-      <c r="AA164">
-        <v>2.13</v>
-      </c>
-      <c r="AB164">
-        <v>1.67</v>
-      </c>
-      <c r="AC164">
-        <v>4.2</v>
-      </c>
-      <c r="AD164">
-        <v>1.18</v>
-      </c>
-      <c r="AE164">
-        <v>1.03</v>
-      </c>
-      <c r="AF164">
-        <v>2</v>
-      </c>
-      <c r="AG164">
-        <v>1.73</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ164">
-        <v>1.29</v>
-      </c>
-      <c r="AK164">
-        <v>1.61</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -30310,16 +30310,16 @@
         <v>2.75</v>
       </c>
       <c r="Q184">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="R184">
         <v>1.81</v>
       </c>
       <c r="S184">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="T184">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="U184">
         <v>4</v>
@@ -30358,7 +30358,7 @@
         <v>2.3</v>
       </c>
       <c r="AG184">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK184">
         <v>1.44</v>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O201">
         <v>2.75</v>
@@ -33087,13 +33087,13 @@
         <v>2</v>
       </c>
       <c r="S201">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="T201">
         <v>2.25</v>
       </c>
       <c r="U201">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="V201">
         <v>1.19</v>
@@ -33102,31 +33102,31 @@
         <v>1.04</v>
       </c>
       <c r="X201">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y201">
         <v>1.6</v>
       </c>
       <c r="Z201">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AA201">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="AB201">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC201">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="AD201">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE201">
         <v>1.03</v>
       </c>
       <c r="AF201">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG201">
         <v>1.61</v>
@@ -33410,43 +33410,43 @@
         <v>3.52</v>
       </c>
       <c r="R203">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="S203">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="T203">
         <v>2.05</v>
       </c>
       <c r="U203">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="V203">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="W203">
         <v>1.02</v>
       </c>
       <c r="X203">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Y203">
         <v>1.75</v>
       </c>
       <c r="Z203">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AA203">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AB203">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AC203">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="AD203">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE203">
         <v>1.02</v>
@@ -33573,52 +33573,52 @@
         <v>2.4</v>
       </c>
       <c r="R204">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="S204">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T204">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="U204">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V204">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="W204">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X204">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y204">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Z204">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AA204">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AB204">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AC204">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="AD204">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE204">
         <v>1.03</v>
       </c>
       <c r="AF204">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AG204">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK204">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33730,7 +33730,7 @@
         <v>2.7</v>
       </c>
       <c r="P205">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q205">
         <v>2.95</v>
@@ -33739,13 +33739,13 @@
         <v>1.92</v>
       </c>
       <c r="S205">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="T205">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U205">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="V205">
         <v>1.16</v>
@@ -33754,10 +33754,10 @@
         <v>1.03</v>
       </c>
       <c r="X205">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y205">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Z205">
         <v>2.06</v>
@@ -33769,19 +33769,19 @@
         <v>1.3</v>
       </c>
       <c r="AC205">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AD205">
         <v>1.06</v>
       </c>
       <c r="AE205">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF205">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AG205">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK205">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -35843,34 +35843,34 @@
         </is>
       </c>
       <c r="N218">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="O218">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="P218">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Q218">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="R218">
         <v>2.2</v>
       </c>
       <c r="S218">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T218">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="U218">
         <v>2.77</v>
       </c>
       <c r="V218">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W218">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X218">
         <v>1</v>
@@ -35882,25 +35882,25 @@
         <v>3.6</v>
       </c>
       <c r="AA218">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB218">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC218">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AD218">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AE218">
         <v>1.06</v>
       </c>
       <c r="AF218">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG218">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>1.91</v>
       </c>
       <c r="AK218">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36181,13 +36181,13 @@
         <v>2.5</v>
       </c>
       <c r="R220">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="S220">
         <v>1.53</v>
       </c>
       <c r="T220">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U220">
         <v>3.5</v>
@@ -36199,7 +36199,7 @@
         <v>1.04</v>
       </c>
       <c r="X220">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y220">
         <v>1.49</v>
@@ -36226,7 +36226,7 @@
         <v>2.3</v>
       </c>
       <c r="AG220">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK220">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36658,28 +36658,28 @@
         </is>
       </c>
       <c r="N223">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O223">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q223">
         <v>3.3</v>
       </c>
       <c r="R223">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="S223">
         <v>1.48</v>
       </c>
       <c r="T223">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="U223">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="V223">
         <v>1.28</v>
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O224">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q224">
         <v>6.07</v>
@@ -36894,7 +36894,7 @@
         <v>1.21</v>
       </c>
       <c r="AK224">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -37802,61 +37802,61 @@
         <v>2.46</v>
       </c>
       <c r="O230">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="P230">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q230">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R230">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S230">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T230">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U230">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="V230">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W230">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X230">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y230">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z230">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA230">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AB230">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC230">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="AD230">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE230">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF230">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG230">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK230">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38134,55 +38134,55 @@
         <v>8.050000000000001</v>
       </c>
       <c r="Q232">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R232">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S232">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T232">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U232">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V232">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W232">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X232">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y232">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z232">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA232">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB232">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC232">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD232">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE232">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF232">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG232">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK232">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="O238">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P238">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39927,16 +39927,16 @@
         <v>0</v>
       </c>
       <c r="Q243">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="R243">
         <v>2.25</v>
       </c>
       <c r="S243">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T243">
-        <v>2.39</v>
+        <v>3.08</v>
       </c>
       <c r="U243">
         <v>2.58</v>
@@ -39945,7 +39945,7 @@
         <v>1.45</v>
       </c>
       <c r="W243">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X243">
         <v>1.04</v>
@@ -39963,7 +39963,7 @@
         <v>1.98</v>
       </c>
       <c r="AC243">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AD243">
         <v>1.29</v>
@@ -39972,7 +39972,7 @@
         <v>1.09</v>
       </c>
       <c r="AF243">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG243">
         <v>2.08</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="O9">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Q9">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="R9">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="U9">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="V9">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="W9">
         <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="AA9">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AB9">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AC9">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="AD9">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AG9">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>2.55</v>
+        <v>1.97</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>2.22</v>
+        <v>1.87</v>
       </c>
       <c r="R10">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="S10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U10">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="W10">
         <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB10">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AC10">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="AD10">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>3.1</v>
       </c>
       <c r="P21">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q21">
         <v>3.6</v>
@@ -3762,7 +3762,7 @@
         <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
         <v>1.29</v>
@@ -3780,7 +3780,7 @@
         <v>3.6</v>
       </c>
       <c r="AD21">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE21">
         <v>1.08</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="O22">
         <v>3.1</v>
@@ -3940,13 +3940,13 @@
         <v>1.7</v>
       </c>
       <c r="AC22">
-        <v>3.62</v>
+        <v>3.79</v>
       </c>
       <c r="AD22">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AE22">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
         <v>1.8</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="O30">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P30">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q30">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="R30">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="S30">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="T30">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U30">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="V30">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
         <v>1.12</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
+        <v>1.2</v>
+      </c>
+      <c r="Z30">
+        <v>4.25</v>
+      </c>
+      <c r="AA30">
+        <v>1.56</v>
+      </c>
+      <c r="AB30">
+        <v>2.23</v>
+      </c>
+      <c r="AC30">
+        <v>2.56</v>
+      </c>
+      <c r="AD30">
+        <v>1.48</v>
+      </c>
+      <c r="AE30">
         <v>1.14</v>
       </c>
-      <c r="Z30">
-        <v>5.07</v>
-      </c>
-      <c r="AA30">
-        <v>1.58</v>
-      </c>
-      <c r="AB30">
-        <v>2.42</v>
-      </c>
-      <c r="AC30">
-        <v>2.35</v>
-      </c>
-      <c r="AD30">
-        <v>1.58</v>
-      </c>
-      <c r="AE30">
-        <v>1.21</v>
-      </c>
       <c r="AF30">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG30">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="O31">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q31">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="R31">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="S31">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="T31">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W31">
         <v>1.12</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z31">
-        <v>4.25</v>
+        <v>5.07</v>
       </c>
       <c r="AA31">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AB31">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="AC31">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AD31">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF31">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG31">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O108">
+        <v>4.25</v>
+      </c>
+      <c r="P108">
+        <v>4.6</v>
+      </c>
+      <c r="Q108">
+        <v>1.92</v>
+      </c>
+      <c r="R108">
+        <v>2.77</v>
+      </c>
+      <c r="S108">
+        <v>1.2</v>
+      </c>
+      <c r="T108">
         <v>4</v>
       </c>
-      <c r="P108">
-        <v>2.25</v>
-      </c>
-      <c r="Q108">
-        <v>2.9</v>
-      </c>
-      <c r="R108">
-        <v>2.56</v>
-      </c>
-      <c r="S108">
-        <v>1.14</v>
-      </c>
-      <c r="T108">
-        <v>5.25</v>
-      </c>
       <c r="U108">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="V108">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="W108">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X108">
         <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Z108">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA108">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AB108">
-        <v>3.58</v>
+        <v>2.9</v>
       </c>
       <c r="AC108">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="AD108">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AE108">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="AF108">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="AG108">
-        <v>3.74</v>
+        <v>2.47</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK108">
-        <v>1.45</v>
+        <v>2.46</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="O109">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P109">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="Q109">
-        <v>3.88</v>
+        <v>2.9</v>
       </c>
       <c r="R109">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="S109">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T109">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="U109">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="V109">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="W109">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z109">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="AA109">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AB109">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="AC109">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AD109">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AE109">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AF109">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AG109">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK109">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
+        <v>3.7</v>
+      </c>
+      <c r="O110">
+        <v>4.6</v>
+      </c>
+      <c r="P110">
+        <v>1.7</v>
+      </c>
+      <c r="Q110">
+        <v>3.88</v>
+      </c>
+      <c r="R110">
+        <v>2.76</v>
+      </c>
+      <c r="S110">
+        <v>1.13</v>
+      </c>
+      <c r="T110">
+        <v>5.05</v>
+      </c>
+      <c r="U110">
+        <v>1.81</v>
+      </c>
+      <c r="V110">
+        <v>1.99</v>
+      </c>
+      <c r="W110">
+        <v>1.28</v>
+      </c>
+      <c r="X110">
+        <v>0</v>
+      </c>
+      <c r="Y110">
+        <v>1.01</v>
+      </c>
+      <c r="Z110">
+        <v>8.4</v>
+      </c>
+      <c r="AA110">
+        <v>1.19</v>
+      </c>
+      <c r="AB110">
+        <v>3.76</v>
+      </c>
+      <c r="AC110">
+        <v>1.62</v>
+      </c>
+      <c r="AD110">
+        <v>2.24</v>
+      </c>
+      <c r="AE110">
         <v>1.5</v>
       </c>
-      <c r="O110">
-        <v>4.25</v>
-      </c>
-      <c r="P110">
-        <v>4.6</v>
-      </c>
-      <c r="Q110">
-        <v>1.92</v>
-      </c>
-      <c r="R110">
-        <v>2.77</v>
-      </c>
-      <c r="S110">
-        <v>1.2</v>
-      </c>
-      <c r="T110">
-        <v>4</v>
-      </c>
-      <c r="U110">
-        <v>2</v>
-      </c>
-      <c r="V110">
-        <v>1.73</v>
-      </c>
-      <c r="W110">
-        <v>1.2</v>
-      </c>
-      <c r="X110">
-        <v>1.01</v>
-      </c>
-      <c r="Y110">
-        <v>1.08</v>
-      </c>
-      <c r="Z110">
-        <v>6.5</v>
-      </c>
-      <c r="AA110">
-        <v>1.36</v>
-      </c>
-      <c r="AB110">
-        <v>2.9</v>
-      </c>
-      <c r="AC110">
-        <v>2.01</v>
-      </c>
-      <c r="AD110">
-        <v>1.78</v>
-      </c>
-      <c r="AE110">
-        <v>1.3</v>
-      </c>
       <c r="AF110">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AG110">
-        <v>2.47</v>
+        <v>3.42</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.16</v>
       </c>
       <c r="AK110">
-        <v>2.46</v>
+        <v>1.23</v>
       </c>
       <c r="AL110">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -9763,40 +9763,40 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="O58">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P58">
-        <v>3.31</v>
+        <v>3.8</v>
       </c>
       <c r="Q58">
         <v>2.5</v>
       </c>
       <c r="R58">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S58">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T58">
         <v>3.1</v>
       </c>
       <c r="U58">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="V58">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W58">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z58">
         <v>3.82</v>
@@ -9811,10 +9811,10 @@
         <v>2.81</v>
       </c>
       <c r="AD58">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE58">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF58">
         <v>1.65</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.83</v>
+        <v>2.81</v>
       </c>
       <c r="O95">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P95">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q95">
-        <v>2.33</v>
+        <v>3.53</v>
       </c>
       <c r="R95">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S95">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T95">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U95">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V95">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W95">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X95">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z95">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AA95">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AB95">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AC95">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AD95">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AE95">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF95">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG95">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.21</v>
+        <v>1.69</v>
       </c>
       <c r="AK95">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.81</v>
+        <v>1.83</v>
       </c>
       <c r="O96">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P96">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q96">
-        <v>3.53</v>
+        <v>2.33</v>
       </c>
       <c r="R96">
+        <v>2.38</v>
+      </c>
+      <c r="S96">
+        <v>1.25</v>
+      </c>
+      <c r="T96">
+        <v>3.4</v>
+      </c>
+      <c r="U96">
+        <v>2.25</v>
+      </c>
+      <c r="V96">
+        <v>1.57</v>
+      </c>
+      <c r="W96">
+        <v>1.11</v>
+      </c>
+      <c r="X96">
+        <v>1.04</v>
+      </c>
+      <c r="Y96">
+        <v>1.14</v>
+      </c>
+      <c r="Z96">
+        <v>4.4</v>
+      </c>
+      <c r="AA96">
+        <v>1.64</v>
+      </c>
+      <c r="AB96">
+        <v>2.29</v>
+      </c>
+      <c r="AC96">
         <v>2.45</v>
       </c>
-      <c r="S96">
-        <v>1.24</v>
-      </c>
-      <c r="T96">
-        <v>4</v>
-      </c>
-      <c r="U96">
-        <v>2.15</v>
-      </c>
-      <c r="V96">
-        <v>1.61</v>
-      </c>
-      <c r="W96">
-        <v>1.13</v>
-      </c>
-      <c r="X96">
-        <v>1.02</v>
-      </c>
-      <c r="Y96">
-        <v>1.17</v>
-      </c>
-      <c r="Z96">
-        <v>4.7</v>
-      </c>
-      <c r="AA96">
+      <c r="AD96">
         <v>1.53</v>
       </c>
-      <c r="AB96">
-        <v>2.45</v>
-      </c>
-      <c r="AC96">
-        <v>2.23</v>
-      </c>
-      <c r="AD96">
-        <v>1.61</v>
-      </c>
       <c r="AE96">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF96">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG96">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.69</v>
+        <v>1.21</v>
       </c>
       <c r="AK96">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -20856,55 +20856,55 @@
         <v>0</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="O140">
-        <v>3.5</v>
+        <v>3.09</v>
       </c>
       <c r="P140">
-        <v>3.44</v>
+        <v>3.23</v>
       </c>
       <c r="Q140">
-        <v>2.57</v>
+        <v>2.83</v>
       </c>
       <c r="R140">
         <v>2.1</v>
       </c>
       <c r="S140">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T140">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="U140">
+        <v>3</v>
+      </c>
+      <c r="V140">
+        <v>1.33</v>
+      </c>
+      <c r="W140">
+        <v>1.07</v>
+      </c>
+      <c r="X140">
+        <v>1.02</v>
+      </c>
+      <c r="Y140">
+        <v>1.32</v>
+      </c>
+      <c r="Z140">
         <v>2.88</v>
       </c>
-      <c r="V140">
-        <v>1.36</v>
-      </c>
-      <c r="W140">
-        <v>1.08</v>
-      </c>
-      <c r="X140">
-        <v>1</v>
-      </c>
-      <c r="Y140">
-        <v>1.26</v>
-      </c>
-      <c r="Z140">
-        <v>3.2</v>
-      </c>
       <c r="AA140">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AB140">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AC140">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="AD140">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE140">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF140">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AG140">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK140">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23301,34 +23301,34 @@
         <v>2.7</v>
       </c>
       <c r="Q141">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="R141">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S141">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T141">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="U141">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="V141">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W141">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X141">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y141">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z141">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA141">
         <v>2.17</v>
@@ -23346,10 +23346,10 @@
         <v>1.02</v>
       </c>
       <c r="AF141">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG141">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK141">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -25085,25 +25085,25 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="O152">
         <v>3.95</v>
       </c>
       <c r="P152">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q152">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="R152">
         <v>2.3</v>
       </c>
       <c r="S152">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T152">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U152">
         <v>2.38</v>
@@ -25112,31 +25112,31 @@
         <v>1.48</v>
       </c>
       <c r="W152">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X152">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y152">
         <v>1.17</v>
       </c>
       <c r="Z152">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA152">
         <v>1.63</v>
       </c>
       <c r="AB152">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC152">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD152">
         <v>1.45</v>
       </c>
       <c r="AE152">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF152">
         <v>1.62</v>
@@ -28354,10 +28354,10 @@
         <v>1.2</v>
       </c>
       <c r="Q172">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="R172">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="S172">
         <v>1.23</v>
@@ -28366,7 +28366,7 @@
         <v>4</v>
       </c>
       <c r="U172">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V172">
         <v>1.59</v>
@@ -28378,16 +28378,16 @@
         <v>1</v>
       </c>
       <c r="Y172">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z172">
         <v>4.8</v>
       </c>
       <c r="AA172">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB172">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC172">
         <v>2.27</v>
@@ -28396,13 +28396,13 @@
         <v>1.6</v>
       </c>
       <c r="AE172">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF172">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AG172">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK172">
         <v>1.03</v>
@@ -31306,7 +31306,7 @@
         <v>1.5</v>
       </c>
       <c r="W190">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X190">
         <v>1.03</v>
@@ -31315,16 +31315,16 @@
         <v>1.18</v>
       </c>
       <c r="Z190">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA190">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB190">
         <v>2.15</v>
       </c>
       <c r="AC190">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="AD190">
         <v>1.44</v>
@@ -31349,7 +31349,7 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK190">
         <v>2.43</v>
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="O212">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P212">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q212">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R212">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S212">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T212">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U212">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V212">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W212">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X212">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y212">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z212">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA212">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB212">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC212">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD212">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE212">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF212">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG212">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK212">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O213">
         <v>3</v>
       </c>
       <c r="P213">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q213">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R213">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S213">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T213">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U213">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V213">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W213">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X213">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y213">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z213">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA213">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB213">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC213">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD213">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE213">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG213">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK213">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -36507,13 +36507,13 @@
         <v>3.3</v>
       </c>
       <c r="R222">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S222">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T222">
-        <v>2.63</v>
+        <v>2.34</v>
       </c>
       <c r="U222">
         <v>3.14</v>
@@ -36522,25 +36522,25 @@
         <v>1.28</v>
       </c>
       <c r="W222">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X222">
         <v>1.04</v>
       </c>
       <c r="Y222">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z222">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA222">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AB222">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC222">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AD222">
         <v>1.18</v>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK222">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AL222">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="O3">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P3">
-        <v>3.21</v>
+        <v>4</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB3">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O4">
-        <v>3.92</v>
+        <v>3.77</v>
       </c>
       <c r="P4">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB4">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="O5">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="P5">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
+        <v>2.56</v>
+      </c>
+      <c r="Q6">
+        <v>3</v>
+      </c>
+      <c r="R6">
         <v>2.2</v>
-      </c>
-      <c r="Q6">
-        <v>3.3</v>
-      </c>
-      <c r="R6">
-        <v>2.25</v>
       </c>
       <c r="S6">
         <v>1.3</v>
@@ -1308,43 +1308,43 @@
         <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA6">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AB6">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AC6">
         <v>2.6</v>
       </c>
       <c r="AD6">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AG6">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="Q7">
-        <v>2.7</v>
+        <v>3.36</v>
       </c>
       <c r="R7">
         <v>2.25</v>
@@ -1471,10 +1471,10 @@
         <v>3.2</v>
       </c>
       <c r="U7">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="V7">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W7">
         <v>1.1</v>
@@ -1486,28 +1486,28 @@
         <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA7">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB7">
         <v>2.21</v>
       </c>
       <c r="AC7">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="AD7">
         <v>1.45</v>
       </c>
       <c r="AE7">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG7">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AK7">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P8">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q8">
-        <v>2.91</v>
+        <v>4.32</v>
       </c>
       <c r="R8">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="S8">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T8">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U8">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z8">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AA8">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB8">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC8">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD8">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AG8">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.21</v>
+        <v>2.1</v>
       </c>
       <c r="AK8">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9">
@@ -1779,61 +1779,61 @@
         <v>1.53</v>
       </c>
       <c r="O9">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P9">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="Q9">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="U9">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V9">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA9">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AB9">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AC9">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AD9">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>4.95</v>
       </c>
       <c r="P10">
-        <v>4.33</v>
+        <v>7.9</v>
       </c>
       <c r="Q10">
-        <v>2.22</v>
+        <v>1.7</v>
       </c>
       <c r="R10">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="S10">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T10">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="U10">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB10">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="AC10">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AD10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AK10">
-        <v>1.97</v>
+        <v>3.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3406,37 +3406,37 @@
         </is>
       </c>
       <c r="N19">
-        <v>5.85</v>
+        <v>4.7</v>
       </c>
       <c r="O19">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P19">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q19">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
         <v>2.85</v>
       </c>
       <c r="U19">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="V19">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
         <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y19">
         <v>1.24</v>
@@ -3445,25 +3445,25 @@
         <v>3.38</v>
       </c>
       <c r="AA19">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB19">
         <v>1.92</v>
       </c>
       <c r="AC19">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AD19">
         <v>1.29</v>
       </c>
       <c r="AE19">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG19">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O20">
         <v>3</v>
@@ -3584,28 +3584,28 @@
         <v>1.95</v>
       </c>
       <c r="S20">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T20">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U20">
         <v>3.48</v>
       </c>
       <c r="V20">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W20">
         <v>1.01</v>
       </c>
       <c r="X20">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Z20">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AA20">
         <v>2.45</v>
@@ -3614,19 +3614,19 @@
         <v>1.53</v>
       </c>
       <c r="AC20">
-        <v>4.96</v>
+        <v>4.45</v>
       </c>
       <c r="AD20">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE20">
         <v>1.01</v>
       </c>
       <c r="AF20">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG20">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK20">
         <v>1.85</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="P21">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="Q21">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R21">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S21">
         <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U21">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="V21">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
+        <v>1.32</v>
+      </c>
+      <c r="Z21">
+        <v>3.1</v>
+      </c>
+      <c r="AA21">
+        <v>2.11</v>
+      </c>
+      <c r="AB21">
+        <v>1.73</v>
+      </c>
+      <c r="AC21">
+        <v>3.62</v>
+      </c>
+      <c r="AD21">
+        <v>1.26</v>
+      </c>
+      <c r="AE21">
+        <v>1.03</v>
+      </c>
+      <c r="AF21">
+        <v>1.8</v>
+      </c>
+      <c r="AG21">
+        <v>1.88</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.29</v>
       </c>
-      <c r="Z21">
-        <v>3.05</v>
-      </c>
-      <c r="AA21">
-        <v>2.09</v>
-      </c>
-      <c r="AB21">
-        <v>1.76</v>
-      </c>
-      <c r="AC21">
-        <v>3.6</v>
-      </c>
-      <c r="AD21">
-        <v>1.27</v>
-      </c>
-      <c r="AE21">
-        <v>1.08</v>
-      </c>
-      <c r="AF21">
-        <v>1.79</v>
-      </c>
-      <c r="AG21">
-        <v>1.92</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.63</v>
-      </c>
       <c r="AK21">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
+        <v>3.03</v>
+      </c>
+      <c r="O22">
+        <v>3.18</v>
+      </c>
+      <c r="P22">
+        <v>2.08</v>
+      </c>
+      <c r="Q22">
+        <v>3.6</v>
+      </c>
+      <c r="R22">
+        <v>2.02</v>
+      </c>
+      <c r="S22">
+        <v>1.4</v>
+      </c>
+      <c r="T22">
         <v>2.75</v>
       </c>
-      <c r="O22">
-        <v>3.1</v>
-      </c>
-      <c r="P22">
-        <v>2.26</v>
-      </c>
-      <c r="Q22">
-        <v>3.26</v>
-      </c>
-      <c r="R22">
-        <v>2</v>
-      </c>
-      <c r="S22">
-        <v>1.42</v>
-      </c>
-      <c r="T22">
-        <v>2.79</v>
-      </c>
       <c r="U22">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V22">
+        <v>1.38</v>
+      </c>
+      <c r="W22">
+        <v>1.03</v>
+      </c>
+      <c r="X22">
+        <v>1.06</v>
+      </c>
+      <c r="Y22">
         <v>1.33</v>
       </c>
-      <c r="W22">
-        <v>1.05</v>
-      </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>1.35</v>
-      </c>
       <c r="Z22">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="AA22">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AB22">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC22">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="AD22">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE22">
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG22">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AK22">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -6192,22 +6192,22 @@
         <v>2.23</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U36">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V36">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36">
         <v>1.21</v>
@@ -6222,13 +6222,13 @@
         <v>1.92</v>
       </c>
       <c r="AC36">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AD36">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
         <v>1.57</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="O37">
         <v>4.2</v>
       </c>
       <c r="P37">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q37">
-        <v>4.5</v>
+        <v>4.88</v>
       </c>
       <c r="R37">
         <v>2.45</v>
@@ -6367,7 +6367,7 @@
         <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6376,16 +6376,16 @@
         <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA37">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB37">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AC37">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AD37">
         <v>1.58</v>
@@ -6394,10 +6394,10 @@
         <v>1.2</v>
       </c>
       <c r="AF37">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG37">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>2.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK37">
         <v>1.17</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="O45">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="P45">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q45">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R45">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="S45">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T45">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U45">
         <v>1.85</v>
       </c>
       <c r="V45">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="W45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z45">
         <v>5.6</v>
       </c>
       <c r="AA45">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB45">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AC45">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AD45">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AE45">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF45">
         <v>1.53</v>
       </c>
       <c r="AG45">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.15</v>
       </c>
       <c r="AK45">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -9274,43 +9274,43 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="O55">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="P55">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q55">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="R55">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="S55">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T55">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U55">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V55">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W55">
         <v>1.08</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z55">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="AA55">
         <v>1.78</v>
@@ -9322,7 +9322,7 @@
         <v>2.91</v>
       </c>
       <c r="AD55">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE55">
         <v>1.13</v>
@@ -9331,7 +9331,7 @@
         <v>1.62</v>
       </c>
       <c r="AG55">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9449,22 +9449,22 @@
         <v>2.95</v>
       </c>
       <c r="R56">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U56">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V56">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
         <v>0</v>
@@ -9482,13 +9482,13 @@
         <v>2.08</v>
       </c>
       <c r="AC56">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AD56">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF56">
         <v>1.5</v>
@@ -9510,7 +9510,7 @@
         <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="O63">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P63">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="Q63">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S63">
         <v>1.46</v>
@@ -10599,13 +10599,13 @@
         <v>2.65</v>
       </c>
       <c r="U63">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V63">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W63">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
         <v>1.08</v>
@@ -10623,19 +10623,19 @@
         <v>1.62</v>
       </c>
       <c r="AC63">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD63">
         <v>1.2</v>
       </c>
       <c r="AE63">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF63">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG63">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK63">
         <v>1.65</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q69">
         <v>1.65</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK70">
         <v>2.33</v>
@@ -13349,10 +13349,10 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="O80">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P80">
         <v>5.06</v>
@@ -13364,7 +13364,7 @@
         <v>2.41</v>
       </c>
       <c r="S80">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T80">
         <v>3.55</v>
@@ -13373,7 +13373,7 @@
         <v>2.15</v>
       </c>
       <c r="V80">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W80">
         <v>1.12</v>
@@ -13382,31 +13382,31 @@
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z80">
         <v>5.09</v>
       </c>
       <c r="AA80">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AB80">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AC80">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AD80">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE80">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF80">
         <v>1.55</v>
       </c>
       <c r="AG80">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="O87">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P87">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -14511,16 +14511,16 @@
         <v>2.73</v>
       </c>
       <c r="U87">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="V87">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W87">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X87">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
         <v>1.27</v>
@@ -14538,16 +14538,16 @@
         <v>3.47</v>
       </c>
       <c r="AD87">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE87">
         <v>1.05</v>
       </c>
       <c r="AF87">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG87">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="O92">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="P92">
-        <v>3.15</v>
+        <v>2.66</v>
       </c>
       <c r="Q92">
         <v>2.6</v>
@@ -15320,49 +15320,49 @@
         <v>2.5</v>
       </c>
       <c r="S92">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T92">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U92">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="V92">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W92">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X92">
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z92">
         <v>5</v>
       </c>
       <c r="AA92">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB92">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AC92">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD92">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE92">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF92">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG92">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK92">
         <v>1.74</v>
@@ -15480,7 +15480,7 @@
         <v>2</v>
       </c>
       <c r="R93">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S93">
         <v>1.22</v>
@@ -15492,7 +15492,7 @@
         <v>2.34</v>
       </c>
       <c r="V93">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W93">
         <v>1.1</v>
@@ -15501,13 +15501,13 @@
         <v>1.04</v>
       </c>
       <c r="Y93">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z93">
         <v>4.7</v>
       </c>
       <c r="AA93">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB93">
         <v>2.35</v>
@@ -15522,7 +15522,7 @@
         <v>1.18</v>
       </c>
       <c r="AF93">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG93">
         <v>2.23</v>
@@ -15541,7 +15541,7 @@
         <v>1.19</v>
       </c>
       <c r="AK93">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="O94">
         <v>3.65</v>
       </c>
       <c r="P94">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="Q94">
         <v>2.9</v>
       </c>
       <c r="R94">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S94">
         <v>1.29</v>
       </c>
       <c r="T94">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="U94">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="V94">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W94">
         <v>1.11</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z94">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA94">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB94">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="AC94">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="AD94">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE94">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF94">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG94">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,28 +15794,28 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="O95">
         <v>3.65</v>
       </c>
       <c r="P95">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q95">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="R95">
         <v>2.45</v>
       </c>
       <c r="S95">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T95">
         <v>4</v>
       </c>
       <c r="U95">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V95">
         <v>1.61</v>
@@ -15827,16 +15827,16 @@
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z95">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA95">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB95">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AC95">
         <v>2.23</v>
@@ -15845,13 +15845,13 @@
         <v>1.61</v>
       </c>
       <c r="AE95">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF95">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG95">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15960,13 +15960,13 @@
         <v>1.83</v>
       </c>
       <c r="O96">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P96">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="Q96">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="R96">
         <v>2.38</v>
@@ -15978,7 +15978,7 @@
         <v>3.4</v>
       </c>
       <c r="U96">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V96">
         <v>1.57</v>
@@ -15993,7 +15993,7 @@
         <v>1.14</v>
       </c>
       <c r="Z96">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA96">
         <v>1.64</v>
@@ -16014,7 +16014,7 @@
         <v>1.55</v>
       </c>
       <c r="AG96">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>1.8</v>
       </c>
       <c r="AD97">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AE97">
         <v>1.37</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O109">
+        <v>4.6</v>
+      </c>
+      <c r="P109">
+        <v>1.66</v>
+      </c>
+      <c r="Q109">
         <v>3.5</v>
       </c>
-      <c r="P109">
-        <v>2.5</v>
-      </c>
-      <c r="Q109">
-        <v>2.8</v>
-      </c>
       <c r="R109">
-        <v>2.31</v>
+        <v>2.76</v>
       </c>
       <c r="S109">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T109">
-        <v>3.7</v>
+        <v>5.05</v>
       </c>
       <c r="U109">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="V109">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="W109">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y109">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z109">
-        <v>5.01</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA109">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="AB109">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AC109">
-        <v>2.31</v>
+        <v>1.74</v>
       </c>
       <c r="AD109">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AE109">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="AF109">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AG109">
-        <v>2.55</v>
+        <v>3.48</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK109">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O110">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P110">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="Q110">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R110">
-        <v>2.76</v>
+        <v>2.31</v>
       </c>
       <c r="S110">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="T110">
-        <v>5.05</v>
+        <v>3.7</v>
       </c>
       <c r="U110">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="V110">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="W110">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="X110">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z110">
-        <v>8.300000000000001</v>
+        <v>5.01</v>
       </c>
       <c r="AA110">
+        <v>1.49</v>
+      </c>
+      <c r="AB110">
+        <v>2.3</v>
+      </c>
+      <c r="AC110">
+        <v>2.31</v>
+      </c>
+      <c r="AD110">
+        <v>1.58</v>
+      </c>
+      <c r="AE110">
         <v>1.19</v>
       </c>
-      <c r="AB110">
-        <v>3.2</v>
-      </c>
-      <c r="AC110">
-        <v>1.74</v>
-      </c>
-      <c r="AD110">
-        <v>1.94</v>
-      </c>
-      <c r="AE110">
-        <v>1.56</v>
-      </c>
       <c r="AF110">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AG110">
-        <v>3.48</v>
+        <v>2.55</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK110">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -28674,7 +28674,7 @@
         <v>1.66</v>
       </c>
       <c r="O174">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="P174">
         <v>4.2</v>
@@ -28683,37 +28683,37 @@
         <v>2.05</v>
       </c>
       <c r="R174">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S174">
         <v>1.3</v>
       </c>
       <c r="T174">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U174">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="V174">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W174">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X174">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y174">
         <v>1.15</v>
       </c>
       <c r="Z174">
-        <v>4.2</v>
+        <v>4.47</v>
       </c>
       <c r="AA174">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AB174">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AC174">
         <v>2.65</v>
@@ -28725,7 +28725,7 @@
         <v>1.18</v>
       </c>
       <c r="AF174">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG174">
         <v>2.1</v>
@@ -29685,7 +29685,7 @@
         <v>1.45</v>
       </c>
       <c r="Z180">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="AA180">
         <v>2.25</v>
@@ -29719,7 +29719,7 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AK180">
         <v>1.48</v>
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O215">
-        <v>4.88</v>
+        <v>4.84</v>
       </c>
       <c r="P215">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="Q215">
         <v>1.85</v>
@@ -35375,19 +35375,19 @@
         <v>3.6</v>
       </c>
       <c r="U215">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="V215">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W215">
         <v>1.08</v>
       </c>
       <c r="X215">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y215">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z215">
         <v>4.35</v>
@@ -35399,13 +35399,13 @@
         <v>2.1</v>
       </c>
       <c r="AC215">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD215">
         <v>1.41</v>
       </c>
       <c r="AE215">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF215">
         <v>1.77</v>
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O216">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P216">
-        <v>4.48</v>
+        <v>4.33</v>
       </c>
       <c r="Q216">
         <v>2.46</v>
@@ -35532,7 +35532,7 @@
         <v>2</v>
       </c>
       <c r="S216">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T216">
         <v>2.69</v>
@@ -35550,19 +35550,19 @@
         <v>1.05</v>
       </c>
       <c r="Y216">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z216">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AA216">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AB216">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC216">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AD216">
         <v>1.24</v>
@@ -35571,10 +35571,10 @@
         <v>1.02</v>
       </c>
       <c r="AF216">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG216">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK216">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35680,28 +35680,28 @@
         </is>
       </c>
       <c r="N217">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="O217">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="P217">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q217">
-        <v>3.93</v>
+        <v>4.5</v>
       </c>
       <c r="R217">
         <v>2.2</v>
       </c>
       <c r="S217">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T217">
         <v>3.03</v>
       </c>
       <c r="U217">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V217">
         <v>1.4</v>
@@ -35728,16 +35728,16 @@
         <v>3.19</v>
       </c>
       <c r="AD217">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE217">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF217">
         <v>1.73</v>
       </c>
       <c r="AG217">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="O235">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="P235">
-        <v>6.2</v>
+        <v>6.07</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -38777,7 +38777,7 @@
         </is>
       </c>
       <c r="N236">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O236">
         <v>3.4</v>
@@ -38795,43 +38795,43 @@
         <v>1.36</v>
       </c>
       <c r="T236">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U236">
         <v>2.88</v>
       </c>
       <c r="V236">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W236">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X236">
         <v>1.06</v>
       </c>
       <c r="Y236">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z236">
         <v>3.25</v>
       </c>
       <c r="AA236">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB236">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC236">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD236">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE236">
         <v>1.1</v>
       </c>
       <c r="AF236">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG236">
         <v>1.95</v>
@@ -38850,7 +38850,7 @@
         <v>1.3</v>
       </c>
       <c r="AK236">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38943,7 +38943,7 @@
         <v>1.48</v>
       </c>
       <c r="O237">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P237">
         <v>5.85</v>
@@ -38961,7 +38961,7 @@
         <v>3.25</v>
       </c>
       <c r="U237">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V237">
         <v>1.5</v>
@@ -38976,28 +38976,28 @@
         <v>1.18</v>
       </c>
       <c r="Z237">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AA237">
         <v>1.75</v>
       </c>
       <c r="AB237">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC237">
         <v>2.84</v>
       </c>
       <c r="AD237">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE237">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF237">
         <v>1.81</v>
       </c>
       <c r="AG237">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>3.6</v>
       </c>
       <c r="P241">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="Q241">
         <v>2.4</v>
@@ -39607,13 +39607,13 @@
         <v>2.16</v>
       </c>
       <c r="S241">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T241">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U241">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V241">
         <v>1.44</v>
@@ -39625,22 +39625,22 @@
         <v>1</v>
       </c>
       <c r="Y241">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z241">
-        <v>3.44</v>
+        <v>3.65</v>
       </c>
       <c r="AA241">
         <v>1.83</v>
       </c>
       <c r="AB241">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC241">
         <v>2.89</v>
       </c>
       <c r="AD241">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE241">
         <v>1.12</v>
@@ -39665,7 +39665,7 @@
         <v>1.22</v>
       </c>
       <c r="AK241">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -40081,31 +40081,31 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="O244">
         <v>3.7</v>
       </c>
       <c r="P244">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="Q244">
         <v>2.4</v>
       </c>
       <c r="R244">
+        <v>2.49</v>
+      </c>
+      <c r="S244">
+        <v>1.27</v>
+      </c>
+      <c r="T244">
+        <v>3.4</v>
+      </c>
+      <c r="U244">
         <v>2.3</v>
       </c>
-      <c r="S244">
-        <v>1.26</v>
-      </c>
-      <c r="T244">
-        <v>3.34</v>
-      </c>
-      <c r="U244">
-        <v>2.34</v>
-      </c>
       <c r="V244">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W244">
         <v>1.15</v>
@@ -40114,25 +40114,25 @@
         <v>1.03</v>
       </c>
       <c r="Y244">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z244">
         <v>4.75</v>
       </c>
       <c r="AA244">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB244">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AC244">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AD244">
         <v>1.54</v>
       </c>
       <c r="AE244">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF244">
         <v>1.5</v>
@@ -40244,7 +40244,7 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="O245">
         <v>3.8</v>
@@ -40253,10 +40253,10 @@
         <v>4.8</v>
       </c>
       <c r="Q245">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R245">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S245">
         <v>1.3</v>
@@ -40265,10 +40265,10 @@
         <v>3.2</v>
       </c>
       <c r="U245">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="V245">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W245">
         <v>1.11</v>
@@ -40280,25 +40280,25 @@
         <v>1.22</v>
       </c>
       <c r="Z245">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA245">
         <v>1.7</v>
       </c>
       <c r="AB245">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AC245">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD245">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE245">
         <v>1.12</v>
       </c>
       <c r="AF245">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG245">
         <v>1.84</v>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK245">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AL245">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.72</v>
+        <v>3.03</v>
       </c>
       <c r="O21">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P21">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="Q21">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R21">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S21">
         <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U21">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="V21">
+        <v>1.38</v>
+      </c>
+      <c r="W21">
+        <v>1.03</v>
+      </c>
+      <c r="X21">
+        <v>1.06</v>
+      </c>
+      <c r="Y21">
         <v>1.33</v>
       </c>
-      <c r="W21">
-        <v>1.07</v>
-      </c>
-      <c r="X21">
-        <v>1.02</v>
-      </c>
-      <c r="Y21">
-        <v>1.32</v>
-      </c>
       <c r="Z21">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="AA21">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AB21">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC21">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AD21">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG21">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AK21">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.03</v>
+        <v>2.72</v>
       </c>
       <c r="O22">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P22">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="Q22">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R22">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S22">
         <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U22">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="V22">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
+        <v>1.07</v>
+      </c>
+      <c r="X22">
+        <v>1.02</v>
+      </c>
+      <c r="Y22">
+        <v>1.32</v>
+      </c>
+      <c r="Z22">
+        <v>3.1</v>
+      </c>
+      <c r="AA22">
+        <v>2.11</v>
+      </c>
+      <c r="AB22">
+        <v>1.73</v>
+      </c>
+      <c r="AC22">
+        <v>3.62</v>
+      </c>
+      <c r="AD22">
+        <v>1.26</v>
+      </c>
+      <c r="AE22">
         <v>1.03</v>
       </c>
-      <c r="X22">
-        <v>1.06</v>
-      </c>
-      <c r="Y22">
-        <v>1.33</v>
-      </c>
-      <c r="Z22">
-        <v>3.32</v>
-      </c>
-      <c r="AA22">
-        <v>2.09</v>
-      </c>
-      <c r="AB22">
-        <v>1.76</v>
-      </c>
-      <c r="AC22">
-        <v>3.6</v>
-      </c>
-      <c r="AD22">
-        <v>1.25</v>
-      </c>
-      <c r="AE22">
-        <v>1.05</v>
-      </c>
       <c r="AF22">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG22">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O109">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P109">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="Q109">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R109">
-        <v>2.76</v>
+        <v>2.31</v>
       </c>
       <c r="S109">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="T109">
-        <v>5.05</v>
+        <v>3.7</v>
       </c>
       <c r="U109">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="V109">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="W109">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="X109">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z109">
-        <v>8.300000000000001</v>
+        <v>5.01</v>
       </c>
       <c r="AA109">
+        <v>1.49</v>
+      </c>
+      <c r="AB109">
+        <v>2.3</v>
+      </c>
+      <c r="AC109">
+        <v>2.31</v>
+      </c>
+      <c r="AD109">
+        <v>1.58</v>
+      </c>
+      <c r="AE109">
         <v>1.19</v>
       </c>
-      <c r="AB109">
-        <v>3.2</v>
-      </c>
-      <c r="AC109">
-        <v>1.74</v>
-      </c>
-      <c r="AD109">
-        <v>1.94</v>
-      </c>
-      <c r="AE109">
-        <v>1.56</v>
-      </c>
       <c r="AF109">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AG109">
-        <v>3.48</v>
+        <v>2.55</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK109">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O110">
+        <v>4.6</v>
+      </c>
+      <c r="P110">
+        <v>1.66</v>
+      </c>
+      <c r="Q110">
         <v>3.5</v>
       </c>
-      <c r="P110">
-        <v>2.5</v>
-      </c>
-      <c r="Q110">
-        <v>2.8</v>
-      </c>
       <c r="R110">
-        <v>2.31</v>
+        <v>2.76</v>
       </c>
       <c r="S110">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T110">
-        <v>3.7</v>
+        <v>5.05</v>
       </c>
       <c r="U110">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="V110">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="W110">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z110">
-        <v>5.01</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA110">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="AB110">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AC110">
-        <v>2.31</v>
+        <v>1.74</v>
       </c>
       <c r="AD110">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AE110">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="AF110">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AG110">
-        <v>2.55</v>
+        <v>3.48</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK110">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -40256,7 +40256,7 @@
         <v>2.05</v>
       </c>
       <c r="R245">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S245">
         <v>1.3</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -2117,19 +2117,19 @@
         <v>2.3</v>
       </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
         <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V11">
         <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2144,10 +2144,10 @@
         <v>1.56</v>
       </c>
       <c r="AB11">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AD11">
         <v>1.49</v>
@@ -2156,10 +2156,10 @@
         <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
         <v>1.8</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.9</v>
+        <v>3.43</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P38">
         <v>1.91</v>
@@ -6527,7 +6527,7 @@
         <v>2.89</v>
       </c>
       <c r="V38">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W38">
         <v>1.05</v>
@@ -6560,7 +6560,7 @@
         <v>1.78</v>
       </c>
       <c r="AG38">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
         <v>1.28</v>
@@ -9600,37 +9600,37 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="O57">
+        <v>3.4</v>
+      </c>
+      <c r="P57">
+        <v>2.28</v>
+      </c>
+      <c r="Q57">
         <v>3.23</v>
       </c>
-      <c r="P57">
-        <v>2.21</v>
-      </c>
-      <c r="Q57">
-        <v>3.82</v>
-      </c>
       <c r="R57">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T57">
         <v>2.79</v>
       </c>
       <c r="U57">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="V57">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W57">
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y57">
         <v>1.32</v>
@@ -9651,13 +9651,13 @@
         <v>1.25</v>
       </c>
       <c r="AE57">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG57">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AK57">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>3.4</v>
       </c>
       <c r="P58">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q58">
         <v>2.5</v>
@@ -9784,10 +9784,10 @@
         <v>3.1</v>
       </c>
       <c r="U58">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V58">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W58">
         <v>1.05</v>
@@ -9796,7 +9796,7 @@
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z58">
         <v>3.82</v>
@@ -9808,10 +9808,10 @@
         <v>2.01</v>
       </c>
       <c r="AC58">
-        <v>2.81</v>
+        <v>3.03</v>
       </c>
       <c r="AD58">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE58">
         <v>1.12</v>
@@ -9836,7 +9836,7 @@
         <v>1.24</v>
       </c>
       <c r="AK58">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9929,34 +9929,34 @@
         <v>1.98</v>
       </c>
       <c r="O59">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="P59">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q59">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="R59">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S59">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T59">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="U59">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V59">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W59">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X59">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
         <v>1.25</v>
@@ -9968,7 +9968,7 @@
         <v>1.75</v>
       </c>
       <c r="AB59">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC59">
         <v>2.88</v>
@@ -9977,13 +9977,13 @@
         <v>1.39</v>
       </c>
       <c r="AE59">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF59">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG59">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK59">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -11882,28 +11882,28 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O71">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P71">
         <v>2.3</v>
       </c>
       <c r="Q71">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="R71">
         <v>2.28</v>
       </c>
       <c r="S71">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T71">
         <v>3.6</v>
       </c>
       <c r="U71">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="V71">
         <v>1.54</v>
@@ -11915,31 +11915,31 @@
         <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z71">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA71">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB71">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="AC71">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AD71">
         <v>1.46</v>
       </c>
       <c r="AE71">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF71">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG71">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK71">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O81">
         <v>5</v>
       </c>
       <c r="P81">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="Q81">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="R81">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="S81">
         <v>1.3</v>
@@ -13533,34 +13533,34 @@
         <v>3.38</v>
       </c>
       <c r="U81">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V81">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W81">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AA81">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB81">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AC81">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="AD81">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE81">
         <v>1.19</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK81">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13678,16 +13678,16 @@
         <v>2.25</v>
       </c>
       <c r="O82">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q82">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="R82">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S82">
         <v>1.41</v>
@@ -13696,7 +13696,7 @@
         <v>2.9</v>
       </c>
       <c r="U82">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="V82">
         <v>1.39</v>
@@ -13705,13 +13705,13 @@
         <v>1.03</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z82">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA82">
         <v>1.95</v>
@@ -13720,19 +13720,19 @@
         <v>1.83</v>
       </c>
       <c r="AC82">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AD82">
         <v>1.3</v>
       </c>
       <c r="AE82">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF82">
         <v>1.74</v>
       </c>
       <c r="AG82">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.36</v>
       </c>
       <c r="AK82">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -16286,10 +16286,10 @@
         <v>2.9</v>
       </c>
       <c r="O98">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P98">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q98">
         <v>3.35</v>
@@ -16298,7 +16298,7 @@
         <v>2.13</v>
       </c>
       <c r="S98">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T98">
         <v>2.94</v>
@@ -16310,16 +16310,16 @@
         <v>1.39</v>
       </c>
       <c r="W98">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X98">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
         <v>1.29</v>
       </c>
       <c r="Z98">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AA98">
         <v>1.89</v>
@@ -16328,7 +16328,7 @@
         <v>1.78</v>
       </c>
       <c r="AC98">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD98">
         <v>1.26</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK98">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16452,13 +16452,13 @@
         <v>3.6</v>
       </c>
       <c r="P99">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="Q99">
-        <v>2.55</v>
+        <v>2.77</v>
       </c>
       <c r="R99">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S99">
         <v>1.25</v>
@@ -16467,7 +16467,7 @@
         <v>3.4</v>
       </c>
       <c r="U99">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="V99">
         <v>1.53</v>
@@ -16482,16 +16482,16 @@
         <v>1.14</v>
       </c>
       <c r="Z99">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA99">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AB99">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AC99">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AD99">
         <v>1.45</v>
@@ -16503,7 +16503,7 @@
         <v>1.46</v>
       </c>
       <c r="AG99">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK99">
         <v>1.64</v>
@@ -16935,61 +16935,61 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O102">
         <v>3.5</v>
       </c>
       <c r="P102">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q102">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="R102">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S102">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T102">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U102">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="V102">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W102">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z102">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AA102">
         <v>1.62</v>
       </c>
       <c r="AB102">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AC102">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AD102">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE102">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF102">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG102">
         <v>2.34</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK102">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -20032,28 +20032,28 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="O121">
         <v>3.1</v>
       </c>
       <c r="P121">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="Q121">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="R121">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S121">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T121">
         <v>2.75</v>
       </c>
       <c r="U121">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="V121">
         <v>1.28</v>
@@ -20065,22 +20065,22 @@
         <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z121">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AA121">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB121">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC121">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD121">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE121">
         <v>1.02</v>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK121">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20204,22 +20204,22 @@
         <v>3.3</v>
       </c>
       <c r="Q122">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="R122">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S122">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T122">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U122">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V122">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W122">
         <v>1.1</v>
@@ -20231,28 +20231,28 @@
         <v>1.22</v>
       </c>
       <c r="Z122">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AA122">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB122">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC122">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD122">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE122">
         <v>1.1</v>
       </c>
       <c r="AF122">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG122">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK122">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,16 +20358,16 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="O123">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P123">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="Q123">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R123">
         <v>2</v>
@@ -20376,7 +20376,7 @@
         <v>1.4</v>
       </c>
       <c r="T123">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U123">
         <v>2.97</v>
@@ -20394,10 +20394,10 @@
         <v>1.31</v>
       </c>
       <c r="Z123">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AA123">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB123">
         <v>1.67</v>
@@ -20431,7 +20431,7 @@
         <v>1.26</v>
       </c>
       <c r="AK123">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,10 +20521,10 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="O124">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P124">
         <v>3.2</v>
@@ -20539,46 +20539,46 @@
         <v>1.29</v>
       </c>
       <c r="T124">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U124">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="V124">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W124">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X124">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z124">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AA124">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AB124">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AC124">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AD124">
         <v>1.47</v>
       </c>
       <c r="AE124">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF124">
         <v>1.54</v>
       </c>
       <c r="AG124">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK124">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20856,55 +20856,55 @@
         <v>0</v>
       </c>
       <c r="Q126">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R126">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="S126">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T126">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U126">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V126">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W126">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X126">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z126">
-        <v>2.97</v>
+        <v>3.11</v>
       </c>
       <c r="AA126">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB126">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC126">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD126">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE126">
         <v>1.05</v>
       </c>
       <c r="AF126">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG126">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK126">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -22492,22 +22492,22 @@
         <v>2.2</v>
       </c>
       <c r="S136">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T136">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U136">
         <v>2.66</v>
       </c>
       <c r="V136">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W136">
         <v>1.08</v>
       </c>
       <c r="X136">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y136">
         <v>1.27</v>
@@ -22522,16 +22522,16 @@
         <v>1.91</v>
       </c>
       <c r="AC136">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AD136">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE136">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF136">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG136">
         <v>1.96</v>
@@ -22550,7 +22550,7 @@
         <v>1.2</v>
       </c>
       <c r="AK136">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -23129,34 +23129,34 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="O140">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="P140">
-        <v>3.23</v>
+        <v>3.44</v>
       </c>
       <c r="Q140">
-        <v>2.83</v>
+        <v>2.96</v>
       </c>
       <c r="R140">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S140">
         <v>1.44</v>
       </c>
       <c r="T140">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="U140">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V140">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W140">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X140">
         <v>1.02</v>
@@ -23168,25 +23168,25 @@
         <v>2.88</v>
       </c>
       <c r="AA140">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AB140">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC140">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AD140">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE140">
         <v>1.03</v>
       </c>
       <c r="AF140">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG140">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>1.31</v>
       </c>
       <c r="AK140">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23292,31 +23292,31 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O141">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P141">
         <v>2.7</v>
       </c>
       <c r="Q141">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R141">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S141">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T141">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="U141">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="V141">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W141">
         <v>1.01</v>
@@ -23325,31 +23325,31 @@
         <v>1.04</v>
       </c>
       <c r="Y141">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z141">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AA141">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AB141">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC141">
-        <v>3.88</v>
+        <v>4.35</v>
       </c>
       <c r="AD141">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE141">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF141">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG141">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK141">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S142">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T142">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U142">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V142">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W142">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X142">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y142">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z142">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA142">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB142">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD142">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE142">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF142">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG142">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK142">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="O143">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P143">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S143">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T143">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U143">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V143">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W143">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X143">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y143">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z143">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA143">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE143">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF143">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG143">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK143">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -24970,7 +24970,7 @@
         <v>2.54</v>
       </c>
       <c r="AD151">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE151">
         <v>1.13</v>
@@ -25085,19 +25085,19 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="O152">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="P152">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="Q152">
         <v>2</v>
       </c>
       <c r="R152">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S152">
         <v>1.29</v>
@@ -25109,40 +25109,40 @@
         <v>2.38</v>
       </c>
       <c r="V152">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W152">
         <v>1.09</v>
       </c>
       <c r="X152">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y152">
         <v>1.17</v>
       </c>
       <c r="Z152">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA152">
         <v>1.63</v>
       </c>
       <c r="AB152">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC152">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD152">
         <v>1.45</v>
       </c>
       <c r="AE152">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF152">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AG152">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -27530,46 +27530,46 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O167">
         <v>4.7</v>
       </c>
       <c r="P167">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="Q167">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R167">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="S167">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T167">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="U167">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="V167">
         <v>1.66</v>
       </c>
       <c r="W167">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X167">
         <v>1.02</v>
       </c>
       <c r="Y167">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z167">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA167">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AB167">
         <v>2.6</v>
@@ -27578,13 +27578,13 @@
         <v>2.19</v>
       </c>
       <c r="AD167">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE167">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AF167">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG167">
         <v>2.1</v>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AK167">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27699,28 +27699,28 @@
         <v>3</v>
       </c>
       <c r="P168">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q168">
         <v>3</v>
       </c>
       <c r="R168">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="S168">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="T168">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U168">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="V168">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W168">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X168">
         <v>1.05</v>
@@ -27729,28 +27729,28 @@
         <v>1.46</v>
       </c>
       <c r="Z168">
-        <v>2.73</v>
+        <v>2.51</v>
       </c>
       <c r="AA168">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AB168">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AC168">
         <v>4.9</v>
       </c>
       <c r="AD168">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE168">
         <v>1</v>
       </c>
       <c r="AF168">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AG168">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK168">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -28019,31 +28019,31 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="O170">
         <v>3.1</v>
       </c>
       <c r="P170">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q170">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
       <c r="R170">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S170">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T170">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="U170">
         <v>2.95</v>
       </c>
       <c r="V170">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W170">
         <v>1</v>
@@ -28052,25 +28052,25 @@
         <v>1.1</v>
       </c>
       <c r="Y170">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z170">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AA170">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AB170">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC170">
         <v>4.8</v>
       </c>
       <c r="AD170">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE170">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF170">
         <v>2</v>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK170">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28363,10 +28363,10 @@
         <v>1.23</v>
       </c>
       <c r="T172">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U172">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V172">
         <v>1.59</v>
@@ -28375,28 +28375,28 @@
         <v>1.16</v>
       </c>
       <c r="X172">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y172">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z172">
         <v>4.8</v>
       </c>
       <c r="AA172">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB172">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC172">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD172">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE172">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF172">
         <v>2.1</v>
@@ -28415,7 +28415,7 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK172">
         <v>1.03</v>
@@ -31291,10 +31291,10 @@
         <v>1.95</v>
       </c>
       <c r="R190">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="S190">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T190">
         <v>3.3</v>
@@ -31306,25 +31306,25 @@
         <v>1.5</v>
       </c>
       <c r="W190">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X190">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y190">
         <v>1.18</v>
       </c>
       <c r="Z190">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA190">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB190">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AC190">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="AD190">
         <v>1.44</v>
@@ -31333,7 +31333,7 @@
         <v>1.13</v>
       </c>
       <c r="AF190">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG190">
         <v>2</v>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK190">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="O205">
         <v>3.45</v>
       </c>
       <c r="P205">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q205">
         <v>2.8</v>
       </c>
       <c r="R205">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S205">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T205">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="U205">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="V205">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W205">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X205">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y205">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z205">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA205">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB205">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC205">
         <v>3.08</v>
       </c>
       <c r="AD205">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE205">
         <v>1.11</v>
       </c>
       <c r="AF205">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG205">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O212">
         <v>3.1</v>
       </c>
       <c r="P212">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q212">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="R212">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S212">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T212">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U212">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="V212">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W212">
         <v>1.02</v>
       </c>
       <c r="X212">
+        <v>1.03</v>
+      </c>
+      <c r="Y212">
+        <v>1.35</v>
+      </c>
+      <c r="Z212">
+        <v>2.74</v>
+      </c>
+      <c r="AA212">
+        <v>2.15</v>
+      </c>
+      <c r="AB212">
+        <v>1.61</v>
+      </c>
+      <c r="AC212">
+        <v>3.84</v>
+      </c>
+      <c r="AD212">
+        <v>1.18</v>
+      </c>
+      <c r="AE212">
         <v>1.02</v>
       </c>
-      <c r="Y212">
-        <v>1.32</v>
-      </c>
-      <c r="Z212">
-        <v>2.88</v>
-      </c>
-      <c r="AA212">
-        <v>2.08</v>
-      </c>
-      <c r="AB212">
-        <v>1.65</v>
-      </c>
-      <c r="AC212">
-        <v>3.7</v>
-      </c>
-      <c r="AD212">
-        <v>1.2</v>
-      </c>
-      <c r="AE212">
-        <v>1.03</v>
-      </c>
       <c r="AF212">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG212">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="AK212">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35028,31 +35028,31 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="O213">
         <v>3</v>
       </c>
       <c r="P213">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q213">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="R213">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S213">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T213">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="U213">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="V213">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W213">
         <v>1.01</v>
@@ -35061,31 +35061,31 @@
         <v>1.03</v>
       </c>
       <c r="Y213">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z213">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AA213">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="AB213">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AC213">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AD213">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE213">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF213">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AG213">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK213">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -36495,64 +36495,64 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="O222">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="P222">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q222">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="R222">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S222">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T222">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="U222">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="V222">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W222">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X222">
         <v>1.04</v>
       </c>
       <c r="Y222">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z222">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA222">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="AB222">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AC222">
-        <v>3.88</v>
+        <v>4.3</v>
       </c>
       <c r="AD222">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE222">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF222">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="AG222">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK222">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36658,64 +36658,64 @@
         </is>
       </c>
       <c r="N223">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="O223">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P223">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="Q223">
-        <v>6.07</v>
+        <v>7.28</v>
       </c>
       <c r="R223">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="S223">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="T223">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="U223">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="V223">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W223">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X223">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y223">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z223">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AA223">
-        <v>1.89</v>
+        <v>2.21</v>
       </c>
       <c r="AB223">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AC223">
-        <v>3.08</v>
+        <v>3.92</v>
       </c>
       <c r="AD223">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AE223">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF223">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AG223">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK223">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -37648,7 +37648,7 @@
         <v>2.62</v>
       </c>
       <c r="R229">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="S229">
         <v>1.46</v>
@@ -37657,40 +37657,40 @@
         <v>2.41</v>
       </c>
       <c r="U229">
-        <v>2.95</v>
+        <v>3.33</v>
       </c>
       <c r="V229">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W229">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X229">
         <v>1.03</v>
       </c>
       <c r="Y229">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z229">
         <v>2.72</v>
       </c>
       <c r="AA229">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AB229">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AC229">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AD229">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE229">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF229">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG229">
         <v>1.75</v>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK229">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -39942,7 +39942,7 @@
         <v>2.58</v>
       </c>
       <c r="V243">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W243">
         <v>1.09</v>
@@ -39951,7 +39951,7 @@
         <v>1.04</v>
       </c>
       <c r="Y243">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z243">
         <v>3.82</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="O9">
-        <v>4.95</v>
+        <v>4.45</v>
       </c>
       <c r="P9">
-        <v>7.9</v>
+        <v>4.75</v>
       </c>
       <c r="Q9">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="R9">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="S9">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U9">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="V9">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AA9">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AB9">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AC9">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AD9">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AK9">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
+        <v>1.27</v>
+      </c>
+      <c r="O10">
+        <v>4.95</v>
+      </c>
+      <c r="P10">
+        <v>7.9</v>
+      </c>
+      <c r="Q10">
+        <v>1.7</v>
+      </c>
+      <c r="R10">
+        <v>2.47</v>
+      </c>
+      <c r="S10">
+        <v>1.29</v>
+      </c>
+      <c r="T10">
+        <v>3.25</v>
+      </c>
+      <c r="U10">
+        <v>2.41</v>
+      </c>
+      <c r="V10">
         <v>1.46</v>
       </c>
-      <c r="O10">
-        <v>4.45</v>
-      </c>
-      <c r="P10">
-        <v>4.75</v>
-      </c>
-      <c r="Q10">
-        <v>2.06</v>
-      </c>
-      <c r="R10">
-        <v>2.18</v>
-      </c>
-      <c r="S10">
-        <v>1.31</v>
-      </c>
-      <c r="T10">
-        <v>3.1</v>
-      </c>
-      <c r="U10">
-        <v>2.6</v>
-      </c>
-      <c r="V10">
-        <v>1.44</v>
-      </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="AA10">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AB10">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AC10">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="AG10">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AK10">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="P16">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q16">
-        <v>3.86</v>
+        <v>4.3</v>
       </c>
       <c r="R16">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S16">
         <v>1.17</v>
@@ -2938,7 +2938,7 @@
         <v>4.5</v>
       </c>
       <c r="U16">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="V16">
         <v>1.75</v>
@@ -2956,10 +2956,10 @@
         <v>6.3</v>
       </c>
       <c r="AA16">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AC16">
         <v>1.9</v>
@@ -2971,10 +2971,10 @@
         <v>1.29</v>
       </c>
       <c r="AF16">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG16">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="O21">
         <v>3.1</v>
       </c>
       <c r="P21">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="Q21">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="U21">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="V21">
+        <v>1.36</v>
+      </c>
+      <c r="W21">
+        <v>1.02</v>
+      </c>
+      <c r="X21">
+        <v>1.04</v>
+      </c>
+      <c r="Y21">
         <v>1.35</v>
       </c>
-      <c r="W21">
-        <v>1.03</v>
-      </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
-      <c r="Y21">
-        <v>1.28</v>
-      </c>
       <c r="Z21">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA21">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="AB21">
         <v>1.73</v>
       </c>
       <c r="AC21">
-        <v>3.44</v>
+        <v>3.62</v>
       </c>
       <c r="AD21">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE21">
         <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG21">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AK21">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="O22">
         <v>3.1</v>
       </c>
       <c r="P22">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="Q22">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="R22">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="U22">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA22">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="AB22">
         <v>1.73</v>
       </c>
       <c r="AC22">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AD22">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE22">
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG22">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="Q23">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="R23">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="S23">
         <v>1.25</v>
@@ -4079,19 +4079,19 @@
         <v>3.5</v>
       </c>
       <c r="U23">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="V23">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
         <v>4.5</v>
@@ -4100,7 +4100,7 @@
         <v>1.56</v>
       </c>
       <c r="AB23">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC23">
         <v>2.35</v>
@@ -4112,10 +4112,10 @@
         <v>1.2</v>
       </c>
       <c r="AF23">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG23">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="O24">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q24">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="R24">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S24">
         <v>1.42</v>
@@ -4245,7 +4245,7 @@
         <v>2.74</v>
       </c>
       <c r="V24">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W24">
         <v>1.05</v>
@@ -4257,16 +4257,16 @@
         <v>1.3</v>
       </c>
       <c r="Z24">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA24">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB24">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC24">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AD24">
         <v>1.23</v>
@@ -4294,7 +4294,7 @@
         <v>1.53</v>
       </c>
       <c r="AK24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,31 +5199,31 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="O30">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
-        <v>2.77</v>
+        <v>3.85</v>
       </c>
       <c r="Q30">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="R30">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="T30">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U30">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="V30">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
         <v>1.12</v>
@@ -5232,31 +5232,31 @@
         <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="AA30">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AB30">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AC30">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="AD30">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE30">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG30">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P31">
-        <v>3.85</v>
+        <v>2.77</v>
       </c>
       <c r="Q31">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S31">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="T31">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
-        <v>2.47</v>
+        <v>2.27</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W31">
         <v>1.12</v>
@@ -5395,31 +5395,31 @@
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z31">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="AA31">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AC31">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="AD31">
+        <v>1.57</v>
+      </c>
+      <c r="AE31">
+        <v>1.18</v>
+      </c>
+      <c r="AF31">
         <v>1.5</v>
       </c>
-      <c r="AE31">
-        <v>1.14</v>
-      </c>
-      <c r="AF31">
-        <v>1.55</v>
-      </c>
       <c r="AG31">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -7810,10 +7810,10 @@
         <v>1.14</v>
       </c>
       <c r="O46">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="P46">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q46">
         <v>1.46</v>
@@ -7828,7 +7828,7 @@
         <v>4.8</v>
       </c>
       <c r="U46">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="V46">
         <v>1.9</v>
@@ -7846,13 +7846,13 @@
         <v>8.5</v>
       </c>
       <c r="AA46">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AB46">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
       <c r="AC46">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AD46">
         <v>2.05</v>
@@ -7864,7 +7864,7 @@
         <v>1.78</v>
       </c>
       <c r="AG46">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK46">
-        <v>5.45</v>
+        <v>5.15</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,34 +7970,34 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="O47">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="P47">
         <v>1.7</v>
       </c>
       <c r="Q47">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="R47">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S47">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T47">
         <v>4</v>
       </c>
       <c r="U47">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V47">
         <v>1.71</v>
       </c>
       <c r="W47">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X47">
         <v>1.02</v>
@@ -8006,7 +8006,7 @@
         <v>1.08</v>
       </c>
       <c r="Z47">
-        <v>5.55</v>
+        <v>5.95</v>
       </c>
       <c r="AA47">
         <v>1.47</v>
@@ -8015,10 +8015,10 @@
         <v>2.6</v>
       </c>
       <c r="AC47">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AD47">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AE47">
         <v>1.26</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,80 +12534,80 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.55</v>
+        <v>2.03</v>
       </c>
       <c r="O75">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P75">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Q75">
-        <v>2.07</v>
+        <v>2.52</v>
       </c>
       <c r="R75">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="S75">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="T75">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="U75">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="V75">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="W75">
+        <v>1.14</v>
+      </c>
+      <c r="X75">
+        <v>1.02</v>
+      </c>
+      <c r="Y75">
+        <v>1.11</v>
+      </c>
+      <c r="Z75">
+        <v>5.25</v>
+      </c>
+      <c r="AA75">
+        <v>1.49</v>
+      </c>
+      <c r="AB75">
+        <v>2.37</v>
+      </c>
+      <c r="AC75">
+        <v>2.17</v>
+      </c>
+      <c r="AD75">
+        <v>1.59</v>
+      </c>
+      <c r="AE75">
         <v>1.22</v>
       </c>
-      <c r="X75">
-        <v>1.01</v>
-      </c>
-      <c r="Y75">
-        <v>1.08</v>
-      </c>
-      <c r="Z75">
-        <v>7.1</v>
-      </c>
-      <c r="AA75">
-        <v>1.34</v>
-      </c>
-      <c r="AB75">
-        <v>3.18</v>
-      </c>
-      <c r="AC75">
-        <v>1.8</v>
-      </c>
-      <c r="AD75">
-        <v>1.98</v>
-      </c>
-      <c r="AE75">
-        <v>1.38</v>
-      </c>
       <c r="AF75">
+        <v>1.44</v>
+      </c>
+      <c r="AG75">
+        <v>2.6</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
         <v>1.35</v>
       </c>
-      <c r="AG75">
-        <v>2.9</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.17</v>
-      </c>
       <c r="AK75">
-        <v>2.16</v>
+        <v>1.72</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="O76">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P76">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="Q76">
-        <v>2.52</v>
+        <v>2.07</v>
       </c>
       <c r="R76">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="S76">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="T76">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="U76">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="V76">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="W76">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X76">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z76">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="AA76">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AB76">
-        <v>2.37</v>
+        <v>3.18</v>
       </c>
       <c r="AC76">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AD76">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="AE76">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AF76">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AG76">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AK76">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>4.78</v>
+        <v>4.15</v>
       </c>
       <c r="O83">
-        <v>4.58</v>
+        <v>4.4</v>
       </c>
       <c r="P83">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q83">
         <v>4.6</v>
       </c>
       <c r="R83">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="S83">
         <v>1.17</v>
@@ -13862,7 +13862,7 @@
         <v>1.99</v>
       </c>
       <c r="V83">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W83">
         <v>1.17</v>
@@ -13871,22 +13871,22 @@
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z83">
         <v>6.05</v>
       </c>
       <c r="AA83">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB83">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="AC83">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AD83">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE83">
         <v>1.31</v>
@@ -13895,7 +13895,7 @@
         <v>1.45</v>
       </c>
       <c r="AG83">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.15</v>
+        <v>2.31</v>
       </c>
       <c r="AK83">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="O90">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="P90">
-        <v>2.84</v>
+        <v>8.75</v>
       </c>
       <c r="Q90">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="R90">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="S90">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="T90">
-        <v>2.95</v>
+        <v>3.68</v>
       </c>
       <c r="U90">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="V90">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="W90">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X90">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z90">
-        <v>3.58</v>
+        <v>5.2</v>
       </c>
       <c r="AA90">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="AB90">
-        <v>1.85</v>
+        <v>2.54</v>
       </c>
       <c r="AC90">
-        <v>3.3</v>
+        <v>2.13</v>
       </c>
       <c r="AD90">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AE90">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AF90">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG90">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK90">
-        <v>1.57</v>
+        <v>3.6</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,65 +15142,65 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.25</v>
+        <v>2.34</v>
       </c>
       <c r="O91">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>8.75</v>
+        <v>2.84</v>
       </c>
       <c r="Q91">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="R91">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="S91">
+        <v>1.34</v>
+      </c>
+      <c r="T91">
+        <v>2.95</v>
+      </c>
+      <c r="U91">
+        <v>2.66</v>
+      </c>
+      <c r="V91">
+        <v>1.41</v>
+      </c>
+      <c r="W91">
+        <v>1.04</v>
+      </c>
+      <c r="X91">
+        <v>1.03</v>
+      </c>
+      <c r="Y91">
         <v>1.21</v>
       </c>
-      <c r="T91">
-        <v>3.68</v>
-      </c>
-      <c r="U91">
-        <v>2.12</v>
-      </c>
-      <c r="V91">
-        <v>1.63</v>
-      </c>
-      <c r="W91">
-        <v>1.13</v>
-      </c>
-      <c r="X91">
-        <v>1.02</v>
-      </c>
-      <c r="Y91">
-        <v>1.08</v>
-      </c>
       <c r="Z91">
-        <v>5.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA91">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AB91">
-        <v>2.54</v>
+        <v>1.85</v>
       </c>
       <c r="AC91">
+        <v>3.3</v>
+      </c>
+      <c r="AD91">
+        <v>1.3</v>
+      </c>
+      <c r="AE91">
+        <v>1.12</v>
+      </c>
+      <c r="AF91">
+        <v>1.7</v>
+      </c>
+      <c r="AG91">
         <v>2.13</v>
       </c>
-      <c r="AD91">
-        <v>1.61</v>
-      </c>
-      <c r="AE91">
-        <v>1.25</v>
-      </c>
-      <c r="AF91">
-        <v>1.79</v>
-      </c>
-      <c r="AG91">
-        <v>1.92</v>
-      </c>
       <c r="AH91" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK91">
-        <v>3.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.49</v>
+        <v>4.85</v>
       </c>
       <c r="O104">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="P104">
-        <v>4.15</v>
+        <v>1.54</v>
       </c>
       <c r="Q104">
+        <v>4.6</v>
+      </c>
+      <c r="R104">
+        <v>2.62</v>
+      </c>
+      <c r="S104">
+        <v>1.16</v>
+      </c>
+      <c r="T104">
+        <v>4.2</v>
+      </c>
+      <c r="U104">
+        <v>1.97</v>
+      </c>
+      <c r="V104">
+        <v>1.73</v>
+      </c>
+      <c r="W104">
+        <v>1.2</v>
+      </c>
+      <c r="X104">
+        <v>1.01</v>
+      </c>
+      <c r="Y104">
+        <v>1.06</v>
+      </c>
+      <c r="Z104">
+        <v>6.6</v>
+      </c>
+      <c r="AA104">
+        <v>1.36</v>
+      </c>
+      <c r="AB104">
+        <v>3.1</v>
+      </c>
+      <c r="AC104">
         <v>1.89</v>
       </c>
-      <c r="R104">
-        <v>2.86</v>
-      </c>
-      <c r="S104">
-        <v>1.1</v>
-      </c>
-      <c r="T104">
-        <v>5.3</v>
-      </c>
-      <c r="U104">
-        <v>1.67</v>
-      </c>
-      <c r="V104">
-        <v>2.11</v>
-      </c>
-      <c r="W104">
-        <v>1.3</v>
-      </c>
-      <c r="X104">
-        <v>1</v>
-      </c>
-      <c r="Y104">
-        <v>1</v>
-      </c>
-      <c r="Z104">
-        <v>9</v>
-      </c>
-      <c r="AA104">
-        <v>1.22</v>
-      </c>
-      <c r="AB104">
-        <v>4.27</v>
-      </c>
-      <c r="AC104">
-        <v>1.55</v>
-      </c>
       <c r="AD104">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="AE104">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AF104">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AG104">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
+        <v>1.16</v>
+      </c>
+      <c r="AK104">
         <v>1.14</v>
-      </c>
-      <c r="AK104">
-        <v>2.43</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>4.85</v>
+        <v>2.07</v>
       </c>
       <c r="O105">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="P105">
-        <v>1.54</v>
+        <v>2.68</v>
       </c>
       <c r="Q105">
-        <v>4.6</v>
+        <v>2.51</v>
       </c>
       <c r="R105">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="S105">
+        <v>1.22</v>
+      </c>
+      <c r="T105">
+        <v>4</v>
+      </c>
+      <c r="U105">
+        <v>2.05</v>
+      </c>
+      <c r="V105">
+        <v>1.71</v>
+      </c>
+      <c r="W105">
         <v>1.16</v>
-      </c>
-      <c r="T105">
-        <v>4.2</v>
-      </c>
-      <c r="U105">
-        <v>1.97</v>
-      </c>
-      <c r="V105">
-        <v>1.73</v>
-      </c>
-      <c r="W105">
-        <v>1.2</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z105">
-        <v>6.6</v>
+        <v>5.69</v>
       </c>
       <c r="AA105">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB105">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AC105">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AD105">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AE105">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF105">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG105">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>1.14</v>
+        <v>1.65</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="O106">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P106">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="Q106">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="R106">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="S106">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="U106">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="V106">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="W106">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z106">
-        <v>5.69</v>
+        <v>5</v>
       </c>
       <c r="AA106">
+        <v>1.53</v>
+      </c>
+      <c r="AB106">
+        <v>2.29</v>
+      </c>
+      <c r="AC106">
+        <v>2.33</v>
+      </c>
+      <c r="AD106">
+        <v>1.5</v>
+      </c>
+      <c r="AE106">
+        <v>1.2</v>
+      </c>
+      <c r="AF106">
         <v>1.44</v>
       </c>
-      <c r="AB106">
-        <v>2.7</v>
-      </c>
-      <c r="AC106">
-        <v>2</v>
-      </c>
-      <c r="AD106">
-        <v>1.69</v>
-      </c>
-      <c r="AE106">
-        <v>1.25</v>
-      </c>
-      <c r="AF106">
-        <v>1.39</v>
-      </c>
       <c r="AG106">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AK106">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,80 +17750,80 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O107">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P107">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="Q107">
-        <v>2.74</v>
+        <v>3.88</v>
       </c>
       <c r="R107">
+        <v>2.61</v>
+      </c>
+      <c r="S107">
+        <v>1.13</v>
+      </c>
+      <c r="T107">
+        <v>5</v>
+      </c>
+      <c r="U107">
+        <v>1.72</v>
+      </c>
+      <c r="V107">
+        <v>2.03</v>
+      </c>
+      <c r="W107">
+        <v>1.29</v>
+      </c>
+      <c r="X107">
+        <v>1</v>
+      </c>
+      <c r="Y107">
+        <v>1.07</v>
+      </c>
+      <c r="Z107">
+        <v>8.4</v>
+      </c>
+      <c r="AA107">
+        <v>1.29</v>
+      </c>
+      <c r="AB107">
+        <v>3.78</v>
+      </c>
+      <c r="AC107">
+        <v>1.74</v>
+      </c>
+      <c r="AD107">
         <v>2.24</v>
       </c>
-      <c r="S107">
-        <v>1.25</v>
-      </c>
-      <c r="T107">
-        <v>3.36</v>
-      </c>
-      <c r="U107">
-        <v>2.28</v>
-      </c>
-      <c r="V107">
-        <v>1.59</v>
-      </c>
-      <c r="W107">
-        <v>1.12</v>
-      </c>
-      <c r="X107">
-        <v>1.01</v>
-      </c>
-      <c r="Y107">
+      <c r="AE107">
+        <v>1.5</v>
+      </c>
+      <c r="AF107">
+        <v>1.3</v>
+      </c>
+      <c r="AG107">
+        <v>3.05</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
         <v>1.16</v>
       </c>
-      <c r="Z107">
-        <v>5</v>
-      </c>
-      <c r="AA107">
-        <v>1.53</v>
-      </c>
-      <c r="AB107">
-        <v>2.29</v>
-      </c>
-      <c r="AC107">
-        <v>2.33</v>
-      </c>
-      <c r="AD107">
-        <v>1.5</v>
-      </c>
-      <c r="AE107">
-        <v>1.2</v>
-      </c>
-      <c r="AF107">
-        <v>1.44</v>
-      </c>
-      <c r="AG107">
-        <v>2.6</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.47</v>
-      </c>
       <c r="AK107">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>3.55</v>
+        <v>2.55</v>
       </c>
       <c r="O108">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="P108">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="Q108">
-        <v>3.88</v>
+        <v>2.69</v>
       </c>
       <c r="R108">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="S108">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T108">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="U108">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="V108">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="W108">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X108">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z108">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AA108">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AB108">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AC108">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AD108">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AE108">
         <v>1.5</v>
       </c>
       <c r="AF108">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AG108">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK108">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.55</v>
+        <v>1.47</v>
       </c>
       <c r="O109">
-        <v>3.95</v>
+        <v>4.25</v>
       </c>
       <c r="P109">
-        <v>2.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q109">
-        <v>2.69</v>
+        <v>1.92</v>
       </c>
       <c r="R109">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="S109">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T109">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="U109">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="V109">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="W109">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="X109">
         <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z109">
-        <v>8</v>
+        <v>5.65</v>
       </c>
       <c r="AA109">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AB109">
-        <v>4</v>
+        <v>2.87</v>
       </c>
       <c r="AC109">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AD109">
-        <v>2.21</v>
+        <v>1.78</v>
       </c>
       <c r="AE109">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AF109">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AG109">
-        <v>3.65</v>
+        <v>2.47</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK109">
-        <v>1.44</v>
+        <v>2.42</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="O110">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P110">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="Q110">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R110">
-        <v>2.59</v>
+        <v>2.86</v>
       </c>
       <c r="S110">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T110">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="U110">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="V110">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="W110">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Z110">
-        <v>5.65</v>
+        <v>9</v>
       </c>
       <c r="AA110">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AB110">
-        <v>2.87</v>
+        <v>4.27</v>
       </c>
       <c r="AC110">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="AD110">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AE110">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AF110">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AG110">
-        <v>2.47</v>
+        <v>3.42</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK110">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -31608,61 +31608,61 @@
         <v>7.5</v>
       </c>
       <c r="O192">
-        <v>5.3</v>
+        <v>5.05</v>
       </c>
       <c r="P192">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Q192">
-        <v>6</v>
+        <v>6.35</v>
       </c>
       <c r="R192">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="S192">
         <v>1.22</v>
       </c>
       <c r="T192">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="U192">
         <v>2.07</v>
       </c>
       <c r="V192">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W192">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X192">
         <v>1.01</v>
       </c>
       <c r="Y192">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z192">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA192">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB192">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC192">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AD192">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE192">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AF192">
         <v>1.65</v>
       </c>
       <c r="AG192">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,31 +5199,31 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="O30">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
-        <v>3.85</v>
+        <v>2.77</v>
       </c>
       <c r="Q30">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S30">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="T30">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U30">
-        <v>2.47</v>
+        <v>2.27</v>
       </c>
       <c r="V30">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W30">
         <v>1.12</v>
@@ -5232,31 +5232,31 @@
         <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z30">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="AA30">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AC30">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="AD30">
+        <v>1.57</v>
+      </c>
+      <c r="AE30">
+        <v>1.18</v>
+      </c>
+      <c r="AF30">
         <v>1.5</v>
       </c>
-      <c r="AE30">
-        <v>1.14</v>
-      </c>
-      <c r="AF30">
-        <v>1.55</v>
-      </c>
       <c r="AG30">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="O31">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>2.77</v>
+        <v>3.85</v>
       </c>
       <c r="Q31">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="R31">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="T31">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U31">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="V31">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
         <v>1.12</v>
@@ -5395,31 +5395,31 @@
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="AA31">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AB31">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="AD31">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE31">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG31">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -9763,34 +9763,34 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O58">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P58">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="Q58">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R58">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="S58">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T58">
         <v>3.1</v>
       </c>
       <c r="U58">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V58">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W58">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
         <v>1.02</v>
@@ -9802,10 +9802,10 @@
         <v>3.82</v>
       </c>
       <c r="AA58">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB58">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AC58">
         <v>3.03</v>
@@ -9814,13 +9814,13 @@
         <v>1.33</v>
       </c>
       <c r="AE58">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF58">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG58">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.24</v>
       </c>
       <c r="AK58">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="O75">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P75">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="Q75">
-        <v>2.52</v>
+        <v>2.07</v>
       </c>
       <c r="R75">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="S75">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="T75">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="U75">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="V75">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="W75">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z75">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="AA75">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AB75">
-        <v>2.37</v>
+        <v>3.18</v>
       </c>
       <c r="AC75">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AD75">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="AE75">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AF75">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AG75">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AK75">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.55</v>
+        <v>2.03</v>
       </c>
       <c r="O76">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P76">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Q76">
-        <v>2.07</v>
+        <v>2.52</v>
       </c>
       <c r="R76">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="S76">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="T76">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="U76">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="V76">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="W76">
+        <v>1.14</v>
+      </c>
+      <c r="X76">
+        <v>1.02</v>
+      </c>
+      <c r="Y76">
+        <v>1.11</v>
+      </c>
+      <c r="Z76">
+        <v>5.25</v>
+      </c>
+      <c r="AA76">
+        <v>1.49</v>
+      </c>
+      <c r="AB76">
+        <v>2.37</v>
+      </c>
+      <c r="AC76">
+        <v>2.17</v>
+      </c>
+      <c r="AD76">
+        <v>1.59</v>
+      </c>
+      <c r="AE76">
         <v>1.22</v>
       </c>
-      <c r="X76">
-        <v>1.01</v>
-      </c>
-      <c r="Y76">
-        <v>1.08</v>
-      </c>
-      <c r="Z76">
-        <v>7.1</v>
-      </c>
-      <c r="AA76">
-        <v>1.34</v>
-      </c>
-      <c r="AB76">
-        <v>3.18</v>
-      </c>
-      <c r="AC76">
-        <v>1.8</v>
-      </c>
-      <c r="AD76">
-        <v>1.98</v>
-      </c>
-      <c r="AE76">
-        <v>1.38</v>
-      </c>
       <c r="AF76">
+        <v>1.44</v>
+      </c>
+      <c r="AG76">
+        <v>2.6</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.35</v>
       </c>
-      <c r="AG76">
-        <v>2.9</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.17</v>
-      </c>
       <c r="AK76">
-        <v>2.16</v>
+        <v>1.72</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -20856,22 +20856,22 @@
         <v>0</v>
       </c>
       <c r="Q126">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="R126">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S126">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T126">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U126">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="V126">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W126">
         <v>1.03</v>
@@ -20886,10 +20886,10 @@
         <v>3.11</v>
       </c>
       <c r="AA126">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB126">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC126">
         <v>3.48</v>
@@ -20920,7 +20920,7 @@
         <v>1.28</v>
       </c>
       <c r="AK126">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
+        <v>6.94</v>
+      </c>
+      <c r="O138">
         <v>4.1</v>
       </c>
-      <c r="O138">
-        <v>3.55</v>
-      </c>
       <c r="P138">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="Q138">
-        <v>5</v>
+        <v>5.97</v>
       </c>
       <c r="R138">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S138">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T138">
-        <v>2.69</v>
+        <v>2.98</v>
       </c>
       <c r="U138">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="V138">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W138">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X138">
         <v>1.02</v>
       </c>
       <c r="Y138">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z138">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="AA138">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB138">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC138">
-        <v>3.36</v>
+        <v>2.9</v>
       </c>
       <c r="AD138">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE138">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF138">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG138">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AK138">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>6.94</v>
+        <v>4.1</v>
       </c>
       <c r="O139">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="P139">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="Q139">
-        <v>5.97</v>
+        <v>5</v>
       </c>
       <c r="R139">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S139">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T139">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="U139">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="V139">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W139">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X139">
         <v>1.02</v>
       </c>
       <c r="Y139">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z139">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="AA139">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AB139">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC139">
-        <v>2.9</v>
+        <v>3.36</v>
       </c>
       <c r="AD139">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE139">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF139">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG139">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AK139">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23292,52 +23292,52 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="O141">
         <v>3.5</v>
       </c>
       <c r="P141">
-        <v>3.44</v>
+        <v>2.82</v>
       </c>
       <c r="Q141">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="R141">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S141">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T141">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="U141">
         <v>3.2</v>
       </c>
       <c r="V141">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W141">
         <v>1.06</v>
       </c>
       <c r="X141">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y141">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z141">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA141">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB141">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC141">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="AD141">
         <v>1.2</v>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AK141">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23464,16 +23464,16 @@
         <v>2.7</v>
       </c>
       <c r="Q142">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R142">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="S142">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="T142">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="U142">
         <v>3.34</v>
@@ -23494,10 +23494,10 @@
         <v>2.56</v>
       </c>
       <c r="AA142">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AB142">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC142">
         <v>4.35</v>
@@ -23627,55 +23627,55 @@
         <v>2.5</v>
       </c>
       <c r="Q143">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="R143">
         <v>1.91</v>
       </c>
       <c r="S143">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T143">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U143">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="V143">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W143">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X143">
         <v>1.03</v>
       </c>
       <c r="Y143">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z143">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AA143">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AB143">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC143">
-        <v>3.74</v>
+        <v>3.88</v>
       </c>
       <c r="AD143">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE143">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF143">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG143">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>1.3</v>
       </c>
       <c r="AK143">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23781,25 +23781,25 @@
         </is>
       </c>
       <c r="N144">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O144">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P144">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q144">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="R144">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="S144">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="T144">
-        <v>2.27</v>
+        <v>2.57</v>
       </c>
       <c r="U144">
         <v>3.2</v>
@@ -23811,22 +23811,22 @@
         <v>1.01</v>
       </c>
       <c r="X144">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y144">
         <v>1.36</v>
       </c>
       <c r="Z144">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="AA144">
         <v>2.21</v>
       </c>
       <c r="AB144">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC144">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="AD144">
         <v>1.18</v>
@@ -23835,7 +23835,7 @@
         <v>1.02</v>
       </c>
       <c r="AF144">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG144">
         <v>1.75</v>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AK144">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -25251,19 +25251,19 @@
         <v>1.55</v>
       </c>
       <c r="O153">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P153">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q153">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R153">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="S153">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T153">
         <v>3.12</v>
@@ -25284,19 +25284,19 @@
         <v>1.17</v>
       </c>
       <c r="Z153">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA153">
         <v>1.63</v>
       </c>
       <c r="AB153">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC153">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AD153">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE153">
         <v>1.14</v>
@@ -25305,7 +25305,7 @@
         <v>1.68</v>
       </c>
       <c r="AG153">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,80 +25737,80 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.98</v>
+        <v>3.55</v>
       </c>
       <c r="O156">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P156">
+        <v>2.25</v>
+      </c>
+      <c r="Q156">
+        <v>4.33</v>
+      </c>
+      <c r="R156">
+        <v>1.95</v>
+      </c>
+      <c r="S156">
+        <v>1.4</v>
+      </c>
+      <c r="T156">
+        <v>2.39</v>
+      </c>
+      <c r="U156">
         <v>3.3</v>
       </c>
-      <c r="Q156">
-        <v>2.62</v>
-      </c>
-      <c r="R156">
-        <v>2.1</v>
-      </c>
-      <c r="S156">
-        <v>1.41</v>
-      </c>
-      <c r="T156">
-        <v>2.81</v>
-      </c>
-      <c r="U156">
-        <v>2.85</v>
-      </c>
       <c r="V156">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X156">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
+        <v>1.43</v>
+      </c>
+      <c r="Z156">
+        <v>2.82</v>
+      </c>
+      <c r="AA156">
+        <v>2.35</v>
+      </c>
+      <c r="AB156">
+        <v>1.57</v>
+      </c>
+      <c r="AC156">
+        <v>4.25</v>
+      </c>
+      <c r="AD156">
+        <v>1.18</v>
+      </c>
+      <c r="AE156">
+        <v>1.02</v>
+      </c>
+      <c r="AF156">
+        <v>1.89</v>
+      </c>
+      <c r="AG156">
+        <v>1.76</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
+        <v>1.28</v>
+      </c>
+      <c r="AK156">
         <v>1.3</v>
-      </c>
-      <c r="Z156">
-        <v>3.1</v>
-      </c>
-      <c r="AA156">
-        <v>1.99</v>
-      </c>
-      <c r="AB156">
-        <v>1.7</v>
-      </c>
-      <c r="AC156">
-        <v>3.6</v>
-      </c>
-      <c r="AD156">
-        <v>1.25</v>
-      </c>
-      <c r="AE156">
-        <v>1.05</v>
-      </c>
-      <c r="AF156">
-        <v>1.79</v>
-      </c>
-      <c r="AG156">
-        <v>1.9</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>1.22</v>
-      </c>
-      <c r="AK156">
-        <v>1.76</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,80 +25900,80 @@
         </is>
       </c>
       <c r="N157">
-        <v>3.55</v>
+        <v>1.98</v>
       </c>
       <c r="O157">
+        <v>3.2</v>
+      </c>
+      <c r="P157">
+        <v>3.3</v>
+      </c>
+      <c r="Q157">
+        <v>2.62</v>
+      </c>
+      <c r="R157">
+        <v>2.1</v>
+      </c>
+      <c r="S157">
+        <v>1.41</v>
+      </c>
+      <c r="T157">
+        <v>2.81</v>
+      </c>
+      <c r="U157">
+        <v>2.85</v>
+      </c>
+      <c r="V157">
+        <v>1.35</v>
+      </c>
+      <c r="W157">
+        <v>1.05</v>
+      </c>
+      <c r="X157">
+        <v>1.01</v>
+      </c>
+      <c r="Y157">
+        <v>1.3</v>
+      </c>
+      <c r="Z157">
         <v>3.1</v>
       </c>
-      <c r="P157">
-        <v>2.25</v>
-      </c>
-      <c r="Q157">
-        <v>4.33</v>
-      </c>
-      <c r="R157">
-        <v>1.95</v>
-      </c>
-      <c r="S157">
-        <v>1.4</v>
-      </c>
-      <c r="T157">
-        <v>2.39</v>
-      </c>
-      <c r="U157">
-        <v>3.3</v>
-      </c>
-      <c r="V157">
-        <v>1.29</v>
-      </c>
-      <c r="W157">
-        <v>1.03</v>
-      </c>
-      <c r="X157">
-        <v>1.03</v>
-      </c>
-      <c r="Y157">
-        <v>1.43</v>
-      </c>
-      <c r="Z157">
-        <v>2.82</v>
-      </c>
       <c r="AA157">
-        <v>2.35</v>
+        <v>1.99</v>
       </c>
       <c r="AB157">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC157">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AD157">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE157">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF157">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AG157">
+        <v>1.9</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
+        <v>1.22</v>
+      </c>
+      <c r="AK157">
         <v>1.76</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>1.28</v>
-      </c>
-      <c r="AK157">
-        <v>1.3</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -28511,31 +28511,31 @@
         <v>13.5</v>
       </c>
       <c r="O173">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="P173">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Q173">
-        <v>10.6</v>
+        <v>7.14</v>
       </c>
       <c r="R173">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="S173">
         <v>1.23</v>
       </c>
       <c r="T173">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U173">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V173">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="W173">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X173">
         <v>1.02</v>
@@ -28562,10 +28562,10 @@
         <v>1.19</v>
       </c>
       <c r="AF173">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG173">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -31451,10 +31451,10 @@
         <v>0</v>
       </c>
       <c r="Q191">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R191">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="S191">
         <v>1.24</v>
@@ -31475,19 +31475,19 @@
         <v>1.01</v>
       </c>
       <c r="Y191">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z191">
         <v>4.15</v>
       </c>
       <c r="AA191">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB191">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AC191">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD191">
         <v>1.44</v>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK191">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -35040,19 +35040,19 @@
         <v>3.88</v>
       </c>
       <c r="R213">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="S213">
         <v>1.46</v>
       </c>
       <c r="T213">
-        <v>2.41</v>
+        <v>2.58</v>
       </c>
       <c r="U213">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="V213">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W213">
         <v>1.02</v>
@@ -35061,10 +35061,10 @@
         <v>1.03</v>
       </c>
       <c r="Y213">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z213">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="AA213">
         <v>2.15</v>
@@ -35085,7 +35085,7 @@
         <v>1.85</v>
       </c>
       <c r="AG213">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>1.54</v>
       </c>
       <c r="AK213">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
+        <v>3.15</v>
+      </c>
+      <c r="O214">
         <v>3.1</v>
       </c>
-      <c r="O214">
-        <v>3</v>
-      </c>
       <c r="P214">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q214">
         <v>4.05</v>
@@ -35206,13 +35206,13 @@
         <v>1.95</v>
       </c>
       <c r="S214">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T214">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U214">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V214">
         <v>1.26</v>
@@ -35224,13 +35224,13 @@
         <v>1.03</v>
       </c>
       <c r="Y214">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z214">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AA214">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AB214">
         <v>1.52</v>
@@ -35261,7 +35261,7 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.26</v>
+        <v>1.59</v>
       </c>
       <c r="AK214">
         <v>1.26</v>
@@ -36495,34 +36495,34 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O222">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P222">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q222">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="R222">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S222">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="T222">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="U222">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="V222">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W222">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X222">
         <v>1.04</v>
@@ -36531,28 +36531,28 @@
         <v>1.43</v>
       </c>
       <c r="Z222">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="AA222">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="AB222">
         <v>1.53</v>
       </c>
       <c r="AC222">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD222">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE222">
         <v>1.01</v>
       </c>
       <c r="AF222">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AG222">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK222">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36658,31 +36658,31 @@
         </is>
       </c>
       <c r="N223">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="O223">
         <v>3.75</v>
       </c>
       <c r="P223">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="Q223">
-        <v>7.28</v>
+        <v>7.22</v>
       </c>
       <c r="R223">
         <v>2.17</v>
       </c>
       <c r="S223">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T223">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="U223">
         <v>3.14</v>
       </c>
       <c r="V223">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W223">
         <v>1.02</v>
@@ -36691,19 +36691,19 @@
         <v>1.04</v>
       </c>
       <c r="Y223">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z223">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AA223">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AB223">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC223">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AD223">
         <v>1.18</v>
@@ -36712,10 +36712,10 @@
         <v>1.03</v>
       </c>
       <c r="AF223">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AG223">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>1.2</v>
       </c>
       <c r="AK223">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AL223">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
+        <v>2.65</v>
+      </c>
+      <c r="O8">
+        <v>3.55</v>
+      </c>
+      <c r="P8">
+        <v>2.09</v>
+      </c>
+      <c r="Q8">
+        <v>2.99</v>
+      </c>
+      <c r="R8">
+        <v>2.22</v>
+      </c>
+      <c r="S8">
         <v>1.27</v>
       </c>
-      <c r="O8">
-        <v>4.95</v>
-      </c>
-      <c r="P8">
-        <v>7.9</v>
-      </c>
-      <c r="Q8">
-        <v>1.67</v>
-      </c>
-      <c r="R8">
-        <v>2.41</v>
-      </c>
-      <c r="S8">
-        <v>1.3</v>
-      </c>
       <c r="T8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z8">
-        <v>3.84</v>
+        <v>4.25</v>
       </c>
       <c r="AA8">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB8">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC8">
-        <v>2.71</v>
+        <v>2.48</v>
       </c>
       <c r="AD8">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE8">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>2.13</v>
+        <v>1.49</v>
       </c>
       <c r="AG8">
-        <v>1.61</v>
+        <v>2.34</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AK8">
-        <v>2.65</v>
+        <v>1.36</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
+        <v>1.27</v>
+      </c>
+      <c r="O9">
+        <v>4.95</v>
+      </c>
+      <c r="P9">
+        <v>7.9</v>
+      </c>
+      <c r="Q9">
+        <v>1.67</v>
+      </c>
+      <c r="R9">
+        <v>2.41</v>
+      </c>
+      <c r="S9">
+        <v>1.3</v>
+      </c>
+      <c r="T9">
+        <v>3.25</v>
+      </c>
+      <c r="U9">
+        <v>2.41</v>
+      </c>
+      <c r="V9">
+        <v>1.46</v>
+      </c>
+      <c r="W9">
+        <v>1.11</v>
+      </c>
+      <c r="X9">
+        <v>1.02</v>
+      </c>
+      <c r="Y9">
+        <v>1.18</v>
+      </c>
+      <c r="Z9">
+        <v>3.84</v>
+      </c>
+      <c r="AA9">
+        <v>1.7</v>
+      </c>
+      <c r="AB9">
+        <v>2.1</v>
+      </c>
+      <c r="AC9">
+        <v>2.71</v>
+      </c>
+      <c r="AD9">
+        <v>1.42</v>
+      </c>
+      <c r="AE9">
+        <v>1.12</v>
+      </c>
+      <c r="AF9">
+        <v>2.13</v>
+      </c>
+      <c r="AG9">
+        <v>1.61</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.09</v>
+      </c>
+      <c r="AK9">
         <v>2.65</v>
-      </c>
-      <c r="O9">
-        <v>3.55</v>
-      </c>
-      <c r="P9">
-        <v>2.09</v>
-      </c>
-      <c r="Q9">
-        <v>2.99</v>
-      </c>
-      <c r="R9">
-        <v>2.22</v>
-      </c>
-      <c r="S9">
-        <v>1.27</v>
-      </c>
-      <c r="T9">
-        <v>3.2</v>
-      </c>
-      <c r="U9">
-        <v>2.3</v>
-      </c>
-      <c r="V9">
-        <v>1.55</v>
-      </c>
-      <c r="W9">
-        <v>1.12</v>
-      </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
-        <v>1.15</v>
-      </c>
-      <c r="Z9">
-        <v>4.25</v>
-      </c>
-      <c r="AA9">
-        <v>1.57</v>
-      </c>
-      <c r="AB9">
-        <v>2.25</v>
-      </c>
-      <c r="AC9">
-        <v>2.48</v>
-      </c>
-      <c r="AD9">
-        <v>1.45</v>
-      </c>
-      <c r="AE9">
-        <v>1.15</v>
-      </c>
-      <c r="AF9">
-        <v>1.49</v>
-      </c>
-      <c r="AG9">
-        <v>2.34</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.21</v>
-      </c>
-      <c r="AK9">
-        <v>1.36</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2274,10 +2274,10 @@
         <v>2.25</v>
       </c>
       <c r="Q12">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="R12">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S12">
         <v>1.25</v>
@@ -2295,7 +2295,7 @@
         <v>1.14</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.1</v>
@@ -2316,7 +2316,7 @@
         <v>1.62</v>
       </c>
       <c r="AE12">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF12">
         <v>1.42</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3264,10 +3264,10 @@
         <v>3.4</v>
       </c>
       <c r="U18">
-        <v>2.51</v>
+        <v>2.14</v>
       </c>
       <c r="V18">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W18">
         <v>1.12</v>
@@ -3300,7 +3300,7 @@
         <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="O30">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="P30">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="Q30">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="R30">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S30">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="T30">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V30">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W30">
         <v>1.12</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="AA30">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB30">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AC30">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="AD30">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AE30">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG30">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="O31">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="P31">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q31">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="R31">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="T31">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W31">
         <v>1.12</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z31">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="AA31">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC31">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AD31">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AE31">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF31">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG31">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK31">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="O44">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="P44">
         <v>4</v>
@@ -7644,31 +7644,31 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="O45">
-        <v>5.35</v>
+        <v>5.1</v>
       </c>
       <c r="P45">
         <v>6.6</v>
       </c>
       <c r="Q45">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R45">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="S45">
         <v>1.17</v>
       </c>
       <c r="T45">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="U45">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="V45">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="W45">
         <v>1.21</v>
@@ -7680,28 +7680,28 @@
         <v>1.06</v>
       </c>
       <c r="Z45">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AA45">
         <v>1.33</v>
       </c>
       <c r="AB45">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="AC45">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AD45">
         <v>1.92</v>
       </c>
       <c r="AE45">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AF45">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG45">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.15</v>
       </c>
       <c r="AK45">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P48">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -8184,7 +8184,7 @@
         <v>1.36</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF48">
         <v>1.6</v>
@@ -8311,16 +8311,16 @@
         <v>2.02</v>
       </c>
       <c r="S49">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
         <v>2.9</v>
       </c>
       <c r="U49">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="V49">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W49">
         <v>1.05</v>
@@ -8353,7 +8353,7 @@
         <v>1.76</v>
       </c>
       <c r="AG49">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8462,13 +8462,13 @@
         <v>1.84</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P50">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q50">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R50">
         <v>2.38</v>
@@ -8492,13 +8492,13 @@
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB50">
         <v>2.25</v>
@@ -8510,7 +8510,7 @@
         <v>1.5</v>
       </c>
       <c r="AE50">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF50">
         <v>1.53</v>
@@ -8625,16 +8625,16 @@
         <v>2.5</v>
       </c>
       <c r="O51">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q51">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R51">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S51">
         <v>1.41</v>
@@ -8652,7 +8652,7 @@
         <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y51">
         <v>1.26</v>
@@ -8661,13 +8661,13 @@
         <v>3.4</v>
       </c>
       <c r="AA51">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AB51">
         <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="AD51">
         <v>1.33</v>
@@ -8797,7 +8797,7 @@
         <v>2.5</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S52">
         <v>1.43</v>
@@ -8821,7 +8821,7 @@
         <v>1.36</v>
       </c>
       <c r="Z52">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA52">
         <v>2.06</v>
@@ -8842,7 +8842,7 @@
         <v>1.8</v>
       </c>
       <c r="AG52">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.35</v>
       </c>
       <c r="AK52">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O59">
         <v>3.6</v>
       </c>
       <c r="P59">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q59">
         <v>2.44</v>
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="O63">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="P63">
-        <v>3.35</v>
+        <v>3.07</v>
       </c>
       <c r="Q63">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="R63">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S63">
         <v>1.47</v>
@@ -10599,43 +10599,43 @@
         <v>2.5</v>
       </c>
       <c r="U63">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V63">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X63">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y63">
         <v>1.42</v>
       </c>
       <c r="Z63">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AA63">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AB63">
         <v>1.6</v>
       </c>
       <c r="AC63">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD63">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE63">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF63">
         <v>1.95</v>
       </c>
       <c r="AG63">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -12057,7 +12057,7 @@
         <v>3.1</v>
       </c>
       <c r="R72">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S72">
         <v>1.36</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="O74">
-        <v>3.17</v>
+        <v>3.48</v>
       </c>
       <c r="P74">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -13708,7 +13708,7 @@
         <v>1.06</v>
       </c>
       <c r="Y82">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z82">
         <v>3.3</v>
@@ -13717,13 +13717,13 @@
         <v>1.95</v>
       </c>
       <c r="AB82">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC82">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AD82">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE82">
         <v>1.1</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O85">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P85">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q85">
         <v>2.96</v>
@@ -14182,13 +14182,13 @@
         <v>1.36</v>
       </c>
       <c r="T85">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U85">
         <v>2.96</v>
       </c>
       <c r="V85">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W85">
         <v>1.05</v>
@@ -14493,19 +14493,19 @@
         <v>2.53</v>
       </c>
       <c r="O87">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P87">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q87">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="R87">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S87">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T87">
         <v>2.7</v>
@@ -14517,7 +14517,7 @@
         <v>1.36</v>
       </c>
       <c r="W87">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X87">
         <v>1.01</v>
@@ -14526,25 +14526,25 @@
         <v>1.27</v>
       </c>
       <c r="Z87">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AA87">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB87">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC87">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="AD87">
         <v>1.25</v>
       </c>
       <c r="AE87">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF87">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG87">
         <v>2</v>
@@ -15468,19 +15468,19 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q93">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="R93">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S93">
         <v>1.25</v>
@@ -15489,43 +15489,43 @@
         <v>3.6</v>
       </c>
       <c r="U93">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="V93">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W93">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X93">
         <v>1.04</v>
       </c>
       <c r="Y93">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA93">
         <v>1.57</v>
       </c>
       <c r="AB93">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC93">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AD93">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AE93">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF93">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG93">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK93">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15634,22 +15634,22 @@
         <v>2.2</v>
       </c>
       <c r="O94">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P94">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q94">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="R94">
         <v>2.26</v>
       </c>
       <c r="S94">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T94">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U94">
         <v>2.39</v>
@@ -15667,19 +15667,19 @@
         <v>1.17</v>
       </c>
       <c r="Z94">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA94">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB94">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC94">
         <v>2.55</v>
       </c>
       <c r="AD94">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AE94">
         <v>1.13</v>
@@ -15688,7 +15688,7 @@
         <v>1.5</v>
       </c>
       <c r="AG94">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>1.4</v>
       </c>
       <c r="AK94">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,25 +15794,25 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="O95">
         <v>3.65</v>
       </c>
       <c r="P95">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q95">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="R95">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S95">
         <v>1.25</v>
       </c>
       <c r="T95">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U95">
         <v>2.23</v>
@@ -15830,13 +15830,13 @@
         <v>1.13</v>
       </c>
       <c r="Z95">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA95">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AB95">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AC95">
         <v>2.35</v>
@@ -15851,7 +15851,7 @@
         <v>1.45</v>
       </c>
       <c r="AG95">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK95">
         <v>1.3</v>
@@ -15957,16 +15957,16 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="O96">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="P96">
-        <v>4.2</v>
+        <v>3.96</v>
       </c>
       <c r="Q96">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="R96">
         <v>2.38</v>
@@ -15978,25 +15978,25 @@
         <v>3.4</v>
       </c>
       <c r="U96">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V96">
         <v>1.6</v>
       </c>
       <c r="W96">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X96">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z96">
         <v>4.25</v>
       </c>
       <c r="AA96">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB96">
         <v>2.3</v>
@@ -16005,10 +16005,10 @@
         <v>2.52</v>
       </c>
       <c r="AD96">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE96">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF96">
         <v>1.53</v>
@@ -16120,19 +16120,19 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O97">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="P97">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q97">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R97">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="S97">
         <v>1.18</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="O109">
-        <v>4.45</v>
+        <v>3.45</v>
       </c>
       <c r="P109">
-        <v>4.15</v>
+        <v>2.39</v>
       </c>
       <c r="Q109">
-        <v>1.83</v>
+        <v>3.02</v>
       </c>
       <c r="R109">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="S109">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="T109">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="U109">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="V109">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="W109">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="X109">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="Z109">
-        <v>9.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA109">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="AB109">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC109">
-        <v>1.54</v>
+        <v>2.33</v>
       </c>
       <c r="AD109">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE109">
-        <v>1.58</v>
+        <v>1.2</v>
       </c>
       <c r="AF109">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AG109">
-        <v>3.42</v>
+        <v>2.6</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="AK109">
-        <v>2.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.5</v>
+        <v>1.49</v>
       </c>
       <c r="O110">
-        <v>3.45</v>
+        <v>4.45</v>
       </c>
       <c r="P110">
-        <v>2.39</v>
+        <v>4.15</v>
       </c>
       <c r="Q110">
-        <v>3.02</v>
+        <v>1.83</v>
       </c>
       <c r="R110">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="S110">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="T110">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="U110">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="V110">
+        <v>2.05</v>
+      </c>
+      <c r="W110">
+        <v>1.33</v>
+      </c>
+      <c r="X110">
+        <v>1</v>
+      </c>
+      <c r="Y110">
+        <v>1</v>
+      </c>
+      <c r="Z110">
+        <v>9.1</v>
+      </c>
+      <c r="AA110">
+        <v>1.16</v>
+      </c>
+      <c r="AB110">
+        <v>4.1</v>
+      </c>
+      <c r="AC110">
+        <v>1.54</v>
+      </c>
+      <c r="AD110">
+        <v>2.4</v>
+      </c>
+      <c r="AE110">
         <v>1.58</v>
       </c>
-      <c r="W110">
-        <v>1.14</v>
-      </c>
-      <c r="X110">
-        <v>1.01</v>
-      </c>
-      <c r="Y110">
-        <v>1.16</v>
-      </c>
-      <c r="Z110">
-        <v>4.4</v>
-      </c>
-      <c r="AA110">
-        <v>1.53</v>
-      </c>
-      <c r="AB110">
-        <v>2.25</v>
-      </c>
-      <c r="AC110">
-        <v>2.33</v>
-      </c>
-      <c r="AD110">
-        <v>1.5</v>
-      </c>
-      <c r="AE110">
-        <v>1.2</v>
-      </c>
       <c r="AF110">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AG110">
-        <v>2.6</v>
+        <v>3.42</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="AK110">
-        <v>1.44</v>
+        <v>2.65</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18728,10 +18728,10 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="O113">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P113">
         <v>2.11</v>
@@ -18746,19 +18746,19 @@
         <v>1.35</v>
       </c>
       <c r="T113">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="U113">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="V113">
         <v>1.4</v>
       </c>
       <c r="W113">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y113">
         <v>1.27</v>
@@ -18785,7 +18785,7 @@
         <v>1.67</v>
       </c>
       <c r="AG113">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="O114">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="P114">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Q114">
         <v>1.8</v>
@@ -18924,7 +18924,7 @@
         <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z114">
         <v>5</v>
@@ -18936,10 +18936,10 @@
         <v>2.27</v>
       </c>
       <c r="AC114">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AD114">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE114">
         <v>1.19</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O115">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P115">
-        <v>7.15</v>
+        <v>6</v>
       </c>
       <c r="Q115">
         <v>1.86</v>
@@ -19127,7 +19127,7 @@
         <v>1.11</v>
       </c>
       <c r="AK115">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19220,13 +19220,13 @@
         <v>1.8</v>
       </c>
       <c r="O116">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P116">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q116">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="R116">
         <v>2.28</v>
@@ -19235,7 +19235,7 @@
         <v>1.25</v>
       </c>
       <c r="T116">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U116">
         <v>2.29</v>
@@ -19247,28 +19247,28 @@
         <v>1.12</v>
       </c>
       <c r="X116">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
         <v>1.2</v>
       </c>
       <c r="Z116">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AA116">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB116">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC116">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AD116">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AE116">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF116">
         <v>1.55</v>
@@ -20557,19 +20557,19 @@
         <v>1.17</v>
       </c>
       <c r="Z124">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA124">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB124">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AC124">
         <v>2.72</v>
       </c>
       <c r="AD124">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE124">
         <v>1.17</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q126">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="R126">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="S126">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T126">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U126">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="V126">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W126">
         <v>1.03</v>
       </c>
       <c r="X126">
+        <v>1.04</v>
+      </c>
+      <c r="Y126">
+        <v>1.35</v>
+      </c>
+      <c r="Z126">
+        <v>2.74</v>
+      </c>
+      <c r="AA126">
+        <v>2.14</v>
+      </c>
+      <c r="AB126">
+        <v>1.64</v>
+      </c>
+      <c r="AC126">
+        <v>3.74</v>
+      </c>
+      <c r="AD126">
+        <v>1.19</v>
+      </c>
+      <c r="AE126">
         <v>1.03</v>
       </c>
-      <c r="Y126">
-        <v>1.34</v>
-      </c>
-      <c r="Z126">
-        <v>3.11</v>
-      </c>
-      <c r="AA126">
-        <v>2.04</v>
-      </c>
-      <c r="AB126">
-        <v>1.68</v>
-      </c>
-      <c r="AC126">
-        <v>3.48</v>
-      </c>
-      <c r="AD126">
-        <v>1.22</v>
-      </c>
-      <c r="AE126">
-        <v>1.05</v>
-      </c>
       <c r="AF126">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG126">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>1.28</v>
       </c>
       <c r="AK126">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21013,7 +21013,7 @@
         <v>3.19</v>
       </c>
       <c r="O127">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="P127">
         <v>2.2</v>
@@ -21022,7 +21022,7 @@
         <v>3.84</v>
       </c>
       <c r="R127">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S127">
         <v>1.42</v>
@@ -21043,13 +21043,13 @@
         <v>1.04</v>
       </c>
       <c r="Y127">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z127">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="AA127">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB127">
         <v>1.78</v>
@@ -22160,7 +22160,7 @@
         <v>1.76</v>
       </c>
       <c r="Q134">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="R134">
         <v>2.29</v>
@@ -22205,7 +22205,7 @@
         <v>1.15</v>
       </c>
       <c r="AF134">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG134">
         <v>2.3</v>
@@ -22806,7 +22806,7 @@
         <v>5.25</v>
       </c>
       <c r="O138">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="P138">
         <v>1.53</v>
@@ -22839,7 +22839,7 @@
         <v>1.21</v>
       </c>
       <c r="Z138">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA138">
         <v>1.8</v>
@@ -22969,25 +22969,25 @@
         <v>4.2</v>
       </c>
       <c r="O139">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P139">
         <v>1.72</v>
       </c>
       <c r="Q139">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R139">
         <v>2.15</v>
       </c>
       <c r="S139">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T139">
         <v>2.73</v>
       </c>
       <c r="U139">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V139">
         <v>1.4</v>
@@ -23005,13 +23005,13 @@
         <v>3.14</v>
       </c>
       <c r="AA139">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB139">
         <v>1.85</v>
       </c>
       <c r="AC139">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="AD139">
         <v>1.27</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q150">
         <v>2.64</v>
@@ -24832,7 +24832,7 @@
         <v>1.25</v>
       </c>
       <c r="AK150">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -25411,19 +25411,19 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="O154">
         <v>3.1</v>
       </c>
       <c r="P154">
-        <v>3.06</v>
+        <v>2.93</v>
       </c>
       <c r="Q154">
         <v>2.95</v>
       </c>
       <c r="R154">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S154">
         <v>1.44</v>
@@ -25447,7 +25447,7 @@
         <v>1.4</v>
       </c>
       <c r="Z154">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="AA154">
         <v>2.38</v>
@@ -25456,19 +25456,19 @@
         <v>1.62</v>
       </c>
       <c r="AC154">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AD154">
         <v>1.2</v>
       </c>
       <c r="AE154">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF154">
         <v>1.94</v>
       </c>
       <c r="AG154">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O155">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P155">
-        <v>4.9</v>
+        <v>4.05</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O156">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P156">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q156">
         <v>3.9</v>
@@ -25773,13 +25773,13 @@
         <v>1.43</v>
       </c>
       <c r="Z156">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AA156">
         <v>2.21</v>
       </c>
       <c r="AB156">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC156">
         <v>4.25</v>
@@ -25906,7 +25906,7 @@
         <v>3.3</v>
       </c>
       <c r="P157">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -25918,7 +25918,7 @@
         <v>1.44</v>
       </c>
       <c r="T157">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="U157">
         <v>2.85</v>
@@ -25930,7 +25930,7 @@
         <v>1.03</v>
       </c>
       <c r="X157">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y157">
         <v>1.28</v>
@@ -25939,16 +25939,16 @@
         <v>3.1</v>
       </c>
       <c r="AA157">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AB157">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC157">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="AD157">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE157">
         <v>1.05</v>
@@ -25973,7 +25973,7 @@
         <v>1.29</v>
       </c>
       <c r="AK157">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
+        <v>2.35</v>
+      </c>
+      <c r="O163">
+        <v>3</v>
+      </c>
+      <c r="P163">
+        <v>2.75</v>
+      </c>
+      <c r="Q163">
+        <v>3.2</v>
+      </c>
+      <c r="R163">
+        <v>1.95</v>
+      </c>
+      <c r="S163">
+        <v>1.48</v>
+      </c>
+      <c r="T163">
+        <v>2.5</v>
+      </c>
+      <c r="U163">
+        <v>3.2</v>
+      </c>
+      <c r="V163">
+        <v>1.29</v>
+      </c>
+      <c r="W163">
+        <v>1.05</v>
+      </c>
+      <c r="X163">
+        <v>1.09</v>
+      </c>
+      <c r="Y163">
         <v>1.42</v>
       </c>
-      <c r="O163">
-        <v>4.78</v>
-      </c>
-      <c r="P163">
-        <v>5.56</v>
-      </c>
-      <c r="Q163">
-        <v>1.85</v>
-      </c>
-      <c r="R163">
-        <v>2.46</v>
-      </c>
-      <c r="S163">
-        <v>1.3</v>
-      </c>
-      <c r="T163">
-        <v>3.25</v>
-      </c>
-      <c r="U163">
-        <v>2.45</v>
-      </c>
-      <c r="V163">
-        <v>1.5</v>
-      </c>
-      <c r="W163">
-        <v>1.1</v>
-      </c>
-      <c r="X163">
-        <v>1.02</v>
-      </c>
-      <c r="Y163">
-        <v>1.23</v>
-      </c>
       <c r="Z163">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA163">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="AB163">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="AC163">
-        <v>2.63</v>
+        <v>4.4</v>
       </c>
       <c r="AD163">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AE163">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF163">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG163">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AK163">
-        <v>2.83</v>
+        <v>1.48</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="O164">
-        <v>3</v>
+        <v>4.78</v>
       </c>
       <c r="P164">
-        <v>2.75</v>
+        <v>5.56</v>
       </c>
       <c r="Q164">
-        <v>3.24</v>
+        <v>1.85</v>
       </c>
       <c r="R164">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="S164">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T164">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U164">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="V164">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W164">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X164">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y164">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="Z164">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AA164">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="AB164">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="AC164">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD164">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE164">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AF164">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG164">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK164">
-        <v>1.56</v>
+        <v>2.83</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -28188,10 +28188,10 @@
         <v>3</v>
       </c>
       <c r="P171">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="Q171">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="R171">
         <v>1.95</v>
@@ -28212,25 +28212,25 @@
         <v>1.05</v>
       </c>
       <c r="X171">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y171">
         <v>1.4</v>
       </c>
       <c r="Z171">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AA171">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="AB171">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC171">
         <v>4.75</v>
       </c>
       <c r="AD171">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE171">
         <v>1.05</v>
@@ -28671,19 +28671,19 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O174">
         <v>3.05</v>
       </c>
       <c r="P174">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q174">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="R174">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S174">
         <v>1.48</v>
@@ -28713,7 +28713,7 @@
         <v>2.29</v>
       </c>
       <c r="AB174">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC174">
         <v>4.2</v>
@@ -28834,49 +28834,49 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="O175">
+        <v>3.8</v>
+      </c>
+      <c r="P175">
         <v>4</v>
       </c>
-      <c r="P175">
-        <v>4.2</v>
-      </c>
       <c r="Q175">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="R175">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S175">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T175">
         <v>3.3</v>
       </c>
       <c r="U175">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="V175">
         <v>1.51</v>
       </c>
       <c r="W175">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X175">
         <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z175">
-        <v>4.46</v>
+        <v>4.33</v>
       </c>
       <c r="AA175">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB175">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC175">
         <v>2.62</v>
@@ -28885,13 +28885,13 @@
         <v>1.47</v>
       </c>
       <c r="AE175">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF175">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG175">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK175">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29323,7 +29323,7 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O178">
         <v>3.25</v>
@@ -29335,7 +29335,7 @@
         <v>2.88</v>
       </c>
       <c r="R178">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="S178">
         <v>1.33</v>
@@ -29356,7 +29356,7 @@
         <v>1.04</v>
       </c>
       <c r="Y178">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z178">
         <v>3.45</v>
@@ -29377,10 +29377,10 @@
         <v>1.11</v>
       </c>
       <c r="AF178">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG178">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>1.27</v>
       </c>
       <c r="AK178">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="O179">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P179">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29815,13 +29815,13 @@
         <v>2.42</v>
       </c>
       <c r="O181">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="P181">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Q181">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R181">
         <v>1.95</v>
@@ -29842,22 +29842,22 @@
         <v>1.03</v>
       </c>
       <c r="X181">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y181">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Z181">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AA181">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AB181">
         <v>1.56</v>
       </c>
       <c r="AC181">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD181">
         <v>1.17</v>
@@ -29885,7 +29885,7 @@
         <v>1.33</v>
       </c>
       <c r="AK181">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="O182">
-        <v>8.15</v>
+        <v>4.33</v>
       </c>
       <c r="P182">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="Q182">
         <v>1.5</v>
@@ -32257,19 +32257,19 @@
         </is>
       </c>
       <c r="N196">
-        <v>5</v>
+        <v>5.55</v>
       </c>
       <c r="O196">
         <v>4</v>
       </c>
       <c r="P196">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q196">
-        <v>5.99</v>
+        <v>5.75</v>
       </c>
       <c r="R196">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S196">
         <v>1.34</v>
@@ -32327,7 +32327,7 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK196">
         <v>1.13</v>
@@ -32432,7 +32432,7 @@
         <v>3.3</v>
       </c>
       <c r="R197">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S197">
         <v>1.27</v>
@@ -32441,10 +32441,10 @@
         <v>3.35</v>
       </c>
       <c r="U197">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V197">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W197">
         <v>1.11</v>
@@ -32456,10 +32456,10 @@
         <v>1.17</v>
       </c>
       <c r="Z197">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA197">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB197">
         <v>2.15</v>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK197">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32616,16 +32616,16 @@
         <v>1.01</v>
       </c>
       <c r="Y198">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z198">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AA198">
         <v>1.88</v>
       </c>
       <c r="AB198">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AC198">
         <v>2.97</v>
@@ -32640,7 +32640,7 @@
         <v>1.98</v>
       </c>
       <c r="AG198">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         </is>
       </c>
       <c r="N199">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="O199">
         <v>4.33</v>
@@ -32755,7 +32755,7 @@
         <v>1.6</v>
       </c>
       <c r="Q199">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="R199">
         <v>2.35</v>
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O200">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="P200">
-        <v>4.6</v>
+        <v>4.88</v>
       </c>
       <c r="Q200">
         <v>2.06</v>
@@ -32957,10 +32957,10 @@
         <v>2.88</v>
       </c>
       <c r="AD200">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE200">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF200">
         <v>1.72</v>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK200">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="O206">
         <v>3.25</v>
       </c>
       <c r="P206">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q206">
         <v>2.62</v>
@@ -34056,7 +34056,7 @@
         <v>3.6</v>
       </c>
       <c r="P207">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q207">
         <v>2.72</v>
@@ -34083,7 +34083,7 @@
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z207">
         <v>4.75</v>
@@ -34225,22 +34225,22 @@
         <v>7.1</v>
       </c>
       <c r="R208">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S208">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T208">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="U208">
         <v>2.75</v>
       </c>
       <c r="V208">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W208">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X208">
         <v>1.04</v>
@@ -34249,10 +34249,10 @@
         <v>1.29</v>
       </c>
       <c r="Z208">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="AA208">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB208">
         <v>1.89</v>
@@ -34376,19 +34376,19 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="O209">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P209">
         <v>4</v>
       </c>
       <c r="Q209">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R209">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S209">
         <v>1.49</v>
@@ -34415,10 +34415,10 @@
         <v>2.88</v>
       </c>
       <c r="AA209">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AB209">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC209">
         <v>4.5</v>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK209">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34542,16 +34542,16 @@
         <v>1.8</v>
       </c>
       <c r="O210">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P210">
-        <v>4.52</v>
+        <v>4</v>
       </c>
       <c r="Q210">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R210">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="S210">
         <v>1.4</v>
@@ -34575,7 +34575,7 @@
         <v>1.35</v>
       </c>
       <c r="Z210">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AA210">
         <v>2.19</v>
@@ -34584,13 +34584,13 @@
         <v>1.62</v>
       </c>
       <c r="AC210">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AD210">
         <v>1.19</v>
       </c>
       <c r="AE210">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF210">
         <v>1.99</v>
@@ -34717,7 +34717,7 @@
         <v>2</v>
       </c>
       <c r="S211">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T211">
         <v>2.4</v>
@@ -34732,13 +34732,13 @@
         <v>1.02</v>
       </c>
       <c r="X211">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y211">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z211">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AA211">
         <v>2.23</v>
@@ -34750,7 +34750,7 @@
         <v>3.88</v>
       </c>
       <c r="AD211">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE211">
         <v>1.03</v>
@@ -35034,25 +35034,25 @@
         <v>3.1</v>
       </c>
       <c r="P213">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q213">
-        <v>3.88</v>
+        <v>4.18</v>
       </c>
       <c r="R213">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="S213">
         <v>1.46</v>
       </c>
       <c r="T213">
-        <v>2.58</v>
+        <v>2.41</v>
       </c>
       <c r="U213">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="V213">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W213">
         <v>1.02</v>
@@ -35061,16 +35061,16 @@
         <v>1.03</v>
       </c>
       <c r="Y213">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z213">
-        <v>2.91</v>
+        <v>2.74</v>
       </c>
       <c r="AA213">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB213">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC213">
         <v>3.84</v>
@@ -35085,7 +35085,7 @@
         <v>1.85</v>
       </c>
       <c r="AG213">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AK213">
         <v>1.26</v>
@@ -35191,31 +35191,31 @@
         </is>
       </c>
       <c r="N214">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O214">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P214">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q214">
-        <v>4.05</v>
+        <v>4.24</v>
       </c>
       <c r="R214">
         <v>1.95</v>
       </c>
       <c r="S214">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T214">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="U214">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="V214">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W214">
         <v>1.01</v>
@@ -35224,16 +35224,16 @@
         <v>1.03</v>
       </c>
       <c r="Y214">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z214">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AA214">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AB214">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC214">
         <v>4.4</v>
@@ -35245,10 +35245,10 @@
         <v>1.01</v>
       </c>
       <c r="AF214">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AG214">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.59</v>
+        <v>1.27</v>
       </c>
       <c r="AK214">
         <v>1.26</v>
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O216">
-        <v>4.88</v>
+        <v>4.84</v>
       </c>
       <c r="P216">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q216">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R216">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="S216">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T216">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U216">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V216">
         <v>1.54</v>
       </c>
       <c r="W216">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X216">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y216">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z216">
-        <v>4.4</v>
+        <v>4.56</v>
       </c>
       <c r="AA216">
         <v>1.6</v>
       </c>
       <c r="AB216">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC216">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD216">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AE216">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF216">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AG216">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         </is>
       </c>
       <c r="N217">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="O217">
         <v>3.4</v>
@@ -35689,13 +35689,13 @@
         <v>4.33</v>
       </c>
       <c r="Q217">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="R217">
         <v>2</v>
       </c>
       <c r="S217">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T217">
         <v>2.69</v>
@@ -35704,7 +35704,7 @@
         <v>3.2</v>
       </c>
       <c r="V217">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W217">
         <v>1.01</v>
@@ -35713,10 +35713,10 @@
         <v>1.05</v>
       </c>
       <c r="Y217">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z217">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA217">
         <v>2.12</v>
@@ -35731,10 +35731,10 @@
         <v>1.24</v>
       </c>
       <c r="AE217">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF217">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG217">
         <v>1.78</v>
@@ -35753,7 +35753,7 @@
         <v>1.3</v>
       </c>
       <c r="AK217">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -37319,7 +37319,7 @@
         <v>3.83</v>
       </c>
       <c r="Q227">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R227">
         <v>2.2</v>
@@ -37361,7 +37361,7 @@
         <v>1.36</v>
       </c>
       <c r="AE227">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF227">
         <v>1.7</v>
@@ -37546,7 +37546,7 @@
         <v>1.29</v>
       </c>
       <c r="AK228">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37639,16 +37639,16 @@
         <v>2.15</v>
       </c>
       <c r="O229">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P229">
         <v>3.3</v>
       </c>
       <c r="Q229">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="R229">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="S229">
         <v>1.44</v>
@@ -37669,13 +37669,13 @@
         <v>1.03</v>
       </c>
       <c r="Y229">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z229">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AA229">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AB229">
         <v>1.61</v>
@@ -37687,7 +37687,7 @@
         <v>1.18</v>
       </c>
       <c r="AE229">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF229">
         <v>1.95</v>
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>1.07</v>
+        <v>1.89</v>
       </c>
       <c r="O232">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="P232">
-        <v>8.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="O236">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="P236">
-        <v>6.03</v>
+        <v>5.75</v>
       </c>
       <c r="Q236">
         <v>0</v>
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="O237">
         <v>3.25</v>
       </c>
       <c r="P237">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q237">
         <v>3.9</v>
@@ -38961,10 +38961,10 @@
         <v>2.65</v>
       </c>
       <c r="U237">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="V237">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W237">
         <v>1.05</v>
@@ -38973,31 +38973,31 @@
         <v>1.06</v>
       </c>
       <c r="Y237">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z237">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA237">
         <v>1.99</v>
       </c>
       <c r="AB237">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC237">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="AD237">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE237">
         <v>1.1</v>
       </c>
       <c r="AF237">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AG237">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>1.3</v>
       </c>
       <c r="AK237">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39918,10 +39918,10 @@
         </is>
       </c>
       <c r="N243">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O243">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="P243">
         <v>4</v>
@@ -39942,7 +39942,7 @@
         <v>2.56</v>
       </c>
       <c r="V243">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W243">
         <v>1.06</v>
@@ -39954,22 +39954,22 @@
         <v>1.25</v>
       </c>
       <c r="Z243">
-        <v>3.59</v>
+        <v>3.85</v>
       </c>
       <c r="AA243">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AB243">
         <v>1.95</v>
       </c>
       <c r="AC243">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AD243">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE243">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF243">
         <v>1.73</v>
@@ -39991,7 +39991,7 @@
         <v>1.22</v>
       </c>
       <c r="AK243">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40407,46 +40407,46 @@
         </is>
       </c>
       <c r="N246">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="O246">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P246">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="Q246">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="R246">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="S246">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T246">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="U246">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="V246">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W246">
         <v>1.15</v>
       </c>
       <c r="X246">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y246">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z246">
-        <v>4.74</v>
+        <v>4.8</v>
       </c>
       <c r="AA246">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB246">
         <v>2.21</v>
@@ -40458,7 +40458,7 @@
         <v>1.5</v>
       </c>
       <c r="AE246">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF246">
         <v>1.5</v>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK246">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL246">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="O9">
-        <v>4.95</v>
+        <v>3.8</v>
       </c>
       <c r="P9">
-        <v>7.9</v>
+        <v>4.85</v>
       </c>
       <c r="Q9">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="R9">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U9">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="V9">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="AA9">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC9">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AD9">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK9">
-        <v>2.65</v>
+        <v>2.27</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="O10">
-        <v>3.8</v>
+        <v>4.95</v>
       </c>
       <c r="P10">
-        <v>4.85</v>
+        <v>7.9</v>
       </c>
       <c r="Q10">
+        <v>1.67</v>
+      </c>
+      <c r="R10">
+        <v>2.41</v>
+      </c>
+      <c r="S10">
+        <v>1.3</v>
+      </c>
+      <c r="T10">
+        <v>3.25</v>
+      </c>
+      <c r="U10">
+        <v>2.41</v>
+      </c>
+      <c r="V10">
+        <v>1.46</v>
+      </c>
+      <c r="W10">
+        <v>1.11</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.18</v>
+      </c>
+      <c r="Z10">
+        <v>3.84</v>
+      </c>
+      <c r="AA10">
+        <v>1.7</v>
+      </c>
+      <c r="AB10">
         <v>2.1</v>
       </c>
-      <c r="R10">
-        <v>2.3</v>
-      </c>
-      <c r="S10">
-        <v>1.34</v>
-      </c>
-      <c r="T10">
-        <v>3.1</v>
-      </c>
-      <c r="U10">
-        <v>2.6</v>
-      </c>
-      <c r="V10">
-        <v>1.4</v>
-      </c>
-      <c r="W10">
-        <v>1.1</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.2</v>
-      </c>
-      <c r="Z10">
-        <v>3.75</v>
-      </c>
-      <c r="AA10">
-        <v>1.8</v>
-      </c>
-      <c r="AB10">
-        <v>1.93</v>
-      </c>
       <c r="AC10">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="AD10">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="AG10">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK10">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q21">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="R21">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="S21">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="U21">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
         <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="Z21">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="AA21">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="AB21">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AC21">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD21">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AE21">
         <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AG21">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="O22">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P22">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q22">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="R22">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="S22">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T22">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U22">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="V22">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W22">
         <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="Z22">
-        <v>3.15</v>
+        <v>2.46</v>
       </c>
       <c r="AA22">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="AB22">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AC22">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD22">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE22">
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AG22">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="O75">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P75">
-        <v>4.53</v>
+        <v>3</v>
       </c>
       <c r="Q75">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="R75">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="S75">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="T75">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="U75">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="V75">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="W75">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Z75">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA75">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AB75">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="AC75">
-        <v>1.79</v>
+        <v>2.21</v>
       </c>
       <c r="AD75">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="AE75">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AF75">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AG75">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>2.22</v>
+        <v>1.72</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="O76">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P76">
+        <v>4.53</v>
+      </c>
+      <c r="Q76">
+        <v>2.05</v>
+      </c>
+      <c r="R76">
+        <v>2.55</v>
+      </c>
+      <c r="S76">
+        <v>1.16</v>
+      </c>
+      <c r="T76">
+        <v>4.3</v>
+      </c>
+      <c r="U76">
+        <v>1.86</v>
+      </c>
+      <c r="V76">
+        <v>1.85</v>
+      </c>
+      <c r="W76">
+        <v>1.22</v>
+      </c>
+      <c r="X76">
+        <v>1.01</v>
+      </c>
+      <c r="Y76">
+        <v>1.04</v>
+      </c>
+      <c r="Z76">
+        <v>7.1</v>
+      </c>
+      <c r="AA76">
+        <v>1.32</v>
+      </c>
+      <c r="AB76">
         <v>3</v>
       </c>
-      <c r="Q76">
-        <v>2.37</v>
-      </c>
-      <c r="R76">
-        <v>2.33</v>
-      </c>
-      <c r="S76">
-        <v>1.24</v>
-      </c>
-      <c r="T76">
-        <v>3.5</v>
-      </c>
-      <c r="U76">
-        <v>2.1</v>
-      </c>
-      <c r="V76">
-        <v>1.6</v>
-      </c>
-      <c r="W76">
-        <v>1.15</v>
-      </c>
-      <c r="X76">
-        <v>1.02</v>
-      </c>
-      <c r="Y76">
-        <v>1.11</v>
-      </c>
-      <c r="Z76">
-        <v>4.9</v>
-      </c>
-      <c r="AA76">
-        <v>1.45</v>
-      </c>
-      <c r="AB76">
-        <v>2.42</v>
-      </c>
       <c r="AC76">
-        <v>2.21</v>
+        <v>1.79</v>
       </c>
       <c r="AD76">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="AE76">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AF76">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AG76">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK76">
-        <v>1.72</v>
+        <v>2.22</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="O163">
-        <v>3</v>
+        <v>4.78</v>
       </c>
       <c r="P163">
-        <v>2.75</v>
+        <v>5.56</v>
       </c>
       <c r="Q163">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="R163">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="S163">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="T163">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="U163">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="V163">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="W163">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X163">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y163">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="Z163">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AA163">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="AB163">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="AC163">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="AD163">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE163">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AF163">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG163">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AK163">
-        <v>1.48</v>
+        <v>2.83</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
+        <v>2.35</v>
+      </c>
+      <c r="O164">
+        <v>3</v>
+      </c>
+      <c r="P164">
+        <v>2.75</v>
+      </c>
+      <c r="Q164">
+        <v>3.2</v>
+      </c>
+      <c r="R164">
+        <v>1.95</v>
+      </c>
+      <c r="S164">
+        <v>1.48</v>
+      </c>
+      <c r="T164">
+        <v>2.5</v>
+      </c>
+      <c r="U164">
+        <v>3.2</v>
+      </c>
+      <c r="V164">
+        <v>1.29</v>
+      </c>
+      <c r="W164">
+        <v>1.05</v>
+      </c>
+      <c r="X164">
+        <v>1.09</v>
+      </c>
+      <c r="Y164">
         <v>1.42</v>
       </c>
-      <c r="O164">
-        <v>4.78</v>
-      </c>
-      <c r="P164">
-        <v>5.56</v>
-      </c>
-      <c r="Q164">
-        <v>1.85</v>
-      </c>
-      <c r="R164">
-        <v>2.38</v>
-      </c>
-      <c r="S164">
-        <v>1.3</v>
-      </c>
-      <c r="T164">
-        <v>3.25</v>
-      </c>
-      <c r="U164">
-        <v>2.45</v>
-      </c>
-      <c r="V164">
-        <v>1.5</v>
-      </c>
-      <c r="W164">
-        <v>1.12</v>
-      </c>
-      <c r="X164">
-        <v>1.02</v>
-      </c>
-      <c r="Y164">
-        <v>1.23</v>
-      </c>
       <c r="Z164">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA164">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="AB164">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="AC164">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="AD164">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE164">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF164">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG164">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AK164">
-        <v>2.83</v>
+        <v>1.48</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="O189">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P189">
-        <v>6.1</v>
+        <v>5.25</v>
       </c>
       <c r="Q189">
         <v>2</v>
@@ -31173,7 +31173,7 @@
         <v>1.95</v>
       </c>
       <c r="AG189">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -35843,64 +35843,64 @@
         </is>
       </c>
       <c r="N218">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="O218">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="P218">
         <v>1.75</v>
       </c>
       <c r="Q218">
-        <v>5.03</v>
+        <v>3.93</v>
       </c>
       <c r="R218">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="S218">
         <v>1.35</v>
       </c>
       <c r="T218">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="U218">
         <v>2.78</v>
       </c>
       <c r="V218">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W218">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X218">
         <v>1</v>
       </c>
       <c r="Y218">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z218">
-        <v>3.62</v>
+        <v>3.42</v>
       </c>
       <c r="AA218">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AB218">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC218">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AD218">
         <v>1.28</v>
       </c>
       <c r="AE218">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF218">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG218">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.91</v>
+        <v>1.21</v>
       </c>
       <c r="AK218">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O224">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P224">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q224">
         <v>3.3</v>
@@ -36851,7 +36851,7 @@
         <v>1.05</v>
       </c>
       <c r="X224">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y224">
         <v>1.4</v>
@@ -36863,22 +36863,22 @@
         <v>2.28</v>
       </c>
       <c r="AB224">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC224">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AD224">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE224">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF224">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG224">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36996,16 +36996,16 @@
         <v>1.53</v>
       </c>
       <c r="R225">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="S225">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T225">
         <v>3.2</v>
       </c>
       <c r="U225">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V225">
         <v>1.48</v>
@@ -37020,28 +37020,28 @@
         <v>1.17</v>
       </c>
       <c r="Z225">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="AA225">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB225">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AC225">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AD225">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE225">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF225">
         <v>2.45</v>
       </c>
       <c r="AG225">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37986,19 +37986,19 @@
         <v>3.32</v>
       </c>
       <c r="V231">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W231">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X231">
         <v>1.04</v>
       </c>
       <c r="Y231">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z231">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="AA231">
         <v>2.4</v>
@@ -38007,10 +38007,10 @@
         <v>1.55</v>
       </c>
       <c r="AC231">
-        <v>4.5</v>
+        <v>4.34</v>
       </c>
       <c r="AD231">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE231">
         <v>1.05</v>
@@ -38463,22 +38463,22 @@
         <v>3</v>
       </c>
       <c r="R234">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="S234">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T234">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="U234">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V234">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W234">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X234">
         <v>1.05</v>
@@ -38496,19 +38496,19 @@
         <v>1.58</v>
       </c>
       <c r="AC234">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AD234">
         <v>1.17</v>
       </c>
       <c r="AE234">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF234">
         <v>1.93</v>
       </c>
       <c r="AG234">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>1.39</v>
       </c>
       <c r="AK234">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -39103,25 +39103,25 @@
         </is>
       </c>
       <c r="N238">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O238">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P238">
-        <v>6.29</v>
+        <v>6.2</v>
       </c>
       <c r="Q238">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="R238">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="S238">
         <v>1.29</v>
       </c>
       <c r="T238">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="U238">
         <v>2.56</v>
@@ -39133,25 +39133,25 @@
         <v>1.1</v>
       </c>
       <c r="X238">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y238">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z238">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA238">
         <v>1.72</v>
       </c>
       <c r="AB238">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AC238">
         <v>2.66</v>
       </c>
       <c r="AD238">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AE238">
         <v>1.16</v>
@@ -39429,19 +39429,19 @@
         </is>
       </c>
       <c r="N240">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O240">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P240">
         <v>3.5</v>
       </c>
       <c r="Q240">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R240">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="S240">
         <v>1.46</v>
@@ -39502,7 +39502,7 @@
         <v>1.22</v>
       </c>
       <c r="AK240">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O244">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P244">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="Q244">
         <v>2.41</v>
@@ -40105,7 +40105,7 @@
         <v>3.32</v>
       </c>
       <c r="V244">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W244">
         <v>1.05</v>
@@ -40114,31 +40114,31 @@
         <v>1.08</v>
       </c>
       <c r="Y244">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z244">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AA244">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB244">
         <v>1.55</v>
       </c>
       <c r="AC244">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD244">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE244">
         <v>1.01</v>
       </c>
       <c r="AF244">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AG244">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>1.31</v>
       </c>
       <c r="AK244">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="O247">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P247">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="Q247">
         <v>2.02</v>
@@ -40588,25 +40588,25 @@
         <v>1.3</v>
       </c>
       <c r="T247">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U247">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="V247">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W247">
         <v>1.11</v>
       </c>
       <c r="X247">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y247">
         <v>1.18</v>
       </c>
       <c r="Z247">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA247">
         <v>1.73</v>
@@ -40615,7 +40615,7 @@
         <v>2.1</v>
       </c>
       <c r="AC247">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD247">
         <v>1.43</v>
@@ -40627,7 +40627,7 @@
         <v>1.73</v>
       </c>
       <c r="AG247">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK247">
         <v>2.3</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="O9">
-        <v>3.8</v>
+        <v>4.95</v>
       </c>
       <c r="P9">
-        <v>4.85</v>
+        <v>7.9</v>
       </c>
       <c r="Q9">
+        <v>1.67</v>
+      </c>
+      <c r="R9">
+        <v>2.41</v>
+      </c>
+      <c r="S9">
+        <v>1.3</v>
+      </c>
+      <c r="T9">
+        <v>3.25</v>
+      </c>
+      <c r="U9">
+        <v>2.41</v>
+      </c>
+      <c r="V9">
+        <v>1.46</v>
+      </c>
+      <c r="W9">
+        <v>1.11</v>
+      </c>
+      <c r="X9">
+        <v>1.02</v>
+      </c>
+      <c r="Y9">
+        <v>1.18</v>
+      </c>
+      <c r="Z9">
+        <v>3.84</v>
+      </c>
+      <c r="AA9">
+        <v>1.7</v>
+      </c>
+      <c r="AB9">
         <v>2.1</v>
       </c>
-      <c r="R9">
-        <v>2.3</v>
-      </c>
-      <c r="S9">
-        <v>1.34</v>
-      </c>
-      <c r="T9">
-        <v>3.1</v>
-      </c>
-      <c r="U9">
-        <v>2.6</v>
-      </c>
-      <c r="V9">
-        <v>1.4</v>
-      </c>
-      <c r="W9">
-        <v>1.1</v>
-      </c>
-      <c r="X9">
-        <v>1.03</v>
-      </c>
-      <c r="Y9">
-        <v>1.2</v>
-      </c>
-      <c r="Z9">
-        <v>3.75</v>
-      </c>
-      <c r="AA9">
-        <v>1.8</v>
-      </c>
-      <c r="AB9">
-        <v>1.93</v>
-      </c>
       <c r="AC9">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="AD9">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE9">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="AG9">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK9">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="O10">
-        <v>4.95</v>
+        <v>3.8</v>
       </c>
       <c r="P10">
-        <v>7.9</v>
+        <v>4.85</v>
       </c>
       <c r="Q10">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T10">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U10">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="AA10">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC10">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AD10">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE10">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK10">
-        <v>2.65</v>
+        <v>2.27</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="Q20">
-        <v>3.68</v>
+        <v>3.55</v>
       </c>
       <c r="R20">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="S20">
         <v>1.4</v>
       </c>
       <c r="T20">
+        <v>2.75</v>
+      </c>
+      <c r="U20">
         <v>2.88</v>
       </c>
-      <c r="U20">
-        <v>2.84</v>
-      </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z20">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="AA20">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB20">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AC20">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD20">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG20">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="P21">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="Q21">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="R21">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="S21">
         <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U21">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z21">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AA21">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AB21">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AC21">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD21">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE21">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG21">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="O58">
         <v>3.4</v>
       </c>
       <c r="P58">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q58">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R58">
         <v>2.25</v>
@@ -9808,13 +9808,13 @@
         <v>2.08</v>
       </c>
       <c r="AC58">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AD58">
         <v>1.31</v>
       </c>
       <c r="AE58">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF58">
         <v>1.62</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
         <v>1.86</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="O75">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P75">
+        <v>4.53</v>
+      </c>
+      <c r="Q75">
+        <v>2.05</v>
+      </c>
+      <c r="R75">
+        <v>2.55</v>
+      </c>
+      <c r="S75">
+        <v>1.16</v>
+      </c>
+      <c r="T75">
+        <v>4.3</v>
+      </c>
+      <c r="U75">
+        <v>1.86</v>
+      </c>
+      <c r="V75">
+        <v>1.85</v>
+      </c>
+      <c r="W75">
+        <v>1.22</v>
+      </c>
+      <c r="X75">
+        <v>1.01</v>
+      </c>
+      <c r="Y75">
+        <v>1.04</v>
+      </c>
+      <c r="Z75">
+        <v>7.1</v>
+      </c>
+      <c r="AA75">
+        <v>1.32</v>
+      </c>
+      <c r="AB75">
         <v>3</v>
       </c>
-      <c r="Q75">
-        <v>2.37</v>
-      </c>
-      <c r="R75">
-        <v>2.33</v>
-      </c>
-      <c r="S75">
-        <v>1.24</v>
-      </c>
-      <c r="T75">
-        <v>3.5</v>
-      </c>
-      <c r="U75">
-        <v>2.1</v>
-      </c>
-      <c r="V75">
-        <v>1.6</v>
-      </c>
-      <c r="W75">
-        <v>1.15</v>
-      </c>
-      <c r="X75">
-        <v>1.02</v>
-      </c>
-      <c r="Y75">
-        <v>1.11</v>
-      </c>
-      <c r="Z75">
-        <v>4.9</v>
-      </c>
-      <c r="AA75">
-        <v>1.45</v>
-      </c>
-      <c r="AB75">
-        <v>2.42</v>
-      </c>
       <c r="AC75">
-        <v>2.21</v>
+        <v>1.79</v>
       </c>
       <c r="AD75">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="AE75">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AF75">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AG75">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK75">
-        <v>1.72</v>
+        <v>2.22</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="O76">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P76">
-        <v>4.53</v>
+        <v>3</v>
       </c>
       <c r="Q76">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="R76">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="S76">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="T76">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="U76">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="V76">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="W76">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Z76">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA76">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AB76">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="AC76">
-        <v>1.79</v>
+        <v>2.21</v>
       </c>
       <c r="AD76">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="AE76">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AF76">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AG76">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>2.22</v>
+        <v>1.72</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -20853,55 +20853,55 @@
         <v>3.1</v>
       </c>
       <c r="P126">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="Q126">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="R126">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S126">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T126">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="U126">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="V126">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W126">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X126">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y126">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z126">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AA126">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AB126">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AC126">
-        <v>3.74</v>
+        <v>4.33</v>
       </c>
       <c r="AD126">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE126">
         <v>1.03</v>
       </c>
       <c r="AF126">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG126">
         <v>1.78</v>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK126">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -22480,19 +22480,19 @@
         <v>1.75</v>
       </c>
       <c r="O136">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P136">
         <v>3.9</v>
       </c>
       <c r="Q136">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="R136">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T136">
         <v>2.88</v>
@@ -22510,22 +22510,22 @@
         <v>1</v>
       </c>
       <c r="Y136">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z136">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA136">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB136">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC136">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="AD136">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE136">
         <v>1.08</v>
@@ -22534,7 +22534,7 @@
         <v>1.73</v>
       </c>
       <c r="AG136">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK136">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O141">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P141">
-        <v>2.82</v>
+        <v>3.48</v>
       </c>
       <c r="Q141">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R141">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S141">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T141">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="U141">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V141">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W141">
         <v>1.06</v>
       </c>
       <c r="X141">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y141">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z141">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA141">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AB141">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC141">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AD141">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE141">
         <v>1.03</v>
       </c>
       <c r="AF141">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG141">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AK141">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23455,19 +23455,19 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="O142">
         <v>3.05</v>
       </c>
       <c r="P142">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="Q142">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R142">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="S142">
         <v>1.52</v>
@@ -23488,16 +23488,16 @@
         <v>1.04</v>
       </c>
       <c r="Y142">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z142">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AA142">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AB142">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AC142">
         <v>4.35</v>
@@ -23512,7 +23512,7 @@
         <v>1.95</v>
       </c>
       <c r="AG142">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23621,10 +23621,10 @@
         <v>2.6</v>
       </c>
       <c r="O143">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P143">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q143">
         <v>3.42</v>
@@ -23633,10 +23633,10 @@
         <v>1.91</v>
       </c>
       <c r="S143">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T143">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U143">
         <v>3.15</v>
@@ -23645,7 +23645,7 @@
         <v>1.31</v>
       </c>
       <c r="W143">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X143">
         <v>1.03</v>
@@ -23657,13 +23657,13 @@
         <v>2.74</v>
       </c>
       <c r="AA143">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AB143">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC143">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AD143">
         <v>1.18</v>
@@ -23675,7 +23675,7 @@
         <v>1.84</v>
       </c>
       <c r="AG143">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23781,25 +23781,25 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O144">
         <v>2.8</v>
       </c>
       <c r="P144">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q144">
-        <v>2.53</v>
+        <v>2.68</v>
       </c>
       <c r="R144">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="S144">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="T144">
-        <v>2.57</v>
+        <v>2.24</v>
       </c>
       <c r="U144">
         <v>3.2</v>
@@ -23811,22 +23811,22 @@
         <v>1.01</v>
       </c>
       <c r="X144">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y144">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z144">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AA144">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AB144">
         <v>1.61</v>
       </c>
       <c r="AC144">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="AD144">
         <v>1.18</v>
@@ -23835,7 +23835,7 @@
         <v>1.02</v>
       </c>
       <c r="AF144">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG144">
         <v>1.75</v>
@@ -23854,7 +23854,7 @@
         <v>1.15</v>
       </c>
       <c r="AK144">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -25085,19 +25085,19 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="O152">
         <v>4.1</v>
       </c>
       <c r="P152">
-        <v>4.8</v>
+        <v>4.84</v>
       </c>
       <c r="Q152">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="R152">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="S152">
         <v>1.26</v>
@@ -25106,10 +25106,10 @@
         <v>3.28</v>
       </c>
       <c r="U152">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="V152">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W152">
         <v>1.11</v>
@@ -25118,25 +25118,25 @@
         <v>0</v>
       </c>
       <c r="Y152">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z152">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA152">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB152">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AC152">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AD152">
         <v>1.35</v>
       </c>
       <c r="AE152">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF152">
         <v>1.76</v>
@@ -25158,7 +25158,7 @@
         <v>1.2</v>
       </c>
       <c r="AK152">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25254,7 +25254,7 @@
         <v>3.95</v>
       </c>
       <c r="P153">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q153">
         <v>2.15</v>
@@ -25272,19 +25272,19 @@
         <v>2.31</v>
       </c>
       <c r="V153">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W153">
         <v>1.09</v>
       </c>
       <c r="X153">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y153">
         <v>1.18</v>
       </c>
       <c r="Z153">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="AA153">
         <v>1.63</v>
@@ -25293,16 +25293,16 @@
         <v>2.14</v>
       </c>
       <c r="AC153">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD153">
         <v>1.42</v>
       </c>
       <c r="AE153">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF153">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AG153">
         <v>2.04</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
+        <v>2.35</v>
+      </c>
+      <c r="O163">
+        <v>3</v>
+      </c>
+      <c r="P163">
+        <v>2.75</v>
+      </c>
+      <c r="Q163">
+        <v>3.2</v>
+      </c>
+      <c r="R163">
+        <v>1.95</v>
+      </c>
+      <c r="S163">
+        <v>1.48</v>
+      </c>
+      <c r="T163">
+        <v>2.5</v>
+      </c>
+      <c r="U163">
+        <v>3.2</v>
+      </c>
+      <c r="V163">
+        <v>1.29</v>
+      </c>
+      <c r="W163">
+        <v>1.05</v>
+      </c>
+      <c r="X163">
+        <v>1.09</v>
+      </c>
+      <c r="Y163">
         <v>1.42</v>
       </c>
-      <c r="O163">
-        <v>4.78</v>
-      </c>
-      <c r="P163">
-        <v>5.56</v>
-      </c>
-      <c r="Q163">
-        <v>1.85</v>
-      </c>
-      <c r="R163">
-        <v>2.38</v>
-      </c>
-      <c r="S163">
-        <v>1.3</v>
-      </c>
-      <c r="T163">
-        <v>3.25</v>
-      </c>
-      <c r="U163">
-        <v>2.45</v>
-      </c>
-      <c r="V163">
-        <v>1.5</v>
-      </c>
-      <c r="W163">
-        <v>1.12</v>
-      </c>
-      <c r="X163">
-        <v>1.02</v>
-      </c>
-      <c r="Y163">
-        <v>1.23</v>
-      </c>
       <c r="Z163">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA163">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="AB163">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="AC163">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="AD163">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE163">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF163">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG163">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AK163">
-        <v>2.83</v>
+        <v>1.48</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="O164">
-        <v>3</v>
+        <v>4.78</v>
       </c>
       <c r="P164">
-        <v>2.75</v>
+        <v>5.56</v>
       </c>
       <c r="Q164">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="R164">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="S164">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="T164">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="U164">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="V164">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="W164">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X164">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y164">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="Z164">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AA164">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="AB164">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="AC164">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="AD164">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE164">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AF164">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG164">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AK164">
-        <v>1.48</v>
+        <v>2.83</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -28508,7 +28508,7 @@
         </is>
       </c>
       <c r="N173">
-        <v>13.5</v>
+        <v>9.5</v>
       </c>
       <c r="O173">
         <v>5.5</v>
@@ -28517,19 +28517,19 @@
         <v>1.22</v>
       </c>
       <c r="Q173">
-        <v>7.14</v>
+        <v>10.6</v>
       </c>
       <c r="R173">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="S173">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="T173">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U173">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="V173">
         <v>1.67</v>
@@ -28541,22 +28541,22 @@
         <v>1.02</v>
       </c>
       <c r="Y173">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z173">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AA173">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB173">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC173">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AD173">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE173">
         <v>1.19</v>
@@ -28578,7 +28578,7 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK173">
         <v>1.03</v>
@@ -30304,13 +30304,13 @@
         <v>2.3</v>
       </c>
       <c r="O184">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P184">
         <v>3.2</v>
       </c>
       <c r="Q184">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R184">
         <v>1.81</v>
@@ -30331,7 +30331,7 @@
         <v>1.03</v>
       </c>
       <c r="X184">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y184">
         <v>1.65</v>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK184">
         <v>1.54</v>
@@ -30464,10 +30464,10 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="O185">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="P185">
         <v>5</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="O187">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P187">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Q187">
-        <v>8.6</v>
+        <v>6.5</v>
       </c>
       <c r="R187">
+        <v>2.5</v>
+      </c>
+      <c r="S187">
+        <v>1.29</v>
+      </c>
+      <c r="T187">
+        <v>3.3</v>
+      </c>
+      <c r="U187">
         <v>2.4</v>
       </c>
-      <c r="S187">
-        <v>1.35</v>
-      </c>
-      <c r="T187">
-        <v>2.94</v>
-      </c>
-      <c r="U187">
-        <v>2.73</v>
-      </c>
       <c r="V187">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W187">
         <v>1.08</v>
       </c>
       <c r="X187">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y187">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z187">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA187">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB187">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC187">
-        <v>3.21</v>
+        <v>2.7</v>
       </c>
       <c r="AD187">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE187">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF187">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AG187">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.15</v>
+        <v>2.75</v>
       </c>
       <c r="AK187">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="O188">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P188">
+        <v>1.31</v>
+      </c>
+      <c r="Q188">
+        <v>8.6</v>
+      </c>
+      <c r="R188">
+        <v>2.4</v>
+      </c>
+      <c r="S188">
         <v>1.35</v>
       </c>
-      <c r="Q188">
-        <v>6.5</v>
-      </c>
-      <c r="R188">
-        <v>2.5</v>
-      </c>
-      <c r="S188">
-        <v>1.29</v>
-      </c>
       <c r="T188">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U188">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="V188">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W188">
         <v>1.08</v>
       </c>
       <c r="X188">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y188">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z188">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA188">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB188">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC188">
-        <v>2.7</v>
+        <v>3.21</v>
       </c>
       <c r="AD188">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AE188">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF188">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AG188">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>2.75</v>
+        <v>1.15</v>
       </c>
       <c r="AK188">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31131,43 +31131,43 @@
         <v>2.25</v>
       </c>
       <c r="S189">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T189">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U189">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="V189">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W189">
         <v>1.07</v>
       </c>
       <c r="X189">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y189">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z189">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="AA189">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AB189">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AC189">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AD189">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE189">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF189">
         <v>1.95</v>
@@ -31186,7 +31186,7 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK189">
         <v>2.4</v>
@@ -31442,16 +31442,16 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="Q191">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R191">
         <v>2.52</v>
@@ -31472,10 +31472,10 @@
         <v>1.08</v>
       </c>
       <c r="X191">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y191">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z191">
         <v>4.15</v>
@@ -31484,19 +31484,19 @@
         <v>1.64</v>
       </c>
       <c r="AB191">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC191">
         <v>2.49</v>
       </c>
       <c r="AD191">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE191">
         <v>1.13</v>
       </c>
       <c r="AF191">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG191">
         <v>2</v>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK191">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -33072,19 +33072,19 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="O201">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P201">
-        <v>3.4</v>
+        <v>4.28</v>
       </c>
       <c r="Q201">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="R201">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="S201">
         <v>1.63</v>
@@ -33114,13 +33114,13 @@
         <v>2.88</v>
       </c>
       <c r="AB201">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AC201">
-        <v>6</v>
+        <v>5.45</v>
       </c>
       <c r="AD201">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE201">
         <v>1.03</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="O202">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="P202">
-        <v>5.23</v>
+        <v>5.05</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33407,10 +33407,10 @@
         <v>2.87</v>
       </c>
       <c r="Q203">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="R203">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="S203">
         <v>1.72</v>
@@ -33422,40 +33422,40 @@
         <v>4.35</v>
       </c>
       <c r="V203">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="W203">
         <v>1.02</v>
       </c>
       <c r="X203">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Y203">
         <v>1.75</v>
       </c>
       <c r="Z203">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AA203">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="AB203">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC203">
         <v>6.7</v>
       </c>
       <c r="AD203">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE203">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF203">
         <v>2.5</v>
       </c>
       <c r="AG203">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AK203">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33564,10 +33564,10 @@
         <v>1.66</v>
       </c>
       <c r="O204">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P204">
-        <v>5.65</v>
+        <v>4.7</v>
       </c>
       <c r="Q204">
         <v>2.25</v>
@@ -33576,13 +33576,13 @@
         <v>1.95</v>
       </c>
       <c r="S204">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T204">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="U204">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="V204">
         <v>1.24</v>
@@ -33591,7 +33591,7 @@
         <v>1</v>
       </c>
       <c r="X204">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y204">
         <v>1.46</v>
@@ -33603,16 +33603,16 @@
         <v>2.49</v>
       </c>
       <c r="AB204">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC204">
         <v>4.93</v>
       </c>
       <c r="AD204">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE204">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF204">
         <v>2.3</v>
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O205">
         <v>2.65</v>
       </c>
       <c r="P205">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -33754,28 +33754,28 @@
         <v>1.02</v>
       </c>
       <c r="X205">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Y205">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Z205">
         <v>2.03</v>
       </c>
       <c r="AA205">
-        <v>3.33</v>
+        <v>3.04</v>
       </c>
       <c r="AB205">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC205">
         <v>6.25</v>
       </c>
       <c r="AD205">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE205">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF205">
         <v>2.3</v>
@@ -33896,7 +33896,7 @@
         <v>2.8</v>
       </c>
       <c r="Q206">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="R206">
         <v>2.1</v>
@@ -33905,13 +33905,13 @@
         <v>1.36</v>
       </c>
       <c r="T206">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="U206">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V206">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W206">
         <v>1.05</v>
@@ -33920,7 +33920,7 @@
         <v>1.01</v>
       </c>
       <c r="Y206">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z206">
         <v>3.2</v>
@@ -33938,13 +33938,13 @@
         <v>1.28</v>
       </c>
       <c r="AE206">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF206">
         <v>1.7</v>
       </c>
       <c r="AG206">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK206">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -35031,16 +35031,16 @@
         <v>3.1</v>
       </c>
       <c r="O213">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P213">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q213">
         <v>4.18</v>
       </c>
       <c r="R213">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="S213">
         <v>1.46</v>
@@ -35058,34 +35058,34 @@
         <v>1.02</v>
       </c>
       <c r="X213">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y213">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z213">
         <v>2.74</v>
       </c>
       <c r="AA213">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB213">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC213">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AD213">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE213">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF213">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG213">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK213">
         <v>1.26</v>
@@ -35194,10 +35194,10 @@
         <v>3.1</v>
       </c>
       <c r="O214">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P214">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q214">
         <v>4.24</v>
@@ -35206,10 +35206,10 @@
         <v>1.95</v>
       </c>
       <c r="S214">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T214">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U214">
         <v>3.34</v>
@@ -35227,7 +35227,7 @@
         <v>1.4</v>
       </c>
       <c r="Z214">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AA214">
         <v>2.37</v>
@@ -35245,10 +35245,10 @@
         <v>1.01</v>
       </c>
       <c r="AF214">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AG214">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK214">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -36495,7 +36495,7 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O222">
         <v>2.9</v>
@@ -36504,55 +36504,55 @@
         <v>2.9</v>
       </c>
       <c r="Q222">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="R222">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="S222">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="T222">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U222">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="V222">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W222">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X222">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y222">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z222">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="AA222">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AB222">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC222">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AD222">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE222">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF222">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AG222">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK222">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36658,25 +36658,25 @@
         </is>
       </c>
       <c r="N223">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="O223">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P223">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="Q223">
-        <v>7.22</v>
+        <v>8.1</v>
       </c>
       <c r="R223">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="S223">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T223">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="U223">
         <v>3.14</v>
@@ -36688,34 +36688,34 @@
         <v>1.02</v>
       </c>
       <c r="X223">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y223">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z223">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA223">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB223">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC223">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AD223">
         <v>1.18</v>
       </c>
       <c r="AE223">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF223">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AG223">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>1.2</v>
       </c>
       <c r="AK223">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -37799,19 +37799,19 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="O230">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="P230">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Q230">
-        <v>3.36</v>
+        <v>4.22</v>
       </c>
       <c r="R230">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="S230">
         <v>1.64</v>
@@ -37838,7 +37838,7 @@
         <v>2.14</v>
       </c>
       <c r="AA230">
-        <v>3.07</v>
+        <v>2.83</v>
       </c>
       <c r="AB230">
         <v>1.33</v>
@@ -37847,7 +37847,7 @@
         <v>6.41</v>
       </c>
       <c r="AD230">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE230">
         <v>1.02</v>
@@ -37962,7 +37962,7 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O231">
         <v>3</v>
@@ -37971,34 +37971,34 @@
         <v>3</v>
       </c>
       <c r="Q231">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R231">
         <v>1.89</v>
       </c>
       <c r="S231">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T231">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U231">
         <v>3.32</v>
       </c>
       <c r="V231">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W231">
         <v>1.02</v>
       </c>
       <c r="X231">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y231">
         <v>1.4</v>
       </c>
       <c r="Z231">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AA231">
         <v>2.4</v>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK231">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38294,13 +38294,13 @@
         <v>3.55</v>
       </c>
       <c r="P233">
-        <v>5.75</v>
+        <v>6.45</v>
       </c>
       <c r="Q233">
+        <v>2.1</v>
+      </c>
+      <c r="R233">
         <v>2.04</v>
-      </c>
-      <c r="R233">
-        <v>1.97</v>
       </c>
       <c r="S233">
         <v>1.43</v>
@@ -38321,10 +38321,10 @@
         <v>1.04</v>
       </c>
       <c r="Y233">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z233">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AA233">
         <v>2.3</v>
@@ -38336,7 +38336,7 @@
         <v>4.1</v>
       </c>
       <c r="AD233">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE233">
         <v>1.06</v>
@@ -38345,7 +38345,7 @@
         <v>2.3</v>
       </c>
       <c r="AG233">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>1.25</v>
       </c>
       <c r="AK233">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -39266,16 +39266,16 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="O239">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P239">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q239">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R239">
         <v>1.92</v>
@@ -39290,13 +39290,13 @@
         <v>3.5</v>
       </c>
       <c r="V239">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W239">
         <v>1</v>
       </c>
       <c r="X239">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y239">
         <v>1.4</v>
@@ -39305,7 +39305,7 @@
         <v>2.7</v>
       </c>
       <c r="AA239">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AB239">
         <v>1.47</v>
@@ -39314,16 +39314,16 @@
         <v>5.5</v>
       </c>
       <c r="AD239">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE239">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF239">
         <v>2.5</v>
       </c>
       <c r="AG239">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK239">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39592,49 +39592,49 @@
         </is>
       </c>
       <c r="N241">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="O241">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="P241">
-        <v>3.8</v>
+        <v>4.41</v>
       </c>
       <c r="Q241">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R241">
         <v>1.93</v>
       </c>
       <c r="S241">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T241">
         <v>2.28</v>
       </c>
       <c r="U241">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V241">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W241">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X241">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y241">
         <v>1.5</v>
       </c>
       <c r="Z241">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="AA241">
         <v>2.63</v>
       </c>
       <c r="AB241">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC241">
         <v>5.5</v>
@@ -39643,7 +39643,7 @@
         <v>1.11</v>
       </c>
       <c r="AE241">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF241">
         <v>2.2</v>
@@ -39662,7 +39662,7 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AK241">
         <v>1.75</v>
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="O242">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P242">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q242">
         <v>0</v>
@@ -40081,40 +40081,40 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O244">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P244">
         <v>4.5</v>
       </c>
       <c r="Q244">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="R244">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S244">
         <v>1.5</v>
       </c>
       <c r="T244">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="U244">
         <v>3.32</v>
       </c>
       <c r="V244">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W244">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X244">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y244">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z244">
         <v>2.7</v>
@@ -40129,13 +40129,13 @@
         <v>4.5</v>
       </c>
       <c r="AD244">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE244">
         <v>1.01</v>
       </c>
       <c r="AF244">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AG244">
         <v>1.65</v>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK244">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,19 +40244,19 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="O245">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P245">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q245">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="R245">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S245">
         <v>1.3</v>
@@ -40265,10 +40265,10 @@
         <v>3.3</v>
       </c>
       <c r="U245">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="V245">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="W245">
         <v>1.05</v>
@@ -40280,22 +40280,22 @@
         <v>1.23</v>
       </c>
       <c r="Z245">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="AA245">
         <v>1.58</v>
       </c>
       <c r="AB245">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AC245">
-        <v>2.38</v>
+        <v>2.97</v>
       </c>
       <c r="AD245">
         <v>1.29</v>
       </c>
       <c r="AE245">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF245">
         <v>1.5</v>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK245">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL245">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.7</v>
+        <v>3.31</v>
       </c>
       <c r="O7">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="P7">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="Q7">
-        <v>2.99</v>
+        <v>3.45</v>
       </c>
       <c r="R7">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="S7">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="T7">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U7">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z7">
-        <v>4.35</v>
+        <v>4.65</v>
       </c>
       <c r="AA7">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB7">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC7">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AD7">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE7">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.31</v>
+        <v>2.7</v>
       </c>
       <c r="O9">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="P9">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="Q9">
-        <v>3.45</v>
+        <v>2.99</v>
       </c>
       <c r="R9">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="S9">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="T9">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U9">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>4.65</v>
+        <v>4.35</v>
       </c>
       <c r="AA9">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB9">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AD9">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF9">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG9">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK9">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2597,49 +2597,49 @@
         <v>3.15</v>
       </c>
       <c r="P14">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q14">
-        <v>3.69</v>
+        <v>3.28</v>
       </c>
       <c r="R14">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="S14">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="U14">
         <v>3.1</v>
       </c>
       <c r="V14">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
+        <v>1.04</v>
+      </c>
+      <c r="X14">
         <v>1.02</v>
       </c>
-      <c r="X14">
-        <v>1.05</v>
-      </c>
       <c r="Y14">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z14">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA14">
         <v>2.16</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC14">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="AD14">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
         <v>1.03</v>
@@ -2648,7 +2648,7 @@
         <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AK14">
         <v>1.36</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3409,61 +3409,61 @@
         <v>5.5</v>
       </c>
       <c r="O19">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P19">
         <v>1.48</v>
       </c>
       <c r="Q19">
-        <v>5.88</v>
+        <v>5.5</v>
       </c>
       <c r="R19">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T19">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="U19">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
         <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="AA19">
         <v>1.85</v>
       </c>
       <c r="AB19">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC19">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="AD19">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG19">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.72</v>
+        <v>3.66</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P20">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Q20">
-        <v>3.58</v>
+        <v>2.62</v>
       </c>
       <c r="R20">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S20">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U20">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W20">
         <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="Z20">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AA20">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="AB20">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC20">
-        <v>3.62</v>
+        <v>4.45</v>
       </c>
       <c r="AD20">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF20">
+        <v>2.13</v>
+      </c>
+      <c r="AG20">
+        <v>1.64</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.26</v>
+      </c>
+      <c r="AK20">
         <v>1.8</v>
-      </c>
-      <c r="AG20">
-        <v>1.88</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.53</v>
-      </c>
-      <c r="AK20">
-        <v>1.39</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,58 +3732,58 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
         <v>2.1</v>
       </c>
       <c r="Q21">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="R21">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="S21">
         <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U21">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="V21">
         <v>1.35</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z21">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="AA21">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB21">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC21">
         <v>3.6</v>
       </c>
       <c r="AD21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE21">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF21">
         <v>1.79</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="AK21">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
+        <v>2.71</v>
+      </c>
+      <c r="O22">
+        <v>3.1</v>
+      </c>
+      <c r="P22">
+        <v>2.45</v>
+      </c>
+      <c r="Q22">
+        <v>3.65</v>
+      </c>
+      <c r="R22">
+        <v>2.15</v>
+      </c>
+      <c r="S22">
+        <v>1.4</v>
+      </c>
+      <c r="T22">
+        <v>2.88</v>
+      </c>
+      <c r="U22">
+        <v>2.84</v>
+      </c>
+      <c r="V22">
+        <v>1.33</v>
+      </c>
+      <c r="W22">
+        <v>1.05</v>
+      </c>
+      <c r="X22">
+        <v>1.06</v>
+      </c>
+      <c r="Y22">
+        <v>1.32</v>
+      </c>
+      <c r="Z22">
+        <v>3.25</v>
+      </c>
+      <c r="AA22">
+        <v>2.1</v>
+      </c>
+      <c r="AB22">
+        <v>1.73</v>
+      </c>
+      <c r="AC22">
         <v>3.8</v>
       </c>
-      <c r="O22">
-        <v>3</v>
-      </c>
-      <c r="P22">
-        <v>1.93</v>
-      </c>
-      <c r="Q22">
-        <v>2.61</v>
-      </c>
-      <c r="R22">
-        <v>1.89</v>
-      </c>
-      <c r="S22">
-        <v>1.52</v>
-      </c>
-      <c r="T22">
-        <v>2.36</v>
-      </c>
-      <c r="U22">
-        <v>3.4</v>
-      </c>
-      <c r="V22">
-        <v>1.27</v>
-      </c>
-      <c r="W22">
-        <v>1.01</v>
-      </c>
-      <c r="X22">
-        <v>1.05</v>
-      </c>
-      <c r="Y22">
-        <v>1.47</v>
-      </c>
-      <c r="Z22">
-        <v>2.45</v>
-      </c>
-      <c r="AA22">
-        <v>2.25</v>
-      </c>
-      <c r="AB22">
-        <v>1.53</v>
-      </c>
-      <c r="AC22">
-        <v>4.98</v>
-      </c>
       <c r="AD22">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG22">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AK22">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4109,7 +4109,7 @@
         <v>1.53</v>
       </c>
       <c r="AE23">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF23">
         <v>1.5</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O24">
         <v>3.45</v>
@@ -4236,7 +4236,7 @@
         <v>2.04</v>
       </c>
       <c r="S24">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T24">
         <v>2.8</v>
@@ -4547,34 +4547,34 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.7</v>
+        <v>3.51</v>
       </c>
       <c r="O26">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="Q26">
-        <v>4</v>
+        <v>4.28</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S26">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T26">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="U26">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V26">
         <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
         <v>1.05</v>
@@ -4601,10 +4601,10 @@
         <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AG26">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4719,55 +4719,55 @@
         <v>3.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA27">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,55 +4873,55 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.71</v>
+        <v>2.14</v>
       </c>
       <c r="O28">
         <v>3.25</v>
       </c>
       <c r="P28">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q28">
         <v>3.32</v>
       </c>
       <c r="R28">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="U28">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W28">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z28">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AA28">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AB28">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="AC28">
-        <v>2.27</v>
+        <v>2.01</v>
       </c>
       <c r="AD28">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
         <v>1.18</v>
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="O29">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q29">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R29">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="S29">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U29">
         <v>2.34</v>
@@ -5063,31 +5063,31 @@
         <v>1.62</v>
       </c>
       <c r="W29">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z29">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA29">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB29">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AC29">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="AD29">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE29">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF29">
         <v>1.44</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AK29">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="O30">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>3.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q30">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="R30">
+        <v>2.5</v>
+      </c>
+      <c r="S30">
+        <v>1.22</v>
+      </c>
+      <c r="T30">
+        <v>3.8</v>
+      </c>
+      <c r="U30">
+        <v>2.27</v>
+      </c>
+      <c r="V30">
+        <v>1.58</v>
+      </c>
+      <c r="W30">
+        <v>1.13</v>
+      </c>
+      <c r="X30">
+        <v>1.03</v>
+      </c>
+      <c r="Y30">
+        <v>1.15</v>
+      </c>
+      <c r="Z30">
+        <v>4.75</v>
+      </c>
+      <c r="AA30">
+        <v>1.57</v>
+      </c>
+      <c r="AB30">
         <v>2.4</v>
       </c>
-      <c r="S30">
-        <v>1.28</v>
-      </c>
-      <c r="T30">
-        <v>3.4</v>
-      </c>
-      <c r="U30">
-        <v>2.49</v>
-      </c>
-      <c r="V30">
-        <v>1.55</v>
-      </c>
-      <c r="W30">
-        <v>1.08</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.2</v>
-      </c>
-      <c r="Z30">
-        <v>4.63</v>
-      </c>
-      <c r="AA30">
-        <v>1.56</v>
-      </c>
-      <c r="AB30">
-        <v>2.17</v>
-      </c>
       <c r="AC30">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AD30">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF30">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG30">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="P31">
-        <v>2.9</v>
+        <v>3.88</v>
       </c>
       <c r="Q31">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R31">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U31">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V31">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
+        <v>1.2</v>
+      </c>
+      <c r="Z31">
+        <v>4.5</v>
+      </c>
+      <c r="AA31">
+        <v>1.56</v>
+      </c>
+      <c r="AB31">
+        <v>2.25</v>
+      </c>
+      <c r="AC31">
+        <v>2.44</v>
+      </c>
+      <c r="AD31">
+        <v>1.5</v>
+      </c>
+      <c r="AE31">
         <v>1.15</v>
       </c>
-      <c r="Z31">
-        <v>4.8</v>
-      </c>
-      <c r="AA31">
-        <v>1.57</v>
-      </c>
-      <c r="AB31">
-        <v>2.28</v>
-      </c>
-      <c r="AC31">
-        <v>2.27</v>
-      </c>
-      <c r="AD31">
-        <v>1.54</v>
-      </c>
-      <c r="AE31">
-        <v>1.18</v>
-      </c>
       <c r="AF31">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AG31">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5531,28 +5531,28 @@
         <v>4</v>
       </c>
       <c r="P32">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q32">
-        <v>5.49</v>
+        <v>5.5</v>
       </c>
       <c r="R32">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S32">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
         <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
         <v>1.03</v>
@@ -5561,28 +5561,28 @@
         <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="AA32">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AB32">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AC32">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD32">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE32">
         <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>2.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5694,28 +5694,28 @@
         <v>4.4</v>
       </c>
       <c r="P33">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q33">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R33">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S33">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="V33">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W33">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
         <v>1.01</v>
@@ -5739,13 +5739,13 @@
         <v>1.46</v>
       </c>
       <c r="AE33">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF33">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG33">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK33">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6189,7 +6189,7 @@
         <v>2.93</v>
       </c>
       <c r="R36">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="S36">
         <v>1.31</v>
@@ -6198,7 +6198,7 @@
         <v>2.97</v>
       </c>
       <c r="U36">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="V36">
         <v>1.43</v>
@@ -6210,16 +6210,16 @@
         <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z36">
         <v>3.7</v>
       </c>
       <c r="AA36">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB36">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AC36">
         <v>2.81</v>
@@ -6228,7 +6228,7 @@
         <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
         <v>1.59</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.31</v>
+        <v>2.95</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q41">
         <v>3.75</v>
       </c>
       <c r="R41">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S41">
+        <v>1.34</v>
+      </c>
+      <c r="T41">
+        <v>2.7</v>
+      </c>
+      <c r="U41">
+        <v>2.88</v>
+      </c>
+      <c r="V41">
         <v>1.36</v>
-      </c>
-      <c r="T41">
-        <v>2.9</v>
-      </c>
-      <c r="U41">
-        <v>2.75</v>
-      </c>
-      <c r="V41">
-        <v>1.4</v>
       </c>
       <c r="W41">
         <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y41">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z41">
         <v>3.4</v>
       </c>
       <c r="AA41">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB41">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC41">
         <v>3.4</v>
       </c>
       <c r="AD41">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG41">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK41">
         <v>1.25</v>
@@ -7164,10 +7164,10 @@
         <v>2.14</v>
       </c>
       <c r="Q42">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R42">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S42">
         <v>1.35</v>
@@ -7176,25 +7176,25 @@
         <v>2.9</v>
       </c>
       <c r="U42">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="V42">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z42">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA42">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB42">
         <v>1.9</v>
@@ -7206,7 +7206,7 @@
         <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
         <v>1.78</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AK42">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8157,7 +8157,7 @@
         <v>2.48</v>
       </c>
       <c r="V48">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
         <v>1.07</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
         <v>1.65</v>
@@ -8308,52 +8308,52 @@
         <v>3.06</v>
       </c>
       <c r="R49">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="S49">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T49">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="U49">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="V49">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W49">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
         <v>1.33</v>
       </c>
       <c r="Z49">
-        <v>3.14</v>
+        <v>2.94</v>
       </c>
       <c r="AA49">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AB49">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC49">
         <v>3.25</v>
       </c>
       <c r="AD49">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE49">
         <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG49">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK49">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>3.7</v>
       </c>
       <c r="Q50">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="R50">
         <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="U50">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
         <v>1.57</v>
       </c>
       <c r="W50">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB50">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AC50">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AD50">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE50">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF50">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
         <v>2.05</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O51">
         <v>3.4</v>
@@ -8631,55 +8631,55 @@
         <v>2.73</v>
       </c>
       <c r="Q51">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="R51">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T51">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="U51">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V51">
         <v>1.42</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA51">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AB51">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AC51">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD51">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG51">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AK51">
         <v>1.53</v>
@@ -8794,52 +8794,52 @@
         <v>3.66</v>
       </c>
       <c r="Q52">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="R52">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S52">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="U52">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="V52">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W52">
         <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y52">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z52">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="AA52">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AB52">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AC52">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="AD52">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE52">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG52">
         <v>1.95</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
         <v>1.73</v>
@@ -8957,22 +8957,22 @@
         <v>4.53</v>
       </c>
       <c r="Q53">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="R53">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S53">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="T53">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="U53">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V53">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W53">
         <v>1</v>
@@ -8981,31 +8981,31 @@
         <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z53">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="AA53">
         <v>2.33</v>
       </c>
       <c r="AB53">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC53">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="AD53">
         <v>1.2</v>
       </c>
       <c r="AE53">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF53">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AG53">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AK53">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9277,7 +9277,7 @@
         <v>2.15</v>
       </c>
       <c r="O55">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
         <v>2.55</v>
@@ -9295,43 +9295,43 @@
         <v>2.95</v>
       </c>
       <c r="U55">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="V55">
         <v>1.42</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z55">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="AA55">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB55">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC55">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD55">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE55">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF55">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG55">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK55">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,34 +9446,34 @@
         <v>2.4</v>
       </c>
       <c r="Q56">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="R56">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S56">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T56">
         <v>3.14</v>
       </c>
       <c r="U56">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V56">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W56">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
         <v>0</v>
       </c>
       <c r="Y56">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z56">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA56">
         <v>1.63</v>
@@ -9482,7 +9482,7 @@
         <v>2.12</v>
       </c>
       <c r="AC56">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AD56">
         <v>1.41</v>
@@ -9491,7 +9491,7 @@
         <v>1.13</v>
       </c>
       <c r="AF56">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG56">
         <v>2.33</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
         <v>2.25</v>
       </c>
       <c r="Q57">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="R57">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S57">
         <v>1.44</v>
       </c>
       <c r="T57">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U57">
         <v>2.82</v>
       </c>
       <c r="V57">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W57">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z57">
         <v>3.1</v>
       </c>
       <c r="AA57">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AB57">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AC57">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AD57">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE57">
         <v>1.04</v>
       </c>
       <c r="AF57">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG57">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.32</v>
       </c>
       <c r="AK57">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10913,25 +10913,25 @@
         <v>2.25</v>
       </c>
       <c r="Q65">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="R65">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="S65">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="U65">
         <v>2.2</v>
       </c>
       <c r="V65">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W65">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X65">
         <v>1.01</v>
@@ -10943,25 +10943,25 @@
         <v>5.5</v>
       </c>
       <c r="AA65">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB65">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AC65">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AD65">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE65">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF65">
         <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AK65">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11070,22 +11070,22 @@
         <v>12</v>
       </c>
       <c r="O66">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="P66">
         <v>1.09</v>
       </c>
       <c r="Q66">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R66">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="S66">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T66">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="U66">
         <v>1.93</v>
@@ -11094,16 +11094,16 @@
         <v>1.76</v>
       </c>
       <c r="W66">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X66">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
         <v>1.06</v>
       </c>
       <c r="Z66">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AA66">
         <v>1.3</v>
@@ -11112,19 +11112,19 @@
         <v>2.97</v>
       </c>
       <c r="AC66">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AD66">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE66">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AF66">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AG66">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK66">
         <v>1.01</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O71">
         <v>3.5</v>
       </c>
       <c r="P71">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q71">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R71">
         <v>2.21</v>
       </c>
       <c r="S71">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T71">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U71">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V71">
         <v>1.53</v>
       </c>
       <c r="W71">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z71">
         <v>4.4</v>
       </c>
       <c r="AA71">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB71">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="AC71">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD71">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE71">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF71">
         <v>1.5</v>
       </c>
       <c r="AG71">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="O75">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P75">
-        <v>3.1</v>
+        <v>4.53</v>
       </c>
       <c r="Q75">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="R75">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="S75">
+        <v>1.16</v>
+      </c>
+      <c r="T75">
+        <v>4.5</v>
+      </c>
+      <c r="U75">
+        <v>1.85</v>
+      </c>
+      <c r="V75">
+        <v>1.82</v>
+      </c>
+      <c r="W75">
         <v>1.22</v>
       </c>
-      <c r="T75">
-        <v>3.8</v>
-      </c>
-      <c r="U75">
-        <v>2.14</v>
-      </c>
-      <c r="V75">
-        <v>1.66</v>
-      </c>
-      <c r="W75">
-        <v>1.15</v>
-      </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="Z75">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AA75">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AB75">
-        <v>2.39</v>
+        <v>3.18</v>
       </c>
       <c r="AC75">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="AD75">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="AE75">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AF75">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AG75">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK75">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="O76">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P76">
-        <v>4.53</v>
+        <v>3.1</v>
       </c>
       <c r="Q76">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="R76">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="S76">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T76">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U76">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="V76">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="W76">
+        <v>1.15</v>
+      </c>
+      <c r="X76">
+        <v>1.02</v>
+      </c>
+      <c r="Y76">
+        <v>1.11</v>
+      </c>
+      <c r="Z76">
+        <v>4.9</v>
+      </c>
+      <c r="AA76">
+        <v>1.5</v>
+      </c>
+      <c r="AB76">
+        <v>2.39</v>
+      </c>
+      <c r="AC76">
+        <v>2.16</v>
+      </c>
+      <c r="AD76">
+        <v>1.64</v>
+      </c>
+      <c r="AE76">
         <v>1.22</v>
       </c>
-      <c r="X76">
-        <v>1.01</v>
-      </c>
-      <c r="Y76">
-        <v>1.03</v>
-      </c>
-      <c r="Z76">
-        <v>7.2</v>
-      </c>
-      <c r="AA76">
-        <v>1.27</v>
-      </c>
-      <c r="AB76">
-        <v>3.18</v>
-      </c>
-      <c r="AC76">
-        <v>1.79</v>
-      </c>
-      <c r="AD76">
-        <v>1.99</v>
-      </c>
-      <c r="AE76">
-        <v>1.44</v>
-      </c>
       <c r="AF76">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AG76">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>2.22</v>
+        <v>1.7</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13189,25 +13189,25 @@
         <v>3.4</v>
       </c>
       <c r="O79">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P79">
         <v>1.83</v>
       </c>
       <c r="Q79">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="R79">
         <v>2.45</v>
       </c>
       <c r="S79">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T79">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="U79">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="V79">
         <v>1.7</v>
@@ -13219,25 +13219,25 @@
         <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z79">
-        <v>5.66</v>
+        <v>3.75</v>
       </c>
       <c r="AA79">
         <v>1.38</v>
       </c>
       <c r="AB79">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC79">
         <v>2.03</v>
       </c>
       <c r="AD79">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AE79">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF79">
         <v>1.4</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -15305,46 +15305,46 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="O92">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="P92">
-        <v>2.66</v>
+        <v>2.97</v>
       </c>
       <c r="Q92">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="R92">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S92">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T92">
         <v>4</v>
       </c>
       <c r="U92">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V92">
         <v>1.67</v>
       </c>
       <c r="W92">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X92">
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z92">
-        <v>5.25</v>
+        <v>5.89</v>
       </c>
       <c r="AA92">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB92">
         <v>2.56</v>
@@ -15356,7 +15356,7 @@
         <v>1.7</v>
       </c>
       <c r="AE92">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF92">
         <v>1.4</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>7.35</v>
+        <v>6.42</v>
       </c>
       <c r="O114">
-        <v>3.47</v>
+        <v>3.7</v>
       </c>
       <c r="P114">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q114">
         <v>7.1</v>
@@ -18909,25 +18909,25 @@
         <v>1.37</v>
       </c>
       <c r="T114">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U114">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="V114">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W114">
         <v>1.09</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y114">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z114">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA114">
         <v>1.93</v>
@@ -18948,7 +18948,7 @@
         <v>2.05</v>
       </c>
       <c r="AG114">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>2.34</v>
+        <v>1.21</v>
       </c>
       <c r="AK114">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19392,13 +19392,13 @@
         <v>1.88</v>
       </c>
       <c r="R117">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="S117">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T117">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U117">
         <v>2.36</v>
@@ -19407,19 +19407,19 @@
         <v>1.61</v>
       </c>
       <c r="W117">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X117">
         <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z117">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AA117">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AB117">
         <v>2.33</v>
@@ -19428,16 +19428,16 @@
         <v>2.35</v>
       </c>
       <c r="AD117">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE117">
         <v>1.19</v>
       </c>
       <c r="AF117">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG117">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK117">
-        <v>2.68</v>
+        <v>2.93</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19561,46 +19561,46 @@
         <v>1.29</v>
       </c>
       <c r="T118">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U118">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V118">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W118">
         <v>1.11</v>
       </c>
       <c r="X118">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z118">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA118">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB118">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AC118">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD118">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE118">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF118">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG118">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK118">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -22812,28 +22812,28 @@
         <v>2.3</v>
       </c>
       <c r="Q138">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="R138">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S138">
         <v>1.28</v>
       </c>
       <c r="T138">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U138">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="V138">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W138">
         <v>1.09</v>
       </c>
       <c r="X138">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y138">
         <v>1.13</v>
@@ -22851,13 +22851,13 @@
         <v>2.33</v>
       </c>
       <c r="AD138">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AE138">
         <v>1.16</v>
       </c>
       <c r="AF138">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG138">
         <v>2.32</v>
@@ -25737,10 +25737,10 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="O156">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="P156">
         <v>4.6</v>
@@ -25764,37 +25764,37 @@
         <v>1.52</v>
       </c>
       <c r="W156">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X156">
         <v>1.02</v>
       </c>
       <c r="Y156">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z156">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA156">
         <v>1.63</v>
       </c>
       <c r="AB156">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AC156">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD156">
         <v>1.42</v>
       </c>
       <c r="AE156">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF156">
         <v>1.68</v>
       </c>
       <c r="AG156">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK156">
         <v>2.2</v>
@@ -26715,28 +26715,28 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="O162">
         <v>3.1</v>
       </c>
       <c r="P162">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q162">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R162">
         <v>2.1</v>
       </c>
       <c r="S162">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T162">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U162">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="V162">
         <v>1.33</v>
@@ -26772,7 +26772,7 @@
         <v>1.83</v>
       </c>
       <c r="AG162">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK162">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26878,43 +26878,43 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="O163">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P163">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S163">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T163">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U163">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="V163">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W163">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X163">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y163">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z163">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AA163">
         <v>2.15</v>
@@ -26923,19 +26923,19 @@
         <v>1.66</v>
       </c>
       <c r="AC163">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD163">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG163">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK163">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O164">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P164">
         <v>2.87</v>
       </c>
       <c r="Q164">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="R164">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S164">
         <v>1.46</v>
       </c>
       <c r="T164">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U164">
-        <v>3.16</v>
+        <v>2.91</v>
       </c>
       <c r="V164">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W164">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X164">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y164">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z164">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AA164">
         <v>2.16</v>
       </c>
       <c r="AB164">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC164">
-        <v>3.25</v>
+        <v>3.82</v>
       </c>
       <c r="AD164">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AE164">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF164">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG164">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>1.3</v>
       </c>
       <c r="AK164">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="O183">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P183">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="Q183">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="R183">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="S183">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T183">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="U183">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="V183">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W183">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X183">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y183">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z183">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="AA183">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB183">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC183">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AD183">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE183">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF183">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG183">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>1.25</v>
       </c>
       <c r="AK183">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -32933,7 +32933,7 @@
         <v>2.39</v>
       </c>
       <c r="V200">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W200">
         <v>1.11</v>
@@ -32948,7 +32948,7 @@
         <v>4.33</v>
       </c>
       <c r="AA200">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB200">
         <v>2.25</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="O204">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P204">
-        <v>3.46</v>
+        <v>4.6</v>
       </c>
       <c r="Q204">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R204">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S204">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="T204">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U204">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="V204">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W204">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X204">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y204">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z204">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AA204">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AB204">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC204">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD204">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE204">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF204">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG204">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK204">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,80 +33724,80 @@
         </is>
       </c>
       <c r="N205">
+        <v>2.65</v>
+      </c>
+      <c r="O205">
+        <v>2.65</v>
+      </c>
+      <c r="P205">
+        <v>2.98</v>
+      </c>
+      <c r="Q205">
+        <v>3.37</v>
+      </c>
+      <c r="R205">
         <v>1.75</v>
       </c>
-      <c r="O205">
-        <v>3</v>
-      </c>
-      <c r="P205">
-        <v>4.6</v>
-      </c>
-      <c r="Q205">
-        <v>0</v>
-      </c>
-      <c r="R205">
-        <v>0</v>
-      </c>
       <c r="S205">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T205">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U205">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V205">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W205">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X205">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y205">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z205">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA205">
-        <v>2.87</v>
+        <v>3.14</v>
       </c>
       <c r="AB205">
+        <v>1.3</v>
+      </c>
+      <c r="AC205">
+        <v>6.5</v>
+      </c>
+      <c r="AD205">
+        <v>1.07</v>
+      </c>
+      <c r="AE205">
+        <v>1.02</v>
+      </c>
+      <c r="AF205">
+        <v>2.5</v>
+      </c>
+      <c r="AG205">
+        <v>1.5</v>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ205">
+        <v>1.32</v>
+      </c>
+      <c r="AK205">
         <v>1.4</v>
-      </c>
-      <c r="AC205">
-        <v>0</v>
-      </c>
-      <c r="AD205">
-        <v>0</v>
-      </c>
-      <c r="AE205">
-        <v>0</v>
-      </c>
-      <c r="AF205">
-        <v>0</v>
-      </c>
-      <c r="AG205">
-        <v>0</v>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ205">
-        <v>0</v>
-      </c>
-      <c r="AK205">
-        <v>0</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.65</v>
+        <v>1.65</v>
       </c>
       <c r="O206">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="P206">
-        <v>2.98</v>
+        <v>4.75</v>
       </c>
       <c r="Q206">
-        <v>3.37</v>
+        <v>2.35</v>
       </c>
       <c r="R206">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="S206">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="T206">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="U206">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="V206">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="W206">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X206">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y206">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="Z206">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="AA206">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="AB206">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC206">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD206">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AE206">
         <v>1.02</v>
       </c>
       <c r="AF206">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="AG206">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK206">
-        <v>1.4</v>
+        <v>2.07</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,80 +34050,80 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="O207">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P207">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q207">
-        <v>2.35</v>
+        <v>3.37</v>
       </c>
       <c r="R207">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="S207">
+        <v>1.68</v>
+      </c>
+      <c r="T207">
+        <v>2.08</v>
+      </c>
+      <c r="U207">
+        <v>4.2</v>
+      </c>
+      <c r="V207">
+        <v>1.16</v>
+      </c>
+      <c r="W207">
+        <v>1.02</v>
+      </c>
+      <c r="X207">
+        <v>1.11</v>
+      </c>
+      <c r="Y207">
+        <v>1.72</v>
+      </c>
+      <c r="Z207">
+        <v>2.09</v>
+      </c>
+      <c r="AA207">
+        <v>3.04</v>
+      </c>
+      <c r="AB207">
+        <v>1.33</v>
+      </c>
+      <c r="AC207">
+        <v>6.25</v>
+      </c>
+      <c r="AD207">
+        <v>1.06</v>
+      </c>
+      <c r="AE207">
+        <v>1.01</v>
+      </c>
+      <c r="AF207">
+        <v>2.3</v>
+      </c>
+      <c r="AG207">
         <v>1.5</v>
       </c>
-      <c r="T207">
-        <v>2.33</v>
-      </c>
-      <c r="U207">
-        <v>3.5</v>
-      </c>
-      <c r="V207">
-        <v>1.25</v>
-      </c>
-      <c r="W207">
-        <v>1.04</v>
-      </c>
-      <c r="X207">
-        <v>1.1</v>
-      </c>
-      <c r="Y207">
-        <v>1.47</v>
-      </c>
-      <c r="Z207">
-        <v>2.62</v>
-      </c>
-      <c r="AA207">
-        <v>2.5</v>
-      </c>
-      <c r="AB207">
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ207">
+        <v>1.35</v>
+      </c>
+      <c r="AK207">
         <v>1.5</v>
-      </c>
-      <c r="AC207">
-        <v>4.7</v>
-      </c>
-      <c r="AD207">
-        <v>1.13</v>
-      </c>
-      <c r="AE207">
-        <v>1.02</v>
-      </c>
-      <c r="AF207">
-        <v>2.16</v>
-      </c>
-      <c r="AG207">
-        <v>1.58</v>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ207">
-        <v>1.24</v>
-      </c>
-      <c r="AK207">
-        <v>2.07</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="O208">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P208">
-        <v>3.1</v>
+        <v>3.46</v>
       </c>
       <c r="Q208">
-        <v>3.37</v>
+        <v>2.8</v>
       </c>
       <c r="R208">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S208">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="T208">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="U208">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="V208">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W208">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X208">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y208">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="Z208">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="AA208">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AB208">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC208">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AD208">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AE208">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF208">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG208">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK208">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34539,7 +34539,7 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="O210">
         <v>3.6</v>
@@ -34548,7 +34548,7 @@
         <v>2.4</v>
       </c>
       <c r="Q210">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="R210">
         <v>2.32</v>
@@ -34581,7 +34581,7 @@
         <v>1.6</v>
       </c>
       <c r="AB210">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC210">
         <v>2.38</v>
@@ -34612,7 +34612,7 @@
         <v>1.4</v>
       </c>
       <c r="AK210">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL210">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.31</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="P3">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="Q3">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="R3">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="S3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T3">
         <v>3.5</v>
       </c>
       <c r="U3">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V3">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W3">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z3">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AA3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB3">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AC3">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AD3">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE3">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AG3">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P4">
-        <v>2.05</v>
+        <v>3.85</v>
       </c>
       <c r="Q4">
-        <v>3.46</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S4">
+        <v>1.2</v>
+      </c>
+      <c r="T4">
+        <v>3.58</v>
+      </c>
+      <c r="U4">
+        <v>2.1</v>
+      </c>
+      <c r="V4">
+        <v>1.64</v>
+      </c>
+      <c r="W4">
+        <v>1.14</v>
+      </c>
+      <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
+        <v>1.1</v>
+      </c>
+      <c r="Z4">
+        <v>5.1</v>
+      </c>
+      <c r="AA4">
+        <v>1.44</v>
+      </c>
+      <c r="AB4">
+        <v>2.52</v>
+      </c>
+      <c r="AC4">
+        <v>2.1</v>
+      </c>
+      <c r="AD4">
+        <v>1.64</v>
+      </c>
+      <c r="AE4">
         <v>1.25</v>
-      </c>
-      <c r="T4">
-        <v>3.5</v>
-      </c>
-      <c r="U4">
-        <v>2.3</v>
-      </c>
-      <c r="V4">
-        <v>1.55</v>
-      </c>
-      <c r="W4">
-        <v>1.15</v>
-      </c>
-      <c r="X4">
-        <v>1.01</v>
-      </c>
-      <c r="Y4">
-        <v>1.14</v>
-      </c>
-      <c r="Z4">
-        <v>4.45</v>
-      </c>
-      <c r="AA4">
-        <v>1.57</v>
-      </c>
-      <c r="AB4">
-        <v>2.16</v>
-      </c>
-      <c r="AC4">
-        <v>2.34</v>
-      </c>
-      <c r="AD4">
-        <v>1.46</v>
-      </c>
-      <c r="AE4">
-        <v>1.18</v>
       </c>
       <c r="AF4">
         <v>1.46</v>
       </c>
       <c r="AG4">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>2.06</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.46</v>
+        <v>3.31</v>
       </c>
       <c r="O5">
         <v>4.5</v>
       </c>
       <c r="P5">
-        <v>4.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q5">
-        <v>2.1</v>
+        <v>3.45</v>
       </c>
       <c r="R5">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T5">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
+        <v>1.13</v>
+      </c>
+      <c r="Z5">
+        <v>4.6</v>
+      </c>
+      <c r="AA5">
+        <v>1.58</v>
+      </c>
+      <c r="AB5">
+        <v>2.25</v>
+      </c>
+      <c r="AC5">
+        <v>2.47</v>
+      </c>
+      <c r="AD5">
+        <v>1.49</v>
+      </c>
+      <c r="AE5">
+        <v>1.15</v>
+      </c>
+      <c r="AF5">
+        <v>1.51</v>
+      </c>
+      <c r="AG5">
+        <v>2.34</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.19</v>
       </c>
-      <c r="Z5">
-        <v>3.75</v>
-      </c>
-      <c r="AA5">
-        <v>1.66</v>
-      </c>
-      <c r="AB5">
-        <v>2</v>
-      </c>
-      <c r="AC5">
-        <v>2.9</v>
-      </c>
-      <c r="AD5">
-        <v>1.33</v>
-      </c>
-      <c r="AE5">
-        <v>1.09</v>
-      </c>
-      <c r="AF5">
-        <v>1.78</v>
-      </c>
-      <c r="AG5">
-        <v>1.89</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.14</v>
-      </c>
       <c r="AK5">
-        <v>2.38</v>
+        <v>1.2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P6">
-        <v>3.35</v>
+        <v>5.45</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="R6">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="S6">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U6">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V6">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="W6">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z6">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="AA6">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AB6">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AC6">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AD6">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AE6">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF6">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
-        <v>2.82</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK6">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.65</v>
+        <v>1.26</v>
       </c>
       <c r="O7">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>3.85</v>
+        <v>7.91</v>
       </c>
       <c r="Q7">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="R7">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S7">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="V7">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
+        <v>1.21</v>
+      </c>
+      <c r="Z7">
+        <v>3.94</v>
+      </c>
+      <c r="AA7">
+        <v>1.65</v>
+      </c>
+      <c r="AB7">
+        <v>1.95</v>
+      </c>
+      <c r="AC7">
+        <v>2.65</v>
+      </c>
+      <c r="AD7">
+        <v>1.43</v>
+      </c>
+      <c r="AE7">
+        <v>1.13</v>
+      </c>
+      <c r="AF7">
+        <v>2.06</v>
+      </c>
+      <c r="AG7">
+        <v>1.65</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.1</v>
       </c>
-      <c r="Z7">
-        <v>5.1</v>
-      </c>
-      <c r="AA7">
-        <v>1.44</v>
-      </c>
-      <c r="AB7">
-        <v>2.52</v>
-      </c>
-      <c r="AC7">
-        <v>2.1</v>
-      </c>
-      <c r="AD7">
-        <v>1.64</v>
-      </c>
-      <c r="AE7">
-        <v>1.25</v>
-      </c>
-      <c r="AF7">
-        <v>1.46</v>
-      </c>
-      <c r="AG7">
-        <v>2.55</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.16</v>
-      </c>
       <c r="AK7">
-        <v>2.06</v>
+        <v>3.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="O8">
         <v>4.5</v>
       </c>
       <c r="P8">
-        <v>5.45</v>
+        <v>4.7</v>
       </c>
       <c r="Q8">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="S8">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
+        <v>3.04</v>
+      </c>
+      <c r="U8">
+        <v>2.5</v>
+      </c>
+      <c r="V8">
+        <v>1.44</v>
+      </c>
+      <c r="W8">
+        <v>1.1</v>
+      </c>
+      <c r="X8">
+        <v>1.03</v>
+      </c>
+      <c r="Y8">
+        <v>1.19</v>
+      </c>
+      <c r="Z8">
         <v>3.75</v>
       </c>
-      <c r="U8">
-        <v>2.08</v>
-      </c>
-      <c r="V8">
-        <v>1.7</v>
-      </c>
-      <c r="W8">
+      <c r="AA8">
+        <v>1.66</v>
+      </c>
+      <c r="AB8">
+        <v>2</v>
+      </c>
+      <c r="AC8">
+        <v>2.9</v>
+      </c>
+      <c r="AD8">
+        <v>1.33</v>
+      </c>
+      <c r="AE8">
+        <v>1.09</v>
+      </c>
+      <c r="AF8">
+        <v>1.78</v>
+      </c>
+      <c r="AG8">
+        <v>1.89</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.14</v>
       </c>
-      <c r="X8">
-        <v>1.02</v>
-      </c>
-      <c r="Y8">
-        <v>1.09</v>
-      </c>
-      <c r="Z8">
-        <v>5.4</v>
-      </c>
-      <c r="AA8">
-        <v>1.39</v>
-      </c>
-      <c r="AB8">
-        <v>2.59</v>
-      </c>
-      <c r="AC8">
-        <v>2.07</v>
-      </c>
-      <c r="AD8">
-        <v>1.66</v>
-      </c>
-      <c r="AE8">
-        <v>1.25</v>
-      </c>
-      <c r="AF8">
-        <v>1.6</v>
-      </c>
-      <c r="AG8">
-        <v>2.25</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.11</v>
-      </c>
       <c r="AK8">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P9">
-        <v>2.57</v>
+        <v>3.35</v>
       </c>
       <c r="Q9">
-        <v>2.94</v>
+        <v>2.2</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S9">
+        <v>1.17</v>
+      </c>
+      <c r="T9">
+        <v>4</v>
+      </c>
+      <c r="U9">
+        <v>1.98</v>
+      </c>
+      <c r="V9">
+        <v>1.78</v>
+      </c>
+      <c r="W9">
+        <v>1.17</v>
+      </c>
+      <c r="X9">
+        <v>1.01</v>
+      </c>
+      <c r="Y9">
+        <v>1.06</v>
+      </c>
+      <c r="Z9">
+        <v>6.05</v>
+      </c>
+      <c r="AA9">
         <v>1.33</v>
       </c>
-      <c r="T9">
-        <v>3.12</v>
-      </c>
-      <c r="U9">
-        <v>2.47</v>
-      </c>
-      <c r="V9">
-        <v>1.44</v>
-      </c>
-      <c r="W9">
-        <v>1.11</v>
-      </c>
-      <c r="X9">
-        <v>1.04</v>
-      </c>
-      <c r="Y9">
-        <v>1.17</v>
-      </c>
-      <c r="Z9">
-        <v>3.6</v>
-      </c>
-      <c r="AA9">
-        <v>1.81</v>
-      </c>
       <c r="AB9">
-        <v>2.02</v>
+        <v>2.83</v>
       </c>
       <c r="AC9">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="AD9">
+        <v>1.77</v>
+      </c>
+      <c r="AE9">
+        <v>1.3</v>
+      </c>
+      <c r="AF9">
         <v>1.36</v>
       </c>
-      <c r="AE9">
-        <v>1.1</v>
-      </c>
-      <c r="AF9">
-        <v>1.57</v>
-      </c>
       <c r="AG9">
-        <v>2.25</v>
+        <v>2.82</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK9">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.26</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>7.91</v>
+        <v>2.57</v>
       </c>
       <c r="Q10">
-        <v>1.71</v>
+        <v>2.94</v>
       </c>
       <c r="R10">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U10">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="V10">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
         <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="AA10">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC10">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>2.06</v>
+        <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>3.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
         <v>1.38</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AK14">
         <v>1.36</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="O15">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="Q15">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S15">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T15">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U15">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="V15">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W15">
         <v>1.04</v>
@@ -2787,31 +2787,31 @@
         <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA15">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AB15">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC15">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
         <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>4</v>
       </c>
       <c r="R16">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="S16">
         <v>1.2</v>
@@ -2941,7 +2941,7 @@
         <v>1.95</v>
       </c>
       <c r="V16">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W16">
         <v>1.18</v>
@@ -2950,31 +2950,31 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="AA16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB16">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AC16">
         <v>1.95</v>
       </c>
       <c r="AD16">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AE16">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AF16">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG16">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK16">
         <v>1.17</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>5.5</v>
+        <v>3.66</v>
       </c>
       <c r="O21">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="P21">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="Q21">
-        <v>5.5</v>
+        <v>2.64</v>
       </c>
       <c r="R21">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="S21">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="T21">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="U21">
-        <v>2.62</v>
+        <v>3.48</v>
       </c>
       <c r="V21">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="Z21">
-        <v>3.73</v>
+        <v>2.7</v>
       </c>
       <c r="AA21">
+        <v>2.32</v>
+      </c>
+      <c r="AB21">
+        <v>1.57</v>
+      </c>
+      <c r="AC21">
+        <v>4.5</v>
+      </c>
+      <c r="AD21">
+        <v>1.14</v>
+      </c>
+      <c r="AE21">
+        <v>1.01</v>
+      </c>
+      <c r="AF21">
+        <v>2.13</v>
+      </c>
+      <c r="AG21">
+        <v>1.64</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>1.28</v>
+      </c>
+      <c r="AK21">
         <v>1.8</v>
-      </c>
-      <c r="AB21">
-        <v>1.95</v>
-      </c>
-      <c r="AC21">
-        <v>3.25</v>
-      </c>
-      <c r="AD21">
-        <v>1.35</v>
-      </c>
-      <c r="AE21">
-        <v>1.12</v>
-      </c>
-      <c r="AF21">
-        <v>1.89</v>
-      </c>
-      <c r="AG21">
-        <v>1.81</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.2</v>
-      </c>
-      <c r="AK21">
-        <v>1.1</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.66</v>
+        <v>5.5</v>
       </c>
       <c r="O22">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="P22">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="Q22">
-        <v>2.64</v>
+        <v>5.5</v>
       </c>
       <c r="R22">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="S22">
+        <v>1.32</v>
+      </c>
+      <c r="T22">
+        <v>2.85</v>
+      </c>
+      <c r="U22">
+        <v>2.62</v>
+      </c>
+      <c r="V22">
         <v>1.44</v>
       </c>
-      <c r="T22">
-        <v>2.45</v>
-      </c>
-      <c r="U22">
-        <v>3.48</v>
-      </c>
-      <c r="V22">
-        <v>1.3</v>
-      </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>2.7</v>
+        <v>3.73</v>
       </c>
       <c r="AA22">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AC22">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD22">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AE22">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AF22">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AG22">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5048,19 +5048,19 @@
         <v>2.41</v>
       </c>
       <c r="R29">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="S29">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T29">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U29">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V29">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W29">
         <v>1.13</v>
@@ -5069,7 +5069,7 @@
         <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z29">
         <v>4.75</v>
@@ -5081,13 +5081,13 @@
         <v>2.4</v>
       </c>
       <c r="AC29">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD29">
         <v>1.57</v>
       </c>
       <c r="AE29">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF29">
         <v>1.44</v>
@@ -5202,7 +5202,7 @@
         <v>1.79</v>
       </c>
       <c r="O30">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="P30">
         <v>3.88</v>
@@ -5211,7 +5211,7 @@
         <v>2.3</v>
       </c>
       <c r="R30">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S30">
         <v>1.29</v>
@@ -5241,16 +5241,16 @@
         <v>1.56</v>
       </c>
       <c r="AB30">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="AC30">
         <v>2.44</v>
       </c>
       <c r="AD30">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE30">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF30">
         <v>1.55</v>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5383,7 +5383,7 @@
         <v>3.42</v>
       </c>
       <c r="U31">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V31">
         <v>1.62</v>
@@ -5435,7 +5435,7 @@
         <v>1.72</v>
       </c>
       <c r="AK31">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6035,16 +6035,16 @@
         <v>3.6</v>
       </c>
       <c r="U35">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V35">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W35">
         <v>1.13</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.13</v>
@@ -6056,22 +6056,22 @@
         <v>1.51</v>
       </c>
       <c r="AB35">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AC35">
         <v>2.23</v>
       </c>
       <c r="AD35">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE35">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF35">
         <v>1.44</v>
       </c>
       <c r="AG35">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
         <v>1.65</v>
@@ -7807,16 +7807,16 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="O46">
         <v>4</v>
       </c>
       <c r="P46">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q46">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="R46">
         <v>2.5</v>
@@ -7840,16 +7840,16 @@
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5.75</v>
+        <v>6.11</v>
       </c>
       <c r="AA46">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AB46">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AC46">
         <v>2.1</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>2.06</v>
       </c>
       <c r="AK46">
         <v>1.23</v>
@@ -8003,10 +8003,10 @@
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Z47">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AA47">
         <v>1.28</v>
@@ -8018,10 +8018,10 @@
         <v>1.71</v>
       </c>
       <c r="AD47">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AE47">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AF47">
         <v>1.73</v>
@@ -8043,7 +8043,7 @@
         <v>1.04</v>
       </c>
       <c r="AK47">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O48">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -8157,7 +8157,7 @@
         <v>2.48</v>
       </c>
       <c r="V48">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W48">
         <v>1.07</v>
@@ -8172,7 +8172,7 @@
         <v>3.78</v>
       </c>
       <c r="AA48">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB48">
         <v>1.97</v>
@@ -8181,10 +8181,10 @@
         <v>2.74</v>
       </c>
       <c r="AD48">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF48">
         <v>1.6</v>
@@ -8206,7 +8206,7 @@
         <v>1.29</v>
       </c>
       <c r="AK48">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8836,7 +8836,7 @@
         <v>1.25</v>
       </c>
       <c r="AE52">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
         <v>1.81</v>
@@ -8972,7 +8972,7 @@
         <v>3.2</v>
       </c>
       <c r="V53">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W53">
         <v>1</v>
@@ -8981,22 +8981,22 @@
         <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z53">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AA53">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AB53">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC53">
         <v>4.5</v>
       </c>
       <c r="AD53">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE53">
         <v>1.05</v>
@@ -9005,7 +9005,7 @@
         <v>1.94</v>
       </c>
       <c r="AG53">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.32</v>
       </c>
       <c r="AK53">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -12054,7 +12054,7 @@
         <v>2.4</v>
       </c>
       <c r="Q72">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R72">
         <v>2.1</v>
@@ -12075,28 +12075,28 @@
         <v>1.05</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z72">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="AA72">
         <v>1.83</v>
       </c>
       <c r="AB72">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC72">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="AD72">
         <v>1.3</v>
       </c>
       <c r="AE72">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF72">
         <v>1.66</v>
@@ -12540,10 +12540,10 @@
         <v>3.7</v>
       </c>
       <c r="P75">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q75">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="R75">
         <v>2.33</v>
@@ -12555,10 +12555,10 @@
         <v>3.8</v>
       </c>
       <c r="U75">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V75">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W75">
         <v>1.14</v>
@@ -12582,7 +12582,7 @@
         <v>2.15</v>
       </c>
       <c r="AD75">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE75">
         <v>1.22</v>
@@ -12607,7 +12607,7 @@
         <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12709,13 +12709,13 @@
         <v>2</v>
       </c>
       <c r="R76">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="S76">
         <v>1.16</v>
       </c>
       <c r="T76">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U76">
         <v>1.85</v>
@@ -12724,7 +12724,7 @@
         <v>1.82</v>
       </c>
       <c r="W76">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X76">
         <v>1.01</v>
@@ -12736,16 +12736,16 @@
         <v>7.1</v>
       </c>
       <c r="AA76">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AB76">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AC76">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AD76">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AE76">
         <v>1.44</v>
@@ -12770,7 +12770,7 @@
         <v>1.19</v>
       </c>
       <c r="AK76">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="O83">
         <v>4.5</v>
@@ -13856,7 +13856,7 @@
         <v>1.2</v>
       </c>
       <c r="T83">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="U83">
         <v>1.95</v>
@@ -13880,7 +13880,7 @@
         <v>1.36</v>
       </c>
       <c r="AB83">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AC83">
         <v>2.04</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="O102">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P102">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="O117">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P117">
-        <v>6.5</v>
+        <v>5.77</v>
       </c>
       <c r="Q117">
         <v>1.88</v>
@@ -19712,7 +19712,7 @@
         <v>3.7</v>
       </c>
       <c r="P119">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q119">
         <v>2.4</v>
@@ -19724,10 +19724,10 @@
         <v>1.25</v>
       </c>
       <c r="T119">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U119">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="V119">
         <v>1.57</v>
@@ -19742,13 +19742,13 @@
         <v>1.2</v>
       </c>
       <c r="Z119">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA119">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB119">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AC119">
         <v>2.52</v>
@@ -19757,13 +19757,13 @@
         <v>1.5</v>
       </c>
       <c r="AE119">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF119">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG119">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>1.23</v>
       </c>
       <c r="AK119">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -21360,7 +21360,7 @@
         <v>3.14</v>
       </c>
       <c r="V129">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W129">
         <v>1.02</v>
@@ -21390,7 +21390,7 @@
         <v>1.02</v>
       </c>
       <c r="AF129">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG129">
         <v>1.73</v>
@@ -21409,7 +21409,7 @@
         <v>1.3</v>
       </c>
       <c r="AK129">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="O130">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P130">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q130">
         <v>3.5</v>
@@ -21526,7 +21526,7 @@
         <v>1.35</v>
       </c>
       <c r="W130">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X130">
         <v>1.06</v>
@@ -21538,7 +21538,7 @@
         <v>2.99</v>
       </c>
       <c r="AA130">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AB130">
         <v>1.7</v>
@@ -21553,7 +21553,7 @@
         <v>1.1</v>
       </c>
       <c r="AF130">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AG130">
         <v>1.9</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,80 +21662,80 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O131">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P131">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="R131">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S131">
         <v>1.36</v>
       </c>
       <c r="T131">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U131">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="V131">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W131">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X131">
         <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z131">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AA131">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB131">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AC131">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD131">
+        <v>1.22</v>
+      </c>
+      <c r="AE131">
+        <v>1.03</v>
+      </c>
+      <c r="AF131">
+        <v>1.76</v>
+      </c>
+      <c r="AG131">
+        <v>1.91</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ131">
         <v>1.25</v>
       </c>
-      <c r="AE131">
-        <v>1.05</v>
-      </c>
-      <c r="AF131">
-        <v>1.77</v>
-      </c>
-      <c r="AG131">
-        <v>1.9</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>1.2</v>
-      </c>
       <c r="AK131">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q132">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="R132">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S132">
         <v>1.36</v>
       </c>
       <c r="T132">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U132">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V132">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W132">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X132">
         <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z132">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AA132">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB132">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AC132">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD132">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE132">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF132">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG132">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK132">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22661,10 +22661,10 @@
         <v>3.5</v>
       </c>
       <c r="U137">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="V137">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W137">
         <v>1.13</v>
@@ -22694,10 +22694,10 @@
         <v>1.14</v>
       </c>
       <c r="AF137">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG137">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22966,10 +22966,10 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O139">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P139">
         <v>4</v>
@@ -22981,28 +22981,28 @@
         <v>2.23</v>
       </c>
       <c r="S139">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T139">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="U139">
         <v>2.5</v>
       </c>
       <c r="V139">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W139">
         <v>1.07</v>
       </c>
       <c r="X139">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y139">
         <v>1.23</v>
       </c>
       <c r="Z139">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA139">
         <v>1.85</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK139">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -25094,7 +25094,7 @@
         <v>2.7</v>
       </c>
       <c r="Q152">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="R152">
         <v>2.09</v>
@@ -25124,25 +25124,25 @@
         <v>3.1</v>
       </c>
       <c r="AA152">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB152">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC152">
         <v>2.81</v>
       </c>
       <c r="AD152">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE152">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF152">
         <v>1.6</v>
       </c>
       <c r="AG152">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK152">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25423,7 +25423,7 @@
         <v>2.1</v>
       </c>
       <c r="R154">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S154">
         <v>1.34</v>
@@ -25465,10 +25465,10 @@
         <v>1.12</v>
       </c>
       <c r="AF154">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG154">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK154">
         <v>2.15</v>
@@ -26235,13 +26235,13 @@
         <v>2.06</v>
       </c>
       <c r="Q159">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="R159">
         <v>2</v>
       </c>
       <c r="S159">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T159">
         <v>2.62</v>
@@ -26250,7 +26250,7 @@
         <v>3.22</v>
       </c>
       <c r="V159">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W159">
         <v>1.02</v>
@@ -26265,7 +26265,7 @@
         <v>2.76</v>
       </c>
       <c r="AA159">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AB159">
         <v>1.63</v>
@@ -26283,7 +26283,7 @@
         <v>1.95</v>
       </c>
       <c r="AG159">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O160">
         <v>3.2</v>
@@ -26428,10 +26428,10 @@
         <v>3.05</v>
       </c>
       <c r="AA160">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB160">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC160">
         <v>3.6</v>
@@ -26721,7 +26721,7 @@
         <v>3.1</v>
       </c>
       <c r="P162">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q162">
         <v>3</v>
@@ -26733,7 +26733,7 @@
         <v>1.38</v>
       </c>
       <c r="T162">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="U162">
         <v>2.99</v>
@@ -26769,10 +26769,10 @@
         <v>1.04</v>
       </c>
       <c r="AF162">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG162">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>1.3</v>
       </c>
       <c r="AK162">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26878,10 +26878,10 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O163">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P163">
         <v>2.87</v>
@@ -26908,10 +26908,10 @@
         <v>1.06</v>
       </c>
       <c r="X163">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y163">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z163">
         <v>2.83</v>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK163">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27041,19 +27041,19 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="O164">
         <v>3.1</v>
       </c>
       <c r="P164">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q164">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="R164">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S164">
         <v>1.45</v>
@@ -27062,7 +27062,7 @@
         <v>2.53</v>
       </c>
       <c r="U164">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="V164">
         <v>1.32</v>
@@ -27077,16 +27077,16 @@
         <v>1.38</v>
       </c>
       <c r="Z164">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AA164">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB164">
         <v>1.66</v>
       </c>
       <c r="AC164">
-        <v>4.04</v>
+        <v>4.07</v>
       </c>
       <c r="AD164">
         <v>1.18</v>
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="O173">
-        <v>9.6</v>
+        <v>17.28</v>
       </c>
       <c r="P173">
-        <v>42</v>
+        <v>24.07</v>
       </c>
       <c r="Q173">
         <v>1.24</v>
@@ -28529,10 +28529,10 @@
         <v>6.1</v>
       </c>
       <c r="U173">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V173">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W173">
         <v>1.36</v>
@@ -28553,19 +28553,19 @@
         <v>4.3</v>
       </c>
       <c r="AC173">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AD173">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AE173">
         <v>1.64</v>
       </c>
       <c r="AF173">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="AG173">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         </is>
       </c>
       <c r="N179">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="O179">
         <v>3.8</v>
@@ -29495,7 +29495,7 @@
         <v>1.61</v>
       </c>
       <c r="Q179">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R179">
         <v>2.21</v>
@@ -29507,10 +29507,10 @@
         <v>2.94</v>
       </c>
       <c r="U179">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="V179">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W179">
         <v>1.05</v>
@@ -29543,7 +29543,7 @@
         <v>1.75</v>
       </c>
       <c r="AG179">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>2.59</v>
       </c>
       <c r="V181">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W181">
         <v>1.06</v>
@@ -29869,7 +29869,7 @@
         <v>1.62</v>
       </c>
       <c r="AG181">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -30630,10 +30630,10 @@
         <v>18</v>
       </c>
       <c r="O186">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P186">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Q186">
         <v>15</v>
@@ -30645,7 +30645,7 @@
         <v>1.13</v>
       </c>
       <c r="T186">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="U186">
         <v>1.89</v>
@@ -30654,7 +30654,7 @@
         <v>1.81</v>
       </c>
       <c r="W186">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="X186">
         <v>1.01</v>
@@ -31285,13 +31285,13 @@
         <v>4.8</v>
       </c>
       <c r="P190">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Q190">
-        <v>7.5</v>
+        <v>5.51</v>
       </c>
       <c r="R190">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="S190">
         <v>1.32</v>
@@ -31300,10 +31300,10 @@
         <v>3.15</v>
       </c>
       <c r="U190">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V190">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W190">
         <v>1.09</v>
@@ -31318,10 +31318,10 @@
         <v>4</v>
       </c>
       <c r="AA190">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB190">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC190">
         <v>2.75</v>
@@ -31336,7 +31336,7 @@
         <v>2</v>
       </c>
       <c r="AG190">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK190">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31448,7 +31448,7 @@
         <v>4.6</v>
       </c>
       <c r="P191">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Q191">
         <v>8</v>
@@ -31463,10 +31463,10 @@
         <v>2.94</v>
       </c>
       <c r="U191">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V191">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W191">
         <v>1.1</v>
@@ -31484,7 +31484,7 @@
         <v>1.95</v>
       </c>
       <c r="AB191">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC191">
         <v>3.24</v>
@@ -31789,13 +31789,13 @@
         <v>3.4</v>
       </c>
       <c r="U193">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V193">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W193">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X193">
         <v>1.01</v>
@@ -31822,10 +31822,10 @@
         <v>1.15</v>
       </c>
       <c r="AF193">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG193">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>1.73</v>
       </c>
       <c r="W195">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X195">
         <v>1.01</v>
@@ -32133,19 +32133,19 @@
         <v>5.35</v>
       </c>
       <c r="AA195">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AB195">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AC195">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AD195">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE195">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF195">
         <v>1.64</v>
@@ -32167,7 +32167,7 @@
         <v>1.11</v>
       </c>
       <c r="AK195">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32746,19 +32746,19 @@
         </is>
       </c>
       <c r="N199">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O199">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P199">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q199">
         <v>4.48</v>
       </c>
       <c r="R199">
-        <v>2.55</v>
+        <v>2.26</v>
       </c>
       <c r="S199">
         <v>1.34</v>
@@ -32779,10 +32779,10 @@
         <v>1.01</v>
       </c>
       <c r="Y199">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z199">
-        <v>4.53</v>
+        <v>3.95</v>
       </c>
       <c r="AA199">
         <v>1.62</v>
@@ -32794,7 +32794,7 @@
         <v>2.7</v>
       </c>
       <c r="AD199">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE199">
         <v>1.14</v>
@@ -32803,7 +32803,7 @@
         <v>1.63</v>
       </c>
       <c r="AG199">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.18</v>
+        <v>2.5</v>
       </c>
       <c r="AK199">
         <v>1.1</v>
@@ -32918,7 +32918,7 @@
         <v>2.1</v>
       </c>
       <c r="Q200">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R200">
         <v>2.25</v>
@@ -32927,7 +32927,7 @@
         <v>1.28</v>
       </c>
       <c r="T200">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U200">
         <v>2.39</v>
@@ -32945,7 +32945,7 @@
         <v>1.18</v>
       </c>
       <c r="Z200">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA200">
         <v>1.67</v>
@@ -33265,7 +33265,7 @@
         <v>1.1</v>
       </c>
       <c r="X202">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y202">
         <v>1.17</v>
@@ -33292,7 +33292,7 @@
         <v>1.63</v>
       </c>
       <c r="AG202">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O203">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P203">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="Q203">
         <v>2.02</v>
@@ -33434,7 +33434,7 @@
         <v>1.22</v>
       </c>
       <c r="Z203">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA203">
         <v>1.78</v>
@@ -33446,10 +33446,10 @@
         <v>2.9</v>
       </c>
       <c r="AD203">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE203">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF203">
         <v>1.72</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.87</v>
+        <v>2.7</v>
       </c>
       <c r="O204">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="P204">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S204">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T204">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U204">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V204">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W204">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X204">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y204">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z204">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA204">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="AB204">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AC204">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AD204">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE204">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF204">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG204">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK204">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.7</v>
+        <v>1.87</v>
       </c>
       <c r="O205">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="P205">
+        <v>5.1</v>
+      </c>
+      <c r="Q205">
+        <v>0</v>
+      </c>
+      <c r="R205">
+        <v>0</v>
+      </c>
+      <c r="S205">
+        <v>0</v>
+      </c>
+      <c r="T205">
+        <v>0</v>
+      </c>
+      <c r="U205">
+        <v>0</v>
+      </c>
+      <c r="V205">
+        <v>0</v>
+      </c>
+      <c r="W205">
+        <v>0</v>
+      </c>
+      <c r="X205">
+        <v>0</v>
+      </c>
+      <c r="Y205">
+        <v>0</v>
+      </c>
+      <c r="Z205">
+        <v>0</v>
+      </c>
+      <c r="AA205">
         <v>2.87</v>
       </c>
-      <c r="Q205">
-        <v>3.37</v>
-      </c>
-      <c r="R205">
-        <v>1.75</v>
-      </c>
-      <c r="S205">
-        <v>1.7</v>
-      </c>
-      <c r="T205">
-        <v>2.1</v>
-      </c>
-      <c r="U205">
-        <v>4.4</v>
-      </c>
-      <c r="V205">
-        <v>1.14</v>
-      </c>
-      <c r="W205">
-        <v>1.02</v>
-      </c>
-      <c r="X205">
-        <v>1.18</v>
-      </c>
-      <c r="Y205">
-        <v>1.81</v>
-      </c>
-      <c r="Z205">
-        <v>1.94</v>
-      </c>
-      <c r="AA205">
-        <v>3.2</v>
-      </c>
       <c r="AB205">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AC205">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AD205">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE205">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF205">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG205">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK205">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34379,10 +34379,10 @@
         <v>2.2</v>
       </c>
       <c r="O209">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P209">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="Q209">
         <v>2.7</v>
@@ -34406,13 +34406,13 @@
         <v>1.05</v>
       </c>
       <c r="X209">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y209">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z209">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA209">
         <v>1.95</v>
@@ -34539,7 +34539,7 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="O210">
         <v>3.6</v>
@@ -34551,7 +34551,7 @@
         <v>2.93</v>
       </c>
       <c r="R210">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S210">
         <v>1.28</v>
@@ -34560,10 +34560,10 @@
         <v>3.48</v>
       </c>
       <c r="U210">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V210">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W210">
         <v>1.14</v>
@@ -34572,16 +34572,16 @@
         <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z210">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA210">
         <v>1.6</v>
       </c>
       <c r="AB210">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AC210">
         <v>2.38</v>
@@ -34596,7 +34596,7 @@
         <v>1.4</v>
       </c>
       <c r="AG210">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AK210">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -35031,10 +35031,10 @@
         <v>1.8</v>
       </c>
       <c r="O213">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P213">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q213">
         <v>2.5</v>
@@ -35052,7 +35052,7 @@
         <v>3.15</v>
       </c>
       <c r="V213">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W213">
         <v>1.03</v>
@@ -35082,7 +35082,7 @@
         <v>1.03</v>
       </c>
       <c r="AF213">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AG213">
         <v>1.71</v>
@@ -35215,31 +35215,31 @@
         <v>3.2</v>
       </c>
       <c r="V214">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W214">
         <v>1.02</v>
       </c>
       <c r="X214">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y214">
         <v>1.36</v>
       </c>
       <c r="Z214">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA214">
         <v>2.23</v>
       </c>
       <c r="AB214">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC214">
         <v>4.7</v>
       </c>
       <c r="AD214">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE214">
         <v>1.05</v>
@@ -35354,7 +35354,7 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O215">
         <v>3.3</v>
@@ -35363,10 +35363,10 @@
         <v>3.25</v>
       </c>
       <c r="Q215">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="R215">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S215">
         <v>1.36</v>
@@ -35411,7 +35411,7 @@
         <v>1.67</v>
       </c>
       <c r="AG215">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>1.24</v>
       </c>
       <c r="AK215">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="O216">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P216">
         <v>2.15</v>
       </c>
       <c r="Q216">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R216">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="S216">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T216">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="U216">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V216">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W216">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X216">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y216">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="Z216">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AA216">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="AB216">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC216">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD216">
         <v>1.2</v>
       </c>
       <c r="AE216">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF216">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG216">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK216">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,64 +35680,64 @@
         </is>
       </c>
       <c r="N217">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O217">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P217">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q217">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="R217">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="S217">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T217">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="U217">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="V217">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W217">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X217">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y217">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="Z217">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AA217">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AB217">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC217">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD217">
         <v>1.2</v>
       </c>
       <c r="AE217">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF217">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG217">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AK217">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35843,64 +35843,64 @@
         </is>
       </c>
       <c r="N218">
-        <v>4.87</v>
+        <v>5.25</v>
       </c>
       <c r="O218">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P218">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Q218">
-        <v>6.41</v>
+        <v>6.45</v>
       </c>
       <c r="R218">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S218">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T218">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U218">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="V218">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W218">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X218">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y218">
         <v>1.31</v>
       </c>
       <c r="Z218">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AA218">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="AB218">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC218">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD218">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE218">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF218">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AG218">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK218">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36332,10 +36332,10 @@
         </is>
       </c>
       <c r="N221">
-        <v>4.69</v>
+        <v>4.15</v>
       </c>
       <c r="O221">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P221">
         <v>1.65</v>
@@ -36344,13 +36344,13 @@
         <v>5.05</v>
       </c>
       <c r="R221">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S221">
         <v>1.35</v>
       </c>
       <c r="T221">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="U221">
         <v>2.69</v>
@@ -36386,7 +36386,7 @@
         <v>1.1</v>
       </c>
       <c r="AF221">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG221">
         <v>1.88</v>
@@ -36402,7 +36402,7 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK221">
         <v>1.12</v>
@@ -36498,7 +36498,7 @@
         <v>1.64</v>
       </c>
       <c r="O222">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P222">
         <v>4.95</v>
@@ -36510,16 +36510,16 @@
         <v>2.04</v>
       </c>
       <c r="S222">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T222">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="U222">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="V222">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W222">
         <v>1.07</v>
@@ -36534,7 +36534,7 @@
         <v>3.1</v>
       </c>
       <c r="AA222">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AB222">
         <v>1.62</v>
@@ -36658,64 +36658,64 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O223">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P223">
-        <v>5.2</v>
+        <v>4.13</v>
       </c>
       <c r="Q223">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R223">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="S223">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T223">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="U223">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="V223">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W223">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X223">
         <v>1.01</v>
       </c>
       <c r="Y223">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z223">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="AA223">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AB223">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AC223">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AD223">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE223">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF223">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG223">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK223">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.37</v>
+        <v>1.1</v>
       </c>
       <c r="O227">
-        <v>2.95</v>
+        <v>9.25</v>
       </c>
       <c r="P227">
-        <v>2.85</v>
+        <v>12</v>
       </c>
       <c r="Q227">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="R227">
-        <v>2</v>
+        <v>3.12</v>
       </c>
       <c r="S227">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="T227">
-        <v>2.36</v>
+        <v>3.17</v>
       </c>
       <c r="U227">
-        <v>3.33</v>
+        <v>2.01</v>
       </c>
       <c r="V227">
-        <v>1.29</v>
+        <v>1.76</v>
       </c>
       <c r="W227">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="X227">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y227">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="Z227">
-        <v>2.56</v>
+        <v>5.95</v>
       </c>
       <c r="AA227">
-        <v>2.28</v>
+        <v>1.42</v>
       </c>
       <c r="AB227">
-        <v>1.56</v>
+        <v>2.7</v>
       </c>
       <c r="AC227">
-        <v>4.33</v>
+        <v>1.98</v>
       </c>
       <c r="AD227">
-        <v>1.2</v>
+        <v>1.78</v>
       </c>
       <c r="AE227">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AF227">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AG227">
-        <v>1.87</v>
+        <v>1.51</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AK227">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,80 +37473,80 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="O228">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="P228">
-        <v>9.699999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="Q228">
-        <v>1.62</v>
+        <v>3.2</v>
       </c>
       <c r="R228">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="S228">
+        <v>1.5</v>
+      </c>
+      <c r="T228">
+        <v>2.36</v>
+      </c>
+      <c r="U228">
+        <v>3.33</v>
+      </c>
+      <c r="V228">
         <v>1.29</v>
       </c>
-      <c r="T228">
-        <v>3.17</v>
-      </c>
-      <c r="U228">
-        <v>2.5</v>
-      </c>
-      <c r="V228">
-        <v>1.5</v>
-      </c>
       <c r="W228">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X228">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y228">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="Z228">
-        <v>4.1</v>
+        <v>2.56</v>
       </c>
       <c r="AA228">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="AB228">
-        <v>2.23</v>
+        <v>1.57</v>
       </c>
       <c r="AC228">
-        <v>2.46</v>
+        <v>4.33</v>
       </c>
       <c r="AD228">
+        <v>1.2</v>
+      </c>
+      <c r="AE228">
+        <v>1.06</v>
+      </c>
+      <c r="AF228">
+        <v>1.85</v>
+      </c>
+      <c r="AG228">
+        <v>1.8</v>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ228">
+        <v>1.36</v>
+      </c>
+      <c r="AK228">
         <v>1.44</v>
-      </c>
-      <c r="AE228">
-        <v>1.18</v>
-      </c>
-      <c r="AF228">
-        <v>2.45</v>
-      </c>
-      <c r="AG228">
-        <v>1.5</v>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ228">
-        <v>1.08</v>
-      </c>
-      <c r="AK228">
-        <v>3.25</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -38949,10 +38949,10 @@
         <v>3.63</v>
       </c>
       <c r="Q237">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R237">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="S237">
         <v>1.45</v>
@@ -38964,7 +38964,7 @@
         <v>3.4</v>
       </c>
       <c r="V237">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W237">
         <v>1.03</v>
@@ -38976,10 +38976,10 @@
         <v>1.37</v>
       </c>
       <c r="Z237">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AA237">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AB237">
         <v>1.58</v>
@@ -38988,13 +38988,13 @@
         <v>4.2</v>
       </c>
       <c r="AD237">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE237">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF237">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG237">
         <v>1.75</v>
@@ -39106,10 +39106,10 @@
         <v>2.2</v>
       </c>
       <c r="O238">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P238">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="Q238">
         <v>2.95</v>
@@ -39118,10 +39118,10 @@
         <v>2.15</v>
       </c>
       <c r="S238">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T238">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U238">
         <v>2.62</v>
@@ -39130,7 +39130,7 @@
         <v>1.42</v>
       </c>
       <c r="W238">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X238">
         <v>1</v>
@@ -39592,7 +39592,7 @@
         </is>
       </c>
       <c r="N241">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="O241">
         <v>4.2</v>
@@ -39619,22 +39619,22 @@
         <v>1.47</v>
       </c>
       <c r="W241">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X241">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y241">
         <v>1.17</v>
       </c>
       <c r="Z241">
-        <v>3.94</v>
+        <v>4.3</v>
       </c>
       <c r="AA241">
         <v>1.56</v>
       </c>
       <c r="AB241">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AC241">
         <v>2.62</v>
@@ -39649,7 +39649,7 @@
         <v>1.84</v>
       </c>
       <c r="AG241">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>3.98</v>
       </c>
       <c r="Q243">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R243">
         <v>2</v>
@@ -39936,25 +39936,25 @@
         <v>1.46</v>
       </c>
       <c r="T243">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U243">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="V243">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W243">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X243">
         <v>1.06</v>
       </c>
       <c r="Y243">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z243">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA243">
         <v>2.19</v>
@@ -39969,13 +39969,13 @@
         <v>1.2</v>
       </c>
       <c r="AE243">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF243">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG243">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK243">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -41059,7 +41059,7 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="O250">
         <v>4.1</v>
@@ -41068,7 +41068,7 @@
         <v>5</v>
       </c>
       <c r="Q250">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R250">
         <v>2.25</v>
@@ -41095,7 +41095,7 @@
         <v>1.23</v>
       </c>
       <c r="Z250">
-        <v>4.11</v>
+        <v>4.17</v>
       </c>
       <c r="AA250">
         <v>1.72</v>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK250">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AL250">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="O3">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="P3">
-        <v>2.05</v>
+        <v>5.45</v>
       </c>
       <c r="Q3">
-        <v>3.46</v>
+        <v>1.85</v>
       </c>
       <c r="R3">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="S3">
         <v>1.25</v>
       </c>
       <c r="T3">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U3">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="W3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z3">
-        <v>4.45</v>
+        <v>5.4</v>
       </c>
       <c r="AA3">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AB3">
-        <v>2.16</v>
+        <v>2.59</v>
       </c>
       <c r="AC3">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="AD3">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AE3">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF3">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AG3">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK3">
-        <v>1.36</v>
+        <v>2.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.65</v>
+        <v>1.26</v>
       </c>
       <c r="O4">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>3.85</v>
+        <v>7.91</v>
       </c>
       <c r="Q4">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="R4">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S4">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="U4">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="V4">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W4">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
+        <v>1.21</v>
+      </c>
+      <c r="Z4">
+        <v>3.94</v>
+      </c>
+      <c r="AA4">
+        <v>1.65</v>
+      </c>
+      <c r="AB4">
+        <v>1.95</v>
+      </c>
+      <c r="AC4">
+        <v>2.65</v>
+      </c>
+      <c r="AD4">
+        <v>1.43</v>
+      </c>
+      <c r="AE4">
+        <v>1.13</v>
+      </c>
+      <c r="AF4">
+        <v>2.06</v>
+      </c>
+      <c r="AG4">
+        <v>1.65</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.1</v>
       </c>
-      <c r="Z4">
-        <v>5.1</v>
-      </c>
-      <c r="AA4">
-        <v>1.44</v>
-      </c>
-      <c r="AB4">
-        <v>2.52</v>
-      </c>
-      <c r="AC4">
-        <v>2.1</v>
-      </c>
-      <c r="AD4">
-        <v>1.64</v>
-      </c>
-      <c r="AE4">
-        <v>1.25</v>
-      </c>
-      <c r="AF4">
-        <v>1.46</v>
-      </c>
-      <c r="AG4">
-        <v>2.55</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.16</v>
-      </c>
       <c r="AK4">
-        <v>2.06</v>
+        <v>3.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.31</v>
+        <v>2.65</v>
       </c>
       <c r="O5">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="P5">
-        <v>1.68</v>
+        <v>3.85</v>
       </c>
       <c r="Q5">
-        <v>3.45</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="S5">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T5">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U5">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z5">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA5">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AB5">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="AC5">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="AD5">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF5">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AG5">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>1.2</v>
+        <v>2.06</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.4</v>
+        <v>3.31</v>
       </c>
       <c r="O6">
         <v>4.5</v>
       </c>
       <c r="P6">
-        <v>5.45</v>
+        <v>1.68</v>
       </c>
       <c r="Q6">
-        <v>1.85</v>
+        <v>3.45</v>
       </c>
       <c r="R6">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T6">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U6">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="W6">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z6">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA6">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AB6">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AC6">
-        <v>2.07</v>
+        <v>2.47</v>
       </c>
       <c r="AD6">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AE6">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AG6">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AK6">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>2.25</v>
       </c>
       <c r="O7">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>7.91</v>
+        <v>2.57</v>
       </c>
       <c r="Q7">
-        <v>1.71</v>
+        <v>2.94</v>
       </c>
       <c r="R7">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U7">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="V7">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="AA7">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB7">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC7">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="AD7">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>2.06</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>3.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
+        <v>2.9</v>
+      </c>
+      <c r="O8">
+        <v>3.8</v>
+      </c>
+      <c r="P8">
+        <v>2.05</v>
+      </c>
+      <c r="Q8">
+        <v>3.46</v>
+      </c>
+      <c r="R8">
+        <v>2.32</v>
+      </c>
+      <c r="S8">
+        <v>1.25</v>
+      </c>
+      <c r="T8">
+        <v>3.5</v>
+      </c>
+      <c r="U8">
+        <v>2.3</v>
+      </c>
+      <c r="V8">
+        <v>1.55</v>
+      </c>
+      <c r="W8">
+        <v>1.15</v>
+      </c>
+      <c r="X8">
+        <v>1.01</v>
+      </c>
+      <c r="Y8">
+        <v>1.14</v>
+      </c>
+      <c r="Z8">
+        <v>4.45</v>
+      </c>
+      <c r="AA8">
+        <v>1.57</v>
+      </c>
+      <c r="AB8">
+        <v>2.16</v>
+      </c>
+      <c r="AC8">
+        <v>2.34</v>
+      </c>
+      <c r="AD8">
         <v>1.46</v>
       </c>
-      <c r="O8">
-        <v>4.5</v>
-      </c>
-      <c r="P8">
-        <v>4.7</v>
-      </c>
-      <c r="Q8">
-        <v>2.1</v>
-      </c>
-      <c r="R8">
-        <v>2.18</v>
-      </c>
-      <c r="S8">
-        <v>1.3</v>
-      </c>
-      <c r="T8">
-        <v>3.04</v>
-      </c>
-      <c r="U8">
-        <v>2.5</v>
-      </c>
-      <c r="V8">
-        <v>1.44</v>
-      </c>
-      <c r="W8">
-        <v>1.1</v>
-      </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>1.19</v>
-      </c>
-      <c r="Z8">
-        <v>3.75</v>
-      </c>
-      <c r="AA8">
-        <v>1.66</v>
-      </c>
-      <c r="AB8">
-        <v>2</v>
-      </c>
-      <c r="AC8">
-        <v>2.9</v>
-      </c>
-      <c r="AD8">
-        <v>1.33</v>
-      </c>
       <c r="AE8">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF8">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AG8">
-        <v>1.89</v>
+        <v>2.41</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>2.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="O9">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P9">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="Q9">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R9">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="S9">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
-        <v>4</v>
+        <v>3.04</v>
       </c>
       <c r="U9">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="V9">
+        <v>1.44</v>
+      </c>
+      <c r="W9">
+        <v>1.1</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>1.19</v>
+      </c>
+      <c r="Z9">
+        <v>3.75</v>
+      </c>
+      <c r="AA9">
+        <v>1.66</v>
+      </c>
+      <c r="AB9">
+        <v>2</v>
+      </c>
+      <c r="AC9">
+        <v>2.9</v>
+      </c>
+      <c r="AD9">
+        <v>1.33</v>
+      </c>
+      <c r="AE9">
+        <v>1.09</v>
+      </c>
+      <c r="AF9">
         <v>1.78</v>
       </c>
-      <c r="W9">
-        <v>1.17</v>
-      </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
-        <v>1.06</v>
-      </c>
-      <c r="Z9">
-        <v>6.05</v>
-      </c>
-      <c r="AA9">
-        <v>1.33</v>
-      </c>
-      <c r="AB9">
-        <v>2.83</v>
-      </c>
-      <c r="AC9">
-        <v>1.92</v>
-      </c>
-      <c r="AD9">
-        <v>1.77</v>
-      </c>
-      <c r="AE9">
-        <v>1.3</v>
-      </c>
-      <c r="AF9">
-        <v>1.36</v>
-      </c>
       <c r="AG9">
-        <v>2.82</v>
+        <v>1.89</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK9">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P10">
-        <v>2.57</v>
+        <v>3.35</v>
       </c>
       <c r="Q10">
-        <v>2.94</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S10">
+        <v>1.17</v>
+      </c>
+      <c r="T10">
+        <v>4</v>
+      </c>
+      <c r="U10">
+        <v>1.98</v>
+      </c>
+      <c r="V10">
+        <v>1.78</v>
+      </c>
+      <c r="W10">
+        <v>1.17</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.06</v>
+      </c>
+      <c r="Z10">
+        <v>6.05</v>
+      </c>
+      <c r="AA10">
         <v>1.33</v>
       </c>
-      <c r="T10">
-        <v>3.12</v>
-      </c>
-      <c r="U10">
-        <v>2.47</v>
-      </c>
-      <c r="V10">
-        <v>1.44</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.04</v>
-      </c>
-      <c r="Y10">
-        <v>1.17</v>
-      </c>
-      <c r="Z10">
-        <v>3.6</v>
-      </c>
-      <c r="AA10">
-        <v>1.81</v>
-      </c>
       <c r="AB10">
-        <v>2.02</v>
+        <v>2.83</v>
       </c>
       <c r="AC10">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="AD10">
+        <v>1.77</v>
+      </c>
+      <c r="AE10">
+        <v>1.3</v>
+      </c>
+      <c r="AF10">
         <v>1.36</v>
       </c>
-      <c r="AE10">
-        <v>1.1</v>
-      </c>
-      <c r="AF10">
-        <v>1.57</v>
-      </c>
       <c r="AG10">
-        <v>2.25</v>
+        <v>2.82</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="P29">
-        <v>2.95</v>
+        <v>3.88</v>
       </c>
       <c r="Q29">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="R29">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="S29">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U29">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="W29">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA29">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB29">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AC29">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AD29">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE29">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG29">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="O30">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>3.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q30">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="R30">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T30">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U30">
+        <v>2.25</v>
+      </c>
+      <c r="V30">
+        <v>1.59</v>
+      </c>
+      <c r="W30">
+        <v>1.13</v>
+      </c>
+      <c r="X30">
+        <v>1.03</v>
+      </c>
+      <c r="Y30">
+        <v>1.14</v>
+      </c>
+      <c r="Z30">
+        <v>4.75</v>
+      </c>
+      <c r="AA30">
+        <v>1.57</v>
+      </c>
+      <c r="AB30">
         <v>2.4</v>
       </c>
-      <c r="V30">
-        <v>1.53</v>
-      </c>
-      <c r="W30">
-        <v>1.08</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.2</v>
-      </c>
-      <c r="Z30">
-        <v>4.5</v>
-      </c>
-      <c r="AA30">
-        <v>1.56</v>
-      </c>
-      <c r="AB30">
-        <v>2.26</v>
-      </c>
       <c r="AC30">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AD30">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE30">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF30">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG30">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6201,7 +6201,7 @@
         <v>2.4</v>
       </c>
       <c r="V36">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
         <v>1.11</v>
@@ -6222,7 +6222,7 @@
         <v>2.1</v>
       </c>
       <c r="AC36">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AD36">
         <v>1.4</v>
@@ -6231,10 +6231,10 @@
         <v>1.12</v>
       </c>
       <c r="AF36">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG36">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -9437,34 +9437,34 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O56">
+        <v>3.4</v>
+      </c>
+      <c r="P56">
+        <v>2.6</v>
+      </c>
+      <c r="Q56">
+        <v>2.88</v>
+      </c>
+      <c r="R56">
+        <v>2.25</v>
+      </c>
+      <c r="S56">
+        <v>1.29</v>
+      </c>
+      <c r="T56">
         <v>3.3</v>
       </c>
-      <c r="P56">
-        <v>2.4</v>
-      </c>
-      <c r="Q56">
-        <v>2.78</v>
-      </c>
-      <c r="R56">
-        <v>2.21</v>
-      </c>
-      <c r="S56">
-        <v>1.28</v>
-      </c>
-      <c r="T56">
-        <v>3.14</v>
-      </c>
       <c r="U56">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="V56">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W56">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
         <v>1.03</v>
@@ -9473,22 +9473,22 @@
         <v>1.16</v>
       </c>
       <c r="Z56">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA56">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB56">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC56">
         <v>2.56</v>
       </c>
       <c r="AD56">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE56">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF56">
         <v>1.53</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="O63">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P63">
         <v>3.42</v>
@@ -10590,7 +10590,7 @@
         <v>2.8</v>
       </c>
       <c r="R63">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S63">
         <v>1.48</v>
@@ -10620,7 +10620,7 @@
         <v>2.25</v>
       </c>
       <c r="AB63">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC63">
         <v>4.5</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O132">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P132">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q132">
+        <v>2.38</v>
+      </c>
+      <c r="R132">
+        <v>2.17</v>
+      </c>
+      <c r="S132">
+        <v>1.3</v>
+      </c>
+      <c r="T132">
+        <v>3.1</v>
+      </c>
+      <c r="U132">
         <v>2.5</v>
       </c>
-      <c r="R132">
-        <v>2.05</v>
-      </c>
-      <c r="S132">
-        <v>1.36</v>
-      </c>
-      <c r="T132">
-        <v>2.9</v>
-      </c>
-      <c r="U132">
-        <v>2.82</v>
-      </c>
       <c r="V132">
+        <v>1.5</v>
+      </c>
+      <c r="W132">
+        <v>1.1</v>
+      </c>
+      <c r="X132">
+        <v>1.03</v>
+      </c>
+      <c r="Y132">
+        <v>1.18</v>
+      </c>
+      <c r="Z132">
+        <v>3.92</v>
+      </c>
+      <c r="AA132">
+        <v>1.69</v>
+      </c>
+      <c r="AB132">
+        <v>2.11</v>
+      </c>
+      <c r="AC132">
+        <v>2.62</v>
+      </c>
+      <c r="AD132">
         <v>1.38</v>
       </c>
-      <c r="W132">
-        <v>1.06</v>
-      </c>
-      <c r="X132">
-        <v>1.01</v>
-      </c>
-      <c r="Y132">
-        <v>1.27</v>
-      </c>
-      <c r="Z132">
-        <v>3.14</v>
-      </c>
-      <c r="AA132">
-        <v>2.05</v>
-      </c>
-      <c r="AB132">
-        <v>1.81</v>
-      </c>
-      <c r="AC132">
-        <v>3.28</v>
-      </c>
-      <c r="AD132">
-        <v>1.25</v>
-      </c>
       <c r="AE132">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF132">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AG132">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK132">
         <v>1.8</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O133">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P133">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q133">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R133">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S133">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T133">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U133">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="V133">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W133">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X133">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z133">
-        <v>3.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA133">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="AB133">
-        <v>2.11</v>
+        <v>1.81</v>
       </c>
       <c r="AC133">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="AD133">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE133">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF133">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AG133">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK133">
         <v>1.8</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="O152">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P152">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q152">
         <v>2.96</v>
@@ -25106,13 +25106,13 @@
         <v>2.7</v>
       </c>
       <c r="U152">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="V152">
         <v>1.45</v>
       </c>
       <c r="W152">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X152">
         <v>1.02</v>
@@ -25121,22 +25121,22 @@
         <v>1.21</v>
       </c>
       <c r="Z152">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA152">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB152">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC152">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AD152">
         <v>1.34</v>
       </c>
       <c r="AE152">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF152">
         <v>1.6</v>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AK152">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25583,55 +25583,55 @@
         <v>4.84</v>
       </c>
       <c r="Q155">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="R155">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S155">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T155">
-        <v>3.28</v>
+        <v>2.6</v>
       </c>
       <c r="U155">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V155">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W155">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X155">
         <v>0</v>
       </c>
       <c r="Y155">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z155">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA155">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB155">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC155">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD155">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE155">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF155">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG155">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK155">
         <v>2.3</v>
@@ -30796,13 +30796,13 @@
         <v>2.8</v>
       </c>
       <c r="P187">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q187">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R187">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="S187">
         <v>1.66</v>
@@ -30820,7 +30820,7 @@
         <v>1.03</v>
       </c>
       <c r="X187">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y187">
         <v>1.66</v>
@@ -30832,16 +30832,16 @@
         <v>3</v>
       </c>
       <c r="AB187">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC187">
         <v>6.5</v>
       </c>
       <c r="AD187">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE187">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF187">
         <v>2.45</v>
@@ -30863,7 +30863,7 @@
         <v>1.34</v>
       </c>
       <c r="AK187">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="O188">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="P188">
-        <v>5</v>
+        <v>4.64</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31617,22 +31617,22 @@
         <v>2</v>
       </c>
       <c r="R192">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S192">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T192">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="U192">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V192">
         <v>1.38</v>
       </c>
       <c r="W192">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X192">
         <v>1.04</v>
@@ -31644,13 +31644,13 @@
         <v>3.14</v>
       </c>
       <c r="AA192">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB192">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC192">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="AD192">
         <v>1.29</v>
@@ -31659,10 +31659,10 @@
         <v>1.1</v>
       </c>
       <c r="AF192">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG192">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O204">
         <v>2.55</v>
@@ -33573,10 +33573,10 @@
         <v>3.37</v>
       </c>
       <c r="R204">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S204">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="T204">
         <v>2.1</v>
@@ -33606,7 +33606,7 @@
         <v>1.26</v>
       </c>
       <c r="AC204">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD204">
         <v>1.04</v>
@@ -33615,10 +33615,10 @@
         <v>1.01</v>
       </c>
       <c r="AF204">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AG204">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AK204">
         <v>1.39</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="O205">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P205">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S205">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T205">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U205">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="V205">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W205">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X205">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y205">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z205">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AA205">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="AB205">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC205">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AD205">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE205">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF205">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG205">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK205">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="O206">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P206">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q206">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="R206">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S206">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T206">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U206">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V206">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W206">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X206">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y206">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z206">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA206">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="AB206">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AC206">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD206">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE206">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF206">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG206">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK206">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="O207">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="P207">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="Q207">
-        <v>3.37</v>
+        <v>2.38</v>
       </c>
       <c r="R207">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="S207">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="T207">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
       <c r="U207">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="V207">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="W207">
+        <v>1.04</v>
+      </c>
+      <c r="X207">
+        <v>1.1</v>
+      </c>
+      <c r="Y207">
+        <v>1.46</v>
+      </c>
+      <c r="Z207">
+        <v>2.63</v>
+      </c>
+      <c r="AA207">
+        <v>2.33</v>
+      </c>
+      <c r="AB207">
+        <v>1.47</v>
+      </c>
+      <c r="AC207">
+        <v>4.7</v>
+      </c>
+      <c r="AD207">
+        <v>1.15</v>
+      </c>
+      <c r="AE207">
         <v>1.02</v>
       </c>
-      <c r="X207">
-        <v>1.11</v>
-      </c>
-      <c r="Y207">
-        <v>1.72</v>
-      </c>
-      <c r="Z207">
-        <v>2.1</v>
-      </c>
-      <c r="AA207">
-        <v>3.04</v>
-      </c>
-      <c r="AB207">
-        <v>1.33</v>
-      </c>
-      <c r="AC207">
-        <v>6.25</v>
-      </c>
-      <c r="AD207">
-        <v>1.06</v>
-      </c>
-      <c r="AE207">
-        <v>1.01</v>
-      </c>
       <c r="AF207">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AG207">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK207">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34213,31 +34213,31 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="O208">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P208">
-        <v>3.3</v>
+        <v>4.28</v>
       </c>
       <c r="Q208">
         <v>2.8</v>
       </c>
       <c r="R208">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S208">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="T208">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U208">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="V208">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W208">
         <v>1.03</v>
@@ -34246,19 +34246,19 @@
         <v>1.1</v>
       </c>
       <c r="Y208">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z208">
         <v>2.33</v>
       </c>
       <c r="AA208">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AB208">
         <v>1.36</v>
       </c>
       <c r="AC208">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AD208">
         <v>1.13</v>
@@ -35366,7 +35366,7 @@
         <v>2.63</v>
       </c>
       <c r="R215">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S215">
         <v>1.36</v>
@@ -35375,7 +35375,7 @@
         <v>2.73</v>
       </c>
       <c r="U215">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="V215">
         <v>1.39</v>
@@ -36006,19 +36006,19 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="O219">
-        <v>4.84</v>
+        <v>4.94</v>
       </c>
       <c r="P219">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Q219">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R219">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S219">
         <v>1.27</v>
@@ -36027,13 +36027,13 @@
         <v>3.4</v>
       </c>
       <c r="U219">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="V219">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W219">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X219">
         <v>1.04</v>
@@ -36048,22 +36048,22 @@
         <v>1.6</v>
       </c>
       <c r="AB219">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC219">
         <v>2.63</v>
       </c>
       <c r="AD219">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE219">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF219">
         <v>1.85</v>
       </c>
       <c r="AG219">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>1.18</v>
       </c>
       <c r="AK219">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36172,34 +36172,34 @@
         <v>1.87</v>
       </c>
       <c r="O220">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="P220">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="Q220">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="R220">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S220">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T220">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="U220">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="V220">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W220">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X220">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y220">
         <v>1.34</v>
@@ -36208,25 +36208,25 @@
         <v>2.8</v>
       </c>
       <c r="AA220">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB220">
         <v>1.65</v>
       </c>
       <c r="AC220">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD220">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE220">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF220">
         <v>1.95</v>
       </c>
       <c r="AG220">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>1.2</v>
       </c>
       <c r="AK220">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36332,34 +36332,34 @@
         </is>
       </c>
       <c r="N221">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="O221">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P221">
         <v>1.65</v>
       </c>
       <c r="Q221">
-        <v>5.05</v>
+        <v>5.18</v>
       </c>
       <c r="R221">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S221">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T221">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="U221">
         <v>2.69</v>
       </c>
       <c r="V221">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W221">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X221">
         <v>1.05</v>
@@ -36371,10 +36371,10 @@
         <v>3.6</v>
       </c>
       <c r="AA221">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB221">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC221">
         <v>3.2</v>
@@ -36386,10 +36386,10 @@
         <v>1.1</v>
       </c>
       <c r="AF221">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG221">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="O227">
-        <v>9.25</v>
+        <v>3</v>
       </c>
       <c r="P227">
-        <v>12</v>
+        <v>2.8</v>
       </c>
       <c r="Q227">
+        <v>3.2</v>
+      </c>
+      <c r="R227">
+        <v>2</v>
+      </c>
+      <c r="S227">
+        <v>1.5</v>
+      </c>
+      <c r="T227">
+        <v>2.36</v>
+      </c>
+      <c r="U227">
+        <v>3.33</v>
+      </c>
+      <c r="V227">
+        <v>1.29</v>
+      </c>
+      <c r="W227">
+        <v>1.03</v>
+      </c>
+      <c r="X227">
+        <v>1.09</v>
+      </c>
+      <c r="Y227">
         <v>1.4</v>
       </c>
-      <c r="R227">
-        <v>3.12</v>
-      </c>
-      <c r="S227">
-        <v>1.17</v>
-      </c>
-      <c r="T227">
-        <v>3.17</v>
-      </c>
-      <c r="U227">
-        <v>2.01</v>
-      </c>
-      <c r="V227">
-        <v>1.76</v>
-      </c>
-      <c r="W227">
+      <c r="Z227">
+        <v>2.56</v>
+      </c>
+      <c r="AA227">
+        <v>2.28</v>
+      </c>
+      <c r="AB227">
+        <v>1.57</v>
+      </c>
+      <c r="AC227">
+        <v>4.33</v>
+      </c>
+      <c r="AD227">
         <v>1.2</v>
       </c>
-      <c r="X227">
-        <v>1.02</v>
-      </c>
-      <c r="Y227">
-        <v>1.07</v>
-      </c>
-      <c r="Z227">
-        <v>5.95</v>
-      </c>
-      <c r="AA227">
-        <v>1.42</v>
-      </c>
-      <c r="AB227">
-        <v>2.7</v>
-      </c>
-      <c r="AC227">
-        <v>1.98</v>
-      </c>
-      <c r="AD227">
-        <v>1.78</v>
-      </c>
       <c r="AE227">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="AF227">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG227">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AK227">
-        <v>3.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
+        <v>1.1</v>
+      </c>
+      <c r="O228">
+        <v>9.25</v>
+      </c>
+      <c r="P228">
+        <v>12</v>
+      </c>
+      <c r="Q228">
+        <v>1.4</v>
+      </c>
+      <c r="R228">
+        <v>3.12</v>
+      </c>
+      <c r="S228">
+        <v>1.17</v>
+      </c>
+      <c r="T228">
+        <v>3.17</v>
+      </c>
+      <c r="U228">
+        <v>2.01</v>
+      </c>
+      <c r="V228">
+        <v>1.76</v>
+      </c>
+      <c r="W228">
+        <v>1.2</v>
+      </c>
+      <c r="X228">
+        <v>1.02</v>
+      </c>
+      <c r="Y228">
+        <v>1.07</v>
+      </c>
+      <c r="Z228">
+        <v>5.95</v>
+      </c>
+      <c r="AA228">
+        <v>1.42</v>
+      </c>
+      <c r="AB228">
+        <v>2.7</v>
+      </c>
+      <c r="AC228">
+        <v>1.98</v>
+      </c>
+      <c r="AD228">
+        <v>1.78</v>
+      </c>
+      <c r="AE228">
+        <v>1.28</v>
+      </c>
+      <c r="AF228">
         <v>2.4</v>
       </c>
-      <c r="O228">
-        <v>3</v>
-      </c>
-      <c r="P228">
-        <v>2.8</v>
-      </c>
-      <c r="Q228">
-        <v>3.2</v>
-      </c>
-      <c r="R228">
-        <v>2</v>
-      </c>
-      <c r="S228">
-        <v>1.5</v>
-      </c>
-      <c r="T228">
-        <v>2.36</v>
-      </c>
-      <c r="U228">
-        <v>3.33</v>
-      </c>
-      <c r="V228">
-        <v>1.29</v>
-      </c>
-      <c r="W228">
-        <v>1.03</v>
-      </c>
-      <c r="X228">
-        <v>1.09</v>
-      </c>
-      <c r="Y228">
-        <v>1.4</v>
-      </c>
-      <c r="Z228">
-        <v>2.56</v>
-      </c>
-      <c r="AA228">
-        <v>2.28</v>
-      </c>
-      <c r="AB228">
-        <v>1.57</v>
-      </c>
-      <c r="AC228">
-        <v>4.33</v>
-      </c>
-      <c r="AD228">
-        <v>1.2</v>
-      </c>
-      <c r="AE228">
-        <v>1.06</v>
-      </c>
-      <c r="AF228">
-        <v>1.85</v>
-      </c>
       <c r="AG228">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AK228">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -38291,10 +38291,10 @@
         <v>2.94</v>
       </c>
       <c r="O233">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P233">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="Q233">
         <v>3.55</v>
@@ -38303,16 +38303,16 @@
         <v>1.73</v>
       </c>
       <c r="S233">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="T233">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U233">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="V233">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W233">
         <v>1.03</v>
@@ -38324,19 +38324,19 @@
         <v>1.63</v>
       </c>
       <c r="Z233">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AA233">
         <v>3.1</v>
       </c>
       <c r="AB233">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC233">
-        <v>5.75</v>
+        <v>6.61</v>
       </c>
       <c r="AD233">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE233">
         <v>1.02</v>
@@ -38345,7 +38345,7 @@
         <v>2.3</v>
       </c>
       <c r="AG233">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AK233">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38460,19 +38460,19 @@
         <v>3</v>
       </c>
       <c r="Q234">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="R234">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="S234">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T234">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="U234">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="V234">
         <v>1.2</v>
@@ -38481,28 +38481,28 @@
         <v>1.02</v>
       </c>
       <c r="X234">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y234">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z234">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AA234">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AB234">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC234">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="AD234">
         <v>1.2</v>
       </c>
       <c r="AE234">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF234">
         <v>1.97</v>
@@ -38617,16 +38617,16 @@
         <v>1.95</v>
       </c>
       <c r="O235">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="P235">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q235">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="R235">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="S235">
         <v>1.3</v>
@@ -38644,31 +38644,31 @@
         <v>1.11</v>
       </c>
       <c r="X235">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y235">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z235">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA235">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB235">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AC235">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AD235">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE235">
         <v>1.19</v>
       </c>
       <c r="AF235">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG235">
         <v>2.3</v>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK235">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38777,19 +38777,19 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O236">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P236">
-        <v>6.45</v>
+        <v>5.6</v>
       </c>
       <c r="Q236">
         <v>2.1</v>
       </c>
       <c r="R236">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S236">
         <v>1.46</v>
@@ -38798,7 +38798,7 @@
         <v>2.44</v>
       </c>
       <c r="U236">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V236">
         <v>1.29</v>
@@ -38810,13 +38810,13 @@
         <v>1.04</v>
       </c>
       <c r="Y236">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z236">
         <v>2.8</v>
       </c>
       <c r="AA236">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB236">
         <v>1.57</v>
@@ -39103,25 +39103,25 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O238">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P238">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="Q238">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="R238">
         <v>2.15</v>
       </c>
       <c r="S238">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T238">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U238">
         <v>2.62</v>
@@ -39142,7 +39142,7 @@
         <v>3.42</v>
       </c>
       <c r="AA238">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB238">
         <v>1.74</v>
@@ -39151,7 +39151,7 @@
         <v>3.04</v>
       </c>
       <c r="AD238">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE238">
         <v>1.07</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>3.61</v>
+        <v>1.55</v>
       </c>
       <c r="O239">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P239">
-        <v>2.08</v>
+        <v>6</v>
       </c>
       <c r="Q239">
-        <v>4.2</v>
+        <v>2.06</v>
       </c>
       <c r="R239">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S239">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T239">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="U239">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="V239">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W239">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X239">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y239">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z239">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA239">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AB239">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC239">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="AD239">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE239">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF239">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG239">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AK239">
-        <v>1.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,80 +39429,80 @@
         </is>
       </c>
       <c r="N240">
-        <v>1.56</v>
+        <v>3.74</v>
       </c>
       <c r="O240">
-        <v>3.93</v>
+        <v>3.4</v>
       </c>
       <c r="P240">
-        <v>5.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q240">
-        <v>2.07</v>
+        <v>4.2</v>
       </c>
       <c r="R240">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="S240">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T240">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="U240">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="V240">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W240">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X240">
         <v>1.05</v>
       </c>
       <c r="Y240">
+        <v>1.29</v>
+      </c>
+      <c r="Z240">
+        <v>3.05</v>
+      </c>
+      <c r="AA240">
+        <v>1.99</v>
+      </c>
+      <c r="AB240">
+        <v>1.83</v>
+      </c>
+      <c r="AC240">
+        <v>3.5</v>
+      </c>
+      <c r="AD240">
+        <v>1.29</v>
+      </c>
+      <c r="AE240">
+        <v>1.06</v>
+      </c>
+      <c r="AF240">
+        <v>1.87</v>
+      </c>
+      <c r="AG240">
+        <v>1.9</v>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ240">
+        <v>1.31</v>
+      </c>
+      <c r="AK240">
         <v>1.25</v>
-      </c>
-      <c r="Z240">
-        <v>3.6</v>
-      </c>
-      <c r="AA240">
-        <v>1.85</v>
-      </c>
-      <c r="AB240">
-        <v>1.91</v>
-      </c>
-      <c r="AC240">
-        <v>3.1</v>
-      </c>
-      <c r="AD240">
-        <v>1.33</v>
-      </c>
-      <c r="AE240">
-        <v>1.13</v>
-      </c>
-      <c r="AF240">
-        <v>1.85</v>
-      </c>
-      <c r="AG240">
-        <v>1.85</v>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ240">
-        <v>1.22</v>
-      </c>
-      <c r="AK240">
-        <v>2.38</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O241">
         <v>4.2</v>
       </c>
       <c r="P241">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q241">
         <v>1.78</v>
@@ -39625,25 +39625,25 @@
         <v>1.01</v>
       </c>
       <c r="Y241">
+        <v>1.2</v>
+      </c>
+      <c r="Z241">
+        <v>4.5</v>
+      </c>
+      <c r="AA241">
+        <v>1.7</v>
+      </c>
+      <c r="AB241">
+        <v>2.1</v>
+      </c>
+      <c r="AC241">
+        <v>2.6</v>
+      </c>
+      <c r="AD241">
+        <v>1.4</v>
+      </c>
+      <c r="AE241">
         <v>1.17</v>
-      </c>
-      <c r="Z241">
-        <v>4.3</v>
-      </c>
-      <c r="AA241">
-        <v>1.56</v>
-      </c>
-      <c r="AB241">
-        <v>2.04</v>
-      </c>
-      <c r="AC241">
-        <v>2.62</v>
-      </c>
-      <c r="AD241">
-        <v>1.38</v>
-      </c>
-      <c r="AE241">
-        <v>1.16</v>
       </c>
       <c r="AF241">
         <v>1.84</v>
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O242">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P242">
-        <v>5.5</v>
+        <v>6.17</v>
       </c>
       <c r="Q242">
         <v>2.18</v>
@@ -39812,7 +39812,7 @@
         <v>2.4</v>
       </c>
       <c r="AG242">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -40084,22 +40084,22 @@
         <v>1.9</v>
       </c>
       <c r="O244">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="P244">
-        <v>4.41</v>
+        <v>3.65</v>
       </c>
       <c r="Q244">
         <v>2.63</v>
       </c>
       <c r="R244">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S244">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="T244">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U244">
         <v>3.58</v>
@@ -40117,13 +40117,13 @@
         <v>1.53</v>
       </c>
       <c r="Z244">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AA244">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AB244">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC244">
         <v>4.95</v>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK244">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40265,10 +40265,10 @@
         <v>3.6</v>
       </c>
       <c r="U245">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V245">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W245">
         <v>1.14</v>
@@ -40283,10 +40283,10 @@
         <v>4.8</v>
       </c>
       <c r="AA245">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB245">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AC245">
         <v>2.29</v>
@@ -40407,10 +40407,10 @@
         </is>
       </c>
       <c r="N246">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="O246">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P246">
         <v>4.06</v>
@@ -40419,7 +40419,7 @@
         <v>2.3</v>
       </c>
       <c r="R246">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S246">
         <v>1.37</v>
@@ -40437,10 +40437,10 @@
         <v>1.06</v>
       </c>
       <c r="X246">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y246">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z246">
         <v>3.54</v>
@@ -40449,22 +40449,22 @@
         <v>1.89</v>
       </c>
       <c r="AB246">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC246">
         <v>3.25</v>
       </c>
       <c r="AD246">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE246">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF246">
         <v>1.73</v>
       </c>
       <c r="AG246">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>1.3</v>
       </c>
       <c r="AK246">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40579,10 +40579,10 @@
         <v>3.9</v>
       </c>
       <c r="Q247">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R247">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="S247">
         <v>1.5</v>
@@ -40591,7 +40591,7 @@
         <v>2.33</v>
       </c>
       <c r="U247">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="V247">
         <v>1.28</v>
@@ -40600,13 +40600,13 @@
         <v>1.02</v>
       </c>
       <c r="X247">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y247">
         <v>1.4</v>
       </c>
       <c r="Z247">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="AA247">
         <v>2.33</v>
@@ -40624,7 +40624,7 @@
         <v>1.05</v>
       </c>
       <c r="AF247">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG247">
         <v>1.65</v>
@@ -40643,7 +40643,7 @@
         <v>1.23</v>
       </c>
       <c r="AK247">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40733,55 +40733,55 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="O248">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="P248">
-        <v>3.35</v>
+        <v>2.93</v>
       </c>
       <c r="Q248">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="R248">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S248">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T248">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="U248">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V248">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W248">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X248">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y248">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z248">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="AA248">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AB248">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AC248">
-        <v>2.97</v>
+        <v>2.38</v>
       </c>
       <c r="AD248">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE248">
         <v>1.08</v>
@@ -40806,7 +40806,7 @@
         <v>1.21</v>
       </c>
       <c r="AK248">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -40911,10 +40911,10 @@
         <v>2.3</v>
       </c>
       <c r="S249">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T249">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U249">
         <v>2.38</v>
@@ -40929,7 +40929,7 @@
         <v>1.01</v>
       </c>
       <c r="Y249">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z249">
         <v>5</v>
@@ -40944,10 +40944,10 @@
         <v>2.52</v>
       </c>
       <c r="AD249">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AE249">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF249">
         <v>1.5</v>
@@ -41059,25 +41059,25 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O250">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P250">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q250">
         <v>2</v>
       </c>
       <c r="R250">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S250">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T250">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U250">
         <v>2.4</v>
@@ -41092,10 +41092,10 @@
         <v>1.02</v>
       </c>
       <c r="Y250">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z250">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AA250">
         <v>1.72</v>
@@ -41129,7 +41129,7 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK250">
         <v>2.19</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -2079,130 +2079,130 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O11">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
         <v>3.3</v>
       </c>
       <c r="Q11">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="R11">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
         <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="V11">
         <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z11">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA11">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AB11">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AC11">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AD11">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AG11">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32", "38", "54"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "9", "75"]</t>
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,39 +2242,39 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q12">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="R12">
         <v>2.38</v>
@@ -2301,7 +2301,7 @@
         <v>1.14</v>
       </c>
       <c r="Z12">
-        <v>5.63</v>
+        <v>5.1</v>
       </c>
       <c r="AA12">
         <v>1.43</v>
@@ -2310,10 +2310,10 @@
         <v>2.46</v>
       </c>
       <c r="AC12">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD12">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE12">
         <v>1.22</v>
@@ -2322,20 +2322,20 @@
         <v>1.4</v>
       </c>
       <c r="AG12">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "45", "71", "80", "85"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "90+4"]</t>
         </is>
       </c>
       <c r="AJ12">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
         <v>1.4</v>
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2731,42 +2731,42 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="O15">
         <v>3.4</v>
       </c>
       <c r="P15">
-        <v>4.18</v>
+        <v>4.1</v>
       </c>
       <c r="Q15">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="R15">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
         <v>1.4</v>
@@ -2775,13 +2775,13 @@
         <v>2.6</v>
       </c>
       <c r="U15">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V15">
         <v>1.35</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
         <v>1.04</v>
@@ -2808,19 +2808,19 @@
         <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "72", "77"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,81 +2894,81 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
+        <v>5.1</v>
+      </c>
+      <c r="O16">
+        <v>5</v>
+      </c>
+      <c r="P16">
+        <v>1.5</v>
+      </c>
+      <c r="Q16">
         <v>4.6</v>
       </c>
-      <c r="O16">
-        <v>4.6</v>
-      </c>
-      <c r="P16">
-        <v>1.61</v>
-      </c>
-      <c r="Q16">
-        <v>4.75</v>
-      </c>
       <c r="R16">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="S16">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T16">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U16">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V16">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="W16">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="AA16">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB16">
-        <v>3.25</v>
+        <v>3.49</v>
       </c>
       <c r="AC16">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AD16">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AE16">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AF16">
         <v>1.37</v>
@@ -2978,46 +2978,46 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "45", "76", "86", "88", "90+3"]</t>
         </is>
       </c>
       <c r="AJ16">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK16">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,81 +3057,81 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="O17">
+        <v>4.35</v>
+      </c>
+      <c r="P17">
+        <v>1.6</v>
+      </c>
+      <c r="Q17">
         <v>4.4</v>
       </c>
-      <c r="P17">
-        <v>1.61</v>
-      </c>
-      <c r="Q17">
-        <v>4.55</v>
-      </c>
       <c r="R17">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="S17">
+        <v>1.16</v>
+      </c>
+      <c r="T17">
+        <v>4.2</v>
+      </c>
+      <c r="U17">
+        <v>2.08</v>
+      </c>
+      <c r="V17">
+        <v>1.76</v>
+      </c>
+      <c r="W17">
         <v>1.17</v>
-      </c>
-      <c r="T17">
-        <v>4.15</v>
-      </c>
-      <c r="U17">
-        <v>2</v>
-      </c>
-      <c r="V17">
-        <v>1.74</v>
-      </c>
-      <c r="W17">
-        <v>1.16</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z17">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA17">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB17">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AC17">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD17">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AE17">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF17">
         <v>1.41</v>
@@ -3141,16 +3141,16 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "63", "67"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
         <v>1.17</v>
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="O19">
         <v>3.1</v>
@@ -3415,22 +3415,22 @@
         <v>2.3</v>
       </c>
       <c r="Q19">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="R19">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="S19">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T19">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="U19">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
         <v>1.05</v>
@@ -3442,13 +3442,13 @@
         <v>1.32</v>
       </c>
       <c r="Z19">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="AA19">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AB19">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC19">
         <v>3.9</v>
@@ -3460,7 +3460,7 @@
         <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG19">
         <v>1.88</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK19">
         <v>1.36</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O20">
         <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>4.17</v>
+        <v>4.27</v>
       </c>
       <c r="R20">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
         <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="U20">
         <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W20">
         <v>1.05</v>
       </c>
       <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>1.27</v>
+      </c>
+      <c r="Z20">
+        <v>3.18</v>
+      </c>
+      <c r="AA20">
+        <v>2.02</v>
+      </c>
+      <c r="AB20">
+        <v>1.81</v>
+      </c>
+      <c r="AC20">
+        <v>3.55</v>
+      </c>
+      <c r="AD20">
+        <v>1.25</v>
+      </c>
+      <c r="AE20">
         <v>1.05</v>
       </c>
-      <c r="Y20">
-        <v>1.33</v>
-      </c>
-      <c r="Z20">
-        <v>3.25</v>
-      </c>
-      <c r="AA20">
-        <v>2.05</v>
-      </c>
-      <c r="AB20">
-        <v>1.8</v>
-      </c>
-      <c r="AC20">
-        <v>3.6</v>
-      </c>
-      <c r="AD20">
-        <v>1.29</v>
-      </c>
-      <c r="AE20">
-        <v>1.08</v>
-      </c>
       <c r="AF20">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG20">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AK20">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,28 +3732,28 @@
         </is>
       </c>
       <c r="N21">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="O21">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q21">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="R21">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S21">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T21">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="U21">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V21">
         <v>1.27</v>
@@ -3765,31 +3765,31 @@
         <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="Z21">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AA21">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="AB21">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AD21">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE21">
         <v>1.01</v>
       </c>
       <c r="AF21">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG21">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK21">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,37 +3895,37 @@
         </is>
       </c>
       <c r="N22">
-        <v>6.01</v>
+        <v>5.85</v>
       </c>
       <c r="O22">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="P22">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Q22">
-        <v>6.25</v>
+        <v>6.13</v>
       </c>
       <c r="R22">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="S22">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U22">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V22">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
         <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
         <v>1.22</v>
@@ -3934,25 +3934,25 @@
         <v>3.54</v>
       </c>
       <c r="AA22">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB22">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AC22">
         <v>3.1</v>
       </c>
       <c r="AD22">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE22">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG22">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK22">
         <v>1.1</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="O23">
         <v>3.2</v>
       </c>
       <c r="P23">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R23">
         <v>2.04</v>
       </c>
       <c r="S23">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T23">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="U23">
         <v>2.9</v>
@@ -4085,7 +4085,7 @@
         <v>1.33</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
         <v>1.04</v>
@@ -4103,7 +4103,7 @@
         <v>1.73</v>
       </c>
       <c r="AC23">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="AD23">
         <v>1.28</v>
@@ -4115,7 +4115,7 @@
         <v>1.76</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="O24">
         <v>3.6</v>
@@ -4230,16 +4230,16 @@
         <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="R24">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T24">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="U24">
         <v>2.38</v>
@@ -4248,7 +4248,7 @@
         <v>1.56</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4263,10 +4263,10 @@
         <v>1.56</v>
       </c>
       <c r="AB24">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC24">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AD24">
         <v>1.5</v>
@@ -4547,28 +4547,28 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
         <v>3.25</v>
       </c>
       <c r="P26">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q26">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R26">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="S26">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="V26">
         <v>1.43</v>
@@ -4580,31 +4580,31 @@
         <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="AA26">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB26">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC26">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD26">
         <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF26">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.51</v>
+        <v>2.93</v>
       </c>
       <c r="O27">
-        <v>3.15</v>
+        <v>3.03</v>
       </c>
       <c r="P27">
         <v>1.98</v>
       </c>
       <c r="Q27">
-        <v>3.83</v>
+        <v>3.91</v>
       </c>
       <c r="R27">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S27">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T27">
         <v>2.63</v>
       </c>
       <c r="U27">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
+        <v>1.06</v>
+      </c>
+      <c r="X27">
+        <v>1.02</v>
+      </c>
+      <c r="Y27">
+        <v>1.32</v>
+      </c>
+      <c r="Z27">
+        <v>3.18</v>
+      </c>
+      <c r="AA27">
+        <v>1.98</v>
+      </c>
+      <c r="AB27">
+        <v>1.72</v>
+      </c>
+      <c r="AC27">
+        <v>3.42</v>
+      </c>
+      <c r="AD27">
+        <v>1.23</v>
+      </c>
+      <c r="AE27">
         <v>1.05</v>
-      </c>
-      <c r="X27">
-        <v>1.04</v>
-      </c>
-      <c r="Y27">
-        <v>1.3</v>
-      </c>
-      <c r="Z27">
-        <v>2.97</v>
-      </c>
-      <c r="AA27">
-        <v>1.84</v>
-      </c>
-      <c r="AB27">
-        <v>1.85</v>
-      </c>
-      <c r="AC27">
-        <v>3.6</v>
-      </c>
-      <c r="AD27">
-        <v>1.32</v>
-      </c>
-      <c r="AE27">
-        <v>1.08</v>
       </c>
       <c r="AF27">
         <v>1.81</v>
       </c>
       <c r="AG27">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.14</v>
+        <v>1.73</v>
       </c>
       <c r="AK27">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="P29">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="Q29">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="R29">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S29">
+        <v>1.2</v>
+      </c>
+      <c r="T29">
+        <v>4</v>
+      </c>
+      <c r="U29">
+        <v>2.2</v>
+      </c>
+      <c r="V29">
+        <v>1.58</v>
+      </c>
+      <c r="W29">
+        <v>1.13</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>1.11</v>
+      </c>
+      <c r="Z29">
+        <v>5</v>
+      </c>
+      <c r="AA29">
+        <v>1.47</v>
+      </c>
+      <c r="AB29">
+        <v>2.36</v>
+      </c>
+      <c r="AC29">
+        <v>2.19</v>
+      </c>
+      <c r="AD29">
+        <v>1.58</v>
+      </c>
+      <c r="AE29">
+        <v>1.2</v>
+      </c>
+      <c r="AF29">
+        <v>1.44</v>
+      </c>
+      <c r="AG29">
+        <v>2.6</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.22</v>
       </c>
-      <c r="T29">
-        <v>3.8</v>
-      </c>
-      <c r="U29">
-        <v>2.36</v>
-      </c>
-      <c r="V29">
-        <v>1.62</v>
-      </c>
-      <c r="W29">
-        <v>1.12</v>
-      </c>
-      <c r="X29">
-        <v>1.02</v>
-      </c>
-      <c r="Y29">
-        <v>1.17</v>
-      </c>
-      <c r="Z29">
-        <v>5.32</v>
-      </c>
-      <c r="AA29">
-        <v>1.57</v>
-      </c>
-      <c r="AB29">
-        <v>2.29</v>
-      </c>
-      <c r="AC29">
-        <v>2.33</v>
-      </c>
-      <c r="AD29">
-        <v>1.61</v>
-      </c>
-      <c r="AE29">
-        <v>1.19</v>
-      </c>
-      <c r="AF29">
-        <v>1.45</v>
-      </c>
-      <c r="AG29">
-        <v>2.55</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.24</v>
-      </c>
       <c r="AK29">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,34 +5199,34 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O30">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
-        <v>3.15</v>
+        <v>4.45</v>
       </c>
       <c r="Q30">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T30">
         <v>3.4</v>
       </c>
       <c r="U30">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X30">
         <v>1.01</v>
@@ -5235,28 +5235,28 @@
         <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA30">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AB30">
         <v>2.26</v>
       </c>
       <c r="AC30">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="AD30">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE30">
         <v>1.15</v>
       </c>
       <c r="AF30">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG30">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,52 +5362,52 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.04</v>
+        <v>2.58</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="V31">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z31">
-        <v>5.24</v>
+        <v>5.2</v>
       </c>
       <c r="AA31">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AB31">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="AC31">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AD31">
         <v>1.56</v>
@@ -5416,10 +5416,10 @@
         <v>1.2</v>
       </c>
       <c r="AF31">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG31">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AK31">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>5.45</v>
+        <v>5.2</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P32">
         <v>1.47</v>
       </c>
       <c r="Q32">
-        <v>4.56</v>
+        <v>4.8</v>
       </c>
       <c r="R32">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T32">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V32">
         <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>3.92</v>
+        <v>4.5</v>
       </c>
       <c r="AA32">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB32">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AC32">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AD32">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF32">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.15</v>
+        <v>2.29</v>
       </c>
       <c r="AK32">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O33">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P33">
-        <v>5.78</v>
+        <v>7.1</v>
       </c>
       <c r="Q33">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R33">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T33">
         <v>3.34</v>
       </c>
       <c r="U33">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="V33">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W33">
         <v>1.13</v>
@@ -5721,31 +5721,31 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z33">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA33">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB33">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="AC33">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AD33">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE33">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF33">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG33">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK33">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.39</v>
+        <v>2.95</v>
       </c>
       <c r="O36">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q36">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R36">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="U36">
         <v>2.4</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
         <v>1.03</v>
       </c>
       <c r="Y36">
+        <v>1.15</v>
+      </c>
+      <c r="Z36">
+        <v>4.2</v>
+      </c>
+      <c r="AA36">
+        <v>1.61</v>
+      </c>
+      <c r="AB36">
+        <v>2.15</v>
+      </c>
+      <c r="AC36">
+        <v>2.49</v>
+      </c>
+      <c r="AD36">
+        <v>1.42</v>
+      </c>
+      <c r="AE36">
+        <v>1.14</v>
+      </c>
+      <c r="AF36">
+        <v>1.53</v>
+      </c>
+      <c r="AG36">
+        <v>2.3</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.21</v>
       </c>
-      <c r="Z36">
-        <v>3.6</v>
-      </c>
-      <c r="AA36">
-        <v>1.64</v>
-      </c>
-      <c r="AB36">
-        <v>2.1</v>
-      </c>
-      <c r="AC36">
-        <v>2.56</v>
-      </c>
-      <c r="AD36">
-        <v>1.4</v>
-      </c>
-      <c r="AE36">
-        <v>1.12</v>
-      </c>
-      <c r="AF36">
-        <v>1.52</v>
-      </c>
-      <c r="AG36">
-        <v>2.27</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.22</v>
-      </c>
       <c r="AK36">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O41">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
         <v>1.95</v>
@@ -7004,22 +7004,22 @@
         <v>3.75</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S41">
         <v>1.31</v>
       </c>
       <c r="T41">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="U41">
         <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
         <v>1.03</v>
@@ -7031,25 +7031,25 @@
         <v>3.72</v>
       </c>
       <c r="AA41">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB41">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AC41">
         <v>2.7</v>
       </c>
       <c r="AD41">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF41">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.8</v>
       </c>
       <c r="AK41">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="O42">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="P42">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q42">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="R42">
+        <v>2.21</v>
+      </c>
+      <c r="S42">
+        <v>1.28</v>
+      </c>
+      <c r="T42">
+        <v>3.2</v>
+      </c>
+      <c r="U42">
+        <v>2.63</v>
+      </c>
+      <c r="V42">
+        <v>1.44</v>
+      </c>
+      <c r="W42">
+        <v>1.11</v>
+      </c>
+      <c r="X42">
+        <v>1.02</v>
+      </c>
+      <c r="Y42">
+        <v>1.18</v>
+      </c>
+      <c r="Z42">
+        <v>4.2</v>
+      </c>
+      <c r="AA42">
+        <v>1.75</v>
+      </c>
+      <c r="AB42">
         <v>2.03</v>
       </c>
-      <c r="S42">
-        <v>1.34</v>
-      </c>
-      <c r="T42">
-        <v>2.7</v>
-      </c>
-      <c r="U42">
-        <v>2.65</v>
-      </c>
-      <c r="V42">
-        <v>1.42</v>
-      </c>
-      <c r="W42">
-        <v>1.03</v>
-      </c>
-      <c r="X42">
-        <v>1.01</v>
-      </c>
-      <c r="Y42">
-        <v>1.25</v>
-      </c>
-      <c r="Z42">
-        <v>3.28</v>
-      </c>
-      <c r="AA42">
-        <v>1.93</v>
-      </c>
-      <c r="AB42">
-        <v>1.8</v>
-      </c>
       <c r="AC42">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
+        <v>1.38</v>
+      </c>
+      <c r="AE42">
+        <v>1.1</v>
+      </c>
+      <c r="AF42">
+        <v>1.59</v>
+      </c>
+      <c r="AG42">
+        <v>2.19</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.3</v>
       </c>
-      <c r="AE42">
-        <v>1.05</v>
-      </c>
-      <c r="AF42">
-        <v>1.68</v>
-      </c>
-      <c r="AG42">
-        <v>1.98</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.24</v>
-      </c>
       <c r="AK42">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="O43">
         <v>3.13</v>
@@ -7327,71 +7327,71 @@
         <v>1.77</v>
       </c>
       <c r="Q43">
-        <v>3.7</v>
+        <v>5.31</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S43">
+        <v>1.3</v>
+      </c>
+      <c r="T43">
+        <v>2.33</v>
+      </c>
+      <c r="U43">
+        <v>2.5</v>
+      </c>
+      <c r="V43">
+        <v>1.44</v>
+      </c>
+      <c r="W43">
+        <v>1.1</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
+        <v>1.21</v>
+      </c>
+      <c r="Z43">
+        <v>3.58</v>
+      </c>
+      <c r="AA43">
+        <v>1.79</v>
+      </c>
+      <c r="AB43">
+        <v>1.92</v>
+      </c>
+      <c r="AC43">
+        <v>2.85</v>
+      </c>
+      <c r="AD43">
+        <v>1.31</v>
+      </c>
+      <c r="AE43">
+        <v>1.08</v>
+      </c>
+      <c r="AF43">
+        <v>1.73</v>
+      </c>
+      <c r="AG43">
+        <v>2.05</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
         <v>1.25</v>
       </c>
-      <c r="T43">
-        <v>2.55</v>
-      </c>
-      <c r="U43">
-        <v>2.44</v>
-      </c>
-      <c r="V43">
-        <v>1.5</v>
-      </c>
-      <c r="W43">
-        <v>1.06</v>
-      </c>
-      <c r="X43">
-        <v>1.02</v>
-      </c>
-      <c r="Y43">
+      <c r="AK43">
         <v>1.14</v>
-      </c>
-      <c r="Z43">
-        <v>3.1</v>
-      </c>
-      <c r="AA43">
-        <v>1.68</v>
-      </c>
-      <c r="AB43">
-        <v>2.06</v>
-      </c>
-      <c r="AC43">
-        <v>2.64</v>
-      </c>
-      <c r="AD43">
-        <v>1.42</v>
-      </c>
-      <c r="AE43">
-        <v>1.11</v>
-      </c>
-      <c r="AF43">
-        <v>1.47</v>
-      </c>
-      <c r="AG43">
-        <v>1.93</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.08</v>
-      </c>
-      <c r="AK43">
-        <v>1.25</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7807,22 +7807,22 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P46">
         <v>1.7</v>
       </c>
       <c r="Q46">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="R46">
         <v>2.5</v>
       </c>
       <c r="S46">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
         <v>3.85</v>
@@ -7831,7 +7831,7 @@
         <v>2</v>
       </c>
       <c r="V46">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W46">
         <v>1.16</v>
@@ -7840,25 +7840,25 @@
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA46">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB46">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC46">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AD46">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AE46">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF46">
         <v>1.42</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK46">
         <v>1.25</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="O47">
-        <v>7.5</v>
+        <v>8.65</v>
       </c>
       <c r="P47">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q47">
         <v>1.47</v>
       </c>
       <c r="R47">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="S47">
         <v>1.11</v>
@@ -7991,10 +7991,10 @@
         <v>5.5</v>
       </c>
       <c r="U47">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V47">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="W47">
         <v>1.25</v>
@@ -8003,31 +8003,31 @@
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z47">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA47">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AB47">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AC47">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AD47">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AE47">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AF47">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG47">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.03</v>
       </c>
       <c r="AK47">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,34 +8133,34 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O48">
+        <v>3.6</v>
+      </c>
+      <c r="P48">
         <v>3.4</v>
-      </c>
-      <c r="P48">
-        <v>2.73</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S48">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="U48">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="V48">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>1.02</v>
@@ -8169,28 +8169,28 @@
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AA48">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB48">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC48">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AD48">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE48">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG48">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O49">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P49">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
       </c>
       <c r="R49">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="S49">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T49">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="U49">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="V49">
         <v>1.38</v>
@@ -8329,31 +8329,31 @@
         <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z49">
-        <v>2.93</v>
+        <v>3.47</v>
       </c>
       <c r="AA49">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB49">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC49">
         <v>3.25</v>
       </c>
       <c r="AD49">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF49">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG49">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AK49">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,31 +8459,31 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O50">
+        <v>3.4</v>
+      </c>
+      <c r="P50">
         <v>4</v>
       </c>
-      <c r="P50">
-        <v>3.6</v>
-      </c>
       <c r="Q50">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R50">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
         <v>3.25</v>
       </c>
       <c r="U50">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="V50">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
         <v>1.11</v>
@@ -8492,31 +8492,31 @@
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z50">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA50">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AB50">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC50">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AD50">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE50">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF50">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK50">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,28 +8622,28 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P51">
         <v>2.73</v>
       </c>
       <c r="Q51">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S51">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T51">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="U51">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V51">
         <v>1.44</v>
@@ -8655,10 +8655,10 @@
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z51">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AA51">
         <v>1.9</v>
@@ -8667,19 +8667,19 @@
         <v>2</v>
       </c>
       <c r="AC51">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD51">
         <v>1.34</v>
       </c>
       <c r="AE51">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG51">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AK51">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9274,65 +9274,65 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O55">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P55">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q55">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="R55">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S55">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T55">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="U55">
-        <v>2.59</v>
+        <v>2.84</v>
       </c>
       <c r="V55">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W55">
+        <v>1.03</v>
+      </c>
+      <c r="X55">
+        <v>1.02</v>
+      </c>
+      <c r="Y55">
+        <v>1.25</v>
+      </c>
+      <c r="Z55">
+        <v>3.28</v>
+      </c>
+      <c r="AA55">
+        <v>1.93</v>
+      </c>
+      <c r="AB55">
+        <v>1.83</v>
+      </c>
+      <c r="AC55">
+        <v>3.4</v>
+      </c>
+      <c r="AD55">
+        <v>1.28</v>
+      </c>
+      <c r="AE55">
         <v>1.05</v>
       </c>
-      <c r="X55">
-        <v>1.04</v>
-      </c>
-      <c r="Y55">
-        <v>1.22</v>
-      </c>
-      <c r="Z55">
-        <v>4</v>
-      </c>
-      <c r="AA55">
+      <c r="AF55">
         <v>1.8</v>
       </c>
-      <c r="AB55">
+      <c r="AG55">
         <v>2</v>
       </c>
-      <c r="AC55">
-        <v>3</v>
-      </c>
-      <c r="AD55">
-        <v>1.4</v>
-      </c>
-      <c r="AE55">
-        <v>1.09</v>
-      </c>
-      <c r="AF55">
-        <v>1.65</v>
-      </c>
-      <c r="AG55">
-        <v>2.25</v>
-      </c>
       <c r="AH55" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK55">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,34 +9437,34 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="O56">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P56">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="Q56">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="R56">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S56">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U56">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="V56">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X56">
         <v>1.03</v>
@@ -9479,10 +9479,10 @@
         <v>1.6</v>
       </c>
       <c r="AB56">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AC56">
-        <v>2.48</v>
+        <v>2.67</v>
       </c>
       <c r="AD56">
         <v>1.43</v>
@@ -9491,10 +9491,10 @@
         <v>1.13</v>
       </c>
       <c r="AF56">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG56">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK56">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,43 +9600,43 @@
         </is>
       </c>
       <c r="N57">
+        <v>3</v>
+      </c>
+      <c r="O57">
+        <v>3.4</v>
+      </c>
+      <c r="P57">
+        <v>2.25</v>
+      </c>
+      <c r="Q57">
+        <v>3.89</v>
+      </c>
+      <c r="R57">
+        <v>2.1</v>
+      </c>
+      <c r="S57">
+        <v>1.41</v>
+      </c>
+      <c r="T57">
+        <v>2.65</v>
+      </c>
+      <c r="U57">
+        <v>3.06</v>
+      </c>
+      <c r="V57">
+        <v>1.37</v>
+      </c>
+      <c r="W57">
+        <v>1.07</v>
+      </c>
+      <c r="X57">
+        <v>1.01</v>
+      </c>
+      <c r="Y57">
+        <v>1.33</v>
+      </c>
+      <c r="Z57">
         <v>3.05</v>
-      </c>
-      <c r="O57">
-        <v>3.5</v>
-      </c>
-      <c r="P57">
-        <v>2.12</v>
-      </c>
-      <c r="Q57">
-        <v>3.45</v>
-      </c>
-      <c r="R57">
-        <v>2.05</v>
-      </c>
-      <c r="S57">
-        <v>1.44</v>
-      </c>
-      <c r="T57">
-        <v>2.75</v>
-      </c>
-      <c r="U57">
-        <v>2.82</v>
-      </c>
-      <c r="V57">
-        <v>1.36</v>
-      </c>
-      <c r="W57">
-        <v>1.05</v>
-      </c>
-      <c r="X57">
-        <v>1.02</v>
-      </c>
-      <c r="Y57">
-        <v>1.35</v>
-      </c>
-      <c r="Z57">
-        <v>2.94</v>
       </c>
       <c r="AA57">
         <v>2.1</v>
@@ -9645,19 +9645,19 @@
         <v>1.73</v>
       </c>
       <c r="AC57">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AD57">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE57">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF57">
         <v>1.77</v>
       </c>
       <c r="AG57">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AK57">
         <v>1.33</v>
@@ -10904,34 +10904,34 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="O65">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
         <v>2.25</v>
       </c>
       <c r="Q65">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="R65">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S65">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U65">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V65">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W65">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X65">
         <v>1.01</v>
@@ -10940,22 +10940,22 @@
         <v>1.14</v>
       </c>
       <c r="Z65">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AA65">
         <v>1.45</v>
       </c>
       <c r="AB65">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AC65">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD65">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE65">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF65">
         <v>1.44</v>
@@ -11882,58 +11882,58 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O71">
-        <v>3.57</v>
+        <v>3.7</v>
       </c>
       <c r="P71">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="Q71">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S71">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T71">
         <v>3.34</v>
       </c>
       <c r="U71">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V71">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W71">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z71">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="AA71">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AB71">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC71">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="AD71">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE71">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AF71">
         <v>1.48</v>
@@ -11955,7 +11955,7 @@
         <v>1.47</v>
       </c>
       <c r="AK71">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
       <c r="O83">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P83">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="Q83">
-        <v>4.11</v>
+        <v>4.77</v>
       </c>
       <c r="R83">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T83">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="U83">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="V83">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="W83">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="Z83">
-        <v>6.25</v>
+        <v>7.2</v>
       </c>
       <c r="AA83">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AB83">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="AC83">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AD83">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AE83">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AF83">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG83">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.19</v>
+        <v>2.8</v>
       </c>
       <c r="AK83">
         <v>1.11</v>
@@ -14001,16 +14001,16 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O84">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P84">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q84">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="R84">
         <v>2.5</v>
@@ -14022,37 +14022,37 @@
         <v>4.1</v>
       </c>
       <c r="U84">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="V84">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="W84">
         <v>1.16</v>
       </c>
       <c r="X84">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z84">
-        <v>6.56</v>
+        <v>5.8</v>
       </c>
       <c r="AA84">
         <v>1.4</v>
       </c>
       <c r="AB84">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AC84">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD84">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE84">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF84">
         <v>1.33</v>
@@ -14074,7 +14074,7 @@
         <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -15308,46 +15308,46 @@
         <v>1.98</v>
       </c>
       <c r="O92">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P92">
         <v>2.66</v>
       </c>
       <c r="Q92">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="R92">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S92">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T92">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="U92">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V92">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W92">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X92">
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z92">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="AA92">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB92">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AC92">
         <v>2.1</v>
@@ -15356,13 +15356,13 @@
         <v>1.7</v>
       </c>
       <c r="AE92">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF92">
         <v>1.4</v>
       </c>
       <c r="AG92">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AK92">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.79</v>
+        <v>3.03</v>
       </c>
       <c r="O93">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P93">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q93">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="R93">
         <v>2.38</v>
       </c>
       <c r="S93">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T93">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U93">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="V93">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X93">
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z93">
-        <v>4.82</v>
+        <v>5.5</v>
       </c>
       <c r="AA93">
+        <v>1.53</v>
+      </c>
+      <c r="AB93">
+        <v>2.4</v>
+      </c>
+      <c r="AC93">
+        <v>2.3</v>
+      </c>
+      <c r="AD93">
         <v>1.6</v>
       </c>
-      <c r="AB93">
-        <v>2.29</v>
-      </c>
-      <c r="AC93">
-        <v>2.56</v>
-      </c>
-      <c r="AD93">
-        <v>1.47</v>
-      </c>
       <c r="AE93">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF93">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AG93">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>1.9</v>
+        <v>1.27</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="O94">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P94">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="Q94">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="R94">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="S94">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="T94">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="U94">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="V94">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="W94">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X94">
         <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="Z94">
-        <v>7.59</v>
+        <v>4.82</v>
       </c>
       <c r="AA94">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AB94">
-        <v>3.18</v>
+        <v>2.29</v>
       </c>
       <c r="AC94">
-        <v>1.78</v>
+        <v>2.56</v>
       </c>
       <c r="AD94">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AE94">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="AF94">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AG94">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK94">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="O95">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P95">
-        <v>4.05</v>
+        <v>2.28</v>
       </c>
       <c r="Q95">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="R95">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="S95">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T95">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="U95">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="V95">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="W95">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X95">
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z95">
-        <v>4.7</v>
+        <v>7.59</v>
       </c>
       <c r="AA95">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="AB95">
-        <v>2.38</v>
+        <v>3.18</v>
       </c>
       <c r="AC95">
-        <v>2.34</v>
+        <v>1.78</v>
       </c>
       <c r="AD95">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AE95">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AF95">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AG95">
-        <v>2.26</v>
+        <v>3.25</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK95">
-        <v>2.21</v>
+        <v>1.44</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="O96">
+        <v>3.85</v>
+      </c>
+      <c r="P96">
+        <v>4.05</v>
+      </c>
+      <c r="Q96">
+        <v>2.15</v>
+      </c>
+      <c r="R96">
+        <v>2.38</v>
+      </c>
+      <c r="S96">
+        <v>1.25</v>
+      </c>
+      <c r="T96">
         <v>3.6</v>
       </c>
-      <c r="P96">
-        <v>2.62</v>
-      </c>
-      <c r="Q96">
-        <v>2.8</v>
-      </c>
-      <c r="R96">
-        <v>2.3</v>
-      </c>
-      <c r="S96">
-        <v>1.3</v>
-      </c>
-      <c r="T96">
-        <v>3.25</v>
-      </c>
       <c r="U96">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V96">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="W96">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X96">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z96">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="AA96">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AB96">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AC96">
-        <v>2.74</v>
+        <v>2.34</v>
       </c>
       <c r="AD96">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AE96">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF96">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG96">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK96">
-        <v>1.57</v>
+        <v>2.21</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>3.03</v>
+        <v>2.2</v>
       </c>
       <c r="O97">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P97">
+        <v>2.62</v>
+      </c>
+      <c r="Q97">
+        <v>2.8</v>
+      </c>
+      <c r="R97">
+        <v>2.3</v>
+      </c>
+      <c r="S97">
+        <v>1.3</v>
+      </c>
+      <c r="T97">
+        <v>3.25</v>
+      </c>
+      <c r="U97">
+        <v>2.5</v>
+      </c>
+      <c r="V97">
+        <v>1.51</v>
+      </c>
+      <c r="W97">
+        <v>1.1</v>
+      </c>
+      <c r="X97">
+        <v>1.02</v>
+      </c>
+      <c r="Y97">
+        <v>1.16</v>
+      </c>
+      <c r="Z97">
+        <v>4.33</v>
+      </c>
+      <c r="AA97">
+        <v>1.7</v>
+      </c>
+      <c r="AB97">
         <v>2.1</v>
       </c>
-      <c r="Q97">
-        <v>3.52</v>
-      </c>
-      <c r="R97">
-        <v>2.38</v>
-      </c>
-      <c r="S97">
-        <v>1.2</v>
-      </c>
-      <c r="T97">
-        <v>4</v>
-      </c>
-      <c r="U97">
-        <v>2.14</v>
-      </c>
-      <c r="V97">
-        <v>1.61</v>
-      </c>
-      <c r="W97">
-        <v>1.13</v>
-      </c>
-      <c r="X97">
-        <v>1.01</v>
-      </c>
-      <c r="Y97">
-        <v>1.13</v>
-      </c>
-      <c r="Z97">
-        <v>5.5</v>
-      </c>
-      <c r="AA97">
-        <v>1.53</v>
-      </c>
-      <c r="AB97">
-        <v>2.4</v>
-      </c>
       <c r="AC97">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="AD97">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE97">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AF97">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AG97">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK97">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O102">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P102">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17261,10 +17261,10 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O104">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P104">
         <v>2.4</v>
@@ -17273,52 +17273,52 @@
         <v>2.91</v>
       </c>
       <c r="R104">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S104">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T104">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U104">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V104">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W104">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X104">
         <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z104">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA104">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB104">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC104">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="AD104">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE104">
         <v>1.12</v>
       </c>
       <c r="AF104">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG104">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AK104">
         <v>1.45</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O106">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="P106">
-        <v>1.48</v>
+        <v>2.47</v>
       </c>
       <c r="Q106">
-        <v>5.25</v>
+        <v>3.02</v>
       </c>
       <c r="R106">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="S106">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>4.25</v>
+        <v>3.36</v>
       </c>
       <c r="U106">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="V106">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="W106">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z106">
-        <v>6.91</v>
+        <v>5.09</v>
       </c>
       <c r="AA106">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AB106">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="AC106">
-        <v>1.87</v>
+        <v>2.33</v>
       </c>
       <c r="AD106">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AE106">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AF106">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG106">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AK106">
-        <v>1.12</v>
+        <v>1.47</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="O107">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P107">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q107">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="R107">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="S107">
+        <v>1.1</v>
+      </c>
+      <c r="T107">
+        <v>5.4</v>
+      </c>
+      <c r="U107">
+        <v>1.65</v>
+      </c>
+      <c r="V107">
+        <v>2.2</v>
+      </c>
+      <c r="W107">
+        <v>1.32</v>
+      </c>
+      <c r="X107">
+        <v>1</v>
+      </c>
+      <c r="Y107">
+        <v>1.04</v>
+      </c>
+      <c r="Z107">
+        <v>11</v>
+      </c>
+      <c r="AA107">
         <v>1.2</v>
       </c>
-      <c r="T107">
-        <v>3.78</v>
-      </c>
-      <c r="U107">
-        <v>2.12</v>
-      </c>
-      <c r="V107">
-        <v>1.7</v>
-      </c>
-      <c r="W107">
-        <v>1.17</v>
-      </c>
-      <c r="X107">
-        <v>1.01</v>
-      </c>
-      <c r="Y107">
-        <v>1.09</v>
-      </c>
-      <c r="Z107">
-        <v>5.3</v>
-      </c>
-      <c r="AA107">
-        <v>1.44</v>
-      </c>
       <c r="AB107">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="AC107">
-        <v>2.13</v>
+        <v>1.52</v>
       </c>
       <c r="AD107">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="AE107">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AF107">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AG107">
-        <v>2.77</v>
+        <v>3.42</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK107">
-        <v>1.68</v>
+        <v>2.37</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="O108">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="P108">
-        <v>2.18</v>
+        <v>1.48</v>
       </c>
       <c r="Q108">
-        <v>3.05</v>
+        <v>5.25</v>
       </c>
       <c r="R108">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="S108">
         <v>1.17</v>
       </c>
       <c r="T108">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="U108">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="V108">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="W108">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X108">
         <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z108">
-        <v>5.5</v>
+        <v>6.91</v>
       </c>
       <c r="AA108">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB108">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AC108">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AD108">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AE108">
         <v>1.33</v>
       </c>
       <c r="AF108">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AG108">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK108">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.64</v>
+        <v>2.05</v>
       </c>
       <c r="O109">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="P109">
-        <v>1.56</v>
+        <v>2.8</v>
       </c>
       <c r="Q109">
-        <v>3.87</v>
+        <v>2.41</v>
       </c>
       <c r="R109">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S109">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T109">
-        <v>5.15</v>
+        <v>3.78</v>
       </c>
       <c r="U109">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="V109">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="W109">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="X109">
         <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z109">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="AA109">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AB109">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="AC109">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="AD109">
-        <v>2.17</v>
+        <v>1.72</v>
       </c>
       <c r="AE109">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AF109">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AG109">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK109">
-        <v>1.14</v>
+        <v>1.68</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,80 +18239,80 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="O110">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="P110">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="Q110">
-        <v>2.59</v>
+        <v>3.05</v>
       </c>
       <c r="R110">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="S110">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T110">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="U110">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="V110">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="W110">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="X110">
         <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z110">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AA110">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AB110">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="AC110">
-        <v>1.61</v>
+        <v>2.04</v>
       </c>
       <c r="AD110">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AE110">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF110">
+        <v>1.36</v>
+      </c>
+      <c r="AG110">
+        <v>2.9</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ110">
         <v>1.22</v>
       </c>
-      <c r="AG110">
-        <v>3.75</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ110">
-        <v>1.21</v>
-      </c>
       <c r="AK110">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.44</v>
+        <v>3.64</v>
       </c>
       <c r="O111">
         <v>4.33</v>
       </c>
       <c r="P111">
-        <v>5</v>
+        <v>1.56</v>
       </c>
       <c r="Q111">
-        <v>1.89</v>
+        <v>3.87</v>
       </c>
       <c r="R111">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="S111">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T111">
-        <v>4.5</v>
+        <v>5.15</v>
       </c>
       <c r="U111">
+        <v>1.75</v>
+      </c>
+      <c r="V111">
         <v>2</v>
       </c>
-      <c r="V111">
-        <v>1.73</v>
-      </c>
       <c r="W111">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="X111">
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z111">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AA111">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AB111">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="AC111">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AD111">
-        <v>1.82</v>
+        <v>2.17</v>
       </c>
       <c r="AE111">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AF111">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AG111">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK111">
-        <v>2.5</v>
+        <v>1.14</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G112">
@@ -18568,61 +18568,61 @@
         <v>2.2</v>
       </c>
       <c r="O112">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="P112">
         <v>2.47</v>
       </c>
       <c r="Q112">
-        <v>3.02</v>
+        <v>2.59</v>
       </c>
       <c r="R112">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="S112">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="T112">
-        <v>3.36</v>
+        <v>4.7</v>
       </c>
       <c r="U112">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="V112">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="W112">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="Z112">
-        <v>5.09</v>
+        <v>8</v>
       </c>
       <c r="AA112">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AB112">
-        <v>2.41</v>
+        <v>3.9</v>
       </c>
       <c r="AC112">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="AD112">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="AE112">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AF112">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AG112">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK112">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="O113">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="P113">
+        <v>5</v>
+      </c>
+      <c r="Q113">
+        <v>1.89</v>
+      </c>
+      <c r="R113">
+        <v>2.62</v>
+      </c>
+      <c r="S113">
+        <v>1.2</v>
+      </c>
+      <c r="T113">
         <v>4.5</v>
       </c>
-      <c r="Q113">
-        <v>1.88</v>
-      </c>
-      <c r="R113">
-        <v>2.64</v>
-      </c>
-      <c r="S113">
-        <v>1.1</v>
-      </c>
-      <c r="T113">
-        <v>5.4</v>
-      </c>
       <c r="U113">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="V113">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="W113">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="X113">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z113">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="AA113">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AB113">
-        <v>4.2</v>
+        <v>2.78</v>
       </c>
       <c r="AC113">
-        <v>1.52</v>
+        <v>1.94</v>
       </c>
       <c r="AD113">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="AE113">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AF113">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AG113">
-        <v>3.42</v>
+        <v>2.47</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK113">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18897,58 +18897,58 @@
         <v>3.7</v>
       </c>
       <c r="P114">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Q114">
-        <v>5.8</v>
+        <v>5.25</v>
       </c>
       <c r="R114">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S114">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T114">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="U114">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="V114">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W114">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X114">
         <v>1.04</v>
       </c>
       <c r="Y114">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z114">
         <v>3.5</v>
       </c>
       <c r="AA114">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AB114">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC114">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD114">
         <v>1.3</v>
       </c>
       <c r="AE114">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF114">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG114">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK114">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="O118">
-        <v>2.9</v>
+        <v>4.95</v>
       </c>
       <c r="P118">
-        <v>6.91</v>
+        <v>6.5</v>
       </c>
       <c r="Q118">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="R118">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="S118">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T118">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="U118">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="V118">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W118">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X118">
         <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z118">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="AA118">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB118">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC118">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD118">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE118">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AF118">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG118">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AK118">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,65 +19706,65 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="O119">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P119">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="Q119">
-        <v>2.26</v>
+        <v>2.47</v>
       </c>
       <c r="R119">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S119">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T119">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U119">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V119">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W119">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X119">
         <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z119">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AA119">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB119">
+        <v>2.3</v>
+      </c>
+      <c r="AC119">
+        <v>2.59</v>
+      </c>
+      <c r="AD119">
+        <v>1.4</v>
+      </c>
+      <c r="AE119">
+        <v>1.2</v>
+      </c>
+      <c r="AF119">
+        <v>1.6</v>
+      </c>
+      <c r="AG119">
         <v>2.2</v>
       </c>
-      <c r="AC119">
-        <v>2.52</v>
-      </c>
-      <c r="AD119">
-        <v>1.5</v>
-      </c>
-      <c r="AE119">
-        <v>1.19</v>
-      </c>
-      <c r="AF119">
-        <v>1.53</v>
-      </c>
-      <c r="AG119">
-        <v>2.28</v>
-      </c>
       <c r="AH119" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK119">
         <v>1.86</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O131">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P131">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q131">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R131">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S131">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T131">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="U131">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="V131">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W131">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X131">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z131">
-        <v>3.88</v>
+        <v>3.14</v>
       </c>
       <c r="AA131">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB131">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC131">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="AD131">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE131">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF131">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AG131">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK131">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O132">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P132">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q132">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="R132">
         <v>2.1</v>
       </c>
       <c r="S132">
+        <v>1.4</v>
+      </c>
+      <c r="T132">
+        <v>2.72</v>
+      </c>
+      <c r="U132">
+        <v>2.75</v>
+      </c>
+      <c r="V132">
         <v>1.36</v>
       </c>
-      <c r="T132">
-        <v>2.71</v>
-      </c>
-      <c r="U132">
-        <v>2.8</v>
-      </c>
-      <c r="V132">
-        <v>1.38</v>
-      </c>
       <c r="W132">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X132">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y132">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z132">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA132">
         <v>2</v>
       </c>
       <c r="AB132">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC132">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD132">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE132">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF132">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG132">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK132">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q134">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="R134">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S134">
+        <v>1.33</v>
+      </c>
+      <c r="T134">
+        <v>2.88</v>
+      </c>
+      <c r="U134">
+        <v>2.6</v>
+      </c>
+      <c r="V134">
         <v>1.4</v>
       </c>
-      <c r="T134">
-        <v>2.72</v>
-      </c>
-      <c r="U134">
-        <v>2.75</v>
-      </c>
-      <c r="V134">
-        <v>1.36</v>
-      </c>
       <c r="W134">
+        <v>1.1</v>
+      </c>
+      <c r="X134">
+        <v>1</v>
+      </c>
+      <c r="Y134">
+        <v>1.21</v>
+      </c>
+      <c r="Z134">
+        <v>3.58</v>
+      </c>
+      <c r="AA134">
+        <v>1.8</v>
+      </c>
+      <c r="AB134">
+        <v>2</v>
+      </c>
+      <c r="AC134">
+        <v>2.86</v>
+      </c>
+      <c r="AD134">
+        <v>1.38</v>
+      </c>
+      <c r="AE134">
         <v>1.08</v>
       </c>
-      <c r="X134">
-        <v>1.05</v>
-      </c>
-      <c r="Y134">
-        <v>1.3</v>
-      </c>
-      <c r="Z134">
-        <v>3.08</v>
-      </c>
-      <c r="AA134">
-        <v>2</v>
-      </c>
-      <c r="AB134">
-        <v>1.75</v>
-      </c>
-      <c r="AC134">
-        <v>3.5</v>
-      </c>
-      <c r="AD134">
-        <v>1.29</v>
-      </c>
-      <c r="AE134">
-        <v>1.03</v>
-      </c>
       <c r="AF134">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG134">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>1.33</v>
       </c>
       <c r="AK134">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="O135">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P135">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q135">
-        <v>2.87</v>
+        <v>2.42</v>
       </c>
       <c r="R135">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S135">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T135">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U135">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V135">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W135">
         <v>1.1</v>
       </c>
       <c r="X135">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y135">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z135">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="AA135">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB135">
         <v>2</v>
       </c>
       <c r="AC135">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="AD135">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE135">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF135">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG135">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK135">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O138">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P138">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q138">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="R138">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S138">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T138">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="U138">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="V138">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W138">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X138">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y138">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z138">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA138">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AB138">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AC138">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="AD138">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE138">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF138">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG138">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK138">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O145">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P145">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="Q145">
+        <v>2.67</v>
+      </c>
+      <c r="R145">
+        <v>1.89</v>
+      </c>
+      <c r="S145">
+        <v>1.53</v>
+      </c>
+      <c r="T145">
+        <v>2.36</v>
+      </c>
+      <c r="U145">
         <v>3.2</v>
       </c>
-      <c r="R145">
-        <v>1.91</v>
-      </c>
-      <c r="S145">
-        <v>1.46</v>
-      </c>
-      <c r="T145">
-        <v>2.6</v>
-      </c>
-      <c r="U145">
-        <v>3.14</v>
-      </c>
       <c r="V145">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W145">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X145">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y145">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z145">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA145">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AB145">
         <v>1.6</v>
       </c>
       <c r="AC145">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AD145">
         <v>1.18</v>
       </c>
       <c r="AE145">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF145">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG145">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK145">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O146">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P146">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="Q146">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="R146">
         <v>1.91</v>
       </c>
       <c r="S146">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T146">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="U146">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="V146">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W146">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X146">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y146">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z146">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="AA146">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AB146">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC146">
-        <v>4.35</v>
+        <v>3.9</v>
       </c>
       <c r="AD146">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE146">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF146">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG146">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK146">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O147">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P147">
-        <v>3.95</v>
+        <v>2.87</v>
       </c>
       <c r="Q147">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="R147">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S147">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="T147">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="U147">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V147">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W147">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X147">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y147">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z147">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AA147">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="AB147">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC147">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AD147">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE147">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF147">
         <v>1.95</v>
       </c>
       <c r="AG147">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK147">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -25574,31 +25574,31 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="O155">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P155">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q155">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="R155">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S155">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T155">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U155">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="V155">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W155">
         <v>1.1</v>
@@ -25628,10 +25628,10 @@
         <v>1.1</v>
       </c>
       <c r="AF155">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG155">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AK155">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -28508,28 +28508,28 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="O173">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="P173">
-        <v>19</v>
+        <v>14.61</v>
       </c>
       <c r="Q173">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R173">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="S173">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="T173">
         <v>6.5</v>
       </c>
       <c r="U173">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V173">
         <v>2.11</v>
@@ -28544,28 +28544,28 @@
         <v>1.04</v>
       </c>
       <c r="Z173">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA173">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AB173">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AC173">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AD173">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AE173">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AF173">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="AG173">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>1.02</v>
       </c>
       <c r="AK173">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="O195">
-        <v>5.25</v>
+        <v>5.7</v>
       </c>
       <c r="P195">
         <v>1.36</v>
       </c>
       <c r="Q195">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="R195">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S195">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T195">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U195">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="V195">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="W195">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X195">
         <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z195">
-        <v>6.14</v>
+        <v>5.8</v>
       </c>
       <c r="AA195">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AB195">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AC195">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AD195">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AE195">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AF195">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AG195">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK195">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32909,7 +32909,7 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="O200">
         <v>3.4</v>
@@ -32921,52 +32921,52 @@
         <v>3.4</v>
       </c>
       <c r="R200">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S200">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T200">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U200">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V200">
         <v>1.53</v>
       </c>
       <c r="W200">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X200">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y200">
         <v>1.18</v>
       </c>
       <c r="Z200">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA200">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AB200">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC200">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AD200">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE200">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF200">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG200">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AK200">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -36658,31 +36658,31 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="O223">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="P223">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="Q223">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="R223">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S223">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T223">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U223">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V223">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W223">
         <v>1.11</v>
@@ -36700,22 +36700,22 @@
         <v>1.62</v>
       </c>
       <c r="AB223">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AC223">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="AD223">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE223">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF223">
         <v>1.67</v>
       </c>
       <c r="AG223">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK223">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.37</v>
+        <v>6.36</v>
       </c>
       <c r="O225">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="P225">
-        <v>2.8</v>
+        <v>1.45</v>
       </c>
       <c r="Q225">
-        <v>3.22</v>
+        <v>8.1</v>
       </c>
       <c r="R225">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="S225">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T225">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U225">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="V225">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W225">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X225">
         <v>1.06</v>
       </c>
       <c r="Y225">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z225">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AA225">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB225">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AC225">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD225">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE225">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF225">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AG225">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK225">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,64 +37147,64 @@
         </is>
       </c>
       <c r="N226">
-        <v>6.36</v>
+        <v>2.37</v>
       </c>
       <c r="O226">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="P226">
-        <v>1.45</v>
+        <v>2.8</v>
       </c>
       <c r="Q226">
-        <v>8.1</v>
+        <v>3.22</v>
       </c>
       <c r="R226">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="S226">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T226">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U226">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="V226">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W226">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X226">
         <v>1.06</v>
       </c>
       <c r="Y226">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z226">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AA226">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB226">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AC226">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD226">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE226">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF226">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AG226">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK226">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>3.6</v>
+        <v>1.56</v>
       </c>
       <c r="O239">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="P239">
-        <v>2.01</v>
+        <v>5.1</v>
       </c>
       <c r="Q239">
-        <v>4.2</v>
+        <v>1.91</v>
       </c>
       <c r="R239">
-        <v>2.03</v>
+        <v>2.43</v>
       </c>
       <c r="S239">
+        <v>1.35</v>
+      </c>
+      <c r="T239">
+        <v>2.94</v>
+      </c>
+      <c r="U239">
+        <v>2.79</v>
+      </c>
+      <c r="V239">
         <v>1.43</v>
       </c>
-      <c r="T239">
-        <v>2.62</v>
-      </c>
-      <c r="U239">
-        <v>2.85</v>
-      </c>
-      <c r="V239">
-        <v>1.37</v>
-      </c>
       <c r="W239">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X239">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y239">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z239">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="AA239">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AB239">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC239">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="AD239">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE239">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF239">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG239">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AK239">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,80 +39429,80 @@
         </is>
       </c>
       <c r="N240">
-        <v>1.56</v>
+        <v>3.6</v>
       </c>
       <c r="O240">
+        <v>3.18</v>
+      </c>
+      <c r="P240">
+        <v>2.01</v>
+      </c>
+      <c r="Q240">
         <v>4.2</v>
       </c>
-      <c r="P240">
-        <v>5.1</v>
-      </c>
-      <c r="Q240">
-        <v>1.91</v>
-      </c>
       <c r="R240">
-        <v>2.43</v>
+        <v>2.03</v>
       </c>
       <c r="S240">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T240">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="U240">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="V240">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W240">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X240">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y240">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z240">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="AA240">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AB240">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AC240">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="AD240">
+        <v>1.28</v>
+      </c>
+      <c r="AE240">
+        <v>1.06</v>
+      </c>
+      <c r="AF240">
+        <v>1.8</v>
+      </c>
+      <c r="AG240">
+        <v>1.95</v>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ240">
         <v>1.31</v>
       </c>
-      <c r="AE240">
-        <v>1.13</v>
-      </c>
-      <c r="AF240">
-        <v>1.85</v>
-      </c>
-      <c r="AG240">
-        <v>1.85</v>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ240">
-        <v>1.13</v>
-      </c>
       <c r="AK240">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -40733,40 +40733,40 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O248">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="P248">
-        <v>3.45</v>
+        <v>2.93</v>
       </c>
       <c r="Q248">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R248">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S248">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T248">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="U248">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="V248">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W248">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X248">
         <v>1.03</v>
       </c>
       <c r="Y248">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z248">
         <v>3.9</v>
@@ -40778,19 +40778,19 @@
         <v>2.01</v>
       </c>
       <c r="AC248">
-        <v>2.92</v>
+        <v>2.3</v>
       </c>
       <c r="AD248">
         <v>1.35</v>
       </c>
       <c r="AE248">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF248">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AG248">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK248">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AL248">
         <v>0</v>

--- a/jogos_2026-08-30.xlsx
+++ b/jogos_2026-08-30.xlsx
@@ -14630,10 +14630,10 @@
         </is>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -14642,14 +14642,14 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N88">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89", "90+7"]</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75"]</t>
         </is>
       </c>
       <c r="AJ88">
@@ -14732,28 +14732,28 @@
         <v>0</v>
       </c>
       <c r="AM88">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN88">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO88">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP88">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ88">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR88">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS88">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT88">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
@@ -24410,10 +24410,10 @@
         </is>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -24422,14 +24422,14 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N148">
@@ -24494,12 +24494,12 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+5"]</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AJ148">
@@ -24512,28 +24512,28 @@
         <v>0</v>
       </c>
       <c r="AM148">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN148">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO148">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP148">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ148">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR148">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS148">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT148">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
@@ -24573,13 +24573,13 @@
         </is>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149">
         <v>0</v>
       </c>
       <c r="I149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J149">
         <v>0</v>
@@ -24592,7 +24592,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N149">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3"]</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
@@ -24675,28 +24675,28 @@
         <v>0</v>
       </c>
       <c r="AM149">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN149">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO149">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP149">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ149">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR149">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS149">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT149">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
@@ -24736,26 +24736,26 @@
         </is>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J150">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K150">
         <v>0</v>
       </c>
       <c r="L150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N150">
@@ -24820,12 +24820,12 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "19", "57"]</t>
         </is>
       </c>
       <c r="AJ150">
@@ -24838,28 +24838,28 @@
         <v>0</v>
       </c>
       <c r="AM150">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN150">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO150">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP150">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ150">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR150">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS150">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT150">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
@@ -24899,16 +24899,16 @@
         </is>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151">
         <v>0</v>
@@ -24918,7 +24918,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N151">
@@ -24983,12 +24983,12 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AJ151">
@@ -25001,28 +25001,28 @@
         <v>0</v>
       </c>
       <c r="AM151">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN151">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO151">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP151">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ151">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR151">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS151">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT151">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
@@ -25065,23 +25065,23 @@
         <v>0</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I152">
         <v>0</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K152">
         <v>0</v>
       </c>
       <c r="L152">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N152">
@@ -25151,7 +25151,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "64", "68", "88"]</t>
         </is>
       </c>
       <c r="AJ152">
@@ -25164,28 +25164,28 @@
         <v>0</v>
       </c>
       <c r="AM152">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN152">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO152">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP152">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ152">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR152">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS152">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT152">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
@@ -25225,26 +25225,26 @@
         </is>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153">
         <v>0</v>
       </c>
       <c r="K153">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N153">
@@ -25309,12 +25309,12 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "57", "60", "90+2"]</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49"]</t>
         </is>
       </c>
       <c r="AJ153">
@@ -25327,28 +25327,28 @@
         <v>0</v>
       </c>
       <c r="AM153">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN153">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO153">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP153">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ153">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AR153">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS153">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AT153">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
@@ -25388,26 +25388,26 @@
         </is>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J154">
         <v>0</v>
       </c>
       <c r="K154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N154">
@@ -25472,12 +25472,12 @@
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "68"]</t>
         </is>
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+5"]</t>
         </is>
       </c>
       <c r="AJ154">
@@ -25490,28 +25490,28 @@
         <v>0</v>
       </c>
       <c r="AM154">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN154">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO154">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP154">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ154">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR154">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS154">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT154">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
@@ -25551,13 +25551,13 @@
         </is>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155">
         <v>0</v>
       </c>
       <c r="I155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -25570,7 +25570,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N155">
@@ -25635,7 +25635,7 @@
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+4"]</t>
         </is>
       </c>
       <c r="AI155" t="inlineStr">
@@ -25653,28 +25653,28 @@
         <v>0</v>
       </c>
       <c r="AM155">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN155">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO155">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP155">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ155">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR155">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS155">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT155">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
@@ -25714,26 +25714,26 @@
         </is>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L156">
         <v>0</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N156">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "89"]</t>
         </is>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AJ156">
@@ -25816,28 +25816,28 @@
         <v>0</v>
       </c>
       <c r="AM156">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN156">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO156">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP156">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ156">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AR156">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS156">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT156">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
@@ -26203,26 +26203,26 @@
         </is>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I159">
         <v>0</v>
       </c>
       <c r="J159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K159">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L159">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N159">
@@ -26287,12 +26287,12 @@
       </c>
       <c r="AH159" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60", "74"]</t>
         </is>
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "55", "90+4"]</t>
         </is>
       </c>
       <c r="AJ159">
@@ -26305,28 +26305,28 @@
         <v>0</v>
       </c>
       <c r="AM159">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN159">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO159">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP159">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ159">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR159">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS159">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT159">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
@@ -26366,10 +26366,10 @@
         </is>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160">
         <v>0</v>
@@ -26378,14 +26378,14 @@
         <v>0</v>
       </c>
       <c r="K160">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N160">
@@ -26450,12 +26450,12 @@
       </c>
       <c r="AH160" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "61", "90"]</t>
         </is>
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AJ160">
@@ -26468,28 +26468,28 @@
         <v>0</v>
       </c>
       <c r="AM160">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN160">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO160">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP160">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ160">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR160">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS160">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT160">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
@@ -26529,13 +26529,13 @@
         </is>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H161">
         <v>0</v>
       </c>
       <c r="I161">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J161">
         <v>0</v>
@@ -26548,7 +26548,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N161">
@@ -26613,7 +26613,7 @@
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "26", "40"]</t>
         </is>
       </c>
       <c r="AI161" t="inlineStr">
@@ -26631,28 +26631,28 @@
         <v>0</v>
       </c>
       <c r="AM161">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN161">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO161">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP161">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ161">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR161">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS161">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT161">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
@@ -26692,26 +26692,26 @@
         </is>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162">
         <v>0</v>
       </c>
       <c r="K162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N162">
@@ -26776,12 +26776,12 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "48"]</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AJ162">
@@ -26794,28 +26794,28 @@
         <v>0</v>
       </c>
       <c r="AM162">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN162">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO162">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP162">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ162">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AR162">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS162">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT162">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
@@ -26858,23 +26858,23 @@
         <v>0</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I163">
         <v>0</v>
       </c>
       <c r="J163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K163">
         <v>0</v>
       </c>
       <c r="L163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N163">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "35", "50"]</t>
         </is>
       </c>
       <c r="AJ163">
@@ -26957,28 +26957,28 @@
         <v>0</v>
       </c>
       <c r="AM163">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN163">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO163">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP163">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ163">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR163">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS163">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT163">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
@@ -27018,26 +27018,26 @@
         </is>
       </c>
       <c r="G164">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164">
         <v>0</v>
       </c>
       <c r="K164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N164">
@@ -27102,12 +27102,12 @@
       </c>
       <c r="AH164" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "90+4"]</t>
         </is>
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68"]</t>
         </is>
       </c>
       <c r="AJ164">
@@ -27120,28 +27120,28 @@
         <v>0</v>
       </c>
       <c r="AM164">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN164">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO164">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP164">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ164">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AR164">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS164">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT164">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
@@ -27181,26 +27181,26 @@
         </is>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I165">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K165">
         <v>0</v>
       </c>
       <c r="L165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N165">
@@ -27265,12 +27265,12 @@
       </c>
       <c r="AH165" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "25"]</t>
         </is>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "62"]</t>
         </is>
       </c>
       <c r="AJ165">
@@ -27283,16 +27283,16 @@
         <v>0</v>
       </c>
       <c r="AM165">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN165">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO165">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP165">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ165">
         <v>0</v>
@@ -27344,26 +27344,26 @@
         </is>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H166">
         <v>0</v>
       </c>
       <c r="I166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J166">
         <v>0</v>
       </c>
       <c r="K166">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L166">
         <v>0</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N166">
@@ -27428,7 +27428,7 @@
       </c>
       <c r="AH166" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "50", "89"]</t>
         </is>
       </c>
       <c r="AI166" t="inlineStr">
@@ -27446,28 +27446,28 @@
         <v>0</v>
       </c>
       <c r="AM166">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN166">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO166">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP166">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ166">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR166">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="AS166">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT166">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
@@ -27507,16 +27507,16 @@
         </is>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K167">
         <v>0</v>
@@ -27526,7 +27526,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N167">
@@ -27591,12 +27591,12 @@
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17"]</t>
         </is>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AJ167">
@@ -27609,28 +27609,28 @@
         <v>0</v>
       </c>
       <c r="AM167">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN167">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO167">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP167">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ167">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR167">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS167">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT167">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
@@ -27670,10 +27670,10 @@
         </is>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I168">
         <v>0</v>
@@ -27682,14 +27682,14 @@
         <v>0</v>
       </c>
       <c r="K168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L168">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N168">
@@ -27754,12 +27754,12 @@
       </c>
       <c r="AH168" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "63"]</t>
         </is>
       </c>
       <c r="AJ168">
@@ -27772,28 +27772,28 @@
         <v>0</v>
       </c>
       <c r="AM168">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN168">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO168">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP168">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ168">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AR168">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS168">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT168">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
@@ -27833,26 +27833,26 @@
         </is>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L169">
         <v>0</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N169">
@@ -27917,12 +27917,12 @@
       </c>
       <c r="AH169" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "52"]</t>
         </is>
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AJ169">
@@ -27935,28 +27935,28 @@
         <v>0</v>
       </c>
       <c r="AM169">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN169">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO169">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP169">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ169">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AR169">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS169">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT169">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
@@ -27996,26 +27996,26 @@
         </is>
       </c>
       <c r="G170">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H170">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N170">
@@ -28080,12 +28080,12 @@
       </c>
       <c r="AH170" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "80"]</t>
         </is>
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "50"]</t>
         </is>
       </c>
       <c r="AJ170">
@@ -28098,28 +28098,28 @@
         <v>0</v>
       </c>
       <c r="AM170">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN170">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO170">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP170">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ170">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR170">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS170">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="AT170">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
@@ -28159,26 +28159,26 @@
         </is>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J171">
         <v>0</v>
       </c>
       <c r="K171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N171">
@@ -28243,12 +28243,12 @@
       </c>
       <c r="AH171" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "19", "31", "55"]</t>
         </is>
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47"]</t>
         </is>
       </c>
       <c r="AJ171">
@@ -28261,28 +28261,28 @@
         <v>0</v>
       </c>
       <c r="AM171">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN171">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO171">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP171">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ171">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR171">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AS171">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT171">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
@@ -28322,10 +28322,10 @@
         </is>
       </c>
       <c r="G172">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172">
         <v>0</v>
@@ -28334,14 +28334,14 @@
         <v>0</v>
       </c>
       <c r="K172">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N172">
@@ -28406,12 +28406,12 @@
       </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62", "87", "90+5"]</t>
         </is>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AJ172">
@@ -28424,28 +28424,28 @@
         <v>0</v>
       </c>
       <c r="AM172">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN172">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO172">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP172">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ172">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR172">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS172">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT172">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
@@ -28485,26 +28485,26 @@
         </is>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H173">
         <v>0</v>
       </c>
       <c r="I173">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J173">
         <v>0</v>
       </c>
       <c r="K173">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L173">
         <v>0</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N173">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "39", "48", "52", "63"]</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
@@ -28587,28 +28587,28 @@
         <v>0</v>
       </c>
       <c r="AM173">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN173">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO173">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP173">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ173">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AR173">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="AS173">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AT173">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
@@ -28651,13 +28651,13 @@
         <v>0</v>
       </c>
       <c r="H174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I174">
         <v>0</v>
       </c>
       <c r="J174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K174">
         <v>0</v>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N174">
@@ -28737,7 +28737,7 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24"]</t>
         </is>
       </c>
       <c r="AJ174">
@@ -28750,28 +28750,28 @@
         <v>0</v>
       </c>
       <c r="AM174">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN174">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO174">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP174">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ174">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR174">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS174">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT174">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
@@ -29137,26 +29137,26 @@
         </is>
       </c>
       <c r="G177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H177">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I177">
         <v>0</v>
       </c>
       <c r="J177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L177">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N177">
@@ -29221,12 +29221,12 @@
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "64", "84"]</t>
         </is>
       </c>
       <c r="AJ177">
@@ -29239,28 +29239,28 @@
         <v>0</v>
       </c>
       <c r="AM177">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN177">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO177">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP177">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ177">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR177">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS177">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT177">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
@@ -29300,26 +29300,26 @@
         </is>
       </c>
       <c r="G178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J178">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K178">
         <v>0</v>
       </c>
       <c r="L178">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N178">
@@ -29384,12 +29384,12 @@
       </c>
       <c r="AH178" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37"]</t>
         </is>
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "18", "65", "79"]</t>
         </is>
       </c>
       <c r="AJ178">
@@ -29402,28 +29402,28 @@
         <v>0</v>
       </c>
       <c r="AM178">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN178">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO178">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP178">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ178">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR178">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS178">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT178">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
@@ -29463,26 +29463,26 @@
         </is>
       </c>
       <c r="G179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H179">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K179">
         <v>0</v>
       </c>
       <c r="L179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N179">
@@ -29547,12 +29547,12 @@
       </c>
       <c r="AH179" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19"]</t>
         </is>
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43", "64"]</t>
         </is>
       </c>
       <c r="AJ179">
@@ -29565,28 +29565,28 @@
         <v>0</v>
       </c>
       <c r="AM179">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN179">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO179">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP179">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ179">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR179">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS179">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT179">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
@@ -29645,7 +29645,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N180">
@@ -29728,28 +29728,28 @@
         <v>0</v>
       </c>
       <c r="AM180">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN180">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO180">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP180">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ180">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AR180">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS180">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT180">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
@@ -29789,13 +29789,13 @@
         </is>
       </c>
       <c r="G181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J181">
         <v>0</v>
@@ -29804,11 +29804,11 @@
         <v>0</v>
       </c>
       <c r="L181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N181">
@@ -29873,12 +29873,12 @@
       </c>
       <c r="AH181" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49"]</t>
         </is>
       </c>
       <c r="AJ181">
@@ -29891,28 +29891,28 @@
         <v>0</v>
       </c>
       <c r="AM181">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN181">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO181">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP181">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ181">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR181">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS181">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT181">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
@@ -29952,26 +29952,26 @@
         </is>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H182">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N182">
@@ -30036,12 +30036,12 @@
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "48"]</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "63"]</t>
         </is>
       </c>
       <c r="AJ182">
@@ -30054,28 +30054,28 @@
         <v>0</v>
       </c>
       <c r="AM182">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN182">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO182">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP182">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ182">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR182">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS182">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT182">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
@@ -30115,26 +30115,26 @@
         </is>
       </c>
       <c r="G183">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I183">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L183">
         <v>0</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N183">
@@ -30199,12 +30199,12 @@
       </c>
       <c r="AH183" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "12", "43", "89"]</t>
         </is>
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20"]</t>
         </is>
       </c>
       <c r="AJ183">
@@ -30217,28 +30217,28 @@
         <v>0</v>
       </c>
       <c r="AM183">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN183">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO183">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP183">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ183">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AR183">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS183">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT183">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
@@ -30278,26 +30278,26 @@
         </is>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I184">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L184">
         <v>0</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N184">
@@ -30362,12 +30362,12 @@
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "17", "59"]</t>
         </is>
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AJ184">
@@ -30380,28 +30380,28 @@
         <v>0</v>
       </c>
       <c r="AM184">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN184">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO184">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP184">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ184">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR184">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS184">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT184">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
@@ -30441,26 +30441,26 @@
         </is>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I185">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L185">
         <v>0</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N185">
@@ -30525,12 +30525,12 @@
       </c>
       <c r="AH185" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "30", "56"]</t>
         </is>
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AJ185">
@@ -30543,28 +30543,28 @@
         <v>0</v>
       </c>
       <c r="AM185">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN185">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO185">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP185">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ185">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR185">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AS185">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT185">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>0</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I186">
         <v>0</v>
@@ -30619,11 +30619,11 @@
         <v>0</v>
       </c>
       <c r="L186">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N186">
@@ -30693,7 +30693,7 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "90+2"]</t>
         </is>
       </c>
       <c r="AJ186">
@@ -30706,28 +30706,28 @@
         <v>0</v>
       </c>
       <c r="AM186">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN186">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AO186">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP186">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AQ186">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR186">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AS186">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT186">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
@@ -30767,13 +30767,13 @@
         </is>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H187">
         <v>0</v>
       </c>
       <c r="I187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J187">
         <v>0</v>
@@ -30786,41 +30786,41 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N187">
         <v>2.3</v>
       </c>
       <c r="O187">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P187">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="Q187">
         <v>3.1</v>
       </c>
       <c r="R187">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S187">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="T187">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U187">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="V187">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W187">
         <v>1.03</v>
       </c>
       <c r="X187">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y187">
         <v>1.67</v>
@@ -30838,59 +30838,59 @@
         <v>7.5</v>
       </c>
       <c r="AD187">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE187">
         <v>1.01</v>
       </c>
       <c r="AF187">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AG187">
         <v>1.5</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
+          <t>["17"]</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ187">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AK187">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL187">
         <v>0</v>
       </c>
       <c r="AM187">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN187">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO187">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP187">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ187">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR187">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS187">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT187">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
@@ -30930,13 +30930,13 @@
         </is>
       </c>
       <c r="G188">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H188">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I188">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J188">
         <v>0</v>
@@ -30945,51 +30945,51 @@
         <v>0</v>
       </c>
       <c r="L188">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N188">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O188">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P188">
-        <v>4.72</v>
+        <v>4.7</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S188">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T188">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U188">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V188">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W188">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X188">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y188">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z188">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA188">
         <v>2.87</v>
@@ -30998,62 +30998,62 @@
         <v>1.4</v>
       </c>
       <c r="AC188">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD188">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE188">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF188">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG188">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "44"]</t>
         </is>
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85", "90+5"]</t>
         </is>
       </c>
       <c r="AJ188">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK188">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL188">
         <v>0</v>
       </c>
       <c r="AM188">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN188">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO188">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP188">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ188">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AR188">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AS188">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT188">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
@@ -31096,23 +31096,23 @@
         <v>0</v>
       </c>
       <c r="H189">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I189">
         <v>0</v>
       </c>
       <c r="J189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K189">
         <v>0</v>
       </c>
       <c r="L189">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N189">
@@ -31182,7 +31182,7 @@
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "59", "90+2"]</t>
         </is>
       </c>
       <c r="AJ189">
@@ -31195,28 +31195,28 @@
         <v>0</v>
       </c>
       <c r="AM189">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN189">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO189">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP189">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ189">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AR189">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS189">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT189">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
@@ -31256,10 +31256,10 @@
         </is>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I190">
         <v>0</v>
@@ -31268,14 +31268,14 @@
         <v>0</v>
       </c>
       <c r="K190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N190">
@@ -31340,12 +31340,12 @@
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+7"]</t>
         </is>
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AJ190">
@@ -31358,28 +31358,28 @@
         <v>0</v>
       </c>
       <c r="AM190">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN190">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO190">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP190">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ190">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR190">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS190">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT190">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
@@ -31422,13 +31422,13 @@
         <v>0</v>
       </c>
       <c r="H191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I191">
         <v>0</v>
       </c>
       <c r="J191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K191">
         <v>0</v>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N191">
@@ -31508,7 +31508,7 @@
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31"]</t>
         </is>
       </c>
       <c r="AJ191">
@@ -31521,28 +31521,28 @@
         <v>0</v>
       </c>
       <c r="AM191">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN191">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO191">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP191">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ191">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AR191">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS191">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT191">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         </is>
       </c>
       <c r="G192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H192">
         <v>0</v>
@@ -31594,42 +31594,42 @@
         <v>0</v>
       </c>
       <c r="K192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L192">
         <v>0</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N192">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O192">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P192">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="Q192">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="R192">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="S192">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T192">
-        <v>2.92</v>
+        <v>2.24</v>
       </c>
       <c r="U192">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="V192">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W192">
         <v>1.04</v>
@@ -31641,19 +31641,19 @@
         <v>1.3</v>
       </c>
       <c r="Z192">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="AA192">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AB192">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC192">
         <v>3.34</v>
       </c>
       <c r="AD192">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE192">
         <v>1.06</v>
@@ -31666,46 +31666,46 @@
       </c>
       <c r="AH192" t="inlineStr">
         <is>
+          <t>["77"]</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ192">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AK192">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AL192">
         <v>0</v>
       </c>
       <c r="AM192">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN192">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO192">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP192">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ192">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR192">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS192">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT192">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
@@ -31745,26 +31745,26 @@
         </is>
       </c>
       <c r="G193">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
       <c r="I193">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J193">
         <v>0</v>
       </c>
       <c r="K193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L193">
         <v>0</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N193">
@@ -31829,7 +31829,7 @@
       </c>
       <c r="AH193" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "37", "51"]</t>
         </is>
       </c>
       <c r="AI193" t="inlineStr">
@@ -31847,28 +31847,28 @@
         <v>0</v>
       </c>
       <c r="AM193">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN193">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO193">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP193">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ193">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AR193">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS193">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AT193">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
@@ -31908,26 +31908,26 @@
         </is>
       </c>
       <c r="G194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I194">
         <v>0</v>
       </c>
       <c r="J194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L194">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N194">
@@ -31992,12 +31992,12 @@
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49"]</t>
         </is>
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "54", "78"]</t>
         </is>
       </c>
       <c r="AJ194">
@@ -32010,28 +32010,28 @@
         <v>0</v>
       </c>
       <c r="AM194">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN194">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO194">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP194">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ194">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR194">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS194">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT194">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
@@ -32071,26 +32071,26 @@
         </is>
       </c>
       <c r="G195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I195">
         <v>0</v>
       </c>
       <c r="J195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N195">
@@ -32155,12 +32155,12 @@
       </c>
       <c r="AH195" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "26", "47", "82"]</t>
         </is>
       </c>
       <c r="AJ195">
@@ -32173,28 +32173,28 @@
         <v>0</v>
       </c>
       <c r="AM195">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN195">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO195">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP195">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ195">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AR195">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AS195">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT195">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N196">
@@ -32336,28 +32336,28 @@
         <v>0</v>
       </c>
       <c r="AM196">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN196">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO196">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP196">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ196">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR196">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS196">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT196">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
@@ -32388,63 +32388,63 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G197">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L197">
         <v>0</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N197">
-        <v>2.8</v>
+        <v>1.52</v>
       </c>
       <c r="O197">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="P197">
-        <v>2.3</v>
+        <v>5.37</v>
       </c>
       <c r="Q197">
-        <v>3.77</v>
+        <v>2.09</v>
       </c>
       <c r="R197">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="S197">
         <v>1.44</v>
       </c>
       <c r="T197">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="U197">
         <v>3.3</v>
       </c>
       <c r="V197">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W197">
         <v>1.03</v>
@@ -32459,68 +32459,68 @@
         <v>2.62</v>
       </c>
       <c r="AA197">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB197">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC197">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD197">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE197">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF197">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="AG197">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "53"]</t>
         </is>
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19"]</t>
         </is>
       </c>
       <c r="AJ197">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK197">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL197">
         <v>0</v>
       </c>
       <c r="AM197">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN197">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO197">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP197">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ197">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR197">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS197">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT197">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
@@ -32551,63 +32551,63 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H198">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K198">
         <v>0</v>
       </c>
       <c r="L198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N198">
-        <v>1.52</v>
+        <v>2.8</v>
       </c>
       <c r="O198">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="P198">
-        <v>5.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q198">
-        <v>2.09</v>
+        <v>3.77</v>
       </c>
       <c r="R198">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="S198">
         <v>1.44</v>
       </c>
       <c r="T198">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="U198">
         <v>3.3</v>
       </c>
       <c r="V198">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W198">
         <v>1.03</v>
@@ -32622,68 +32622,68 @@
         <v>2.62</v>
       </c>
       <c r="AA198">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AB198">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC198">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD198">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE198">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF198">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="AG198">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AI198" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "86"]</t>
         </is>
       </c>
       <c r="AJ198">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK198">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL198">
         <v>0</v>
       </c>
       <c r="AM198">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN198">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO198">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP198">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ198">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR198">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS198">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT198">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
@@ -32723,26 +32723,26 @@
         </is>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J199">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N199">
@@ -32807,12 +32807,12 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "52"]</t>
         </is>
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "18", "78"]</t>
         </is>
       </c>
       <c r="AJ199">
@@ -32825,28 +32825,28 @@
         <v>0</v>
       </c>
       <c r="AM199">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN199">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO199">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP199">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ199">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AR199">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AS199">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT199">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
@@ -32886,26 +32886,26 @@
         </is>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H200">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J200">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N200">
@@ -32970,12 +32970,12 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "53"]</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "22", "90+6"]</t>
         </is>
       </c>
       <c r="AJ200">
@@ -32988,28 +32988,28 @@
         <v>0</v>
       </c>
       <c r="AM200">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN200">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO200">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP200">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ200">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR200">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS200">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT200">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
@@ -33049,26 +33049,26 @@
         </is>
       </c>
       <c r="G201">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I201">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L201">
         <v>0</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N201">
@@ -33133,12 +33133,12 @@
       </c>
       <c r="AH201" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "30", "86"]</t>
         </is>
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39"]</t>
         </is>
       </c>
       <c r="AJ201">
@@ -33151,28 +33151,28 @@
         <v>0</v>
       </c>
       <c r="AM201">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN201">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO201">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP201">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ201">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR201">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS201">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT201">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
@@ -33212,13 +33212,13 @@
         </is>
       </c>
       <c r="G202">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I202">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -33227,11 +33227,11 @@
         <v>0</v>
       </c>
       <c r="L202">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N202">
@@ -33296,12 +33296,12 @@
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AJ202">
@@ -33314,28 +33314,28 @@
         <v>0</v>
       </c>
       <c r="AM202">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN202">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO202">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP202">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ202">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR202">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS202">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT202">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
@@ -33378,23 +33378,23 @@
         <v>0</v>
       </c>
       <c r="H203">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I203">
         <v>0</v>
       </c>
       <c r="J203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K203">
         <v>0</v>
       </c>
       <c r="L203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N203">
@@ -33464,7 +33464,7 @@
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "49"]</t>
         </is>
       </c>
       <c r="AJ203">
@@ -33477,28 +33477,28 @@
         <v>0</v>
       </c>
       <c r="AM203">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN203">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO203">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP203">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ203">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AR203">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS203">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT203">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
@@ -33538,130 +33538,130 @@
         </is>
       </c>
       <c r="G204">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H204">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J204">
         <v>0</v>
       </c>
       <c r="K204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L204">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N204">
         <v>2.65</v>
       </c>
       <c r="O204">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="P204">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="Q204">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="R204">
         <v>1.71</v>
       </c>
       <c r="S204">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="T204">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="U204">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="V204">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W204">
         <v>1.02</v>
       </c>
       <c r="X204">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Y204">
         <v>1.77</v>
       </c>
       <c r="Z204">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AA204">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AB204">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC204">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AD204">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE204">
         <v>1.01</v>
       </c>
       <c r="AF204">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AG204">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "79"]</t>
         </is>
       </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61", "75"]</t>
         </is>
       </c>
       <c r="AJ204">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK204">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL204">
         <v>0</v>
       </c>
       <c r="AM204">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN204">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO204">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP204">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ204">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR204">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS204">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT204">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
@@ -33720,62 +33720,62 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N205">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O205">
         <v>2.7</v>
       </c>
       <c r="P205">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q205">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="R205">
         <v>1.83</v>
       </c>
       <c r="S205">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T205">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U205">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="V205">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W205">
         <v>1.03</v>
       </c>
       <c r="X205">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Y205">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Z205">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AA205">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AB205">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC205">
         <v>6.25</v>
       </c>
       <c r="AD205">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE205">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF205">
         <v>2.3</v>
@@ -33794,37 +33794,37 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK205">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL205">
         <v>0</v>
       </c>
       <c r="AM205">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN205">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO205">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP205">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ205">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR205">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS205">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT205">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
@@ -33864,10 +33864,10 @@
         </is>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I206">
         <v>0</v>
@@ -33876,118 +33876,118 @@
         <v>0</v>
       </c>
       <c r="K206">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N206">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="O206">
+        <v>2.95</v>
+      </c>
+      <c r="P206">
+        <v>5.25</v>
+      </c>
+      <c r="Q206">
+        <v>2.4</v>
+      </c>
+      <c r="R206">
+        <v>1.91</v>
+      </c>
+      <c r="S206">
+        <v>1.6</v>
+      </c>
+      <c r="T206">
+        <v>2.18</v>
+      </c>
+      <c r="U206">
+        <v>3.98</v>
+      </c>
+      <c r="V206">
+        <v>1.17</v>
+      </c>
+      <c r="W206">
+        <v>1.04</v>
+      </c>
+      <c r="X206">
+        <v>1.06</v>
+      </c>
+      <c r="Y206">
+        <v>1.62</v>
+      </c>
+      <c r="Z206">
+        <v>2.23</v>
+      </c>
+      <c r="AA206">
+        <v>2.85</v>
+      </c>
+      <c r="AB206">
+        <v>1.35</v>
+      </c>
+      <c r="AC206">
+        <v>5.9</v>
+      </c>
+      <c r="AD206">
+        <v>1.07</v>
+      </c>
+      <c r="AE206">
+        <v>1.03</v>
+      </c>
+      <c r="AF206">
+        <v>2.4</v>
+      </c>
+      <c r="AG206">
+        <v>1.5</v>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>["58", "77"]</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>["66"]</t>
+        </is>
+      </c>
+      <c r="AJ206">
+        <v>1.33</v>
+      </c>
+      <c r="AK206">
+        <v>1.95</v>
+      </c>
+      <c r="AL206">
+        <v>0</v>
+      </c>
+      <c r="AM206">
+        <v>4</v>
+      </c>
+      <c r="AN206">
         <v>3</v>
       </c>
-      <c r="P206">
-        <v>5.1</v>
-      </c>
-      <c r="Q206">
-        <v>0</v>
-      </c>
-      <c r="R206">
-        <v>0</v>
-      </c>
-      <c r="S206">
-        <v>0</v>
-      </c>
-      <c r="T206">
-        <v>0</v>
-      </c>
-      <c r="U206">
-        <v>0</v>
-      </c>
-      <c r="V206">
-        <v>0</v>
-      </c>
-      <c r="W206">
-        <v>0</v>
-      </c>
-      <c r="X206">
-        <v>0</v>
-      </c>
-      <c r="Y206">
-        <v>0</v>
-      </c>
-      <c r="Z206">
-        <v>0</v>
-      </c>
-      <c r="AA206">
-        <v>2.87</v>
-      </c>
-      <c r="AB206">
-        <v>1.4</v>
-      </c>
-      <c r="AC206">
-        <v>0</v>
-      </c>
-      <c r="AD206">
-        <v>0</v>
-      </c>
-      <c r="AE206">
-        <v>0</v>
-      </c>
-      <c r="AF206">
-        <v>0</v>
-      </c>
-      <c r="AG206">
-        <v>0</v>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ206">
-        <v>0</v>
-      </c>
-      <c r="AK206">
-        <v>0</v>
-      </c>
-      <c r="AL206">
-        <v>0</v>
-      </c>
-      <c r="AM206">
-        <v>-1</v>
-      </c>
-      <c r="AN206">
-        <v>-1</v>
-      </c>
       <c r="AO206">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP206">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ206">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR206">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS206">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT206">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
@@ -34030,7 +34030,7 @@
         <v>0</v>
       </c>
       <c r="H207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I207">
         <v>0</v>
@@ -34042,72 +34042,72 @@
         <v>0</v>
       </c>
       <c r="L207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N207">
         <v>1.65</v>
       </c>
       <c r="O207">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P207">
         <v>5</v>
       </c>
       <c r="Q207">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R207">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="S207">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T207">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="U207">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="V207">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="W207">
         <v>1.04</v>
       </c>
       <c r="X207">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y207">
+        <v>1.45</v>
+      </c>
+      <c r="Z207">
+        <v>2.55</v>
+      </c>
+      <c r="AA207">
+        <v>2.4</v>
+      </c>
+      <c r="AB207">
         <v>1.48</v>
       </c>
-      <c r="Z207">
-        <v>2.63</v>
-      </c>
-      <c r="AA207">
-        <v>2.5</v>
-      </c>
-      <c r="AB207">
-        <v>1.47</v>
-      </c>
       <c r="AC207">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD207">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE207">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF207">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AG207">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34116,41 +34116,41 @@
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AJ207">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AK207">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL207">
         <v>0</v>
       </c>
       <c r="AM207">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN207">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO207">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP207">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ207">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR207">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS207">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT207">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>0</v>
       </c>
       <c r="H208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I208">
         <v>0</v>
@@ -34205,39 +34205,39 @@
         <v>0</v>
       </c>
       <c r="L208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N208">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="O208">
         <v>2.85</v>
       </c>
       <c r="P208">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q208">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R208">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S208">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="T208">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U208">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="V208">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W208">
         <v>1.03</v>
@@ -34246,19 +34246,19 @@
         <v>1.1</v>
       </c>
       <c r="Y208">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z208">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AA208">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="AB208">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC208">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AD208">
         <v>1.13</v>
@@ -34270,7 +34270,7 @@
         <v>2.3</v>
       </c>
       <c r="AG208">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34279,41 +34279,41 @@
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AJ208">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK208">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL208">
         <v>0</v>
       </c>
       <c r="AM208">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN208">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO208">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP208">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ208">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR208">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS208">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT208">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N209">
@@ -34455,28 +34455,28 @@
         <v>0</v>
       </c>
       <c r="AM209">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN209">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO209">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP209">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ209">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR209">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS209">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT209">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
@@ -34516,26 +34516,26 @@
         </is>
       </c>
       <c r="G210">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H210">
         <v>0</v>
       </c>
       <c r="I210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J210">
         <v>0</v>
       </c>
       <c r="K210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L210">
         <v>0</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N210">
@@ -34600,7 +34600,7 @@
       </c>
       <c r="AH210" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "53"]</t>
         </is>
       </c>
       <c r="AI210" t="inlineStr">
@@ -34618,28 +34618,28 @@
         <v>0</v>
       </c>
       <c r="AM210">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN210">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO210">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP210">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ210">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR210">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS210">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT210">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
@@ -34682,13 +34682,13 @@
         <v>0</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I211">
         <v>0</v>
       </c>
       <c r="J211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K211">
         <v>0</v>
@@ -34698,7 +34698,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N211">
@@ -34768,7 +34768,7 @@
       </c>
       <c r="AI211" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9"]</t>
         </is>
       </c>
       <c r="AJ211">
@@ -34781,28 +34781,28 @@
         <v>0</v>
       </c>
       <c r="AM211">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN211">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO211">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP211">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="AQ211">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AR211">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AS211">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT211">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
@@ -34842,13 +34842,13 @@
         </is>
       </c>
       <c r="G212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H212">
         <v>0</v>
       </c>
       <c r="I212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J212">
         <v>0</v>
@@ -34861,7 +34861,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N212">
@@ -34926,7 +34926,7 @@
       </c>
       <c r="AH212" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25"]</t>
         </is>
       </c>
       <c r="AI212" t="inlineStr">
@@ -34944,28 +34944,28 @@
         <v>0</v>
       </c>
       <c r="AM212">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN212">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO212">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP212">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ212">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR212">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AS212">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT212">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
@@ -35005,16 +35005,16 @@
         </is>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I213">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K213">
         <v>0</v>
@@ -35024,7 +35024,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N213">
@@ -35089,12 +35089,12 @@
       </c>
       <c r="AH213" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "30"]</t>
         </is>
       </c>
       <c r="AI213" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22"]</t>
         </is>
       </c>
       <c r="AJ213">
@@ -35107,28 +35107,28 @@
         <v>0</v>
       </c>
       <c r="AM213">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN213">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO213">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP213">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ213">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AR213">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS213">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT213">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
@@ -35168,10 +35168,10 @@
         </is>
       </c>
       <c r="G214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I214">
         <v>0</v>
@@ -35180,14 +35180,14 @@
         <v>0</v>
       </c>
       <c r="K214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N214">
@@ -35252,12 +35252,12 @@
       </c>
       <c r="AH214" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+2"]</t>
         </is>
       </c>
       <c r="AI214" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69"]</t>
         </is>
       </c>
       <c r="AJ214">
@@ -35270,28 +35270,28 @@
         <v>0</v>
       </c>
       <c r="AM214">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN214">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO214">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP214">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ214">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AR214">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS214">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT214">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
@@ -35331,26 +35331,26 @@
         </is>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I215">
         <v>0</v>
       </c>
       <c r="J215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K215">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L215">
         <v>0</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N215">
@@ -35415,12 +35415,12 @@
       </c>
       <c r="AH215" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49", "57", "72"]</t>
         </is>
       </c>
       <c r="AI215" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2"]</t>
         </is>
       </c>
       <c r="AJ215">
@@ -35433,28 +35433,28 @@
         <v>0</v>
       </c>
       <c r="AM215">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN215">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO215">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP215">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ215">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AR215">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS215">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT215">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
@@ -35485,139 +35485,139 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I216">
         <v>0</v>
       </c>
       <c r="J216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K216">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N216">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O216">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P216">
         <v>2.05</v>
       </c>
       <c r="Q216">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="R216">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S216">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T216">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="U216">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="V216">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W216">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X216">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y216">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z216">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="AA216">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AB216">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC216">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD216">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE216">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF216">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG216">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "56"]</t>
         </is>
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "79"]</t>
         </is>
       </c>
       <c r="AJ216">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AK216">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AL216">
         <v>0</v>
       </c>
       <c r="AM216">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN216">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO216">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP216">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ216">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR216">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AS216">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT216">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,64 +35680,64 @@
         </is>
       </c>
       <c r="N217">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O217">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P217">
         <v>2.05</v>
       </c>
       <c r="Q217">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="R217">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S217">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T217">
-        <v>2.46</v>
+        <v>2.65</v>
       </c>
       <c r="U217">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="V217">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W217">
+        <v>1.05</v>
+      </c>
+      <c r="X217">
+        <v>1.06</v>
+      </c>
+      <c r="Y217">
+        <v>1.34</v>
+      </c>
+      <c r="Z217">
+        <v>2.78</v>
+      </c>
+      <c r="AA217">
+        <v>2.21</v>
+      </c>
+      <c r="AB217">
+        <v>1.62</v>
+      </c>
+      <c r="AC217">
+        <v>4.2</v>
+      </c>
+      <c r="AD217">
+        <v>1.22</v>
+      </c>
+      <c r="AE217">
         <v>1.04</v>
       </c>
-      <c r="X217">
-        <v>1.07</v>
-      </c>
-      <c r="Y217">
-        <v>1.4</v>
-      </c>
-      <c r="Z217">
-        <v>2.62</v>
-      </c>
-      <c r="AA217">
-        <v>2.35</v>
-      </c>
-      <c r="AB217">
-        <v>1.55</v>
-      </c>
-      <c r="AC217">
-        <v>4.5</v>
-      </c>
-      <c r="AD217">
-        <v>1.18</v>
-      </c>
-      <c r="AE217">
-        <v>1</v>
-      </c>
       <c r="AF217">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG217">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AK217">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35820,26 +35820,26 @@
         </is>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J218">
         <v>0</v>
       </c>
       <c r="K218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L218">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N218">
@@ -35904,12 +35904,12 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "90+1"]</t>
         </is>
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70", "90+7"]</t>
         </is>
       </c>
       <c r="AJ218">
@@ -35922,28 +35922,28 @@
         <v>0</v>
       </c>
       <c r="AM218">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN218">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO218">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP218">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ218">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR218">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS218">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT218">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
@@ -35983,26 +35983,26 @@
         </is>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H219">
         <v>0</v>
       </c>
       <c r="I219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J219">
         <v>0</v>
       </c>
       <c r="K219">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L219">
         <v>0</v>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N219">
@@ -36067,7 +36067,7 @@
       </c>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "86", "90"]</t>
         </is>
       </c>
       <c r="AI219" t="inlineStr">
@@ -36085,28 +36085,28 @@
         <v>0</v>
       </c>
       <c r="AM219">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN219">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO219">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP219">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ219">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AR219">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS219">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT219">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
@@ -36332,19 +36332,19 @@
         </is>
       </c>
       <c r="N221">
-        <v>4.69</v>
+        <v>4.33</v>
       </c>
       <c r="O221">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P221">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q221">
-        <v>5.18</v>
+        <v>5.19</v>
       </c>
       <c r="R221">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S221">
         <v>1.33</v>
@@ -36356,13 +36356,13 @@
         <v>2.69</v>
       </c>
       <c r="V221">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W221">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X221">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y221">
         <v>1.25</v>
@@ -36371,19 +36371,19 @@
         <v>3.8</v>
       </c>
       <c r="AA221">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB221">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AC221">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD221">
         <v>1.3</v>
       </c>
       <c r="AE221">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF221">
         <v>1.83</v>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK221">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36472,26 +36472,26 @@
         </is>
       </c>
       <c r="G222">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H222">
         <v>0</v>
       </c>
       <c r="I222">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J222">
         <v>0</v>
       </c>
       <c r="K222">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L222">
         <v>0</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N222">
@@ -36556,7 +36556,7 @@
       </c>
       <c r="AH222" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "84"]</t>
         </is>
       </c>
       <c r="AI222" t="inlineStr">
@@ -36574,28 +36574,28 @@
         <v>0</v>
       </c>
       <c r="AM222">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN222">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO222">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP222">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ222">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR222">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="AS222">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="AT222">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
@@ -36798,16 +36798,16 @@
         </is>
       </c>
       <c r="G224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K224">
         <v>0</v>
@@ -36817,7 +36817,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N224">
@@ -36882,12 +36882,12 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8"]</t>
         </is>
       </c>
       <c r="AJ224">
@@ -36900,28 +36900,28 @@
         <v>0</v>
       </c>
       <c r="AM224">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN224">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO224">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP224">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ224">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR224">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS224">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT224">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>0</v>
       </c>
       <c r="H225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I225">
         <v>0</v>
@@ -36976,11 +36976,11 @@
         <v>0</v>
       </c>
       <c r="L225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N225">
@@ -37050,7 +37050,7 @@
       </c>
       <c r="AI225" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+7"]</t>
         </is>
       </c>
       <c r="AJ225">
@@ -37063,28 +37063,28 @@
         <v>0</v>
       </c>
       <c r="AM225">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN225">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO225">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP225">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ225">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR225">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS225">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT225">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
@@ -37124,13 +37124,13 @@
         </is>
       </c>
       <c r="G226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H226">
         <v>0</v>
       </c>
       <c r="I226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J226">
         <v>0</v>
@@ -37143,7 +37143,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N226">
@@ -37208,7 +37208,7 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
@@ -37226,28 +37226,28 @@
         <v>0</v>
       </c>
       <c r="AM226">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN226">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO226">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP226">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ226">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AR226">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS226">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AT226">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         </is>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H227">
         <v>0</v>
@@ -37299,14 +37299,14 @@
         <v>0</v>
       </c>
       <c r="K227">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L227">
         <v>0</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N227">
@@ -37371,7 +37371,7 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "59"]</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
@@ -37389,28 +37389,28 @@
         <v>0</v>
       </c>
       <c r="AM227">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN227">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO227">
-        <v>-1</v>
+        <v>35</v>
       </c>
       <c r="AP227">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ227">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AR227">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AS227">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AT227">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>0</v>
       </c>
       <c r="H228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I228">
         <v>0</v>
@@ -37465,11 +37465,11 @@
         <v>0</v>
       </c>
       <c r="L228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N228">
@@ -37539,7 +37539,7 @@
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+4"]</t>
         </is>
       </c>
       <c r="AJ228">
@@ -37552,28 +37552,28 @@
         <v>0</v>
       </c>
       <c r="AM228">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN228">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO228">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP228">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ228">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR228">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS228">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT228">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
@@ -37805,28 +37805,28 @@
         <v>3.31</v>
       </c>
       <c r="P230">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q230">
         <v>2.3</v>
       </c>
       <c r="R230">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S230">
         <v>1.3</v>
       </c>
       <c r="T230">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U230">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="V230">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W230">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X230">
         <v>1</v>
@@ -37838,7 +37838,7 @@
         <v>3.4</v>
       </c>
       <c r="AA230">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB230">
         <v>1.81</v>
@@ -37847,13 +37847,13 @@
         <v>2.57</v>
       </c>
       <c r="AD230">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE230">
         <v>1.16</v>
       </c>
       <c r="AF230">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG230">
         <v>2.05</v>
@@ -37869,7 +37869,7 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK230">
         <v>1.94</v>
@@ -37962,16 +37962,16 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
       <c r="O231">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P231">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q231">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="R231">
         <v>2.06</v>
@@ -37986,40 +37986,40 @@
         <v>3</v>
       </c>
       <c r="V231">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W231">
         <v>1.04</v>
       </c>
       <c r="X231">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y231">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z231">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA231">
         <v>2.1</v>
       </c>
       <c r="AB231">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AC231">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD231">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE231">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF231">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG231">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38288,25 +38288,25 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="O233">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P233">
         <v>2.55</v>
       </c>
       <c r="Q233">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="R233">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="S233">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T233">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="U233">
         <v>3.9</v>
@@ -38321,19 +38321,19 @@
         <v>1.11</v>
       </c>
       <c r="Y233">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="Z233">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AA233">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AB233">
         <v>1.36</v>
       </c>
       <c r="AC233">
-        <v>6.61</v>
+        <v>6.72</v>
       </c>
       <c r="AD233">
         <v>1.07</v>
@@ -38361,7 +38361,7 @@
         <v>1.34</v>
       </c>
       <c r="AK233">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38451,64 +38451,64 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O234">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="P234">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="Q234">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R234">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S234">
         <v>1.49</v>
       </c>
       <c r="T234">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="U234">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="V234">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="W234">
         <v>1.02</v>
       </c>
       <c r="X234">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y234">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z234">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AA234">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AB234">
         <v>1.57</v>
       </c>
       <c r="AC234">
-        <v>4.56</v>
+        <v>4.39</v>
       </c>
       <c r="AD234">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE234">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF234">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG234">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK234">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38614,34 +38614,34 @@
         </is>
       </c>
       <c r="N235">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O235">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="P235">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="Q235">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="R235">
         <v>2.44</v>
       </c>
       <c r="S235">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T235">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U235">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="V235">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W235">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X235">
         <v>1.04</v>
@@ -38650,22 +38650,22 @@
         <v>1.18</v>
       </c>
       <c r="Z235">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA235">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB235">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC235">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AD235">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE235">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF235">
         <v>1.55</v>
@@ -38684,7 +38684,7 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK235">
         <v>1.67</v>
@@ -38777,43 +38777,43 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="O236">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P236">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q236">
         <v>2.1</v>
       </c>
       <c r="R236">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S236">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="T236">
-        <v>2.61</v>
+        <v>2.41</v>
       </c>
       <c r="U236">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V236">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W236">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X236">
         <v>1.04</v>
       </c>
       <c r="Y236">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z236">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AA236">
         <v>2.25</v>
@@ -38822,35 +38822,35 @@
         <v>1.57</v>
       </c>
       <c r="AC236">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD236">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE236">
         <v>1.06</v>
       </c>
       <c r="AF236">
+        <v>2.25</v>
+      </c>
+      <c r="AG236">
+        <v>1.6</v>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ236">
+        <v>1.2</v>
+      </c>
+      <c r="AK236">
         <v>2.3</v>
-      </c>
-      <c r="AG236">
-        <v>1.53</v>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ236">
-        <v>1.25</v>
-      </c>
-      <c r="AK236">
-        <v>2.38</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38943,28 +38943,28 @@
         <v>2.23</v>
       </c>
       <c r="O237">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P237">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q237">
         <v>2.77</v>
       </c>
       <c r="R237">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S237">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T237">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="U237">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V237">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W237">
         <v>1.05</v>
@@ -38973,31 +38973,31 @@
         <v>1.05</v>
       </c>
       <c r="Y237">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z237">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AA237">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AB237">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC237">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AD237">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE237">
         <v>1.04</v>
       </c>
       <c r="AF237">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG237">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK237">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39121,7 +39121,7 @@
         <v>1.35</v>
       </c>
       <c r="T238">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="U238">
         <v>2.62</v>
@@ -39130,7 +39130,7 @@
         <v>1.42</v>
       </c>
       <c r="W238">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X238">
         <v>1</v>
@@ -39145,13 +39145,13 @@
         <v>1.87</v>
       </c>
       <c r="AB238">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC238">
         <v>3.14</v>
       </c>
       <c r="AD238">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE238">
         <v>1.06</v>
@@ -39272,7 +39272,7 @@
         <v>3.18</v>
       </c>
       <c r="P239">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q239">
         <v>4.1</v>
@@ -39281,16 +39281,16 @@
         <v>2.15</v>
       </c>
       <c r="S239">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T239">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="U239">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="V239">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W239">
         <v>1.08</v>
@@ -39299,10 +39299,10 @@
         <v>1.04</v>
       </c>
       <c r="Y239">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z239">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="AA239">
         <v>2</v>
@@ -39336,7 +39336,7 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK239">
         <v>1.29</v>
@@ -39438,10 +39438,10 @@
         <v>5.9</v>
       </c>
       <c r="Q240">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="R240">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S240">
         <v>1.36</v>
@@ -39456,7 +39456,7 @@
         <v>1.43</v>
       </c>
       <c r="W240">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X240">
         <v>1</v>
@@ -39471,13 +39471,13 @@
         <v>1.8</v>
       </c>
       <c r="AB240">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC240">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AD240">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE240">
         <v>1.11</v>
@@ -39486,7 +39486,7 @@
         <v>1.9</v>
       </c>
       <c r="AG240">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39592,31 +39592,31 @@
         </is>
       </c>
       <c r="N241">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O241">
         <v>4.2</v>
       </c>
       <c r="P241">
-        <v>6.48</v>
+        <v>5.5</v>
       </c>
       <c r="Q241">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="R241">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="S241">
         <v>1.3</v>
       </c>
       <c r="T241">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="U241">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="V241">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W241">
         <v>1.11</v>
@@ -39628,28 +39628,28 @@
         <v>1.17</v>
       </c>
       <c r="Z241">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AA241">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB241">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC241">
         <v>2.6</v>
       </c>
       <c r="AD241">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE241">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF241">
         <v>1.84</v>
       </c>
       <c r="AG241">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>1.2</v>
       </c>
       <c r="AK241">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39755,64 +39755,64 @@
         </is>
       </c>
       <c r="N242">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="O242">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P242">
-        <v>6.17</v>
+        <v>6.75</v>
       </c>
       <c r="Q242">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R242">
         <v>2</v>
       </c>
       <c r="S242">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T242">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="U242">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="V242">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W242">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X242">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y242">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="Z242">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AA242">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AB242">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AC242">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD242">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE242">
         <v>1.04</v>
       </c>
       <c r="AF242">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AG242">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK242">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -39921,10 +39921,10 @@
         <v>1.88</v>
       </c>
       <c r="O243">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P243">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q243">
         <v>2.55</v>
@@ -39936,7 +39936,7 @@
         <v>1.49</v>
       </c>
       <c r="T243">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="U243">
         <v>3.3</v>
@@ -39951,13 +39951,13 @@
         <v>1.05</v>
       </c>
       <c r="Y243">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z243">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA243">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AB243">
         <v>1.61</v>
@@ -40081,52 +40081,52 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="O244">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="P244">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="Q244">
         <v>2.63</v>
       </c>
       <c r="R244">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S244">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T244">
         <v>2.31</v>
       </c>
       <c r="U244">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="V244">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W244">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X244">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y244">
         <v>1.53</v>
       </c>
       <c r="Z244">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AA244">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AB244">
         <v>1.44</v>
       </c>
       <c r="AC244">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="AD244">
         <v>1.11</v>
@@ -40138,7 +40138,7 @@
         <v>2.19</v>
       </c>
       <c r="AG244">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40244,64 +40244,64 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O245">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P245">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q245">
         <v>3.3</v>
       </c>
       <c r="R245">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S245">
         <v>1.25</v>
       </c>
       <c r="T245">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U245">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="V245">
         <v>1.57</v>
       </c>
       <c r="W245">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X245">
         <v>1.01</v>
       </c>
       <c r="Y245">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z245">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AA245">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AB245">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC245">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD245">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE245">
         <v>1.17</v>
       </c>
       <c r="AF245">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG245">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK245">
         <v>1.36</v>
@@ -40410,28 +40410,28 @@
         <v>1.83</v>
       </c>
       <c r="O246">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P246">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q246">
         <v>2.4</v>
       </c>
       <c r="R246">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S246">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T246">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U246">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="V246">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W246">
         <v>1.06</v>
@@ -40449,7 +40449,7 @@
         <v>1.87</v>
       </c>
       <c r="AB246">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AC246">
         <v>3.25</v>
@@ -40464,7 +40464,7 @@
         <v>1.73</v>
       </c>
       <c r="AG246">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40570,64 +40570,64 @@
         </is>
       </c>
       <c r="N247">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O247">
+        <v>3.4</v>
+      </c>
+      <c r="P247">
+        <v>4.09</v>
+      </c>
+      <c r="Q247">
+        <v>2.5</v>
+      </c>
+      <c r="R247">
+        <v>2.1</v>
+      </c>
+      <c r="S247">
+        <v>1.49</v>
+      </c>
+      <c r="T247">
+        <v>2.36</v>
+      </c>
+      <c r="U247">
         <v>3.2</v>
       </c>
-      <c r="P247">
-        <v>3.9</v>
-      </c>
-      <c r="Q247">
-        <v>2.49</v>
-      </c>
-      <c r="R247">
-        <v>1.85</v>
-      </c>
-      <c r="S247">
-        <v>1.5</v>
-      </c>
-      <c r="T247">
-        <v>2.33</v>
-      </c>
-      <c r="U247">
-        <v>3.32</v>
-      </c>
       <c r="V247">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W247">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X247">
         <v>1.04</v>
       </c>
       <c r="Y247">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z247">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA247">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AB247">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC247">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="AD247">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE247">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF247">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AG247">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK247">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40896,58 +40896,58 @@
         </is>
       </c>
       <c r="N249">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O249">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P249">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q249">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="R249">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S249">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T249">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U249">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="V249">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W249">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X249">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y249">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z249">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA249">
         <v>1.57</v>
       </c>
       <c r="AB249">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AC249">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD249">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE249">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF249">
         <v>1.5</v>
@@ -40966,7 +40966,7 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK249">
         <v>1.73</v>
@@ -41059,64 +41059,64 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="O250">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="P250">
-        <v>4.65</v>
+        <v>5.5</v>
       </c>
       <c r="Q250">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="R250">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S250">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T250">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U250">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V250">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W250">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X250">
         <v>1.02</v>
       </c>
       <c r="Y250">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z250">
-        <v>4</v>
+        <v>4.34</v>
       </c>
       <c r="AA250">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB250">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC250">
         <v>2.6</v>
       </c>
       <c r="AD250">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AE250">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF250">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG250">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK250">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="AL250">
         <v>0</v>
